--- a/artfynd/A 25855-2025 artfynd.xlsx
+++ b/artfynd/A 25855-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ39"/>
+  <dimension ref="A1:AZ52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,32 +680,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>137016354</v>
+        <v>137044063</v>
       </c>
       <c r="B2" t="n">
-        <v>93427</v>
+        <v>92386</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2059</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -718,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>636530</v>
+        <v>636790</v>
       </c>
       <c r="R2" t="n">
-        <v>7014359</v>
+        <v>7014332</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -748,22 +748,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -776,6 +776,21 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
@@ -784,60 +799,63 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja, Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016354</t>
+          <t>https://artportalen.se/Sighting/137044063</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>137016293</v>
+        <v>137016354</v>
       </c>
       <c r="B3" t="n">
-        <v>93411</v>
+        <v>93429</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Stortannsjön, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>636488</v>
+        <v>636530</v>
       </c>
       <c r="R3" t="n">
-        <v>7014397</v>
+        <v>7014359</v>
       </c>
       <c r="S3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -866,7 +884,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -876,7 +894,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -885,33 +903,34 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja, Markus Borja</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016293</t>
+          <t>https://artportalen.se/Sighting/137016354</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>137016298</v>
+        <v>137016293</v>
       </c>
       <c r="B4" t="n">
-        <v>93449</v>
+        <v>93413</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -919,37 +938,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Stortannsjön, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>636437</v>
+        <v>636488</v>
       </c>
       <c r="R4" t="n">
-        <v>7014437</v>
+        <v>7014397</v>
       </c>
       <c r="S4" t="n">
         <v>3</v>
@@ -981,7 +997,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -991,7 +1007,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1000,7 +1016,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1012,44 +1027,44 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Markus Borja, Diego Borja, Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016298</t>
+          <t>https://artportalen.se/Sighting/137016293</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>137016289</v>
+        <v>137016298</v>
       </c>
       <c r="B5" t="n">
-        <v>79476</v>
+        <v>93451</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>5966</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1062,10 +1077,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>636608</v>
+        <v>636437</v>
       </c>
       <c r="R5" t="n">
-        <v>7014302</v>
+        <v>7014437</v>
       </c>
       <c r="S5" t="n">
         <v>3</v>
@@ -1097,7 +1112,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1107,7 +1122,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1120,21 +1135,6 @@
       <c r="AG5" t="b">
         <v>0</v>
       </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
@@ -1143,22 +1143,22 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Markus Borja, Diego Borja, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016289</t>
+          <t>https://artportalen.se/Sighting/137016298</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>137016306</v>
+        <v>137016289</v>
       </c>
       <c r="B6" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,10 +1193,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>636566</v>
+        <v>636608</v>
       </c>
       <c r="R6" t="n">
-        <v>7014366</v>
+        <v>7014302</v>
       </c>
       <c r="S6" t="n">
         <v>3</v>
@@ -1228,7 +1228,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1238,7 +1238,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1280,16 +1280,16 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016306</t>
+          <t>https://artportalen.se/Sighting/137016289</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>137016332</v>
+        <v>137016306</v>
       </c>
       <c r="B7" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1324,13 +1324,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>636603</v>
+        <v>636566</v>
       </c>
       <c r="R7" t="n">
-        <v>7014322</v>
+        <v>7014366</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1359,7 +1359,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1369,7 +1369,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1400,27 +1400,27 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016332</t>
+          <t>https://artportalen.se/Sighting/137016306</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>137016333</v>
+        <v>137016332</v>
       </c>
       <c r="B8" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1455,10 +1455,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>636623</v>
+        <v>636603</v>
       </c>
       <c r="R8" t="n">
-        <v>7014305</v>
+        <v>7014322</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1490,7 +1490,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1500,7 +1500,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1542,16 +1542,16 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016333</t>
+          <t>https://artportalen.se/Sighting/137016332</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>137016335</v>
+        <v>137016333</v>
       </c>
       <c r="B9" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1586,10 +1586,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>636520</v>
+        <v>636623</v>
       </c>
       <c r="R9" t="n">
-        <v>7014374</v>
+        <v>7014305</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1673,16 +1673,16 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016335</t>
+          <t>https://artportalen.se/Sighting/137016333</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>137016337</v>
+        <v>137016335</v>
       </c>
       <c r="B10" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1717,10 +1717,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>636463</v>
+        <v>636520</v>
       </c>
       <c r="R10" t="n">
-        <v>7014402</v>
+        <v>7014374</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1752,7 +1752,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1762,7 +1762,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1804,16 +1804,16 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016337</t>
+          <t>https://artportalen.se/Sighting/137016335</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>137016340</v>
+        <v>137016337</v>
       </c>
       <c r="B11" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1848,10 +1848,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>636419</v>
+        <v>636463</v>
       </c>
       <c r="R11" t="n">
-        <v>7014437</v>
+        <v>7014402</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1883,7 +1883,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1893,7 +1893,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1935,16 +1935,16 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016340</t>
+          <t>https://artportalen.se/Sighting/137016337</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>137016349</v>
+        <v>137016340</v>
       </c>
       <c r="B12" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1979,10 +1979,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>636488</v>
+        <v>636419</v>
       </c>
       <c r="R12" t="n">
-        <v>7014536</v>
+        <v>7014437</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -2014,7 +2014,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2024,7 +2024,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2066,16 +2066,16 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016349</t>
+          <t>https://artportalen.se/Sighting/137016340</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>137016350</v>
+        <v>137016349</v>
       </c>
       <c r="B13" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2110,10 +2110,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>636466</v>
+        <v>636488</v>
       </c>
       <c r="R13" t="n">
-        <v>7014464</v>
+        <v>7014536</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2145,7 +2145,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2155,7 +2155,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2197,38 +2197,38 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016350</t>
+          <t>https://artportalen.se/Sighting/137016349</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>137016334</v>
+        <v>137016350</v>
       </c>
       <c r="B14" t="n">
-        <v>79500</v>
+        <v>79480</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2241,10 +2241,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>636591</v>
+        <v>636466</v>
       </c>
       <c r="R14" t="n">
-        <v>7014315</v>
+        <v>7014464</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2276,7 +2276,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2286,7 +2286,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2328,38 +2328,38 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016334</t>
+          <t>https://artportalen.se/Sighting/137016350</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>137016341</v>
+        <v>137044055</v>
       </c>
       <c r="B15" t="n">
-        <v>79500</v>
+        <v>79480</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2372,10 +2372,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>636409</v>
+        <v>636694</v>
       </c>
       <c r="R15" t="n">
-        <v>7014452</v>
+        <v>7014252</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2402,22 +2402,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>08:47</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>08:47</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2459,38 +2459,38 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016341</t>
+          <t>https://artportalen.se/Sighting/137044055</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>137016351</v>
+        <v>137044068</v>
       </c>
       <c r="B16" t="n">
-        <v>79500</v>
+        <v>79480</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2503,10 +2503,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>636460</v>
+        <v>636901</v>
       </c>
       <c r="R16" t="n">
-        <v>7014454</v>
+        <v>7014208</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2533,22 +2533,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2563,17 +2563,17 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2590,54 +2590,57 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016351</t>
+          <t>https://artportalen.se/Sighting/137044068</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>137016288</v>
+        <v>137044072</v>
       </c>
       <c r="B17" t="n">
-        <v>80095</v>
+        <v>79480</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Stortannsjön, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>636610</v>
+        <v>636840</v>
       </c>
       <c r="R17" t="n">
-        <v>7014307</v>
+        <v>7014233</v>
       </c>
       <c r="S17" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2661,22 +2664,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2685,71 +2688,90 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016288</t>
+          <t>https://artportalen.se/Sighting/137044072</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>137016299</v>
+        <v>137016334</v>
       </c>
       <c r="B18" t="n">
-        <v>80095</v>
+        <v>79504</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6453</v>
+        <v>6434</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Stortannsjön, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>636418</v>
+        <v>636591</v>
       </c>
       <c r="R18" t="n">
-        <v>7014453</v>
+        <v>7014315</v>
       </c>
       <c r="S18" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2778,7 +2800,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2788,7 +2810,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2797,71 +2819,90 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016299</t>
+          <t>https://artportalen.se/Sighting/137016334</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>137016303</v>
+        <v>137016341</v>
       </c>
       <c r="B19" t="n">
-        <v>80095</v>
+        <v>79504</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6453</v>
+        <v>6434</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Stortannsjön, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>636499</v>
+        <v>636409</v>
       </c>
       <c r="R19" t="n">
-        <v>7014546</v>
+        <v>7014452</v>
       </c>
       <c r="S19" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2890,7 +2931,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2900,7 +2941,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2909,33 +2950,49 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016303</t>
+          <t>https://artportalen.se/Sighting/137016341</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>137016301</v>
+        <v>137016351</v>
       </c>
       <c r="B20" t="n">
-        <v>58005</v>
+        <v>79504</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2943,31 +3000,26 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>6434</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2975,13 +3027,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>636482</v>
+        <v>636460</v>
       </c>
       <c r="R20" t="n">
-        <v>7014533</v>
+        <v>7014454</v>
       </c>
       <c r="S20" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3010,7 +3062,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3020,7 +3072,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3029,65 +3081,76 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016301</t>
+          <t>https://artportalen.se/Sighting/137016351</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>137016287</v>
+        <v>137044056</v>
       </c>
       <c r="B21" t="n">
-        <v>58008</v>
+        <v>79504</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6434</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -3095,13 +3158,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>636606</v>
+        <v>636699</v>
       </c>
       <c r="R21" t="n">
-        <v>7014302</v>
+        <v>7014271</v>
       </c>
       <c r="S21" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3125,27 +3188,22 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:34</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Färska och Äldre ringhack på tall</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3154,33 +3212,49 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja, Diego Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016287</t>
+          <t>https://artportalen.se/Sighting/137044056</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>137016290</v>
+        <v>137016288</v>
       </c>
       <c r="B22" t="n">
-        <v>58008</v>
+        <v>80099</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3188,42 +3262,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Stortannsjön, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>636608</v>
+        <v>636610</v>
       </c>
       <c r="R22" t="n">
-        <v>7014302</v>
+        <v>7014307</v>
       </c>
       <c r="S22" t="n">
         <v>3</v>
@@ -3255,7 +3321,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3265,12 +3331,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:54</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3290,22 +3351,22 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja, Diego Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016290</t>
+          <t>https://artportalen.se/Sighting/137016288</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>137016291</v>
+        <v>137016299</v>
       </c>
       <c r="B23" t="n">
-        <v>58008</v>
+        <v>80099</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3313,42 +3374,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Stortannsjön, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>636578</v>
+        <v>636418</v>
       </c>
       <c r="R23" t="n">
-        <v>7014320</v>
+        <v>7014453</v>
       </c>
       <c r="S23" t="n">
         <v>3</v>
@@ -3380,7 +3433,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3390,12 +3443,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:59</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3415,22 +3463,22 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja, Diego Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016291</t>
+          <t>https://artportalen.se/Sighting/137016299</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>137016292</v>
+        <v>137016303</v>
       </c>
       <c r="B24" t="n">
-        <v>58008</v>
+        <v>80099</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3438,42 +3486,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Stortannsjön, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>636501</v>
+        <v>636499</v>
       </c>
       <c r="R24" t="n">
-        <v>7014381</v>
+        <v>7014546</v>
       </c>
       <c r="S24" t="n">
         <v>3</v>
@@ -3505,7 +3545,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3515,12 +3555,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:09</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3540,39 +3575,39 @@
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016292</t>
+          <t>https://artportalen.se/Sighting/137016303</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>137016294</v>
+        <v>137016301</v>
       </c>
       <c r="B25" t="n">
-        <v>58008</v>
+        <v>58005</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -3585,7 +3620,7 @@
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N25" t="inlineStr"/>
@@ -3595,10 +3630,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>636486</v>
+        <v>636482</v>
       </c>
       <c r="R25" t="n">
-        <v>7014403</v>
+        <v>7014533</v>
       </c>
       <c r="S25" t="n">
         <v>3</v>
@@ -3630,7 +3665,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3640,12 +3675,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:16</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3665,19 +3695,19 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016294</t>
+          <t>https://artportalen.se/Sighting/137016301</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>137016295</v>
+        <v>137016287</v>
       </c>
       <c r="B26" t="n">
         <v>58008</v>
@@ -3710,7 +3740,7 @@
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N26" t="inlineStr"/>
@@ -3720,10 +3750,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>636432</v>
+        <v>636606</v>
       </c>
       <c r="R26" t="n">
-        <v>7014422</v>
+        <v>7014302</v>
       </c>
       <c r="S26" t="n">
         <v>3</v>
@@ -3755,7 +3785,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3765,12 +3795,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>Färska och Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3790,19 +3820,19 @@
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja</t>
+          <t>Markus Borja, Ann-Christine Borja, Diego Borja</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016295</t>
+          <t>https://artportalen.se/Sighting/137016287</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>137016296</v>
+        <v>137016290</v>
       </c>
       <c r="B27" t="n">
         <v>58008</v>
@@ -3835,7 +3865,7 @@
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N27" t="inlineStr"/>
@@ -3845,10 +3875,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>636424</v>
+        <v>636608</v>
       </c>
       <c r="R27" t="n">
-        <v>7014437</v>
+        <v>7014302</v>
       </c>
       <c r="S27" t="n">
         <v>3</v>
@@ -3880,7 +3910,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3890,12 +3920,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack på tall</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3915,19 +3945,19 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja</t>
+          <t>Markus Borja, Ann-Christine Borja, Diego Borja</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016296</t>
+          <t>https://artportalen.se/Sighting/137016290</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>137016297</v>
+        <v>137016291</v>
       </c>
       <c r="B28" t="n">
         <v>58008</v>
@@ -3970,10 +4000,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>636448</v>
+        <v>636578</v>
       </c>
       <c r="R28" t="n">
-        <v>7014424</v>
+        <v>7014320</v>
       </c>
       <c r="S28" t="n">
         <v>3</v>
@@ -4005,7 +4035,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -4015,7 +4045,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
@@ -4040,19 +4070,19 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja</t>
+          <t>Markus Borja, Ann-Christine Borja, Diego Borja</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016297</t>
+          <t>https://artportalen.se/Sighting/137016291</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>137016300</v>
+        <v>137016292</v>
       </c>
       <c r="B29" t="n">
         <v>58008</v>
@@ -4085,7 +4115,7 @@
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N29" t="inlineStr"/>
@@ -4095,10 +4125,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>636398</v>
+        <v>636501</v>
       </c>
       <c r="R29" t="n">
-        <v>7014509</v>
+        <v>7014381</v>
       </c>
       <c r="S29" t="n">
         <v>3</v>
@@ -4130,7 +4160,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4140,12 +4170,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4171,13 +4201,13 @@
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016300</t>
+          <t>https://artportalen.se/Sighting/137016292</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>137016304</v>
+        <v>137016294</v>
       </c>
       <c r="B30" t="n">
         <v>58008</v>
@@ -4220,10 +4250,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>636466</v>
+        <v>636486</v>
       </c>
       <c r="R30" t="n">
-        <v>7014462</v>
+        <v>7014403</v>
       </c>
       <c r="S30" t="n">
         <v>3</v>
@@ -4255,7 +4285,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4265,7 +4295,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
@@ -4290,19 +4320,19 @@
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja, Diego Borja</t>
+          <t>Markus Borja, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016304</t>
+          <t>https://artportalen.se/Sighting/137016294</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>137016307</v>
+        <v>137016295</v>
       </c>
       <c r="B31" t="n">
         <v>58008</v>
@@ -4345,10 +4375,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>636566</v>
+        <v>636432</v>
       </c>
       <c r="R31" t="n">
-        <v>7014367</v>
+        <v>7014422</v>
       </c>
       <c r="S31" t="n">
         <v>3</v>
@@ -4380,7 +4410,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4390,7 +4420,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
@@ -4415,19 +4445,19 @@
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Markus Borja, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016307</t>
+          <t>https://artportalen.se/Sighting/137016295</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>137016344</v>
+        <v>137016296</v>
       </c>
       <c r="B32" t="n">
         <v>58008</v>
@@ -4470,13 +4500,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>636392</v>
+        <v>636424</v>
       </c>
       <c r="R32" t="n">
-        <v>7014473</v>
+        <v>7014437</v>
       </c>
       <c r="S32" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4505,7 +4535,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4515,12 +4545,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall.</t>
+          <t>Färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4535,27 +4565,27 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja, Markus Borja</t>
+          <t>Markus Borja, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016344</t>
+          <t>https://artportalen.se/Sighting/137016296</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>137016336</v>
+        <v>137016297</v>
       </c>
       <c r="B33" t="n">
-        <v>79499</v>
+        <v>58008</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4563,26 +4593,31 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>260591</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4590,13 +4625,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>636512</v>
+        <v>636448</v>
       </c>
       <c r="R33" t="n">
-        <v>7014375</v>
+        <v>7014424</v>
       </c>
       <c r="S33" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4625,7 +4660,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4635,7 +4670,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>11:35</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4644,49 +4684,33 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK33" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja, Markus Borja</t>
+          <t>Markus Borja, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016336</t>
+          <t>https://artportalen.se/Sighting/137016297</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>137016339</v>
+        <v>137016300</v>
       </c>
       <c r="B34" t="n">
-        <v>79499</v>
+        <v>58008</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4694,26 +4718,31 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>260591</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4721,13 +4750,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>636457</v>
+        <v>636398</v>
       </c>
       <c r="R34" t="n">
-        <v>7014405</v>
+        <v>7014509</v>
       </c>
       <c r="S34" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4756,7 +4785,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4766,7 +4795,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:46</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4775,49 +4809,33 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ34" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK34" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO34" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016339</t>
+          <t>https://artportalen.se/Sighting/137016300</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>137016342</v>
+        <v>137016304</v>
       </c>
       <c r="B35" t="n">
-        <v>79499</v>
+        <v>58008</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4825,26 +4843,31 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>260591</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4852,13 +4875,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>636417</v>
+        <v>636466</v>
       </c>
       <c r="R35" t="n">
-        <v>7014452</v>
+        <v>7014462</v>
       </c>
       <c r="S35" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4887,7 +4910,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4897,7 +4920,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>12:24</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4906,49 +4934,33 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ35" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK35" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO35" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja, Ann-Christine Borja, Diego Borja</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016342</t>
+          <t>https://artportalen.se/Sighting/137016304</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>137016345</v>
+        <v>137016307</v>
       </c>
       <c r="B36" t="n">
-        <v>79499</v>
+        <v>58008</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4956,26 +4968,31 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>260591</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4983,13 +5000,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>636407</v>
+        <v>636566</v>
       </c>
       <c r="R36" t="n">
-        <v>7014480</v>
+        <v>7014367</v>
       </c>
       <c r="S36" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -5018,7 +5035,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -5028,7 +5045,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>12:35</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5037,49 +5059,33 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ36" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK36" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO36" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016345</t>
+          <t>https://artportalen.se/Sighting/137016307</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>137016346</v>
+        <v>137016344</v>
       </c>
       <c r="B37" t="n">
-        <v>79499</v>
+        <v>58008</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5087,28 +5093,29 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>260591</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N37" t="inlineStr"/>
@@ -5118,10 +5125,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>636450</v>
+        <v>636392</v>
       </c>
       <c r="R37" t="n">
-        <v>7014535</v>
+        <v>7014473</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -5153,7 +5160,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5163,7 +5170,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5172,24 +5184,8 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ37" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK37" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO37" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
@@ -5199,53 +5195,58 @@
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Ann-Christine Borja, Markus Borja</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016346</t>
+          <t>https://artportalen.se/Sighting/137016344</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>137016348</v>
+        <v>137044057</v>
       </c>
       <c r="B38" t="n">
-        <v>79499</v>
+        <v>99359</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>260591</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -5253,10 +5254,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>636479</v>
+        <v>636762</v>
       </c>
       <c r="R38" t="n">
-        <v>7014523</v>
+        <v>7014263</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -5283,22 +5284,22 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5311,21 +5312,6 @@
       <c r="AG38" t="b">
         <v>0</v>
       </c>
-      <c r="AJ38" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK38" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO38" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
@@ -5334,49 +5320,58 @@
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Ann-Christine Borja, Markus Borja, Vivien Renaut</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016348</t>
+          <t>https://artportalen.se/Sighting/137044057</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>137016353</v>
+        <v>137044059</v>
       </c>
       <c r="B39" t="n">
-        <v>79499</v>
+        <v>99359</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>260591</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -5384,10 +5379,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>636460</v>
+        <v>636736</v>
       </c>
       <c r="R39" t="n">
-        <v>7014451</v>
+        <v>7014341</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -5414,22 +5409,22 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5442,21 +5437,6 @@
       <c r="AG39" t="b">
         <v>0</v>
       </c>
-      <c r="AJ39" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK39" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO39" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
@@ -5465,13 +5445,1698 @@
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Ann-Christine Borja, Markus Borja, Vivien Renaut</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/137044059</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>137044060</v>
+      </c>
+      <c r="B40" t="n">
+        <v>99359</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>159</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Stortannsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>636760</v>
+      </c>
+      <c r="R40" t="n">
+        <v>7014309</v>
+      </c>
+      <c r="S40" t="n">
+        <v>5</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Överlännäs</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>10:02</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>10:02</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF40" t="inlineStr"/>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja, Markus Borja, Vivien Renaut</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137044060</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>137044061</v>
+      </c>
+      <c r="B41" t="n">
+        <v>99359</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Stortannsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>636781</v>
+      </c>
+      <c r="R41" t="n">
+        <v>7014323</v>
+      </c>
+      <c r="S41" t="n">
+        <v>5</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Överlännäs</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF41" t="inlineStr"/>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja, Markus Borja, Vivien Renaut</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137044061</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>137044062</v>
+      </c>
+      <c r="B42" t="n">
+        <v>99359</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>117</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Stortannsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>636772</v>
+      </c>
+      <c r="R42" t="n">
+        <v>7014326</v>
+      </c>
+      <c r="S42" t="n">
+        <v>5</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Överlännäs</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>10:26</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>10:26</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF42" t="inlineStr"/>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja, Markus Borja, Vivien Renaut</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137044062</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>137044064</v>
+      </c>
+      <c r="B43" t="n">
+        <v>99359</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Stortannsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>636806</v>
+      </c>
+      <c r="R43" t="n">
+        <v>7014282</v>
+      </c>
+      <c r="S43" t="n">
+        <v>5</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Överlännäs</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>10:48</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>10:48</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF43" t="inlineStr"/>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja, Markus Borja, Vivien Renaut</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137044064</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>137044080</v>
+      </c>
+      <c r="B44" t="n">
+        <v>99359</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Stortannsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>636598</v>
+      </c>
+      <c r="R44" t="n">
+        <v>7014517</v>
+      </c>
+      <c r="S44" t="n">
+        <v>5</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Överlännäs</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>14:32</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>14:32</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF44" t="inlineStr"/>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja, Markus Borja, Vivien Renaut</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137044080</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>137016336</v>
+      </c>
+      <c r="B45" t="n">
+        <v>79503</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Stortannsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>636512</v>
+      </c>
+      <c r="R45" t="n">
+        <v>7014375</v>
+      </c>
+      <c r="S45" t="n">
+        <v>5</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Överlännäs</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>11:12</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>11:12</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF45" t="inlineStr"/>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja, Markus Borja</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137016336</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>137016339</v>
+      </c>
+      <c r="B46" t="n">
+        <v>79503</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Stortannsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>636457</v>
+      </c>
+      <c r="R46" t="n">
+        <v>7014405</v>
+      </c>
+      <c r="S46" t="n">
+        <v>5</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Överlännäs</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>11:22</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>11:22</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF46" t="inlineStr"/>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ46" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK46" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO46" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137016339</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>137016342</v>
+      </c>
+      <c r="B47" t="n">
+        <v>79503</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Stortannsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>636417</v>
+      </c>
+      <c r="R47" t="n">
+        <v>7014452</v>
+      </c>
+      <c r="S47" t="n">
+        <v>5</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Överlännäs</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF47" t="inlineStr"/>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ47" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK47" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO47" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137016342</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>137016345</v>
+      </c>
+      <c r="B48" t="n">
+        <v>79503</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Stortannsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>636407</v>
+      </c>
+      <c r="R48" t="n">
+        <v>7014480</v>
+      </c>
+      <c r="S48" t="n">
+        <v>5</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Överlännäs</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>11:59</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>11:59</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF48" t="inlineStr"/>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ48" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK48" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO48" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137016345</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>137016346</v>
+      </c>
+      <c r="B49" t="n">
+        <v>79503</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Stortannsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>636450</v>
+      </c>
+      <c r="R49" t="n">
+        <v>7014535</v>
+      </c>
+      <c r="S49" t="n">
+        <v>5</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Överlännäs</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF49" t="inlineStr"/>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ49" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK49" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO49" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137016346</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>137016348</v>
+      </c>
+      <c r="B50" t="n">
+        <v>79503</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Stortannsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>636479</v>
+      </c>
+      <c r="R50" t="n">
+        <v>7014523</v>
+      </c>
+      <c r="S50" t="n">
+        <v>5</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Överlännäs</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>12:09</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>12:09</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF50" t="inlineStr"/>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ50" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK50" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO50" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137016348</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>137016353</v>
+      </c>
+      <c r="B51" t="n">
+        <v>79503</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Stortannsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>636460</v>
+      </c>
+      <c r="R51" t="n">
+        <v>7014451</v>
+      </c>
+      <c r="S51" t="n">
+        <v>5</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Överlännäs</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>12:28</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>12:28</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF51" t="inlineStr"/>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ51" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK51" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO51" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/137016353</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>137044071</v>
+      </c>
+      <c r="B52" t="n">
+        <v>79503</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Stortannsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>636845</v>
+      </c>
+      <c r="R52" t="n">
+        <v>7014233</v>
+      </c>
+      <c r="S52" t="n">
+        <v>5</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Överlännäs</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>12:09</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>12:09</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF52" t="inlineStr"/>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ52" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK52" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO52" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137044071</t>
         </is>
       </c>
     </row>
@@ -5515,6 +7180,19 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 25855-2025 artfynd.xlsx
+++ b/artfynd/A 25855-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ52"/>
+  <dimension ref="A1:AZ62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -683,7 +683,7 @@
         <v>137044063</v>
       </c>
       <c r="B2" t="n">
-        <v>92386</v>
+        <v>92388</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -811,51 +811,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>137016354</v>
+        <v>137040165</v>
       </c>
       <c r="B3" t="n">
-        <v>93429</v>
+        <v>92950</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2059</v>
+        <v>2014</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Koralltaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hericium coralloides</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Scop.) Pers.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Stortannsjön, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>636530</v>
+        <v>636776</v>
       </c>
       <c r="R3" t="n">
-        <v>7014359</v>
+        <v>7014299</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,22 +876,27 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>2st</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -903,72 +905,74 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Vivien Renaut</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja, Markus Borja</t>
+          <t>Vivien Renaut</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016354</t>
+          <t>https://artportalen.se/Sighting/137040165</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>137016293</v>
+        <v>137016354</v>
       </c>
       <c r="B4" t="n">
-        <v>93413</v>
+        <v>93431</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Stortannsjön, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>636488</v>
+        <v>636530</v>
       </c>
       <c r="R4" t="n">
-        <v>7014397</v>
+        <v>7014359</v>
       </c>
       <c r="S4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -997,7 +1001,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1007,7 +1011,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,33 +1020,34 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja, Markus Borja</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016293</t>
+          <t>https://artportalen.se/Sighting/137016354</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>137016298</v>
+        <v>137016293</v>
       </c>
       <c r="B5" t="n">
-        <v>93451</v>
+        <v>93415</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1050,37 +1055,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Stortannsjön, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>636437</v>
+        <v>636488</v>
       </c>
       <c r="R5" t="n">
-        <v>7014437</v>
+        <v>7014397</v>
       </c>
       <c r="S5" t="n">
         <v>3</v>
@@ -1112,7 +1114,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1122,7 +1124,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1131,7 +1133,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1143,44 +1144,44 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Markus Borja, Diego Borja, Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016298</t>
+          <t>https://artportalen.se/Sighting/137016293</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>137016289</v>
+        <v>137016298</v>
       </c>
       <c r="B6" t="n">
-        <v>79480</v>
+        <v>93453</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>5966</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1193,10 +1194,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>636608</v>
+        <v>636437</v>
       </c>
       <c r="R6" t="n">
-        <v>7014302</v>
+        <v>7014437</v>
       </c>
       <c r="S6" t="n">
         <v>3</v>
@@ -1228,7 +1229,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1238,7 +1239,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1251,21 +1252,6 @@
       <c r="AG6" t="b">
         <v>0</v>
       </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
@@ -1274,22 +1260,22 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Markus Borja, Diego Borja, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016289</t>
+          <t>https://artportalen.se/Sighting/137016298</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>137016306</v>
+        <v>137016289</v>
       </c>
       <c r="B7" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1324,10 +1310,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>636566</v>
+        <v>636608</v>
       </c>
       <c r="R7" t="n">
-        <v>7014366</v>
+        <v>7014302</v>
       </c>
       <c r="S7" t="n">
         <v>3</v>
@@ -1359,7 +1345,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1369,7 +1355,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1411,16 +1397,16 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016306</t>
+          <t>https://artportalen.se/Sighting/137016289</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>137016332</v>
+        <v>137016306</v>
       </c>
       <c r="B8" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1455,13 +1441,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>636603</v>
+        <v>636566</v>
       </c>
       <c r="R8" t="n">
-        <v>7014322</v>
+        <v>7014366</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1490,7 +1476,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1500,7 +1486,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1531,27 +1517,27 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016332</t>
+          <t>https://artportalen.se/Sighting/137016306</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>137016333</v>
+        <v>137016332</v>
       </c>
       <c r="B9" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1586,10 +1572,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>636623</v>
+        <v>636603</v>
       </c>
       <c r="R9" t="n">
-        <v>7014305</v>
+        <v>7014322</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1621,7 +1607,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1631,7 +1617,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1673,16 +1659,16 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016333</t>
+          <t>https://artportalen.se/Sighting/137016332</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>137016335</v>
+        <v>137016333</v>
       </c>
       <c r="B10" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1717,10 +1703,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>636520</v>
+        <v>636623</v>
       </c>
       <c r="R10" t="n">
-        <v>7014374</v>
+        <v>7014305</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1752,7 +1738,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1762,7 +1748,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1804,16 +1790,16 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016335</t>
+          <t>https://artportalen.se/Sighting/137016333</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>137016337</v>
+        <v>137016335</v>
       </c>
       <c r="B11" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1848,10 +1834,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>636463</v>
+        <v>636520</v>
       </c>
       <c r="R11" t="n">
-        <v>7014402</v>
+        <v>7014374</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1883,7 +1869,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1893,7 +1879,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1935,16 +1921,16 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016337</t>
+          <t>https://artportalen.se/Sighting/137016335</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>137016340</v>
+        <v>137016337</v>
       </c>
       <c r="B12" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1979,10 +1965,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>636419</v>
+        <v>636463</v>
       </c>
       <c r="R12" t="n">
-        <v>7014437</v>
+        <v>7014402</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -2014,7 +2000,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2024,7 +2010,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2066,16 +2052,16 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016340</t>
+          <t>https://artportalen.se/Sighting/137016337</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>137016349</v>
+        <v>137016340</v>
       </c>
       <c r="B13" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2110,10 +2096,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>636488</v>
+        <v>636419</v>
       </c>
       <c r="R13" t="n">
-        <v>7014536</v>
+        <v>7014437</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2145,7 +2131,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2155,7 +2141,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2197,16 +2183,16 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016349</t>
+          <t>https://artportalen.se/Sighting/137016340</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>137016350</v>
+        <v>137016349</v>
       </c>
       <c r="B14" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2241,10 +2227,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>636466</v>
+        <v>636488</v>
       </c>
       <c r="R14" t="n">
-        <v>7014464</v>
+        <v>7014536</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2276,7 +2262,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2286,7 +2272,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2328,16 +2314,16 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016350</t>
+          <t>https://artportalen.se/Sighting/137016349</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>137044055</v>
+        <v>137016350</v>
       </c>
       <c r="B15" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2372,10 +2358,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>636694</v>
+        <v>636466</v>
       </c>
       <c r="R15" t="n">
-        <v>7014252</v>
+        <v>7014464</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2402,22 +2388,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>08:47</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>08:47</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2459,16 +2445,16 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137044055</t>
+          <t>https://artportalen.se/Sighting/137016350</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>137044068</v>
+        <v>137040167</v>
       </c>
       <c r="B16" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2494,19 +2480,16 @@
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Stortannsjön, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>636901</v>
+        <v>636743</v>
       </c>
       <c r="R16" t="n">
-        <v>7014208</v>
+        <v>7014374</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2538,7 +2521,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2548,7 +2531,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2557,49 +2540,33 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Vivien Renaut</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Vivien Renaut</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137044068</t>
+          <t>https://artportalen.se/Sighting/137040167</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>137044072</v>
+        <v>137040169</v>
       </c>
       <c r="B17" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2625,22 +2592,19 @@
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Stortannsjön, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>636840</v>
+        <v>636844</v>
       </c>
       <c r="R17" t="n">
-        <v>7014233</v>
+        <v>7014273</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2669,7 +2633,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2679,7 +2643,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2688,90 +2652,71 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Vivien Renaut</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Vivien Renaut</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137044072</t>
+          <t>https://artportalen.se/Sighting/137040169</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>137016334</v>
+        <v>137040181</v>
       </c>
       <c r="B18" t="n">
-        <v>79504</v>
+        <v>79482</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Stortannsjön, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>636591</v>
+        <v>636605</v>
       </c>
       <c r="R18" t="n">
-        <v>7014315</v>
+        <v>7014506</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2795,22 +2740,27 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>14:28</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Garnlav på tall</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2819,71 +2769,55 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Vivien Renaut</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Vivien Renaut</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016334</t>
+          <t>https://artportalen.se/Sighting/137040181</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>137016341</v>
+        <v>137044055</v>
       </c>
       <c r="B19" t="n">
-        <v>79504</v>
+        <v>79482</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2896,10 +2830,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>636409</v>
+        <v>636694</v>
       </c>
       <c r="R19" t="n">
-        <v>7014452</v>
+        <v>7014252</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2926,22 +2860,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>08:47</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>08:47</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2983,38 +2917,38 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016341</t>
+          <t>https://artportalen.se/Sighting/137044055</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>137016351</v>
+        <v>137044068</v>
       </c>
       <c r="B20" t="n">
-        <v>79504</v>
+        <v>79482</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -3027,10 +2961,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>636460</v>
+        <v>636901</v>
       </c>
       <c r="R20" t="n">
-        <v>7014454</v>
+        <v>7014208</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -3057,22 +2991,22 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3087,17 +3021,17 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3114,38 +3048,38 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016351</t>
+          <t>https://artportalen.se/Sighting/137044068</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>137044056</v>
+        <v>137044072</v>
       </c>
       <c r="B21" t="n">
-        <v>79504</v>
+        <v>79482</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -3158,10 +3092,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>636699</v>
+        <v>636840</v>
       </c>
       <c r="R21" t="n">
-        <v>7014271</v>
+        <v>7014233</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -3193,7 +3127,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3203,7 +3137,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3245,54 +3179,57 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137044056</t>
+          <t>https://artportalen.se/Sighting/137044072</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>137016288</v>
+        <v>137016334</v>
       </c>
       <c r="B22" t="n">
-        <v>80099</v>
+        <v>79506</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6453</v>
+        <v>6434</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Stortannsjön, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>636610</v>
+        <v>636591</v>
       </c>
       <c r="R22" t="n">
-        <v>7014307</v>
+        <v>7014315</v>
       </c>
       <c r="S22" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3321,7 +3258,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3331,7 +3268,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3340,71 +3277,90 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016288</t>
+          <t>https://artportalen.se/Sighting/137016334</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>137016299</v>
+        <v>137016341</v>
       </c>
       <c r="B23" t="n">
-        <v>80099</v>
+        <v>79506</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6453</v>
+        <v>6434</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Stortannsjön, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>636418</v>
+        <v>636409</v>
       </c>
       <c r="R23" t="n">
-        <v>7014453</v>
+        <v>7014452</v>
       </c>
       <c r="S23" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3433,7 +3389,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3443,7 +3399,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3452,71 +3408,90 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016299</t>
+          <t>https://artportalen.se/Sighting/137016341</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>137016303</v>
+        <v>137016351</v>
       </c>
       <c r="B24" t="n">
-        <v>80099</v>
+        <v>79506</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6453</v>
+        <v>6434</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Stortannsjön, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>636499</v>
+        <v>636460</v>
       </c>
       <c r="R24" t="n">
-        <v>7014546</v>
+        <v>7014454</v>
       </c>
       <c r="S24" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3545,7 +3520,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3555,7 +3530,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3564,33 +3539,49 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016303</t>
+          <t>https://artportalen.se/Sighting/137016351</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>137016301</v>
+        <v>137044056</v>
       </c>
       <c r="B25" t="n">
-        <v>58005</v>
+        <v>79506</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3598,31 +3589,26 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>6434</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3630,13 +3616,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>636482</v>
+        <v>636699</v>
       </c>
       <c r="R25" t="n">
-        <v>7014533</v>
+        <v>7014271</v>
       </c>
       <c r="S25" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3660,22 +3646,22 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3684,33 +3670,49 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016301</t>
+          <t>https://artportalen.se/Sighting/137044056</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>137016287</v>
+        <v>137016288</v>
       </c>
       <c r="B26" t="n">
-        <v>58008</v>
+        <v>80101</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3718,42 +3720,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Stortannsjön, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>636606</v>
+        <v>636610</v>
       </c>
       <c r="R26" t="n">
-        <v>7014302</v>
+        <v>7014307</v>
       </c>
       <c r="S26" t="n">
         <v>3</v>
@@ -3785,7 +3779,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3795,12 +3789,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>10:34</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Färska och Äldre ringhack på tall</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3820,22 +3809,22 @@
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja, Diego Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016287</t>
+          <t>https://artportalen.se/Sighting/137016288</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>137016290</v>
+        <v>137016299</v>
       </c>
       <c r="B27" t="n">
-        <v>58008</v>
+        <v>80101</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3843,42 +3832,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Stortannsjön, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>636608</v>
+        <v>636418</v>
       </c>
       <c r="R27" t="n">
-        <v>7014302</v>
+        <v>7014453</v>
       </c>
       <c r="S27" t="n">
         <v>3</v>
@@ -3910,7 +3891,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3920,12 +3901,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>10:54</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3945,22 +3921,22 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja, Diego Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016290</t>
+          <t>https://artportalen.se/Sighting/137016299</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>137016291</v>
+        <v>137016303</v>
       </c>
       <c r="B28" t="n">
-        <v>58008</v>
+        <v>80101</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3968,42 +3944,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Stortannsjön, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>636578</v>
+        <v>636499</v>
       </c>
       <c r="R28" t="n">
-        <v>7014320</v>
+        <v>7014546</v>
       </c>
       <c r="S28" t="n">
         <v>3</v>
@@ -4035,7 +4003,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -4045,12 +4013,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>10:59</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4070,39 +4033,39 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja, Diego Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016291</t>
+          <t>https://artportalen.se/Sighting/137016303</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>137016292</v>
+        <v>137016301</v>
       </c>
       <c r="B29" t="n">
-        <v>58008</v>
+        <v>58005</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -4115,7 +4078,7 @@
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N29" t="inlineStr"/>
@@ -4125,10 +4088,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>636501</v>
+        <v>636482</v>
       </c>
       <c r="R29" t="n">
-        <v>7014381</v>
+        <v>7014533</v>
       </c>
       <c r="S29" t="n">
         <v>3</v>
@@ -4160,7 +4123,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4170,12 +4133,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>11:09</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4195,39 +4153,39 @@
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016292</t>
+          <t>https://artportalen.se/Sighting/137016301</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>137016294</v>
+        <v>137040182</v>
       </c>
       <c r="B30" t="n">
-        <v>58008</v>
+        <v>58005</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -4240,7 +4198,7 @@
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N30" t="inlineStr"/>
@@ -4250,13 +4208,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>636486</v>
+        <v>636550</v>
       </c>
       <c r="R30" t="n">
-        <v>7014403</v>
+        <v>7014507</v>
       </c>
       <c r="S30" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4280,27 +4238,27 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4315,24 +4273,24 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Vivien Renaut</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja</t>
+          <t>Vivien Renaut</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016294</t>
+          <t>https://artportalen.se/Sighting/137040182</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>137016295</v>
+        <v>137016287</v>
       </c>
       <c r="B31" t="n">
         <v>58008</v>
@@ -4365,7 +4323,7 @@
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N31" t="inlineStr"/>
@@ -4375,10 +4333,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>636432</v>
+        <v>636606</v>
       </c>
       <c r="R31" t="n">
-        <v>7014422</v>
+        <v>7014302</v>
       </c>
       <c r="S31" t="n">
         <v>3</v>
@@ -4410,7 +4368,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4420,12 +4378,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>Färska och Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4445,19 +4403,19 @@
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja</t>
+          <t>Markus Borja, Ann-Christine Borja, Diego Borja</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016295</t>
+          <t>https://artportalen.se/Sighting/137016287</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>137016296</v>
+        <v>137016290</v>
       </c>
       <c r="B32" t="n">
         <v>58008</v>
@@ -4490,7 +4448,7 @@
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N32" t="inlineStr"/>
@@ -4500,10 +4458,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>636424</v>
+        <v>636608</v>
       </c>
       <c r="R32" t="n">
-        <v>7014437</v>
+        <v>7014302</v>
       </c>
       <c r="S32" t="n">
         <v>3</v>
@@ -4535,7 +4493,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4545,12 +4503,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack på tall</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4570,19 +4528,19 @@
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja</t>
+          <t>Markus Borja, Ann-Christine Borja, Diego Borja</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016296</t>
+          <t>https://artportalen.se/Sighting/137016290</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>137016297</v>
+        <v>137016291</v>
       </c>
       <c r="B33" t="n">
         <v>58008</v>
@@ -4625,10 +4583,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>636448</v>
+        <v>636578</v>
       </c>
       <c r="R33" t="n">
-        <v>7014424</v>
+        <v>7014320</v>
       </c>
       <c r="S33" t="n">
         <v>3</v>
@@ -4660,7 +4618,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4670,7 +4628,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
@@ -4695,19 +4653,19 @@
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja</t>
+          <t>Markus Borja, Ann-Christine Borja, Diego Borja</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016297</t>
+          <t>https://artportalen.se/Sighting/137016291</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>137016300</v>
+        <v>137016292</v>
       </c>
       <c r="B34" t="n">
         <v>58008</v>
@@ -4740,7 +4698,7 @@
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N34" t="inlineStr"/>
@@ -4750,10 +4708,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>636398</v>
+        <v>636501</v>
       </c>
       <c r="R34" t="n">
-        <v>7014509</v>
+        <v>7014381</v>
       </c>
       <c r="S34" t="n">
         <v>3</v>
@@ -4785,7 +4743,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4795,12 +4753,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4826,13 +4784,13 @@
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016300</t>
+          <t>https://artportalen.se/Sighting/137016292</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>137016304</v>
+        <v>137016294</v>
       </c>
       <c r="B35" t="n">
         <v>58008</v>
@@ -4875,10 +4833,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>636466</v>
+        <v>636486</v>
       </c>
       <c r="R35" t="n">
-        <v>7014462</v>
+        <v>7014403</v>
       </c>
       <c r="S35" t="n">
         <v>3</v>
@@ -4910,7 +4868,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4920,7 +4878,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
@@ -4945,19 +4903,19 @@
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja, Diego Borja</t>
+          <t>Markus Borja, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016304</t>
+          <t>https://artportalen.se/Sighting/137016294</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>137016307</v>
+        <v>137016295</v>
       </c>
       <c r="B36" t="n">
         <v>58008</v>
@@ -5000,10 +4958,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>636566</v>
+        <v>636432</v>
       </c>
       <c r="R36" t="n">
-        <v>7014367</v>
+        <v>7014422</v>
       </c>
       <c r="S36" t="n">
         <v>3</v>
@@ -5035,7 +4993,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -5045,7 +5003,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
@@ -5070,19 +5028,19 @@
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Markus Borja, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016307</t>
+          <t>https://artportalen.se/Sighting/137016295</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>137016344</v>
+        <v>137016296</v>
       </c>
       <c r="B37" t="n">
         <v>58008</v>
@@ -5125,13 +5083,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>636392</v>
+        <v>636424</v>
       </c>
       <c r="R37" t="n">
-        <v>7014473</v>
+        <v>7014437</v>
       </c>
       <c r="S37" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -5160,7 +5118,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5170,12 +5128,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall.</t>
+          <t>Färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5190,63 +5148,59 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja, Markus Borja</t>
+          <t>Markus Borja, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016344</t>
+          <t>https://artportalen.se/Sighting/137016296</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>137044057</v>
+        <v>137016297</v>
       </c>
       <c r="B38" t="n">
-        <v>99359</v>
+        <v>58008</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -5254,13 +5208,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>636762</v>
+        <v>636448</v>
       </c>
       <c r="R38" t="n">
-        <v>7014263</v>
+        <v>7014424</v>
       </c>
       <c r="S38" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5284,22 +5238,27 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>11:35</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5308,70 +5267,65 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja, Markus Borja, Vivien Renaut</t>
+          <t>Markus Borja, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137044057</t>
+          <t>https://artportalen.se/Sighting/137016297</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>137044059</v>
+        <v>137016300</v>
       </c>
       <c r="B39" t="n">
-        <v>99359</v>
+        <v>58008</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>105</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -5379,13 +5333,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>636736</v>
+        <v>636398</v>
       </c>
       <c r="R39" t="n">
-        <v>7014341</v>
+        <v>7014509</v>
       </c>
       <c r="S39" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5409,22 +5363,27 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>11:46</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5433,70 +5392,65 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja, Markus Borja, Vivien Renaut</t>
+          <t>Markus Borja, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137044059</t>
+          <t>https://artportalen.se/Sighting/137016300</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>137044060</v>
+        <v>137016304</v>
       </c>
       <c r="B40" t="n">
-        <v>99359</v>
+        <v>58008</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>159</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -5504,13 +5458,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>636760</v>
+        <v>636466</v>
       </c>
       <c r="R40" t="n">
-        <v>7014309</v>
+        <v>7014462</v>
       </c>
       <c r="S40" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5534,22 +5488,27 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>12:24</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5558,70 +5517,65 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja, Markus Borja, Vivien Renaut</t>
+          <t>Markus Borja, Ann-Christine Borja, Diego Borja</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137044060</t>
+          <t>https://artportalen.se/Sighting/137016304</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>137044061</v>
+        <v>137016307</v>
       </c>
       <c r="B41" t="n">
-        <v>99359</v>
+        <v>58008</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -5629,13 +5583,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>636781</v>
+        <v>636566</v>
       </c>
       <c r="R41" t="n">
-        <v>7014323</v>
+        <v>7014367</v>
       </c>
       <c r="S41" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5659,22 +5613,27 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>12:35</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5683,70 +5642,65 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja, Markus Borja, Vivien Renaut</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137044061</t>
+          <t>https://artportalen.se/Sighting/137016307</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>137044062</v>
+        <v>137016344</v>
       </c>
       <c r="B42" t="n">
-        <v>99359</v>
+        <v>58008</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>117</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -5754,10 +5708,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>636772</v>
+        <v>636392</v>
       </c>
       <c r="R42" t="n">
-        <v>7014326</v>
+        <v>7014473</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5784,22 +5738,27 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5808,7 +5767,6 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -5820,58 +5778,54 @@
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja, Markus Borja, Vivien Renaut</t>
+          <t>Ann-Christine Borja, Markus Borja</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137044062</t>
+          <t>https://artportalen.se/Sighting/137016344</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>137044064</v>
+        <v>137040177</v>
       </c>
       <c r="B43" t="n">
-        <v>99359</v>
+        <v>58169</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -5879,13 +5833,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>636806</v>
+        <v>636811</v>
       </c>
       <c r="R43" t="n">
-        <v>7014282</v>
+        <v>7014284</v>
       </c>
       <c r="S43" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5914,7 +5868,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5924,7 +5878,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>12:13</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Läte</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5933,34 +5892,33 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Vivien Renaut</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja, Markus Borja, Vivien Renaut</t>
+          <t>Vivien Renaut</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137044064</t>
+          <t>https://artportalen.se/Sighting/137040177</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>137044080</v>
+        <v>137040164</v>
       </c>
       <c r="B44" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5987,7 +5945,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -6004,13 +5962,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>636598</v>
+        <v>636776</v>
       </c>
       <c r="R44" t="n">
-        <v>7014517</v>
+        <v>7014278</v>
       </c>
       <c r="S44" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -6039,7 +5997,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>09:05</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -6049,7 +6007,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>09:05</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6065,54 +6023,63 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Vivien Renaut</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja, Markus Borja, Vivien Renaut</t>
+          <t>Vivien Renaut</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137044080</t>
+          <t>https://artportalen.se/Sighting/137040164</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>137016336</v>
+        <v>137040166</v>
       </c>
       <c r="B45" t="n">
-        <v>79503</v>
+        <v>99361</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>260591</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -6120,13 +6087,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>636512</v>
+        <v>636782</v>
       </c>
       <c r="R45" t="n">
-        <v>7014375</v>
+        <v>7014300</v>
       </c>
       <c r="S45" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -6150,22 +6117,22 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6178,72 +6145,66 @@
       <c r="AG45" t="b">
         <v>0</v>
       </c>
-      <c r="AJ45" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK45" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO45" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Vivien Renaut</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja, Markus Borja</t>
+          <t>Vivien Renaut</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016336</t>
+          <t>https://artportalen.se/Sighting/137040166</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>137016339</v>
+        <v>137040168</v>
       </c>
       <c r="B46" t="n">
-        <v>79503</v>
+        <v>99361</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>260591</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
@@ -6251,13 +6212,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>636457</v>
+        <v>636758</v>
       </c>
       <c r="R46" t="n">
-        <v>7014405</v>
+        <v>7014368</v>
       </c>
       <c r="S46" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -6281,22 +6242,22 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6309,72 +6270,66 @@
       <c r="AG46" t="b">
         <v>0</v>
       </c>
-      <c r="AJ46" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK46" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO46" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Vivien Renaut</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Vivien Renaut</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016339</t>
+          <t>https://artportalen.se/Sighting/137040168</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>137016342</v>
+        <v>137040189</v>
       </c>
       <c r="B47" t="n">
-        <v>79503</v>
+        <v>99361</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>260591</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
@@ -6382,13 +6337,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>636417</v>
+        <v>636424</v>
       </c>
       <c r="R47" t="n">
-        <v>7014452</v>
+        <v>7014610</v>
       </c>
       <c r="S47" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6412,22 +6367,22 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6440,72 +6395,66 @@
       <c r="AG47" t="b">
         <v>0</v>
       </c>
-      <c r="AJ47" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK47" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO47" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Vivien Renaut</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Vivien Renaut</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016342</t>
+          <t>https://artportalen.se/Sighting/137040189</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>137016345</v>
+        <v>137044057</v>
       </c>
       <c r="B48" t="n">
-        <v>79503</v>
+        <v>99361</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>260591</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -6513,10 +6462,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>636407</v>
+        <v>636762</v>
       </c>
       <c r="R48" t="n">
-        <v>7014480</v>
+        <v>7014263</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -6543,22 +6492,22 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6571,21 +6520,6 @@
       <c r="AG48" t="b">
         <v>0</v>
       </c>
-      <c r="AJ48" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK48" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO48" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
@@ -6594,53 +6528,58 @@
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Ann-Christine Borja, Markus Borja, Vivien Renaut</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016345</t>
+          <t>https://artportalen.se/Sighting/137044057</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>137016346</v>
+        <v>137044059</v>
       </c>
       <c r="B49" t="n">
-        <v>79503</v>
+        <v>99361</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>260591</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
@@ -6648,10 +6587,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>636450</v>
+        <v>636736</v>
       </c>
       <c r="R49" t="n">
-        <v>7014535</v>
+        <v>7014341</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -6678,22 +6617,22 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6706,21 +6645,6 @@
       <c r="AG49" t="b">
         <v>0</v>
       </c>
-      <c r="AJ49" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK49" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO49" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
@@ -6729,53 +6653,58 @@
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Ann-Christine Borja, Markus Borja, Vivien Renaut</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016346</t>
+          <t>https://artportalen.se/Sighting/137044059</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>137016348</v>
+        <v>137044060</v>
       </c>
       <c r="B50" t="n">
-        <v>79503</v>
+        <v>99361</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>260591</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>159</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
@@ -6783,10 +6712,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>636479</v>
+        <v>636760</v>
       </c>
       <c r="R50" t="n">
-        <v>7014523</v>
+        <v>7014309</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -6813,22 +6742,22 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6841,21 +6770,6 @@
       <c r="AG50" t="b">
         <v>0</v>
       </c>
-      <c r="AJ50" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK50" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO50" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
@@ -6864,49 +6778,58 @@
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Ann-Christine Borja, Markus Borja, Vivien Renaut</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016348</t>
+          <t>https://artportalen.se/Sighting/137044060</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>137016353</v>
+        <v>137044061</v>
       </c>
       <c r="B51" t="n">
-        <v>79503</v>
+        <v>99361</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>260591</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
@@ -6914,10 +6837,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>636460</v>
+        <v>636781</v>
       </c>
       <c r="R51" t="n">
-        <v>7014451</v>
+        <v>7014323</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6944,22 +6867,22 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6972,21 +6895,6 @@
       <c r="AG51" t="b">
         <v>0</v>
       </c>
-      <c r="AJ51" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK51" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO51" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
@@ -6995,53 +6903,58 @@
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Ann-Christine Borja, Markus Borja, Vivien Renaut</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016353</t>
+          <t>https://artportalen.se/Sighting/137044061</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>137044071</v>
+        <v>137044062</v>
       </c>
       <c r="B52" t="n">
-        <v>79503</v>
+        <v>99361</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>260591</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>117</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
@@ -7049,10 +6962,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>636845</v>
+        <v>636772</v>
       </c>
       <c r="R52" t="n">
-        <v>7014233</v>
+        <v>7014326</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -7084,7 +6997,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -7094,7 +7007,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -7107,21 +7020,6 @@
       <c r="AG52" t="b">
         <v>0</v>
       </c>
-      <c r="AJ52" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK52" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO52" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
@@ -7130,11 +7028,1321 @@
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Ann-Christine Borja, Markus Borja, Vivien Renaut</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137044062</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>137044064</v>
+      </c>
+      <c r="B53" t="n">
+        <v>99361</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Stortannsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>636806</v>
+      </c>
+      <c r="R53" t="n">
+        <v>7014282</v>
+      </c>
+      <c r="S53" t="n">
+        <v>5</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Överlännäs</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>10:48</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>10:48</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF53" t="inlineStr"/>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja, Markus Borja, Vivien Renaut</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137044064</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>137044080</v>
+      </c>
+      <c r="B54" t="n">
+        <v>99361</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Stortannsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>636598</v>
+      </c>
+      <c r="R54" t="n">
+        <v>7014517</v>
+      </c>
+      <c r="S54" t="n">
+        <v>5</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Överlännäs</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>14:32</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>14:32</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF54" t="inlineStr"/>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja, Markus Borja, Vivien Renaut</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137044080</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>137016336</v>
+      </c>
+      <c r="B55" t="n">
+        <v>79505</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Stortannsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>636512</v>
+      </c>
+      <c r="R55" t="n">
+        <v>7014375</v>
+      </c>
+      <c r="S55" t="n">
+        <v>5</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Överlännäs</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>11:12</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>11:12</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF55" t="inlineStr"/>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ55" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK55" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO55" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja, Markus Borja</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137016336</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>137016339</v>
+      </c>
+      <c r="B56" t="n">
+        <v>79505</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Stortannsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>636457</v>
+      </c>
+      <c r="R56" t="n">
+        <v>7014405</v>
+      </c>
+      <c r="S56" t="n">
+        <v>5</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Överlännäs</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>11:22</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>11:22</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF56" t="inlineStr"/>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ56" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK56" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO56" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137016339</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>137016342</v>
+      </c>
+      <c r="B57" t="n">
+        <v>79505</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Stortannsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>636417</v>
+      </c>
+      <c r="R57" t="n">
+        <v>7014452</v>
+      </c>
+      <c r="S57" t="n">
+        <v>5</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Överlännäs</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF57" t="inlineStr"/>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ57" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK57" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO57" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137016342</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>137016345</v>
+      </c>
+      <c r="B58" t="n">
+        <v>79505</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Stortannsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>636407</v>
+      </c>
+      <c r="R58" t="n">
+        <v>7014480</v>
+      </c>
+      <c r="S58" t="n">
+        <v>5</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Överlännäs</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>11:59</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>11:59</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF58" t="inlineStr"/>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ58" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK58" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO58" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137016345</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>137016346</v>
+      </c>
+      <c r="B59" t="n">
+        <v>79505</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Stortannsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>636450</v>
+      </c>
+      <c r="R59" t="n">
+        <v>7014535</v>
+      </c>
+      <c r="S59" t="n">
+        <v>5</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Överlännäs</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF59" t="inlineStr"/>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ59" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK59" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO59" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137016346</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>137016348</v>
+      </c>
+      <c r="B60" t="n">
+        <v>79505</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Stortannsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>636479</v>
+      </c>
+      <c r="R60" t="n">
+        <v>7014523</v>
+      </c>
+      <c r="S60" t="n">
+        <v>5</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Överlännäs</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>12:09</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>12:09</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF60" t="inlineStr"/>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ60" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK60" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO60" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137016348</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>137016353</v>
+      </c>
+      <c r="B61" t="n">
+        <v>79505</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Stortannsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>636460</v>
+      </c>
+      <c r="R61" t="n">
+        <v>7014451</v>
+      </c>
+      <c r="S61" t="n">
+        <v>5</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Överlännäs</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>12:28</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>12:28</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF61" t="inlineStr"/>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ61" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK61" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO61" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137016353</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>137044071</v>
+      </c>
+      <c r="B62" t="n">
+        <v>79505</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Stortannsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>636845</v>
+      </c>
+      <c r="R62" t="n">
+        <v>7014233</v>
+      </c>
+      <c r="S62" t="n">
+        <v>5</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Överlännäs</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>12:09</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>12:09</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF62" t="inlineStr"/>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ62" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK62" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO62" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/137044071</t>
         </is>
@@ -7193,6 +8401,16 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 25855-2025 artfynd.xlsx
+++ b/artfynd/A 25855-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ62"/>
+  <dimension ref="A1:AZ87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1156,48 +1156,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>137016298</v>
+        <v>137040122</v>
       </c>
       <c r="B6" t="n">
-        <v>93453</v>
+        <v>92080</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5966</v>
+        <v>5447</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Stortannsjön, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>636437</v>
+        <v>636830</v>
       </c>
       <c r="R6" t="n">
-        <v>7014437</v>
+        <v>7014277</v>
       </c>
       <c r="S6" t="n">
         <v>3</v>
@@ -1224,22 +1221,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1248,7 +1245,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1260,44 +1256,44 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Markus Borja, Diego Borja, Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016298</t>
+          <t>https://artportalen.se/Sighting/137040122</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>137016289</v>
+        <v>137016298</v>
       </c>
       <c r="B7" t="n">
-        <v>79482</v>
+        <v>93453</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>5966</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1310,10 +1306,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>636608</v>
+        <v>636437</v>
       </c>
       <c r="R7" t="n">
-        <v>7014302</v>
+        <v>7014437</v>
       </c>
       <c r="S7" t="n">
         <v>3</v>
@@ -1345,7 +1341,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1355,7 +1351,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1368,21 +1364,6 @@
       <c r="AG7" t="b">
         <v>0</v>
       </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
@@ -1391,19 +1372,19 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Markus Borja, Diego Borja, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016289</t>
+          <t>https://artportalen.se/Sighting/137016298</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>137016306</v>
+        <v>137016289</v>
       </c>
       <c r="B8" t="n">
         <v>79482</v>
@@ -1441,10 +1422,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>636566</v>
+        <v>636608</v>
       </c>
       <c r="R8" t="n">
-        <v>7014366</v>
+        <v>7014302</v>
       </c>
       <c r="S8" t="n">
         <v>3</v>
@@ -1476,7 +1457,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1486,7 +1467,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1528,13 +1509,13 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016306</t>
+          <t>https://artportalen.se/Sighting/137016289</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>137016332</v>
+        <v>137016306</v>
       </c>
       <c r="B9" t="n">
         <v>79482</v>
@@ -1572,13 +1553,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>636603</v>
+        <v>636566</v>
       </c>
       <c r="R9" t="n">
-        <v>7014322</v>
+        <v>7014366</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1607,7 +1588,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1617,7 +1598,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1648,24 +1629,24 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016332</t>
+          <t>https://artportalen.se/Sighting/137016306</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>137016333</v>
+        <v>137016332</v>
       </c>
       <c r="B10" t="n">
         <v>79482</v>
@@ -1703,10 +1684,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>636623</v>
+        <v>636603</v>
       </c>
       <c r="R10" t="n">
-        <v>7014305</v>
+        <v>7014322</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1738,7 +1719,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1748,7 +1729,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1790,13 +1771,13 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016333</t>
+          <t>https://artportalen.se/Sighting/137016332</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>137016335</v>
+        <v>137016333</v>
       </c>
       <c r="B11" t="n">
         <v>79482</v>
@@ -1834,10 +1815,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>636520</v>
+        <v>636623</v>
       </c>
       <c r="R11" t="n">
-        <v>7014374</v>
+        <v>7014305</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1869,7 +1850,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1879,7 +1860,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1921,13 +1902,13 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016335</t>
+          <t>https://artportalen.se/Sighting/137016333</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>137016337</v>
+        <v>137016335</v>
       </c>
       <c r="B12" t="n">
         <v>79482</v>
@@ -1965,10 +1946,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>636463</v>
+        <v>636520</v>
       </c>
       <c r="R12" t="n">
-        <v>7014402</v>
+        <v>7014374</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -2000,7 +1981,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2010,7 +1991,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2052,13 +2033,13 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016337</t>
+          <t>https://artportalen.se/Sighting/137016335</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>137016340</v>
+        <v>137016337</v>
       </c>
       <c r="B13" t="n">
         <v>79482</v>
@@ -2096,10 +2077,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>636419</v>
+        <v>636463</v>
       </c>
       <c r="R13" t="n">
-        <v>7014437</v>
+        <v>7014402</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2131,7 +2112,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2141,7 +2122,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2183,13 +2164,13 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016340</t>
+          <t>https://artportalen.se/Sighting/137016337</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>137016349</v>
+        <v>137016340</v>
       </c>
       <c r="B14" t="n">
         <v>79482</v>
@@ -2227,10 +2208,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>636488</v>
+        <v>636419</v>
       </c>
       <c r="R14" t="n">
-        <v>7014536</v>
+        <v>7014437</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2262,7 +2243,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2272,7 +2253,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2314,13 +2295,13 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016349</t>
+          <t>https://artportalen.se/Sighting/137016340</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>137016350</v>
+        <v>137016349</v>
       </c>
       <c r="B15" t="n">
         <v>79482</v>
@@ -2358,10 +2339,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>636466</v>
+        <v>636488</v>
       </c>
       <c r="R15" t="n">
-        <v>7014464</v>
+        <v>7014536</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2393,7 +2374,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2403,7 +2384,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2445,13 +2426,13 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016350</t>
+          <t>https://artportalen.se/Sighting/137016349</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>137040167</v>
+        <v>137016350</v>
       </c>
       <c r="B16" t="n">
         <v>79482</v>
@@ -2480,16 +2461,19 @@
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Stortannsjön, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>636743</v>
+        <v>636466</v>
       </c>
       <c r="R16" t="n">
-        <v>7014374</v>
+        <v>7014464</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2516,22 +2500,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2540,30 +2524,46 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Vivien Renaut</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Vivien Renaut</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137040167</t>
+          <t>https://artportalen.se/Sighting/137016350</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>137040169</v>
+        <v>137040102</v>
       </c>
       <c r="B17" t="n">
         <v>79482</v>
@@ -2592,19 +2592,22 @@
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Stortannsjön, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>636844</v>
+        <v>636758</v>
       </c>
       <c r="R17" t="n">
-        <v>7014273</v>
+        <v>7014258</v>
       </c>
       <c r="S17" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2633,7 +2636,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>09:08</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2643,7 +2646,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>09:08</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2652,30 +2655,46 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Vivien Renaut</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Vivien Renaut</t>
+          <t>Markus Borja, Vivien Renaut, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137040169</t>
+          <t>https://artportalen.se/Sighting/137040102</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>137040181</v>
+        <v>137040133</v>
       </c>
       <c r="B18" t="n">
         <v>79482</v>
@@ -2704,19 +2723,22 @@
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Stortannsjön, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>636605</v>
+        <v>636608</v>
       </c>
       <c r="R18" t="n">
-        <v>7014506</v>
+        <v>7014515</v>
       </c>
       <c r="S18" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2745,7 +2767,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2755,12 +2777,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:28</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Garnlav på tall</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2769,30 +2786,46 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Vivien Renaut</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Vivien Renaut</t>
+          <t>Markus Borja, Vivien Renaut, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137040181</t>
+          <t>https://artportalen.se/Sighting/137040133</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>137044055</v>
+        <v>137040161</v>
       </c>
       <c r="B19" t="n">
         <v>79482</v>
@@ -2830,13 +2863,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>636694</v>
+        <v>636549</v>
       </c>
       <c r="R19" t="n">
-        <v>7014252</v>
+        <v>7014491</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2865,7 +2898,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>08:47</t>
+          <t>18:07</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2875,7 +2908,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>08:47</t>
+          <t>18:07</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2906,24 +2939,24 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja, Vivien Renaut, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137044055</t>
+          <t>https://artportalen.se/Sighting/137040161</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>137044068</v>
+        <v>137040162</v>
       </c>
       <c r="B20" t="n">
         <v>79482</v>
@@ -2961,13 +2994,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>636901</v>
+        <v>636606</v>
       </c>
       <c r="R20" t="n">
-        <v>7014208</v>
+        <v>7014419</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2996,7 +3029,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3006,7 +3039,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3021,40 +3054,40 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja, Vivien Renaut, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137044068</t>
+          <t>https://artportalen.se/Sighting/137040162</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>137044072</v>
+        <v>137040167</v>
       </c>
       <c r="B21" t="n">
         <v>79482</v>
@@ -3083,19 +3116,16 @@
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Stortannsjön, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>636840</v>
+        <v>636743</v>
       </c>
       <c r="R21" t="n">
-        <v>7014233</v>
+        <v>7014374</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -3127,7 +3157,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3137,7 +3167,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3146,90 +3176,71 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Vivien Renaut</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Vivien Renaut</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137044072</t>
+          <t>https://artportalen.se/Sighting/137040167</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>137016334</v>
+        <v>137040169</v>
       </c>
       <c r="B22" t="n">
-        <v>79506</v>
+        <v>79482</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Stortannsjön, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>636591</v>
+        <v>636844</v>
       </c>
       <c r="R22" t="n">
-        <v>7014315</v>
+        <v>7014273</v>
       </c>
       <c r="S22" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3253,22 +3264,22 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3277,90 +3288,71 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Vivien Renaut</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Vivien Renaut</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016334</t>
+          <t>https://artportalen.se/Sighting/137040169</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>137016341</v>
+        <v>137040181</v>
       </c>
       <c r="B23" t="n">
-        <v>79506</v>
+        <v>79482</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Stortannsjön, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>636409</v>
+        <v>636605</v>
       </c>
       <c r="R23" t="n">
-        <v>7014452</v>
+        <v>7014506</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3384,22 +3376,27 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>14:28</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Garnlav på tall</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3408,71 +3405,55 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Vivien Renaut</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Vivien Renaut</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016341</t>
+          <t>https://artportalen.se/Sighting/137040181</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>137016351</v>
+        <v>137044055</v>
       </c>
       <c r="B24" t="n">
-        <v>79506</v>
+        <v>79482</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3485,10 +3466,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>636460</v>
+        <v>636694</v>
       </c>
       <c r="R24" t="n">
-        <v>7014454</v>
+        <v>7014252</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3515,22 +3496,22 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>08:47</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>08:47</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3572,38 +3553,38 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016351</t>
+          <t>https://artportalen.se/Sighting/137044055</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>137044056</v>
+        <v>137044068</v>
       </c>
       <c r="B25" t="n">
-        <v>79506</v>
+        <v>79482</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3616,10 +3597,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>636699</v>
+        <v>636901</v>
       </c>
       <c r="R25" t="n">
-        <v>7014271</v>
+        <v>7014208</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3651,7 +3632,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3661,7 +3642,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3703,54 +3684,57 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137044056</t>
+          <t>https://artportalen.se/Sighting/137044068</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>137016288</v>
+        <v>137044072</v>
       </c>
       <c r="B26" t="n">
-        <v>80101</v>
+        <v>79482</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Stortannsjön, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>636610</v>
+        <v>636840</v>
       </c>
       <c r="R26" t="n">
-        <v>7014307</v>
+        <v>7014233</v>
       </c>
       <c r="S26" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3774,22 +3758,22 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3798,71 +3782,90 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016288</t>
+          <t>https://artportalen.se/Sighting/137044072</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>137016299</v>
+        <v>137016334</v>
       </c>
       <c r="B27" t="n">
-        <v>80101</v>
+        <v>79506</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6453</v>
+        <v>6434</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Stortannsjön, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>636418</v>
+        <v>636591</v>
       </c>
       <c r="R27" t="n">
-        <v>7014453</v>
+        <v>7014315</v>
       </c>
       <c r="S27" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3891,7 +3894,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3901,7 +3904,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3910,71 +3913,90 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016299</t>
+          <t>https://artportalen.se/Sighting/137016334</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>137016303</v>
+        <v>137016341</v>
       </c>
       <c r="B28" t="n">
-        <v>80101</v>
+        <v>79506</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6453</v>
+        <v>6434</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Stortannsjön, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>636499</v>
+        <v>636409</v>
       </c>
       <c r="R28" t="n">
-        <v>7014546</v>
+        <v>7014452</v>
       </c>
       <c r="S28" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -4003,7 +4025,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -4013,7 +4035,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4022,33 +4044,49 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016303</t>
+          <t>https://artportalen.se/Sighting/137016341</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>137016301</v>
+        <v>137016351</v>
       </c>
       <c r="B29" t="n">
-        <v>58005</v>
+        <v>79506</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4056,31 +4094,26 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100049</v>
+        <v>6434</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -4088,13 +4121,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>636482</v>
+        <v>636460</v>
       </c>
       <c r="R29" t="n">
-        <v>7014533</v>
+        <v>7014454</v>
       </c>
       <c r="S29" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4123,7 +4156,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4133,7 +4166,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4142,33 +4175,49 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016301</t>
+          <t>https://artportalen.se/Sighting/137016351</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>137040182</v>
+        <v>137040100</v>
       </c>
       <c r="B30" t="n">
-        <v>58005</v>
+        <v>79506</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4176,31 +4225,26 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
+        <v>6434</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -4208,13 +4252,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>636550</v>
+        <v>636705</v>
       </c>
       <c r="R30" t="n">
-        <v>7014507</v>
+        <v>7014244</v>
       </c>
       <c r="S30" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4243,7 +4287,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4253,12 +4297,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:41</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Färska spår</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4267,65 +4306,76 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Vivien Renaut</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Vivien Renaut</t>
+          <t>Markus Borja, Vivien Renaut, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137040182</t>
+          <t>https://artportalen.se/Sighting/137040100</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>137016287</v>
+        <v>137044056</v>
       </c>
       <c r="B31" t="n">
-        <v>58008</v>
+        <v>79506</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>6434</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -4333,13 +4383,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>636606</v>
+        <v>636699</v>
       </c>
       <c r="R31" t="n">
-        <v>7014302</v>
+        <v>7014271</v>
       </c>
       <c r="S31" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4363,27 +4413,22 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>10:34</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Färska och Äldre ringhack på tall</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4392,33 +4437,49 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja, Diego Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016287</t>
+          <t>https://artportalen.se/Sighting/137044056</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>137016290</v>
+        <v>137040105</v>
       </c>
       <c r="B32" t="n">
-        <v>58008</v>
+        <v>79239</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4426,42 +4487,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Stortannsjön, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>636608</v>
+        <v>636730</v>
       </c>
       <c r="R32" t="n">
-        <v>7014302</v>
+        <v>7014286</v>
       </c>
       <c r="S32" t="n">
         <v>3</v>
@@ -4488,27 +4541,22 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>10:54</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4528,22 +4576,22 @@
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja, Diego Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016290</t>
+          <t>https://artportalen.se/Sighting/137040105</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>137016291</v>
+        <v>137040135</v>
       </c>
       <c r="B33" t="n">
-        <v>58008</v>
+        <v>79239</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4551,42 +4599,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Stortannsjön, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>636578</v>
+        <v>636582</v>
       </c>
       <c r="R33" t="n">
-        <v>7014320</v>
+        <v>7014519</v>
       </c>
       <c r="S33" t="n">
         <v>3</v>
@@ -4613,27 +4653,22 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>10:59</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4653,22 +4688,22 @@
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja, Diego Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016291</t>
+          <t>https://artportalen.se/Sighting/137040135</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>137016292</v>
+        <v>137016288</v>
       </c>
       <c r="B34" t="n">
-        <v>58008</v>
+        <v>80101</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4676,42 +4711,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Stortannsjön, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>636501</v>
+        <v>636610</v>
       </c>
       <c r="R34" t="n">
-        <v>7014381</v>
+        <v>7014307</v>
       </c>
       <c r="S34" t="n">
         <v>3</v>
@@ -4743,7 +4770,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4753,12 +4780,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>11:09</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4778,22 +4800,22 @@
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016292</t>
+          <t>https://artportalen.se/Sighting/137016288</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>137016294</v>
+        <v>137016299</v>
       </c>
       <c r="B35" t="n">
-        <v>58008</v>
+        <v>80101</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4801,42 +4823,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Stortannsjön, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>636486</v>
+        <v>636418</v>
       </c>
       <c r="R35" t="n">
-        <v>7014403</v>
+        <v>7014453</v>
       </c>
       <c r="S35" t="n">
         <v>3</v>
@@ -4868,7 +4882,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4878,12 +4892,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:16</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4903,22 +4912,22 @@
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016294</t>
+          <t>https://artportalen.se/Sighting/137016299</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>137016295</v>
+        <v>137016303</v>
       </c>
       <c r="B36" t="n">
-        <v>58008</v>
+        <v>80101</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4926,42 +4935,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Stortannsjön, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>636432</v>
+        <v>636499</v>
       </c>
       <c r="R36" t="n">
-        <v>7014422</v>
+        <v>7014546</v>
       </c>
       <c r="S36" t="n">
         <v>3</v>
@@ -4993,7 +4994,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -5003,12 +5004,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:28</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5028,22 +5024,22 @@
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016295</t>
+          <t>https://artportalen.se/Sighting/137016303</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>137016296</v>
+        <v>137040101</v>
       </c>
       <c r="B37" t="n">
-        <v>58008</v>
+        <v>80101</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5051,42 +5047,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Stortannsjön, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>636424</v>
+        <v>636731</v>
       </c>
       <c r="R37" t="n">
-        <v>7014437</v>
+        <v>7014243</v>
       </c>
       <c r="S37" t="n">
         <v>3</v>
@@ -5113,27 +5101,22 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>09:05</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>11:30</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack på tall</t>
+          <t>09:05</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5153,22 +5136,22 @@
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016296</t>
+          <t>https://artportalen.se/Sighting/137040101</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>137016297</v>
+        <v>137040104</v>
       </c>
       <c r="B38" t="n">
-        <v>58008</v>
+        <v>80101</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5176,42 +5159,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Stortannsjön, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>636448</v>
+        <v>636746</v>
       </c>
       <c r="R38" t="n">
-        <v>7014424</v>
+        <v>7014291</v>
       </c>
       <c r="S38" t="n">
         <v>3</v>
@@ -5238,27 +5213,22 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>11:35</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5278,54 +5248,49 @@
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016297</t>
+          <t>https://artportalen.se/Sighting/137040104</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>137016300</v>
+        <v>137040108</v>
       </c>
       <c r="B39" t="n">
-        <v>58008</v>
+        <v>80491</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>6456</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -5333,13 +5298,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>636398</v>
+        <v>636817</v>
       </c>
       <c r="R39" t="n">
-        <v>7014509</v>
+        <v>7014280</v>
       </c>
       <c r="S39" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5363,27 +5328,22 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>11:46</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5392,8 +5352,24 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ39" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK39" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO39" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
@@ -5403,54 +5379,49 @@
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja</t>
+          <t>Markus Borja, Vivien Renaut, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016300</t>
+          <t>https://artportalen.se/Sighting/137040108</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>137016304</v>
+        <v>137040110</v>
       </c>
       <c r="B40" t="n">
-        <v>58008</v>
+        <v>80491</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>6456</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -5458,10 +5429,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>636466</v>
+        <v>636815</v>
       </c>
       <c r="R40" t="n">
-        <v>7014462</v>
+        <v>7014278</v>
       </c>
       <c r="S40" t="n">
         <v>3</v>
@@ -5488,27 +5459,22 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>12:24</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5517,8 +5483,24 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ40" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK40" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO40" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
@@ -5528,54 +5510,49 @@
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja, Diego Borja</t>
+          <t>Markus Borja, Vivien Renaut, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016304</t>
+          <t>https://artportalen.se/Sighting/137040110</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>137016307</v>
+        <v>137040111</v>
       </c>
       <c r="B41" t="n">
-        <v>58008</v>
+        <v>80491</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>6456</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -5583,13 +5560,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>636566</v>
+        <v>636803</v>
       </c>
       <c r="R41" t="n">
-        <v>7014367</v>
+        <v>7014259</v>
       </c>
       <c r="S41" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5613,27 +5590,22 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>12:35</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5642,8 +5614,24 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
@@ -5653,39 +5641,39 @@
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Markus Borja, Vivien Renaut, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016307</t>
+          <t>https://artportalen.se/Sighting/137040111</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>137016344</v>
+        <v>137016301</v>
       </c>
       <c r="B42" t="n">
-        <v>58008</v>
+        <v>58005</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -5708,13 +5696,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>636392</v>
+        <v>636482</v>
       </c>
       <c r="R42" t="n">
-        <v>7014473</v>
+        <v>7014533</v>
       </c>
       <c r="S42" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5743,7 +5731,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5753,12 +5741,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>11:50</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall.</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5773,49 +5756,49 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja, Markus Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016344</t>
+          <t>https://artportalen.se/Sighting/137016301</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>137040177</v>
+        <v>137040182</v>
       </c>
       <c r="B43" t="n">
-        <v>58169</v>
+        <v>58005</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5823,7 +5806,7 @@
       <c r="L43" t="inlineStr"/>
       <c r="M43" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N43" t="inlineStr"/>
@@ -5833,13 +5816,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>636811</v>
+        <v>636550</v>
       </c>
       <c r="R43" t="n">
-        <v>7014284</v>
+        <v>7014507</v>
       </c>
       <c r="S43" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5868,7 +5851,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5878,12 +5861,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Läte</t>
+          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5909,52 +5892,48 @@
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137040177</t>
+          <t>https://artportalen.se/Sighting/137040182</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>137040164</v>
+        <v>137016287</v>
       </c>
       <c r="B44" t="n">
-        <v>99361</v>
+        <v>58008</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -5962,10 +5941,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>636776</v>
+        <v>636606</v>
       </c>
       <c r="R44" t="n">
-        <v>7014278</v>
+        <v>7014302</v>
       </c>
       <c r="S44" t="n">
         <v>3</v>
@@ -5992,22 +5971,27 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>09:05</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>09:05</t>
+          <t>10:34</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Färska och Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6016,70 +6000,65 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Vivien Renaut</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Vivien Renaut</t>
+          <t>Markus Borja, Ann-Christine Borja, Diego Borja</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137040164</t>
+          <t>https://artportalen.se/Sighting/137016287</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>137040166</v>
+        <v>137016290</v>
       </c>
       <c r="B45" t="n">
-        <v>99361</v>
+        <v>58008</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>115</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -6087,10 +6066,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>636782</v>
+        <v>636608</v>
       </c>
       <c r="R45" t="n">
-        <v>7014300</v>
+        <v>7014302</v>
       </c>
       <c r="S45" t="n">
         <v>3</v>
@@ -6117,22 +6096,27 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>10:54</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6141,70 +6125,65 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Vivien Renaut</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Vivien Renaut</t>
+          <t>Markus Borja, Ann-Christine Borja, Diego Borja</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137040166</t>
+          <t>https://artportalen.se/Sighting/137016290</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>137040168</v>
+        <v>137016291</v>
       </c>
       <c r="B46" t="n">
-        <v>99361</v>
+        <v>58008</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
@@ -6212,10 +6191,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>636758</v>
+        <v>636578</v>
       </c>
       <c r="R46" t="n">
-        <v>7014368</v>
+        <v>7014320</v>
       </c>
       <c r="S46" t="n">
         <v>3</v>
@@ -6242,22 +6221,27 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>10:59</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6266,70 +6250,65 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Vivien Renaut</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Vivien Renaut</t>
+          <t>Markus Borja, Ann-Christine Borja, Diego Borja</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137040168</t>
+          <t>https://artportalen.se/Sighting/137016291</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>137040189</v>
+        <v>137016292</v>
       </c>
       <c r="B47" t="n">
-        <v>99361</v>
+        <v>58008</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
@@ -6337,13 +6316,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>636424</v>
+        <v>636501</v>
       </c>
       <c r="R47" t="n">
-        <v>7014610</v>
+        <v>7014381</v>
       </c>
       <c r="S47" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6367,22 +6346,27 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>11:09</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6391,70 +6375,65 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Vivien Renaut</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Vivien Renaut</t>
+          <t>Markus Borja, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137040189</t>
+          <t>https://artportalen.se/Sighting/137016292</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>137044057</v>
+        <v>137016294</v>
       </c>
       <c r="B48" t="n">
-        <v>99361</v>
+        <v>58008</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -6462,13 +6441,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>636762</v>
+        <v>636486</v>
       </c>
       <c r="R48" t="n">
-        <v>7014263</v>
+        <v>7014403</v>
       </c>
       <c r="S48" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6492,22 +6471,27 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>11:16</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6516,70 +6500,65 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja, Markus Borja, Vivien Renaut</t>
+          <t>Markus Borja, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137044057</t>
+          <t>https://artportalen.se/Sighting/137016294</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>137044059</v>
+        <v>137016295</v>
       </c>
       <c r="B49" t="n">
-        <v>99361</v>
+        <v>58008</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>105</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
@@ -6587,13 +6566,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>636736</v>
+        <v>636432</v>
       </c>
       <c r="R49" t="n">
-        <v>7014341</v>
+        <v>7014422</v>
       </c>
       <c r="S49" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6617,22 +6596,27 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>11:28</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6641,70 +6625,65 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja, Markus Borja, Vivien Renaut</t>
+          <t>Markus Borja, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137044059</t>
+          <t>https://artportalen.se/Sighting/137016295</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>137044060</v>
+        <v>137016296</v>
       </c>
       <c r="B50" t="n">
-        <v>99361</v>
+        <v>58008</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>159</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
@@ -6712,13 +6691,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>636760</v>
+        <v>636424</v>
       </c>
       <c r="R50" t="n">
-        <v>7014309</v>
+        <v>7014437</v>
       </c>
       <c r="S50" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6742,22 +6721,27 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6766,70 +6750,65 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja, Markus Borja, Vivien Renaut</t>
+          <t>Markus Borja, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137044060</t>
+          <t>https://artportalen.se/Sighting/137016296</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>137044061</v>
+        <v>137016297</v>
       </c>
       <c r="B51" t="n">
-        <v>99361</v>
+        <v>58008</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
@@ -6837,13 +6816,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>636781</v>
+        <v>636448</v>
       </c>
       <c r="R51" t="n">
-        <v>7014323</v>
+        <v>7014424</v>
       </c>
       <c r="S51" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6867,22 +6846,27 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>11:35</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6891,70 +6875,65 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja, Markus Borja, Vivien Renaut</t>
+          <t>Markus Borja, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137044061</t>
+          <t>https://artportalen.se/Sighting/137016297</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>137044062</v>
+        <v>137016300</v>
       </c>
       <c r="B52" t="n">
-        <v>99361</v>
+        <v>58008</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>117</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
@@ -6962,13 +6941,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>636772</v>
+        <v>636398</v>
       </c>
       <c r="R52" t="n">
-        <v>7014326</v>
+        <v>7014509</v>
       </c>
       <c r="S52" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6992,22 +6971,27 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>11:46</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -7016,70 +7000,65 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja, Markus Borja, Vivien Renaut</t>
+          <t>Markus Borja, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137044062</t>
+          <t>https://artportalen.se/Sighting/137016300</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>137044064</v>
+        <v>137016304</v>
       </c>
       <c r="B53" t="n">
-        <v>99361</v>
+        <v>58008</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
@@ -7087,13 +7066,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>636806</v>
+        <v>636466</v>
       </c>
       <c r="R53" t="n">
-        <v>7014282</v>
+        <v>7014462</v>
       </c>
       <c r="S53" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -7117,22 +7096,27 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>12:24</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -7141,70 +7125,65 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja, Markus Borja, Vivien Renaut</t>
+          <t>Markus Borja, Ann-Christine Borja, Diego Borja</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137044064</t>
+          <t>https://artportalen.se/Sighting/137016304</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>137044080</v>
+        <v>137016307</v>
       </c>
       <c r="B54" t="n">
-        <v>99361</v>
+        <v>58008</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
@@ -7212,13 +7191,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>636598</v>
+        <v>636566</v>
       </c>
       <c r="R54" t="n">
-        <v>7014517</v>
+        <v>7014367</v>
       </c>
       <c r="S54" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -7242,22 +7221,27 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>12:35</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7266,34 +7250,33 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja, Markus Borja, Vivien Renaut</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137044080</t>
+          <t>https://artportalen.se/Sighting/137016307</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>137016336</v>
+        <v>137016344</v>
       </c>
       <c r="B55" t="n">
-        <v>79505</v>
+        <v>58008</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7301,26 +7284,31 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>260591</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
@@ -7328,10 +7316,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>636512</v>
+        <v>636392</v>
       </c>
       <c r="R55" t="n">
-        <v>7014375</v>
+        <v>7014473</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -7363,7 +7351,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -7373,7 +7361,12 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall.</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7382,24 +7375,8 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ55" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK55" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO55" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
@@ -7415,16 +7392,16 @@
       <c r="AY55" t="inlineStr"/>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016336</t>
+          <t>https://artportalen.se/Sighting/137016344</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>137016339</v>
+        <v>137040097</v>
       </c>
       <c r="B56" t="n">
-        <v>79505</v>
+        <v>58008</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7432,26 +7409,31 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>260591</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
@@ -7459,13 +7441,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>636457</v>
+        <v>636710</v>
       </c>
       <c r="R56" t="n">
-        <v>7014405</v>
+        <v>7014234</v>
       </c>
       <c r="S56" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -7489,22 +7471,27 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>08:39</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>08:39</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7513,49 +7500,33 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
-      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ56" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK56" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO56" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja, Vivien Renaut, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016339</t>
+          <t>https://artportalen.se/Sighting/137040097</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>137016342</v>
+        <v>137040106</v>
       </c>
       <c r="B57" t="n">
-        <v>79505</v>
+        <v>58169</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7563,40 +7534,53 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>260591</v>
+        <v>103021</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="K57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Stortannsjön, Ång</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>636417</v>
+        <v>636783</v>
       </c>
       <c r="R57" t="n">
-        <v>7014452</v>
+        <v>7014328</v>
       </c>
       <c r="S57" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7620,22 +7604,22 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7644,49 +7628,33 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ57" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK57" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO57" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja, Ann-Christine Borja, Vivien Renaut</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016342</t>
+          <t>https://artportalen.se/Sighting/137040106</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>137016345</v>
+        <v>137040109</v>
       </c>
       <c r="B58" t="n">
-        <v>79505</v>
+        <v>58169</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7694,26 +7662,31 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>260591</v>
+        <v>103021</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
@@ -7721,13 +7694,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>636407</v>
+        <v>636808</v>
       </c>
       <c r="R58" t="n">
-        <v>7014480</v>
+        <v>7014272</v>
       </c>
       <c r="S58" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7751,22 +7724,22 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7775,49 +7748,33 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
-      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ58" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK58" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO58" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja, Vivien Renaut</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016345</t>
+          <t>https://artportalen.se/Sighting/137040109</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>137016346</v>
+        <v>137040177</v>
       </c>
       <c r="B59" t="n">
-        <v>79505</v>
+        <v>58169</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7825,28 +7782,29 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>260591</v>
+        <v>103021</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N59" t="inlineStr"/>
@@ -7856,13 +7814,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>636450</v>
+        <v>636811</v>
       </c>
       <c r="R59" t="n">
-        <v>7014535</v>
+        <v>7014284</v>
       </c>
       <c r="S59" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7886,22 +7844,27 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>12:13</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Läte</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7910,80 +7873,69 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
-      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ59" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK59" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO59" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Vivien Renaut</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Vivien Renaut</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016346</t>
+          <t>https://artportalen.se/Sighting/137040177</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>137016348</v>
+        <v>137040107</v>
       </c>
       <c r="B60" t="n">
-        <v>79505</v>
+        <v>99361</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>260591</v>
+        <v>220787</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
       <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
@@ -7991,13 +7943,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>636479</v>
+        <v>636807</v>
       </c>
       <c r="R60" t="n">
-        <v>7014523</v>
+        <v>7014295</v>
       </c>
       <c r="S60" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -8021,22 +7973,22 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -8049,72 +8001,66 @@
       <c r="AG60" t="b">
         <v>0</v>
       </c>
-      <c r="AJ60" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK60" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO60" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja, Vivien Renaut, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016348</t>
+          <t>https://artportalen.se/Sighting/137040107</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>137016353</v>
+        <v>137040121</v>
       </c>
       <c r="B61" t="n">
-        <v>79505</v>
+        <v>99361</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>260591</v>
+        <v>220787</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
       <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
@@ -8122,13 +8068,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>636460</v>
+        <v>636854</v>
       </c>
       <c r="R61" t="n">
-        <v>7014451</v>
+        <v>7014229</v>
       </c>
       <c r="S61" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -8152,22 +8098,22 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -8180,76 +8126,66 @@
       <c r="AG61" t="b">
         <v>0</v>
       </c>
-      <c r="AJ61" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK61" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO61" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja, Vivien Renaut, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016353</t>
+          <t>https://artportalen.se/Sighting/137040121</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>137044071</v>
+        <v>137040123</v>
       </c>
       <c r="B62" t="n">
-        <v>79505</v>
+        <v>99361</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>260591</v>
+        <v>220787</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr"/>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
       <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
@@ -8257,13 +8193,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>636845</v>
+        <v>636843</v>
       </c>
       <c r="R62" t="n">
-        <v>7014233</v>
+        <v>7014251</v>
       </c>
       <c r="S62" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -8292,7 +8228,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -8302,7 +8238,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8315,34 +8251,3165 @@
       <c r="AG62" t="b">
         <v>0</v>
       </c>
-      <c r="AJ62" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK62" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO62" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja, Vivien Renaut, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
       <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137040123</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>137040138</v>
+      </c>
+      <c r="B63" t="n">
+        <v>99361</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Stortannsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>636527</v>
+      </c>
+      <c r="R63" t="n">
+        <v>7014608</v>
+      </c>
+      <c r="S63" t="n">
+        <v>4</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Överlännäs</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>15:02</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>15:02</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF63" t="inlineStr"/>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Markus Borja, Vivien Renaut, Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137040138</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>137040160</v>
+      </c>
+      <c r="B64" t="n">
+        <v>99361</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="N64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Stortannsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>636474</v>
+      </c>
+      <c r="R64" t="n">
+        <v>7014608</v>
+      </c>
+      <c r="S64" t="n">
+        <v>3</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Överlännäs</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF64" t="inlineStr"/>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Markus Borja, Vivien Renaut, Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137040160</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>137040163</v>
+      </c>
+      <c r="B65" t="n">
+        <v>99361</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Stortannsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>636595</v>
+      </c>
+      <c r="R65" t="n">
+        <v>7014422</v>
+      </c>
+      <c r="S65" t="n">
+        <v>3</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Överlännäs</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>18:17</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>18:17</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF65" t="inlineStr"/>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Markus Borja, Vivien Renaut, Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137040163</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>137040164</v>
+      </c>
+      <c r="B66" t="n">
+        <v>99361</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="N66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Stortannsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>636776</v>
+      </c>
+      <c r="R66" t="n">
+        <v>7014278</v>
+      </c>
+      <c r="S66" t="n">
+        <v>3</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Överlännäs</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>09:05</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>09:05</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF66" t="inlineStr"/>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Vivien Renaut</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Vivien Renaut</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137040164</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>137040166</v>
+      </c>
+      <c r="B67" t="n">
+        <v>99361</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="N67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Stortannsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>636782</v>
+      </c>
+      <c r="R67" t="n">
+        <v>7014300</v>
+      </c>
+      <c r="S67" t="n">
+        <v>3</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Överlännäs</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF67" t="inlineStr"/>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Vivien Renaut</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Vivien Renaut</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137040166</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>137040168</v>
+      </c>
+      <c r="B68" t="n">
+        <v>99361</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="N68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Stortannsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>636758</v>
+      </c>
+      <c r="R68" t="n">
+        <v>7014368</v>
+      </c>
+      <c r="S68" t="n">
+        <v>3</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Överlännäs</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>09:42</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>09:42</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF68" t="inlineStr"/>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Vivien Renaut</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Vivien Renaut</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137040168</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>137040189</v>
+      </c>
+      <c r="B69" t="n">
+        <v>99361</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="N69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Stortannsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>636424</v>
+      </c>
+      <c r="R69" t="n">
+        <v>7014610</v>
+      </c>
+      <c r="S69" t="n">
+        <v>15</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Överlännäs</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>17:52</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>17:52</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF69" t="inlineStr"/>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Vivien Renaut</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Vivien Renaut</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137040189</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>137044057</v>
+      </c>
+      <c r="B70" t="n">
+        <v>99361</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="N70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Stortannsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>636762</v>
+      </c>
+      <c r="R70" t="n">
+        <v>7014263</v>
+      </c>
+      <c r="S70" t="n">
+        <v>5</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Överlännäs</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF70" t="inlineStr"/>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja, Markus Borja, Vivien Renaut</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137044057</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>137044059</v>
+      </c>
+      <c r="B71" t="n">
+        <v>99361</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="N71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Stortannsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>636736</v>
+      </c>
+      <c r="R71" t="n">
+        <v>7014341</v>
+      </c>
+      <c r="S71" t="n">
+        <v>5</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Överlännäs</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>09:41</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>09:41</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF71" t="inlineStr"/>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja, Markus Borja, Vivien Renaut</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137044059</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>137044060</v>
+      </c>
+      <c r="B72" t="n">
+        <v>99361</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>159</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
+      <c r="N72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Stortannsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>636760</v>
+      </c>
+      <c r="R72" t="n">
+        <v>7014309</v>
+      </c>
+      <c r="S72" t="n">
+        <v>5</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Överlännäs</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>10:02</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>10:02</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF72" t="inlineStr"/>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja, Markus Borja, Vivien Renaut</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137044060</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>137044061</v>
+      </c>
+      <c r="B73" t="n">
+        <v>99361</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
+      <c r="N73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Stortannsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>636781</v>
+      </c>
+      <c r="R73" t="n">
+        <v>7014323</v>
+      </c>
+      <c r="S73" t="n">
+        <v>5</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Överlännäs</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF73" t="inlineStr"/>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja, Markus Borja, Vivien Renaut</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137044061</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>137044062</v>
+      </c>
+      <c r="B74" t="n">
+        <v>99361</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>117</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr"/>
+      <c r="N74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Stortannsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>636772</v>
+      </c>
+      <c r="R74" t="n">
+        <v>7014326</v>
+      </c>
+      <c r="S74" t="n">
+        <v>5</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Överlännäs</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>10:26</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>10:26</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF74" t="inlineStr"/>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja, Markus Borja, Vivien Renaut</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137044062</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>137044064</v>
+      </c>
+      <c r="B75" t="n">
+        <v>99361</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr"/>
+      <c r="N75" t="inlineStr"/>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Stortannsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>636806</v>
+      </c>
+      <c r="R75" t="n">
+        <v>7014282</v>
+      </c>
+      <c r="S75" t="n">
+        <v>5</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Överlännäs</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>10:48</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>10:48</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="inlineStr"/>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja, Markus Borja, Vivien Renaut</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137044064</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>137044080</v>
+      </c>
+      <c r="B76" t="n">
+        <v>99361</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr"/>
+      <c r="N76" t="inlineStr"/>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Stortannsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>636598</v>
+      </c>
+      <c r="R76" t="n">
+        <v>7014517</v>
+      </c>
+      <c r="S76" t="n">
+        <v>5</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Överlännäs</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>14:32</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>14:32</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF76" t="inlineStr"/>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja, Markus Borja, Vivien Renaut</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137044080</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>137040134</v>
+      </c>
+      <c r="B77" t="n">
+        <v>79240</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Stortannsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>636580</v>
+      </c>
+      <c r="R77" t="n">
+        <v>7014518</v>
+      </c>
+      <c r="S77" t="n">
+        <v>3</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Överlännäs</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>14:37</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>14:37</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137040134</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>137040136</v>
+      </c>
+      <c r="B78" t="n">
+        <v>79240</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Stortannsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>636552</v>
+      </c>
+      <c r="R78" t="n">
+        <v>7014536</v>
+      </c>
+      <c r="S78" t="n">
+        <v>3</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Överlännäs</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>14:47</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>14:47</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137040136</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>137016336</v>
+      </c>
+      <c r="B79" t="n">
+        <v>79505</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="J79" t="inlineStr"/>
+      <c r="K79" t="inlineStr"/>
+      <c r="N79" t="inlineStr"/>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Stortannsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>636512</v>
+      </c>
+      <c r="R79" t="n">
+        <v>7014375</v>
+      </c>
+      <c r="S79" t="n">
+        <v>5</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Överlännäs</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>11:12</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>11:12</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF79" t="inlineStr"/>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ79" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK79" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO79" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja, Markus Borja</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137016336</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>137016339</v>
+      </c>
+      <c r="B80" t="n">
+        <v>79505</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="J80" t="inlineStr"/>
+      <c r="K80" t="inlineStr"/>
+      <c r="N80" t="inlineStr"/>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Stortannsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>636457</v>
+      </c>
+      <c r="R80" t="n">
+        <v>7014405</v>
+      </c>
+      <c r="S80" t="n">
+        <v>5</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Överlännäs</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>11:22</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="AB80" t="inlineStr">
+        <is>
+          <t>11:22</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF80" t="inlineStr"/>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ80" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK80" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO80" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137016339</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>137016342</v>
+      </c>
+      <c r="B81" t="n">
+        <v>79505</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="J81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
+      <c r="N81" t="inlineStr"/>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Stortannsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>636417</v>
+      </c>
+      <c r="R81" t="n">
+        <v>7014452</v>
+      </c>
+      <c r="S81" t="n">
+        <v>5</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Överlännäs</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF81" t="inlineStr"/>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ81" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK81" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO81" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137016342</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>137016345</v>
+      </c>
+      <c r="B82" t="n">
+        <v>79505</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="J82" t="inlineStr"/>
+      <c r="K82" t="inlineStr"/>
+      <c r="N82" t="inlineStr"/>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Stortannsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>636407</v>
+      </c>
+      <c r="R82" t="n">
+        <v>7014480</v>
+      </c>
+      <c r="S82" t="n">
+        <v>5</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Överlännäs</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="Z82" t="inlineStr">
+        <is>
+          <t>11:59</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="AB82" t="inlineStr">
+        <is>
+          <t>11:59</t>
+        </is>
+      </c>
+      <c r="AD82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF82" t="inlineStr"/>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ82" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK82" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO82" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137016345</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>137016346</v>
+      </c>
+      <c r="B83" t="n">
+        <v>79505</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="J83" t="inlineStr"/>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr"/>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Stortannsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>636450</v>
+      </c>
+      <c r="R83" t="n">
+        <v>7014535</v>
+      </c>
+      <c r="S83" t="n">
+        <v>5</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Överlännäs</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="Z83" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="AB83" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="AD83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF83" t="inlineStr"/>
+      <c r="AG83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ83" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK83" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO83" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT83" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137016346</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>137016348</v>
+      </c>
+      <c r="B84" t="n">
+        <v>79505</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="J84" t="inlineStr"/>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr"/>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Stortannsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q84" t="n">
+        <v>636479</v>
+      </c>
+      <c r="R84" t="n">
+        <v>7014523</v>
+      </c>
+      <c r="S84" t="n">
+        <v>5</v>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>Överlännäs</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="Z84" t="inlineStr">
+        <is>
+          <t>12:09</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="AB84" t="inlineStr">
+        <is>
+          <t>12:09</t>
+        </is>
+      </c>
+      <c r="AD84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF84" t="inlineStr"/>
+      <c r="AG84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ84" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK84" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO84" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT84" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137016348</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>137016353</v>
+      </c>
+      <c r="B85" t="n">
+        <v>79505</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
+      <c r="J85" t="inlineStr"/>
+      <c r="K85" t="inlineStr"/>
+      <c r="N85" t="inlineStr"/>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>Stortannsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q85" t="n">
+        <v>636460</v>
+      </c>
+      <c r="R85" t="n">
+        <v>7014451</v>
+      </c>
+      <c r="S85" t="n">
+        <v>5</v>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>Överlännäs</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="Z85" t="inlineStr">
+        <is>
+          <t>12:28</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="AB85" t="inlineStr">
+        <is>
+          <t>12:28</t>
+        </is>
+      </c>
+      <c r="AD85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF85" t="inlineStr"/>
+      <c r="AG85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ85" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK85" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO85" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT85" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AX85" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137016353</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>137040099</v>
+      </c>
+      <c r="B86" t="n">
+        <v>79505</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>Stortannsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q86" t="n">
+        <v>636705</v>
+      </c>
+      <c r="R86" t="n">
+        <v>7014243</v>
+      </c>
+      <c r="S86" t="n">
+        <v>3</v>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>Överlännäs</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="Z86" t="inlineStr">
+        <is>
+          <t>08:49</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="AB86" t="inlineStr">
+        <is>
+          <t>08:49</t>
+        </is>
+      </c>
+      <c r="AD86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT86" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>Markus Borja, Vivien Renaut, Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137040099</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>137044071</v>
+      </c>
+      <c r="B87" t="n">
+        <v>79505</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
+      <c r="J87" t="inlineStr"/>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr"/>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>Stortannsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q87" t="n">
+        <v>636845</v>
+      </c>
+      <c r="R87" t="n">
+        <v>7014233</v>
+      </c>
+      <c r="S87" t="n">
+        <v>5</v>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>Överlännäs</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="Z87" t="inlineStr">
+        <is>
+          <t>12:09</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="AB87" t="inlineStr">
+        <is>
+          <t>12:09</t>
+        </is>
+      </c>
+      <c r="AD87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF87" t="inlineStr"/>
+      <c r="AG87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ87" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK87" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO87" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT87" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AX87" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/137044071</t>
         </is>
@@ -8411,6 +11478,31 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 25855-2025 artfynd.xlsx
+++ b/artfynd/A 25855-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137044063</v>
       </c>
       <c r="B2" t="n">
-        <v>92388</v>
+        <v>92389</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -814,7 +814,7 @@
         <v>137040165</v>
       </c>
       <c r="B3" t="n">
-        <v>92950</v>
+        <v>92951</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -931,7 +931,7 @@
         <v>137016354</v>
       </c>
       <c r="B4" t="n">
-        <v>93431</v>
+        <v>93432</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1047,7 +1047,7 @@
         <v>137016293</v>
       </c>
       <c r="B5" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1159,7 +1159,7 @@
         <v>137040122</v>
       </c>
       <c r="B6" t="n">
-        <v>92080</v>
+        <v>92081</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1271,7 +1271,7 @@
         <v>137016298</v>
       </c>
       <c r="B7" t="n">
-        <v>93453</v>
+        <v>93454</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1387,7 +1387,7 @@
         <v>137016289</v>
       </c>
       <c r="B8" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1518,7 +1518,7 @@
         <v>137016306</v>
       </c>
       <c r="B9" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1649,7 +1649,7 @@
         <v>137016332</v>
       </c>
       <c r="B10" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1780,7 +1780,7 @@
         <v>137016333</v>
       </c>
       <c r="B11" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1911,7 +1911,7 @@
         <v>137016335</v>
       </c>
       <c r="B12" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2042,7 +2042,7 @@
         <v>137016337</v>
       </c>
       <c r="B13" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2173,7 +2173,7 @@
         <v>137016340</v>
       </c>
       <c r="B14" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2304,7 +2304,7 @@
         <v>137016349</v>
       </c>
       <c r="B15" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2435,7 +2435,7 @@
         <v>137016350</v>
       </c>
       <c r="B16" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2566,7 +2566,7 @@
         <v>137040102</v>
       </c>
       <c r="B17" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2697,7 +2697,7 @@
         <v>137040133</v>
       </c>
       <c r="B18" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2828,7 +2828,7 @@
         <v>137040161</v>
       </c>
       <c r="B19" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2959,7 +2959,7 @@
         <v>137040162</v>
       </c>
       <c r="B20" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3090,7 +3090,7 @@
         <v>137040167</v>
       </c>
       <c r="B21" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3202,7 +3202,7 @@
         <v>137040169</v>
       </c>
       <c r="B22" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3314,7 +3314,7 @@
         <v>137040181</v>
       </c>
       <c r="B23" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3431,7 +3431,7 @@
         <v>137044055</v>
       </c>
       <c r="B24" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3562,7 +3562,7 @@
         <v>137044068</v>
       </c>
       <c r="B25" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3693,7 +3693,7 @@
         <v>137044072</v>
       </c>
       <c r="B26" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3824,7 +3824,7 @@
         <v>137016334</v>
       </c>
       <c r="B27" t="n">
-        <v>79506</v>
+        <v>79507</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3955,7 +3955,7 @@
         <v>137016341</v>
       </c>
       <c r="B28" t="n">
-        <v>79506</v>
+        <v>79507</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4086,7 +4086,7 @@
         <v>137016351</v>
       </c>
       <c r="B29" t="n">
-        <v>79506</v>
+        <v>79507</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4217,7 +4217,7 @@
         <v>137040100</v>
       </c>
       <c r="B30" t="n">
-        <v>79506</v>
+        <v>79507</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4348,7 +4348,7 @@
         <v>137044056</v>
       </c>
       <c r="B31" t="n">
-        <v>79506</v>
+        <v>79507</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4479,7 +4479,7 @@
         <v>137040105</v>
       </c>
       <c r="B32" t="n">
-        <v>79239</v>
+        <v>79240</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4591,7 +4591,7 @@
         <v>137040135</v>
       </c>
       <c r="B33" t="n">
-        <v>79239</v>
+        <v>79240</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4703,7 +4703,7 @@
         <v>137016288</v>
       </c>
       <c r="B34" t="n">
-        <v>80101</v>
+        <v>80102</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4815,7 +4815,7 @@
         <v>137016299</v>
       </c>
       <c r="B35" t="n">
-        <v>80101</v>
+        <v>80102</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4927,7 +4927,7 @@
         <v>137016303</v>
       </c>
       <c r="B36" t="n">
-        <v>80101</v>
+        <v>80102</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5039,7 +5039,7 @@
         <v>137040101</v>
       </c>
       <c r="B37" t="n">
-        <v>80101</v>
+        <v>80102</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5151,7 +5151,7 @@
         <v>137040104</v>
       </c>
       <c r="B38" t="n">
-        <v>80101</v>
+        <v>80102</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5263,7 +5263,7 @@
         <v>137040108</v>
       </c>
       <c r="B39" t="n">
-        <v>80491</v>
+        <v>80492</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5394,7 +5394,7 @@
         <v>137040110</v>
       </c>
       <c r="B40" t="n">
-        <v>80491</v>
+        <v>80492</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5525,7 +5525,7 @@
         <v>137040111</v>
       </c>
       <c r="B41" t="n">
-        <v>80491</v>
+        <v>80492</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -7899,7 +7899,7 @@
         <v>137040107</v>
       </c>
       <c r="B60" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -8024,7 +8024,7 @@
         <v>137040121</v>
       </c>
       <c r="B61" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -8149,7 +8149,7 @@
         <v>137040123</v>
       </c>
       <c r="B62" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -8274,7 +8274,7 @@
         <v>137040138</v>
       </c>
       <c r="B63" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8399,7 +8399,7 @@
         <v>137040160</v>
       </c>
       <c r="B64" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8524,7 +8524,7 @@
         <v>137040163</v>
       </c>
       <c r="B65" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8649,7 +8649,7 @@
         <v>137040164</v>
       </c>
       <c r="B66" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8774,7 +8774,7 @@
         <v>137040166</v>
       </c>
       <c r="B67" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8899,7 +8899,7 @@
         <v>137040168</v>
       </c>
       <c r="B68" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -9024,7 +9024,7 @@
         <v>137040189</v>
       </c>
       <c r="B69" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -9149,7 +9149,7 @@
         <v>137044057</v>
       </c>
       <c r="B70" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -9274,7 +9274,7 @@
         <v>137044059</v>
       </c>
       <c r="B71" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9399,7 +9399,7 @@
         <v>137044060</v>
       </c>
       <c r="B72" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9524,7 +9524,7 @@
         <v>137044061</v>
       </c>
       <c r="B73" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9649,7 +9649,7 @@
         <v>137044062</v>
       </c>
       <c r="B74" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9774,7 +9774,7 @@
         <v>137044064</v>
       </c>
       <c r="B75" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9899,7 +9899,7 @@
         <v>137044080</v>
       </c>
       <c r="B76" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -10024,7 +10024,7 @@
         <v>137040134</v>
       </c>
       <c r="B77" t="n">
-        <v>79240</v>
+        <v>79241</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -10136,7 +10136,7 @@
         <v>137040136</v>
       </c>
       <c r="B78" t="n">
-        <v>79240</v>
+        <v>79241</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -10248,7 +10248,7 @@
         <v>137016336</v>
       </c>
       <c r="B79" t="n">
-        <v>79505</v>
+        <v>79506</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -10379,7 +10379,7 @@
         <v>137016339</v>
       </c>
       <c r="B80" t="n">
-        <v>79505</v>
+        <v>79506</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -10510,7 +10510,7 @@
         <v>137016342</v>
       </c>
       <c r="B81" t="n">
-        <v>79505</v>
+        <v>79506</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10641,7 +10641,7 @@
         <v>137016345</v>
       </c>
       <c r="B82" t="n">
-        <v>79505</v>
+        <v>79506</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10772,7 +10772,7 @@
         <v>137016346</v>
       </c>
       <c r="B83" t="n">
-        <v>79505</v>
+        <v>79506</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10907,7 +10907,7 @@
         <v>137016348</v>
       </c>
       <c r="B84" t="n">
-        <v>79505</v>
+        <v>79506</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -11042,7 +11042,7 @@
         <v>137016353</v>
       </c>
       <c r="B85" t="n">
-        <v>79505</v>
+        <v>79506</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -11173,7 +11173,7 @@
         <v>137040099</v>
       </c>
       <c r="B86" t="n">
-        <v>79505</v>
+        <v>79506</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -11285,7 +11285,7 @@
         <v>137044071</v>
       </c>
       <c r="B87" t="n">
-        <v>79505</v>
+        <v>79506</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>

--- a/artfynd/A 25855-2025 artfynd.xlsx
+++ b/artfynd/A 25855-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137044063</v>
       </c>
       <c r="B2" t="n">
-        <v>92389</v>
+        <v>92395</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -814,7 +814,7 @@
         <v>137040165</v>
       </c>
       <c r="B3" t="n">
-        <v>92951</v>
+        <v>92957</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -931,7 +931,7 @@
         <v>137016354</v>
       </c>
       <c r="B4" t="n">
-        <v>93432</v>
+        <v>93438</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1047,7 +1047,7 @@
         <v>137016293</v>
       </c>
       <c r="B5" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1159,7 +1159,7 @@
         <v>137040122</v>
       </c>
       <c r="B6" t="n">
-        <v>92081</v>
+        <v>92087</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1271,7 +1271,7 @@
         <v>137016298</v>
       </c>
       <c r="B7" t="n">
-        <v>93454</v>
+        <v>93460</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -7899,7 +7899,7 @@
         <v>137040107</v>
       </c>
       <c r="B60" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -8024,7 +8024,7 @@
         <v>137040121</v>
       </c>
       <c r="B61" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -8149,7 +8149,7 @@
         <v>137040123</v>
       </c>
       <c r="B62" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -8274,7 +8274,7 @@
         <v>137040138</v>
       </c>
       <c r="B63" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8399,7 +8399,7 @@
         <v>137040160</v>
       </c>
       <c r="B64" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8524,7 +8524,7 @@
         <v>137040163</v>
       </c>
       <c r="B65" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8649,7 +8649,7 @@
         <v>137040164</v>
       </c>
       <c r="B66" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8774,7 +8774,7 @@
         <v>137040166</v>
       </c>
       <c r="B67" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8899,7 +8899,7 @@
         <v>137040168</v>
       </c>
       <c r="B68" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -9024,7 +9024,7 @@
         <v>137040189</v>
       </c>
       <c r="B69" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -9149,7 +9149,7 @@
         <v>137044057</v>
       </c>
       <c r="B70" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -9274,7 +9274,7 @@
         <v>137044059</v>
       </c>
       <c r="B71" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9399,7 +9399,7 @@
         <v>137044060</v>
       </c>
       <c r="B72" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9524,7 +9524,7 @@
         <v>137044061</v>
       </c>
       <c r="B73" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9649,7 +9649,7 @@
         <v>137044062</v>
       </c>
       <c r="B74" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9774,7 +9774,7 @@
         <v>137044064</v>
       </c>
       <c r="B75" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9899,7 +9899,7 @@
         <v>137044080</v>
       </c>
       <c r="B76" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>

--- a/artfynd/A 25855-2025 artfynd.xlsx
+++ b/artfynd/A 25855-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ87"/>
+  <dimension ref="A1:AZ62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -683,7 +683,7 @@
         <v>137044063</v>
       </c>
       <c r="B2" t="n">
-        <v>92395</v>
+        <v>92399</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -814,7 +814,7 @@
         <v>137040165</v>
       </c>
       <c r="B3" t="n">
-        <v>92957</v>
+        <v>92961</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -931,7 +931,7 @@
         <v>137016354</v>
       </c>
       <c r="B4" t="n">
-        <v>93438</v>
+        <v>93442</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1047,7 +1047,7 @@
         <v>137016293</v>
       </c>
       <c r="B5" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1156,45 +1156,48 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>137040122</v>
+        <v>137016298</v>
       </c>
       <c r="B6" t="n">
-        <v>92087</v>
+        <v>93464</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5447</v>
+        <v>5966</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Stortannsjön, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>636830</v>
+        <v>636437</v>
       </c>
       <c r="R6" t="n">
-        <v>7014277</v>
+        <v>7014437</v>
       </c>
       <c r="S6" t="n">
         <v>3</v>
@@ -1221,22 +1224,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1245,6 +1248,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1256,44 +1260,44 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Markus Borja, Diego Borja, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137040122</t>
+          <t>https://artportalen.se/Sighting/137016298</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>137016298</v>
+        <v>137016289</v>
       </c>
       <c r="B7" t="n">
-        <v>93460</v>
+        <v>79485</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5966</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1306,10 +1310,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>636437</v>
+        <v>636608</v>
       </c>
       <c r="R7" t="n">
-        <v>7014437</v>
+        <v>7014302</v>
       </c>
       <c r="S7" t="n">
         <v>3</v>
@@ -1341,7 +1345,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1351,7 +1355,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1364,6 +1368,21 @@
       <c r="AG7" t="b">
         <v>0</v>
       </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
@@ -1372,22 +1391,22 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Markus Borja, Diego Borja, Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016298</t>
+          <t>https://artportalen.se/Sighting/137016289</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>137016289</v>
+        <v>137016306</v>
       </c>
       <c r="B8" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1422,10 +1441,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>636608</v>
+        <v>636566</v>
       </c>
       <c r="R8" t="n">
-        <v>7014302</v>
+        <v>7014366</v>
       </c>
       <c r="S8" t="n">
         <v>3</v>
@@ -1457,7 +1476,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1467,7 +1486,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1509,16 +1528,16 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016289</t>
+          <t>https://artportalen.se/Sighting/137016306</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>137016306</v>
+        <v>137016332</v>
       </c>
       <c r="B9" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1553,13 +1572,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>636566</v>
+        <v>636603</v>
       </c>
       <c r="R9" t="n">
-        <v>7014366</v>
+        <v>7014322</v>
       </c>
       <c r="S9" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1588,7 +1607,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1598,7 +1617,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1629,27 +1648,27 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016306</t>
+          <t>https://artportalen.se/Sighting/137016332</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>137016332</v>
+        <v>137016333</v>
       </c>
       <c r="B10" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1684,10 +1703,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>636603</v>
+        <v>636623</v>
       </c>
       <c r="R10" t="n">
-        <v>7014322</v>
+        <v>7014305</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1719,7 +1738,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1729,7 +1748,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1771,16 +1790,16 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016332</t>
+          <t>https://artportalen.se/Sighting/137016333</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>137016333</v>
+        <v>137016335</v>
       </c>
       <c r="B11" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1815,10 +1834,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>636623</v>
+        <v>636520</v>
       </c>
       <c r="R11" t="n">
-        <v>7014305</v>
+        <v>7014374</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1850,7 +1869,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1860,7 +1879,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1902,16 +1921,16 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016333</t>
+          <t>https://artportalen.se/Sighting/137016335</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>137016335</v>
+        <v>137016337</v>
       </c>
       <c r="B12" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1946,10 +1965,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>636520</v>
+        <v>636463</v>
       </c>
       <c r="R12" t="n">
-        <v>7014374</v>
+        <v>7014402</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1981,7 +2000,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1991,7 +2010,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2033,16 +2052,16 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016335</t>
+          <t>https://artportalen.se/Sighting/137016337</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>137016337</v>
+        <v>137016340</v>
       </c>
       <c r="B13" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2077,10 +2096,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>636463</v>
+        <v>636419</v>
       </c>
       <c r="R13" t="n">
-        <v>7014402</v>
+        <v>7014437</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2112,7 +2131,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2122,7 +2141,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2164,16 +2183,16 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016337</t>
+          <t>https://artportalen.se/Sighting/137016340</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>137016340</v>
+        <v>137016349</v>
       </c>
       <c r="B14" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2208,10 +2227,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>636419</v>
+        <v>636488</v>
       </c>
       <c r="R14" t="n">
-        <v>7014437</v>
+        <v>7014536</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2243,7 +2262,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2253,7 +2272,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2295,16 +2314,16 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016340</t>
+          <t>https://artportalen.se/Sighting/137016349</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>137016349</v>
+        <v>137016350</v>
       </c>
       <c r="B15" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2339,10 +2358,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>636488</v>
+        <v>636466</v>
       </c>
       <c r="R15" t="n">
-        <v>7014536</v>
+        <v>7014464</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2374,7 +2393,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2384,7 +2403,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2426,16 +2445,16 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016349</t>
+          <t>https://artportalen.se/Sighting/137016350</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>137016350</v>
+        <v>137040167</v>
       </c>
       <c r="B16" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2461,19 +2480,16 @@
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Stortannsjön, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>636466</v>
+        <v>636743</v>
       </c>
       <c r="R16" t="n">
-        <v>7014464</v>
+        <v>7014374</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2500,22 +2516,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2524,49 +2540,33 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Vivien Renaut</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Vivien Renaut</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016350</t>
+          <t>https://artportalen.se/Sighting/137040167</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>137040102</v>
+        <v>137040169</v>
       </c>
       <c r="B17" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2592,22 +2592,19 @@
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Stortannsjön, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>636758</v>
+        <v>636844</v>
       </c>
       <c r="R17" t="n">
-        <v>7014258</v>
+        <v>7014273</v>
       </c>
       <c r="S17" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2636,7 +2633,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>09:08</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2646,7 +2643,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>09:08</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2655,49 +2652,33 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Vivien Renaut</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Markus Borja, Vivien Renaut, Ann-Christine Borja</t>
+          <t>Vivien Renaut</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137040102</t>
+          <t>https://artportalen.se/Sighting/137040169</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>137040133</v>
+        <v>137040181</v>
       </c>
       <c r="B18" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2723,22 +2704,19 @@
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Stortannsjön, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>636608</v>
+        <v>636605</v>
       </c>
       <c r="R18" t="n">
-        <v>7014515</v>
+        <v>7014506</v>
       </c>
       <c r="S18" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2767,7 +2745,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2777,7 +2755,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:28</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Garnlav på tall</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2786,49 +2769,33 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Vivien Renaut</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Markus Borja, Vivien Renaut, Ann-Christine Borja</t>
+          <t>Vivien Renaut</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137040133</t>
+          <t>https://artportalen.se/Sighting/137040181</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>137040161</v>
+        <v>137044055</v>
       </c>
       <c r="B19" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2863,13 +2830,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>636549</v>
+        <v>636694</v>
       </c>
       <c r="R19" t="n">
-        <v>7014491</v>
+        <v>7014252</v>
       </c>
       <c r="S19" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2898,7 +2865,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>18:07</t>
+          <t>08:47</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2908,7 +2875,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>18:07</t>
+          <t>08:47</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2939,27 +2906,27 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Markus Borja, Vivien Renaut, Ann-Christine Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137040161</t>
+          <t>https://artportalen.se/Sighting/137044055</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>137040162</v>
+        <v>137044068</v>
       </c>
       <c r="B20" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2994,13 +2961,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>636606</v>
+        <v>636901</v>
       </c>
       <c r="R20" t="n">
-        <v>7014419</v>
+        <v>7014208</v>
       </c>
       <c r="S20" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3029,7 +2996,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3039,7 +3006,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3054,43 +3021,43 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Markus Borja, Vivien Renaut, Ann-Christine Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137040162</t>
+          <t>https://artportalen.se/Sighting/137044068</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>137040167</v>
+        <v>137044072</v>
       </c>
       <c r="B21" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3116,16 +3083,19 @@
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Stortannsjön, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>636743</v>
+        <v>636840</v>
       </c>
       <c r="R21" t="n">
-        <v>7014374</v>
+        <v>7014233</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -3157,7 +3127,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3167,7 +3137,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3176,71 +3146,90 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Vivien Renaut</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Vivien Renaut</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137040167</t>
+          <t>https://artportalen.se/Sighting/137044072</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>137040169</v>
+        <v>137016334</v>
       </c>
       <c r="B22" t="n">
-        <v>79483</v>
+        <v>79509</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Stortannsjön, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>636844</v>
+        <v>636591</v>
       </c>
       <c r="R22" t="n">
-        <v>7014273</v>
+        <v>7014315</v>
       </c>
       <c r="S22" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3264,22 +3253,22 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3288,71 +3277,90 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Vivien Renaut</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Vivien Renaut</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137040169</t>
+          <t>https://artportalen.se/Sighting/137016334</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>137040181</v>
+        <v>137016341</v>
       </c>
       <c r="B23" t="n">
-        <v>79483</v>
+        <v>79509</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Stortannsjön, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>636605</v>
+        <v>636409</v>
       </c>
       <c r="R23" t="n">
-        <v>7014506</v>
+        <v>7014452</v>
       </c>
       <c r="S23" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3376,27 +3384,22 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:28</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Garnlav på tall</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3405,55 +3408,71 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Vivien Renaut</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Vivien Renaut</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137040181</t>
+          <t>https://artportalen.se/Sighting/137016341</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>137044055</v>
+        <v>137016351</v>
       </c>
       <c r="B24" t="n">
-        <v>79483</v>
+        <v>79509</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3466,10 +3485,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>636694</v>
+        <v>636460</v>
       </c>
       <c r="R24" t="n">
-        <v>7014252</v>
+        <v>7014454</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3496,22 +3515,22 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>08:47</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>08:47</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3553,38 +3572,38 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137044055</t>
+          <t>https://artportalen.se/Sighting/137016351</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>137044068</v>
+        <v>137044056</v>
       </c>
       <c r="B25" t="n">
-        <v>79483</v>
+        <v>79509</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3597,10 +3616,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>636901</v>
+        <v>636699</v>
       </c>
       <c r="R25" t="n">
-        <v>7014208</v>
+        <v>7014271</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3632,7 +3651,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3642,7 +3661,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3684,57 +3703,54 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137044068</t>
+          <t>https://artportalen.se/Sighting/137044056</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>137044072</v>
+        <v>137016288</v>
       </c>
       <c r="B26" t="n">
-        <v>79483</v>
+        <v>80104</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Stortannsjön, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>636840</v>
+        <v>636610</v>
       </c>
       <c r="R26" t="n">
-        <v>7014233</v>
+        <v>7014307</v>
       </c>
       <c r="S26" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3758,22 +3774,22 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3782,90 +3798,71 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ26" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK26" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137044072</t>
+          <t>https://artportalen.se/Sighting/137016288</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>137016334</v>
+        <v>137016299</v>
       </c>
       <c r="B27" t="n">
-        <v>79507</v>
+        <v>80104</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6434</v>
+        <v>6453</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Stortannsjön, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>636591</v>
+        <v>636418</v>
       </c>
       <c r="R27" t="n">
-        <v>7014315</v>
+        <v>7014453</v>
       </c>
       <c r="S27" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3894,7 +3891,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3904,7 +3901,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3913,90 +3910,71 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016334</t>
+          <t>https://artportalen.se/Sighting/137016299</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>137016341</v>
+        <v>137016303</v>
       </c>
       <c r="B28" t="n">
-        <v>79507</v>
+        <v>80104</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6434</v>
+        <v>6453</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Stortannsjön, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>636409</v>
+        <v>636499</v>
       </c>
       <c r="R28" t="n">
-        <v>7014452</v>
+        <v>7014546</v>
       </c>
       <c r="S28" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -4025,7 +4003,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -4035,7 +4013,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4044,49 +4022,33 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ28" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK28" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO28" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016341</t>
+          <t>https://artportalen.se/Sighting/137016303</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>137016351</v>
+        <v>137016301</v>
       </c>
       <c r="B29" t="n">
-        <v>79507</v>
+        <v>58005</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4094,26 +4056,31 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6434</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -4121,13 +4088,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>636460</v>
+        <v>636482</v>
       </c>
       <c r="R29" t="n">
-        <v>7014454</v>
+        <v>7014533</v>
       </c>
       <c r="S29" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4156,7 +4123,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4166,7 +4133,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4175,49 +4142,33 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ29" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK29" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016351</t>
+          <t>https://artportalen.se/Sighting/137016301</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>137040100</v>
+        <v>137040182</v>
       </c>
       <c r="B30" t="n">
-        <v>79507</v>
+        <v>58005</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4225,26 +4176,31 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6434</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -4252,13 +4208,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>636705</v>
+        <v>636550</v>
       </c>
       <c r="R30" t="n">
-        <v>7014244</v>
+        <v>7014507</v>
       </c>
       <c r="S30" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4287,7 +4243,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4297,7 +4253,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>14:41</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4306,76 +4267,65 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ30" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK30" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Vivien Renaut</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Markus Borja, Vivien Renaut, Ann-Christine Borja</t>
+          <t>Vivien Renaut</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137040100</t>
+          <t>https://artportalen.se/Sighting/137040182</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>137044056</v>
+        <v>137016287</v>
       </c>
       <c r="B31" t="n">
-        <v>79507</v>
+        <v>58008</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6434</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -4383,13 +4333,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>636699</v>
+        <v>636606</v>
       </c>
       <c r="R31" t="n">
-        <v>7014271</v>
+        <v>7014302</v>
       </c>
       <c r="S31" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4413,22 +4363,27 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>10:34</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Färska och Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4437,49 +4392,33 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja, Ann-Christine Borja, Diego Borja</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137044056</t>
+          <t>https://artportalen.se/Sighting/137016287</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>137040105</v>
+        <v>137016290</v>
       </c>
       <c r="B32" t="n">
-        <v>79240</v>
+        <v>58008</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4487,34 +4426,42 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Stortannsjön, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>636730</v>
+        <v>636608</v>
       </c>
       <c r="R32" t="n">
-        <v>7014286</v>
+        <v>7014302</v>
       </c>
       <c r="S32" t="n">
         <v>3</v>
@@ -4541,22 +4488,27 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>10:54</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4576,22 +4528,22 @@
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Markus Borja, Ann-Christine Borja, Diego Borja</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137040105</t>
+          <t>https://artportalen.se/Sighting/137016290</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>137040135</v>
+        <v>137016291</v>
       </c>
       <c r="B33" t="n">
-        <v>79240</v>
+        <v>58008</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4599,34 +4551,42 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Stortannsjön, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>636582</v>
+        <v>636578</v>
       </c>
       <c r="R33" t="n">
-        <v>7014519</v>
+        <v>7014320</v>
       </c>
       <c r="S33" t="n">
         <v>3</v>
@@ -4653,22 +4613,27 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>10:59</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4688,22 +4653,22 @@
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Markus Borja, Ann-Christine Borja, Diego Borja</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137040135</t>
+          <t>https://artportalen.se/Sighting/137016291</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>137016288</v>
+        <v>137016292</v>
       </c>
       <c r="B34" t="n">
-        <v>80102</v>
+        <v>58008</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4711,34 +4676,42 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Stortannsjön, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>636610</v>
+        <v>636501</v>
       </c>
       <c r="R34" t="n">
-        <v>7014307</v>
+        <v>7014381</v>
       </c>
       <c r="S34" t="n">
         <v>3</v>
@@ -4770,7 +4743,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4780,7 +4753,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>11:09</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4800,22 +4778,22 @@
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Markus Borja, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016288</t>
+          <t>https://artportalen.se/Sighting/137016292</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>137016299</v>
+        <v>137016294</v>
       </c>
       <c r="B35" t="n">
-        <v>80102</v>
+        <v>58008</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4823,34 +4801,42 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Stortannsjön, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>636418</v>
+        <v>636486</v>
       </c>
       <c r="R35" t="n">
-        <v>7014453</v>
+        <v>7014403</v>
       </c>
       <c r="S35" t="n">
         <v>3</v>
@@ -4882,7 +4868,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4892,7 +4878,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>11:16</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4912,22 +4903,22 @@
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Markus Borja, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016299</t>
+          <t>https://artportalen.se/Sighting/137016294</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>137016303</v>
+        <v>137016295</v>
       </c>
       <c r="B36" t="n">
-        <v>80102</v>
+        <v>58008</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4935,34 +4926,42 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Stortannsjön, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>636499</v>
+        <v>636432</v>
       </c>
       <c r="R36" t="n">
-        <v>7014546</v>
+        <v>7014422</v>
       </c>
       <c r="S36" t="n">
         <v>3</v>
@@ -4994,7 +4993,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -5004,7 +5003,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:28</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5024,22 +5028,22 @@
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Markus Borja, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016303</t>
+          <t>https://artportalen.se/Sighting/137016295</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>137040101</v>
+        <v>137016296</v>
       </c>
       <c r="B37" t="n">
-        <v>80102</v>
+        <v>58008</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5047,34 +5051,42 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Stortannsjön, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>636731</v>
+        <v>636424</v>
       </c>
       <c r="R37" t="n">
-        <v>7014243</v>
+        <v>7014437</v>
       </c>
       <c r="S37" t="n">
         <v>3</v>
@@ -5101,22 +5113,27 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>09:05</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>09:05</t>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5136,22 +5153,22 @@
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Markus Borja, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137040101</t>
+          <t>https://artportalen.se/Sighting/137016296</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>137040104</v>
+        <v>137016297</v>
       </c>
       <c r="B38" t="n">
-        <v>80102</v>
+        <v>58008</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5159,34 +5176,42 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Stortannsjön, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>636746</v>
+        <v>636448</v>
       </c>
       <c r="R38" t="n">
-        <v>7014291</v>
+        <v>7014424</v>
       </c>
       <c r="S38" t="n">
         <v>3</v>
@@ -5213,22 +5238,27 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>11:35</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5248,49 +5278,54 @@
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Markus Borja, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137040104</t>
+          <t>https://artportalen.se/Sighting/137016297</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>137040108</v>
+        <v>137016300</v>
       </c>
       <c r="B39" t="n">
-        <v>80492</v>
+        <v>58008</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6456</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -5298,13 +5333,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>636817</v>
+        <v>636398</v>
       </c>
       <c r="R39" t="n">
-        <v>7014280</v>
+        <v>7014509</v>
       </c>
       <c r="S39" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5328,22 +5363,27 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>11:46</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5352,24 +5392,8 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ39" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK39" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO39" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
@@ -5379,49 +5403,54 @@
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Markus Borja, Vivien Renaut, Ann-Christine Borja</t>
+          <t>Markus Borja, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137040108</t>
+          <t>https://artportalen.se/Sighting/137016300</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>137040110</v>
+        <v>137016304</v>
       </c>
       <c r="B40" t="n">
-        <v>80492</v>
+        <v>58008</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6456</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -5429,10 +5458,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>636815</v>
+        <v>636466</v>
       </c>
       <c r="R40" t="n">
-        <v>7014278</v>
+        <v>7014462</v>
       </c>
       <c r="S40" t="n">
         <v>3</v>
@@ -5459,22 +5488,27 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>12:24</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5483,24 +5517,8 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ40" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK40" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO40" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
@@ -5510,49 +5528,54 @@
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Markus Borja, Vivien Renaut, Ann-Christine Borja</t>
+          <t>Markus Borja, Ann-Christine Borja, Diego Borja</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137040110</t>
+          <t>https://artportalen.se/Sighting/137016304</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>137040111</v>
+        <v>137016307</v>
       </c>
       <c r="B41" t="n">
-        <v>80492</v>
+        <v>58008</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6456</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -5560,13 +5583,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>636803</v>
+        <v>636566</v>
       </c>
       <c r="R41" t="n">
-        <v>7014259</v>
+        <v>7014367</v>
       </c>
       <c r="S41" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5590,22 +5613,27 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>12:35</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5614,24 +5642,8 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ41" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK41" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO41" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
@@ -5641,39 +5653,39 @@
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Markus Borja, Vivien Renaut, Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137040111</t>
+          <t>https://artportalen.se/Sighting/137016307</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>137016301</v>
+        <v>137016344</v>
       </c>
       <c r="B42" t="n">
-        <v>58005</v>
+        <v>58008</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -5696,13 +5708,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>636482</v>
+        <v>636392</v>
       </c>
       <c r="R42" t="n">
-        <v>7014533</v>
+        <v>7014473</v>
       </c>
       <c r="S42" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5731,7 +5743,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5741,7 +5753,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5756,49 +5773,49 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja, Markus Borja</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016301</t>
+          <t>https://artportalen.se/Sighting/137016344</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>137040182</v>
+        <v>137040177</v>
       </c>
       <c r="B43" t="n">
-        <v>58005</v>
+        <v>58169</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5806,7 +5823,7 @@
       <c r="L43" t="inlineStr"/>
       <c r="M43" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N43" t="inlineStr"/>
@@ -5816,13 +5833,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>636550</v>
+        <v>636811</v>
       </c>
       <c r="R43" t="n">
-        <v>7014507</v>
+        <v>7014284</v>
       </c>
       <c r="S43" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5851,7 +5868,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5861,12 +5878,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Färska spår</t>
+          <t>Läte</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5892,48 +5909,52 @@
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137040182</t>
+          <t>https://artportalen.se/Sighting/137040177</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>137016287</v>
+        <v>137040164</v>
       </c>
       <c r="B44" t="n">
-        <v>58008</v>
+        <v>99372</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -5941,10 +5962,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>636606</v>
+        <v>636776</v>
       </c>
       <c r="R44" t="n">
-        <v>7014302</v>
+        <v>7014278</v>
       </c>
       <c r="S44" t="n">
         <v>3</v>
@@ -5971,27 +5992,22 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>09:05</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>10:34</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Färska och Äldre ringhack på tall</t>
+          <t>09:05</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6000,65 +6016,70 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Vivien Renaut</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja, Diego Borja</t>
+          <t>Vivien Renaut</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016287</t>
+          <t>https://artportalen.se/Sighting/137040164</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>137016290</v>
+        <v>137040166</v>
       </c>
       <c r="B45" t="n">
-        <v>58008</v>
+        <v>99372</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -6066,10 +6087,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>636608</v>
+        <v>636782</v>
       </c>
       <c r="R45" t="n">
-        <v>7014302</v>
+        <v>7014300</v>
       </c>
       <c r="S45" t="n">
         <v>3</v>
@@ -6096,27 +6117,22 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>10:54</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6125,65 +6141,70 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Vivien Renaut</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja, Diego Borja</t>
+          <t>Vivien Renaut</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016290</t>
+          <t>https://artportalen.se/Sighting/137040166</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>137016291</v>
+        <v>137040168</v>
       </c>
       <c r="B46" t="n">
-        <v>58008</v>
+        <v>99372</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
@@ -6191,10 +6212,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>636578</v>
+        <v>636758</v>
       </c>
       <c r="R46" t="n">
-        <v>7014320</v>
+        <v>7014368</v>
       </c>
       <c r="S46" t="n">
         <v>3</v>
@@ -6221,27 +6242,22 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>10:59</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6250,65 +6266,70 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Vivien Renaut</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja, Diego Borja</t>
+          <t>Vivien Renaut</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016291</t>
+          <t>https://artportalen.se/Sighting/137040168</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>137016292</v>
+        <v>137040189</v>
       </c>
       <c r="B47" t="n">
-        <v>58008</v>
+        <v>99372</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
@@ -6316,13 +6337,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>636501</v>
+        <v>636424</v>
       </c>
       <c r="R47" t="n">
-        <v>7014381</v>
+        <v>7014610</v>
       </c>
       <c r="S47" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6346,27 +6367,22 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>11:09</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6375,65 +6391,70 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Vivien Renaut</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja</t>
+          <t>Vivien Renaut</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016292</t>
+          <t>https://artportalen.se/Sighting/137040189</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>137016294</v>
+        <v>137044057</v>
       </c>
       <c r="B48" t="n">
-        <v>58008</v>
+        <v>99372</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -6441,13 +6462,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>636486</v>
+        <v>636762</v>
       </c>
       <c r="R48" t="n">
-        <v>7014403</v>
+        <v>7014263</v>
       </c>
       <c r="S48" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6471,27 +6492,22 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>11:16</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6500,65 +6516,70 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja</t>
+          <t>Ann-Christine Borja, Markus Borja, Vivien Renaut</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016294</t>
+          <t>https://artportalen.se/Sighting/137044057</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>137016295</v>
+        <v>137044059</v>
       </c>
       <c r="B49" t="n">
-        <v>58008</v>
+        <v>99372</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
@@ -6566,13 +6587,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>636432</v>
+        <v>636736</v>
       </c>
       <c r="R49" t="n">
-        <v>7014422</v>
+        <v>7014341</v>
       </c>
       <c r="S49" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6596,27 +6617,22 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>11:28</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6625,65 +6641,70 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja</t>
+          <t>Ann-Christine Borja, Markus Borja, Vivien Renaut</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016295</t>
+          <t>https://artportalen.se/Sighting/137044059</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>137016296</v>
+        <v>137044060</v>
       </c>
       <c r="B50" t="n">
-        <v>58008</v>
+        <v>99372</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>159</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
@@ -6691,13 +6712,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>636424</v>
+        <v>636760</v>
       </c>
       <c r="R50" t="n">
-        <v>7014437</v>
+        <v>7014309</v>
       </c>
       <c r="S50" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6721,27 +6742,22 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>11:30</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack på tall</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6750,65 +6766,70 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja</t>
+          <t>Ann-Christine Borja, Markus Borja, Vivien Renaut</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016296</t>
+          <t>https://artportalen.se/Sighting/137044060</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>137016297</v>
+        <v>137044061</v>
       </c>
       <c r="B51" t="n">
-        <v>58008</v>
+        <v>99372</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
@@ -6816,13 +6837,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>636448</v>
+        <v>636781</v>
       </c>
       <c r="R51" t="n">
-        <v>7014424</v>
+        <v>7014323</v>
       </c>
       <c r="S51" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6846,27 +6867,22 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>11:35</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6875,65 +6891,70 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja</t>
+          <t>Ann-Christine Borja, Markus Borja, Vivien Renaut</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016297</t>
+          <t>https://artportalen.se/Sighting/137044061</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>137016300</v>
+        <v>137044062</v>
       </c>
       <c r="B52" t="n">
-        <v>58008</v>
+        <v>99372</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>117</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
@@ -6941,13 +6962,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>636398</v>
+        <v>636772</v>
       </c>
       <c r="R52" t="n">
-        <v>7014509</v>
+        <v>7014326</v>
       </c>
       <c r="S52" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6971,27 +6992,22 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>11:46</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -7000,65 +7016,70 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja</t>
+          <t>Ann-Christine Borja, Markus Borja, Vivien Renaut</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016300</t>
+          <t>https://artportalen.se/Sighting/137044062</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>137016304</v>
+        <v>137044064</v>
       </c>
       <c r="B53" t="n">
-        <v>58008</v>
+        <v>99372</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
@@ -7066,13 +7087,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>636466</v>
+        <v>636806</v>
       </c>
       <c r="R53" t="n">
-        <v>7014462</v>
+        <v>7014282</v>
       </c>
       <c r="S53" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -7096,27 +7117,22 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>12:24</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -7125,65 +7141,70 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja, Diego Borja</t>
+          <t>Ann-Christine Borja, Markus Borja, Vivien Renaut</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016304</t>
+          <t>https://artportalen.se/Sighting/137044064</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>137016307</v>
+        <v>137044080</v>
       </c>
       <c r="B54" t="n">
-        <v>58008</v>
+        <v>99372</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
@@ -7191,13 +7212,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>636566</v>
+        <v>636598</v>
       </c>
       <c r="R54" t="n">
-        <v>7014367</v>
+        <v>7014517</v>
       </c>
       <c r="S54" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -7221,27 +7242,22 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>12:35</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7250,33 +7266,34 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja, Markus Borja, Vivien Renaut</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016307</t>
+          <t>https://artportalen.se/Sighting/137044080</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>137016344</v>
+        <v>137016336</v>
       </c>
       <c r="B55" t="n">
-        <v>58008</v>
+        <v>79508</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7284,31 +7301,26 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100109</v>
+        <v>260591</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltagel</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria fremontii</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
@@ -7316,10 +7328,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>636392</v>
+        <v>636512</v>
       </c>
       <c r="R55" t="n">
-        <v>7014473</v>
+        <v>7014375</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -7351,7 +7363,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -7361,12 +7373,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>11:50</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall.</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7375,8 +7382,24 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ55" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK55" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO55" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
@@ -7392,16 +7415,16 @@
       <c r="AY55" t="inlineStr"/>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016344</t>
+          <t>https://artportalen.se/Sighting/137016336</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>137040097</v>
+        <v>137016339</v>
       </c>
       <c r="B56" t="n">
-        <v>58008</v>
+        <v>79508</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7409,31 +7432,26 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>260591</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltagel</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria fremontii</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
@@ -7441,13 +7459,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>636710</v>
+        <v>636457</v>
       </c>
       <c r="R56" t="n">
-        <v>7014234</v>
+        <v>7014405</v>
       </c>
       <c r="S56" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -7471,27 +7489,22 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>08:39</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>08:39</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7500,33 +7513,49 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
+      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ56" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK56" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO56" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Markus Borja, Vivien Renaut, Ann-Christine Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137040097</t>
+          <t>https://artportalen.se/Sighting/137016339</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>137040106</v>
+        <v>137016342</v>
       </c>
       <c r="B57" t="n">
-        <v>58169</v>
+        <v>79508</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7534,53 +7563,40 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>103021</v>
+        <v>260591</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Talltagel</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Bryoria fremontii</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N57" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Stortannsjön, Ång</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>636783</v>
+        <v>636417</v>
       </c>
       <c r="R57" t="n">
-        <v>7014328</v>
+        <v>7014452</v>
       </c>
       <c r="S57" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7604,22 +7620,22 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7628,33 +7644,49 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ57" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK57" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO57" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja, Vivien Renaut</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137040106</t>
+          <t>https://artportalen.se/Sighting/137016342</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>137040109</v>
+        <v>137016345</v>
       </c>
       <c r="B58" t="n">
-        <v>58169</v>
+        <v>79508</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7662,31 +7694,26 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>103021</v>
+        <v>260591</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Talltagel</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Bryoria fremontii</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
@@ -7694,13 +7721,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>636808</v>
+        <v>636407</v>
       </c>
       <c r="R58" t="n">
-        <v>7014272</v>
+        <v>7014480</v>
       </c>
       <c r="S58" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7724,22 +7751,22 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7748,33 +7775,49 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ58" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK58" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO58" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Markus Borja, Vivien Renaut</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137040109</t>
+          <t>https://artportalen.se/Sighting/137016345</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>137040177</v>
+        <v>137016346</v>
       </c>
       <c r="B59" t="n">
-        <v>58169</v>
+        <v>79508</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7782,29 +7825,28 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>103021</v>
+        <v>260591</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Talltagel</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Bryoria fremontii</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="N59" t="inlineStr"/>
@@ -7814,13 +7856,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>636811</v>
+        <v>636450</v>
       </c>
       <c r="R59" t="n">
-        <v>7014284</v>
+        <v>7014535</v>
       </c>
       <c r="S59" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7844,27 +7886,22 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>12:13</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Läte</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7873,69 +7910,80 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
+      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ59" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK59" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO59" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Vivien Renaut</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Vivien Renaut</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137040177</t>
+          <t>https://artportalen.se/Sighting/137016346</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>137040107</v>
+        <v>137016348</v>
       </c>
       <c r="B60" t="n">
-        <v>99368</v>
+        <v>79508</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220787</v>
+        <v>260591</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltagel</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria fremontii</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
@@ -7943,13 +7991,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>636807</v>
+        <v>636479</v>
       </c>
       <c r="R60" t="n">
-        <v>7014295</v>
+        <v>7014523</v>
       </c>
       <c r="S60" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7973,22 +8021,22 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -8001,66 +8049,72 @@
       <c r="AG60" t="b">
         <v>0</v>
       </c>
+      <c r="AJ60" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK60" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO60" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Markus Borja, Vivien Renaut, Ann-Christine Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137040107</t>
+          <t>https://artportalen.se/Sighting/137016348</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>137040121</v>
+        <v>137016353</v>
       </c>
       <c r="B61" t="n">
-        <v>99368</v>
+        <v>79508</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220787</v>
+        <v>260591</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltagel</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria fremontii</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
       <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
@@ -8068,13 +8122,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>636854</v>
+        <v>636460</v>
       </c>
       <c r="R61" t="n">
-        <v>7014229</v>
+        <v>7014451</v>
       </c>
       <c r="S61" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -8098,22 +8152,22 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -8126,66 +8180,76 @@
       <c r="AG61" t="b">
         <v>0</v>
       </c>
+      <c r="AJ61" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK61" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO61" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Markus Borja, Vivien Renaut, Ann-Christine Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137040121</t>
+          <t>https://artportalen.se/Sighting/137016353</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>137040123</v>
+        <v>137044071</v>
       </c>
       <c r="B62" t="n">
-        <v>99368</v>
+        <v>79508</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>220787</v>
+        <v>260591</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltagel</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria fremontii</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
@@ -8193,13 +8257,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>636843</v>
+        <v>636845</v>
       </c>
       <c r="R62" t="n">
-        <v>7014251</v>
+        <v>7014233</v>
       </c>
       <c r="S62" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -8228,7 +8292,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -8238,7 +8302,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8251,3165 +8315,34 @@
       <c r="AG62" t="b">
         <v>0</v>
       </c>
+      <c r="AJ62" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK62" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO62" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Markus Borja, Vivien Renaut, Ann-Christine Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
       <c r="AZ62" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/137040123</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="n">
-        <v>137040138</v>
-      </c>
-      <c r="B63" t="n">
-        <v>99368</v>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E63" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
-      <c r="N63" t="inlineStr"/>
-      <c r="P63" t="inlineStr">
-        <is>
-          <t>Stortannsjön, Ång</t>
-        </is>
-      </c>
-      <c r="Q63" t="n">
-        <v>636527</v>
-      </c>
-      <c r="R63" t="n">
-        <v>7014608</v>
-      </c>
-      <c r="S63" t="n">
-        <v>4</v>
-      </c>
-      <c r="T63" t="inlineStr">
-        <is>
-          <t>Västernorrland</t>
-        </is>
-      </c>
-      <c r="U63" t="inlineStr">
-        <is>
-          <t>Sollefteå</t>
-        </is>
-      </c>
-      <c r="V63" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W63" t="inlineStr">
-        <is>
-          <t>Överlännäs</t>
-        </is>
-      </c>
-      <c r="Y63" t="inlineStr">
-        <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="Z63" t="inlineStr">
-        <is>
-          <t>15:02</t>
-        </is>
-      </c>
-      <c r="AA63" t="inlineStr">
-        <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="AB63" t="inlineStr">
-        <is>
-          <t>15:02</t>
-        </is>
-      </c>
-      <c r="AD63" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE63" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF63" t="inlineStr"/>
-      <c r="AG63" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT63" t="inlineStr"/>
-      <c r="AW63" t="inlineStr">
-        <is>
-          <t>Markus Borja</t>
-        </is>
-      </c>
-      <c r="AX63" t="inlineStr">
-        <is>
-          <t>Markus Borja, Vivien Renaut, Ann-Christine Borja</t>
-        </is>
-      </c>
-      <c r="AY63" t="inlineStr"/>
-      <c r="AZ63" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/137040138</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="n">
-        <v>137040160</v>
-      </c>
-      <c r="B64" t="n">
-        <v>99368</v>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E64" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr"/>
-      <c r="N64" t="inlineStr"/>
-      <c r="P64" t="inlineStr">
-        <is>
-          <t>Stortannsjön, Ång</t>
-        </is>
-      </c>
-      <c r="Q64" t="n">
-        <v>636474</v>
-      </c>
-      <c r="R64" t="n">
-        <v>7014608</v>
-      </c>
-      <c r="S64" t="n">
-        <v>3</v>
-      </c>
-      <c r="T64" t="inlineStr">
-        <is>
-          <t>Västernorrland</t>
-        </is>
-      </c>
-      <c r="U64" t="inlineStr">
-        <is>
-          <t>Sollefteå</t>
-        </is>
-      </c>
-      <c r="V64" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W64" t="inlineStr">
-        <is>
-          <t>Överlännäs</t>
-        </is>
-      </c>
-      <c r="Y64" t="inlineStr">
-        <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="Z64" t="inlineStr">
-        <is>
-          <t>18:00</t>
-        </is>
-      </c>
-      <c r="AA64" t="inlineStr">
-        <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="AB64" t="inlineStr">
-        <is>
-          <t>18:00</t>
-        </is>
-      </c>
-      <c r="AD64" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE64" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF64" t="inlineStr"/>
-      <c r="AG64" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT64" t="inlineStr"/>
-      <c r="AW64" t="inlineStr">
-        <is>
-          <t>Markus Borja</t>
-        </is>
-      </c>
-      <c r="AX64" t="inlineStr">
-        <is>
-          <t>Markus Borja, Vivien Renaut, Ann-Christine Borja</t>
-        </is>
-      </c>
-      <c r="AY64" t="inlineStr"/>
-      <c r="AZ64" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/137040160</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="n">
-        <v>137040163</v>
-      </c>
-      <c r="B65" t="n">
-        <v>99368</v>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E65" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
-      <c r="N65" t="inlineStr"/>
-      <c r="P65" t="inlineStr">
-        <is>
-          <t>Stortannsjön, Ång</t>
-        </is>
-      </c>
-      <c r="Q65" t="n">
-        <v>636595</v>
-      </c>
-      <c r="R65" t="n">
-        <v>7014422</v>
-      </c>
-      <c r="S65" t="n">
-        <v>3</v>
-      </c>
-      <c r="T65" t="inlineStr">
-        <is>
-          <t>Västernorrland</t>
-        </is>
-      </c>
-      <c r="U65" t="inlineStr">
-        <is>
-          <t>Sollefteå</t>
-        </is>
-      </c>
-      <c r="V65" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W65" t="inlineStr">
-        <is>
-          <t>Överlännäs</t>
-        </is>
-      </c>
-      <c r="Y65" t="inlineStr">
-        <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="Z65" t="inlineStr">
-        <is>
-          <t>18:17</t>
-        </is>
-      </c>
-      <c r="AA65" t="inlineStr">
-        <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="AB65" t="inlineStr">
-        <is>
-          <t>18:17</t>
-        </is>
-      </c>
-      <c r="AD65" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE65" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF65" t="inlineStr"/>
-      <c r="AG65" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT65" t="inlineStr"/>
-      <c r="AW65" t="inlineStr">
-        <is>
-          <t>Markus Borja</t>
-        </is>
-      </c>
-      <c r="AX65" t="inlineStr">
-        <is>
-          <t>Markus Borja, Vivien Renaut, Ann-Christine Borja</t>
-        </is>
-      </c>
-      <c r="AY65" t="inlineStr"/>
-      <c r="AZ65" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/137040163</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="n">
-        <v>137040164</v>
-      </c>
-      <c r="B66" t="n">
-        <v>99368</v>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E66" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
-      <c r="N66" t="inlineStr"/>
-      <c r="P66" t="inlineStr">
-        <is>
-          <t>Stortannsjön, Ång</t>
-        </is>
-      </c>
-      <c r="Q66" t="n">
-        <v>636776</v>
-      </c>
-      <c r="R66" t="n">
-        <v>7014278</v>
-      </c>
-      <c r="S66" t="n">
-        <v>3</v>
-      </c>
-      <c r="T66" t="inlineStr">
-        <is>
-          <t>Västernorrland</t>
-        </is>
-      </c>
-      <c r="U66" t="inlineStr">
-        <is>
-          <t>Sollefteå</t>
-        </is>
-      </c>
-      <c r="V66" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W66" t="inlineStr">
-        <is>
-          <t>Överlännäs</t>
-        </is>
-      </c>
-      <c r="Y66" t="inlineStr">
-        <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="Z66" t="inlineStr">
-        <is>
-          <t>09:05</t>
-        </is>
-      </c>
-      <c r="AA66" t="inlineStr">
-        <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="AB66" t="inlineStr">
-        <is>
-          <t>09:05</t>
-        </is>
-      </c>
-      <c r="AD66" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE66" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF66" t="inlineStr"/>
-      <c r="AG66" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT66" t="inlineStr"/>
-      <c r="AW66" t="inlineStr">
-        <is>
-          <t>Vivien Renaut</t>
-        </is>
-      </c>
-      <c r="AX66" t="inlineStr">
-        <is>
-          <t>Vivien Renaut</t>
-        </is>
-      </c>
-      <c r="AY66" t="inlineStr"/>
-      <c r="AZ66" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/137040164</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="n">
-        <v>137040166</v>
-      </c>
-      <c r="B67" t="n">
-        <v>99368</v>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E67" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>115</t>
-        </is>
-      </c>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
-      <c r="N67" t="inlineStr"/>
-      <c r="P67" t="inlineStr">
-        <is>
-          <t>Stortannsjön, Ång</t>
-        </is>
-      </c>
-      <c r="Q67" t="n">
-        <v>636782</v>
-      </c>
-      <c r="R67" t="n">
-        <v>7014300</v>
-      </c>
-      <c r="S67" t="n">
-        <v>3</v>
-      </c>
-      <c r="T67" t="inlineStr">
-        <is>
-          <t>Västernorrland</t>
-        </is>
-      </c>
-      <c r="U67" t="inlineStr">
-        <is>
-          <t>Sollefteå</t>
-        </is>
-      </c>
-      <c r="V67" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W67" t="inlineStr">
-        <is>
-          <t>Överlännäs</t>
-        </is>
-      </c>
-      <c r="Y67" t="inlineStr">
-        <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="Z67" t="inlineStr">
-        <is>
-          <t>09:15</t>
-        </is>
-      </c>
-      <c r="AA67" t="inlineStr">
-        <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="AB67" t="inlineStr">
-        <is>
-          <t>09:15</t>
-        </is>
-      </c>
-      <c r="AD67" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE67" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF67" t="inlineStr"/>
-      <c r="AG67" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT67" t="inlineStr"/>
-      <c r="AW67" t="inlineStr">
-        <is>
-          <t>Vivien Renaut</t>
-        </is>
-      </c>
-      <c r="AX67" t="inlineStr">
-        <is>
-          <t>Vivien Renaut</t>
-        </is>
-      </c>
-      <c r="AY67" t="inlineStr"/>
-      <c r="AZ67" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/137040166</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="n">
-        <v>137040168</v>
-      </c>
-      <c r="B68" t="n">
-        <v>99368</v>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E68" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
-      <c r="N68" t="inlineStr"/>
-      <c r="P68" t="inlineStr">
-        <is>
-          <t>Stortannsjön, Ång</t>
-        </is>
-      </c>
-      <c r="Q68" t="n">
-        <v>636758</v>
-      </c>
-      <c r="R68" t="n">
-        <v>7014368</v>
-      </c>
-      <c r="S68" t="n">
-        <v>3</v>
-      </c>
-      <c r="T68" t="inlineStr">
-        <is>
-          <t>Västernorrland</t>
-        </is>
-      </c>
-      <c r="U68" t="inlineStr">
-        <is>
-          <t>Sollefteå</t>
-        </is>
-      </c>
-      <c r="V68" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W68" t="inlineStr">
-        <is>
-          <t>Överlännäs</t>
-        </is>
-      </c>
-      <c r="Y68" t="inlineStr">
-        <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="Z68" t="inlineStr">
-        <is>
-          <t>09:42</t>
-        </is>
-      </c>
-      <c r="AA68" t="inlineStr">
-        <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="AB68" t="inlineStr">
-        <is>
-          <t>09:42</t>
-        </is>
-      </c>
-      <c r="AD68" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE68" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF68" t="inlineStr"/>
-      <c r="AG68" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT68" t="inlineStr"/>
-      <c r="AW68" t="inlineStr">
-        <is>
-          <t>Vivien Renaut</t>
-        </is>
-      </c>
-      <c r="AX68" t="inlineStr">
-        <is>
-          <t>Vivien Renaut</t>
-        </is>
-      </c>
-      <c r="AY68" t="inlineStr"/>
-      <c r="AZ68" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/137040168</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="n">
-        <v>137040189</v>
-      </c>
-      <c r="B69" t="n">
-        <v>99368</v>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E69" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
-      <c r="N69" t="inlineStr"/>
-      <c r="P69" t="inlineStr">
-        <is>
-          <t>Stortannsjön, Ång</t>
-        </is>
-      </c>
-      <c r="Q69" t="n">
-        <v>636424</v>
-      </c>
-      <c r="R69" t="n">
-        <v>7014610</v>
-      </c>
-      <c r="S69" t="n">
-        <v>15</v>
-      </c>
-      <c r="T69" t="inlineStr">
-        <is>
-          <t>Västernorrland</t>
-        </is>
-      </c>
-      <c r="U69" t="inlineStr">
-        <is>
-          <t>Sollefteå</t>
-        </is>
-      </c>
-      <c r="V69" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W69" t="inlineStr">
-        <is>
-          <t>Överlännäs</t>
-        </is>
-      </c>
-      <c r="Y69" t="inlineStr">
-        <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="Z69" t="inlineStr">
-        <is>
-          <t>17:52</t>
-        </is>
-      </c>
-      <c r="AA69" t="inlineStr">
-        <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="AB69" t="inlineStr">
-        <is>
-          <t>17:52</t>
-        </is>
-      </c>
-      <c r="AD69" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE69" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF69" t="inlineStr"/>
-      <c r="AG69" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT69" t="inlineStr"/>
-      <c r="AW69" t="inlineStr">
-        <is>
-          <t>Vivien Renaut</t>
-        </is>
-      </c>
-      <c r="AX69" t="inlineStr">
-        <is>
-          <t>Vivien Renaut</t>
-        </is>
-      </c>
-      <c r="AY69" t="inlineStr"/>
-      <c r="AZ69" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/137040189</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="n">
-        <v>137044057</v>
-      </c>
-      <c r="B70" t="n">
-        <v>99368</v>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E70" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
-      <c r="N70" t="inlineStr"/>
-      <c r="P70" t="inlineStr">
-        <is>
-          <t>Stortannsjön, Ång</t>
-        </is>
-      </c>
-      <c r="Q70" t="n">
-        <v>636762</v>
-      </c>
-      <c r="R70" t="n">
-        <v>7014263</v>
-      </c>
-      <c r="S70" t="n">
-        <v>5</v>
-      </c>
-      <c r="T70" t="inlineStr">
-        <is>
-          <t>Västernorrland</t>
-        </is>
-      </c>
-      <c r="U70" t="inlineStr">
-        <is>
-          <t>Sollefteå</t>
-        </is>
-      </c>
-      <c r="V70" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W70" t="inlineStr">
-        <is>
-          <t>Överlännäs</t>
-        </is>
-      </c>
-      <c r="Y70" t="inlineStr">
-        <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="Z70" t="inlineStr">
-        <is>
-          <t>09:10</t>
-        </is>
-      </c>
-      <c r="AA70" t="inlineStr">
-        <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="AB70" t="inlineStr">
-        <is>
-          <t>09:10</t>
-        </is>
-      </c>
-      <c r="AD70" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE70" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF70" t="inlineStr"/>
-      <c r="AG70" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT70" t="inlineStr"/>
-      <c r="AW70" t="inlineStr">
-        <is>
-          <t>Ann-Christine Borja</t>
-        </is>
-      </c>
-      <c r="AX70" t="inlineStr">
-        <is>
-          <t>Ann-Christine Borja, Markus Borja, Vivien Renaut</t>
-        </is>
-      </c>
-      <c r="AY70" t="inlineStr"/>
-      <c r="AZ70" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/137044057</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="n">
-        <v>137044059</v>
-      </c>
-      <c r="B71" t="n">
-        <v>99368</v>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E71" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>105</t>
-        </is>
-      </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr"/>
-      <c r="N71" t="inlineStr"/>
-      <c r="P71" t="inlineStr">
-        <is>
-          <t>Stortannsjön, Ång</t>
-        </is>
-      </c>
-      <c r="Q71" t="n">
-        <v>636736</v>
-      </c>
-      <c r="R71" t="n">
-        <v>7014341</v>
-      </c>
-      <c r="S71" t="n">
-        <v>5</v>
-      </c>
-      <c r="T71" t="inlineStr">
-        <is>
-          <t>Västernorrland</t>
-        </is>
-      </c>
-      <c r="U71" t="inlineStr">
-        <is>
-          <t>Sollefteå</t>
-        </is>
-      </c>
-      <c r="V71" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W71" t="inlineStr">
-        <is>
-          <t>Överlännäs</t>
-        </is>
-      </c>
-      <c r="Y71" t="inlineStr">
-        <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="Z71" t="inlineStr">
-        <is>
-          <t>09:41</t>
-        </is>
-      </c>
-      <c r="AA71" t="inlineStr">
-        <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="AB71" t="inlineStr">
-        <is>
-          <t>09:41</t>
-        </is>
-      </c>
-      <c r="AD71" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE71" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF71" t="inlineStr"/>
-      <c r="AG71" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT71" t="inlineStr"/>
-      <c r="AW71" t="inlineStr">
-        <is>
-          <t>Ann-Christine Borja</t>
-        </is>
-      </c>
-      <c r="AX71" t="inlineStr">
-        <is>
-          <t>Ann-Christine Borja, Markus Borja, Vivien Renaut</t>
-        </is>
-      </c>
-      <c r="AY71" t="inlineStr"/>
-      <c r="AZ71" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/137044059</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="n">
-        <v>137044060</v>
-      </c>
-      <c r="B72" t="n">
-        <v>99368</v>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E72" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>159</t>
-        </is>
-      </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K72" t="inlineStr"/>
-      <c r="L72" t="inlineStr"/>
-      <c r="N72" t="inlineStr"/>
-      <c r="P72" t="inlineStr">
-        <is>
-          <t>Stortannsjön, Ång</t>
-        </is>
-      </c>
-      <c r="Q72" t="n">
-        <v>636760</v>
-      </c>
-      <c r="R72" t="n">
-        <v>7014309</v>
-      </c>
-      <c r="S72" t="n">
-        <v>5</v>
-      </c>
-      <c r="T72" t="inlineStr">
-        <is>
-          <t>Västernorrland</t>
-        </is>
-      </c>
-      <c r="U72" t="inlineStr">
-        <is>
-          <t>Sollefteå</t>
-        </is>
-      </c>
-      <c r="V72" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W72" t="inlineStr">
-        <is>
-          <t>Överlännäs</t>
-        </is>
-      </c>
-      <c r="Y72" t="inlineStr">
-        <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="Z72" t="inlineStr">
-        <is>
-          <t>10:02</t>
-        </is>
-      </c>
-      <c r="AA72" t="inlineStr">
-        <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="AB72" t="inlineStr">
-        <is>
-          <t>10:02</t>
-        </is>
-      </c>
-      <c r="AD72" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE72" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF72" t="inlineStr"/>
-      <c r="AG72" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT72" t="inlineStr"/>
-      <c r="AW72" t="inlineStr">
-        <is>
-          <t>Ann-Christine Borja</t>
-        </is>
-      </c>
-      <c r="AX72" t="inlineStr">
-        <is>
-          <t>Ann-Christine Borja, Markus Borja, Vivien Renaut</t>
-        </is>
-      </c>
-      <c r="AY72" t="inlineStr"/>
-      <c r="AZ72" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/137044060</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="n">
-        <v>137044061</v>
-      </c>
-      <c r="B73" t="n">
-        <v>99368</v>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E73" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K73" t="inlineStr"/>
-      <c r="L73" t="inlineStr"/>
-      <c r="N73" t="inlineStr"/>
-      <c r="P73" t="inlineStr">
-        <is>
-          <t>Stortannsjön, Ång</t>
-        </is>
-      </c>
-      <c r="Q73" t="n">
-        <v>636781</v>
-      </c>
-      <c r="R73" t="n">
-        <v>7014323</v>
-      </c>
-      <c r="S73" t="n">
-        <v>5</v>
-      </c>
-      <c r="T73" t="inlineStr">
-        <is>
-          <t>Västernorrland</t>
-        </is>
-      </c>
-      <c r="U73" t="inlineStr">
-        <is>
-          <t>Sollefteå</t>
-        </is>
-      </c>
-      <c r="V73" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W73" t="inlineStr">
-        <is>
-          <t>Överlännäs</t>
-        </is>
-      </c>
-      <c r="Y73" t="inlineStr">
-        <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="Z73" t="inlineStr">
-        <is>
-          <t>10:10</t>
-        </is>
-      </c>
-      <c r="AA73" t="inlineStr">
-        <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="AB73" t="inlineStr">
-        <is>
-          <t>10:10</t>
-        </is>
-      </c>
-      <c r="AD73" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE73" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF73" t="inlineStr"/>
-      <c r="AG73" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT73" t="inlineStr"/>
-      <c r="AW73" t="inlineStr">
-        <is>
-          <t>Ann-Christine Borja</t>
-        </is>
-      </c>
-      <c r="AX73" t="inlineStr">
-        <is>
-          <t>Ann-Christine Borja, Markus Borja, Vivien Renaut</t>
-        </is>
-      </c>
-      <c r="AY73" t="inlineStr"/>
-      <c r="AZ73" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/137044061</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="n">
-        <v>137044062</v>
-      </c>
-      <c r="B74" t="n">
-        <v>99368</v>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E74" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>117</t>
-        </is>
-      </c>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K74" t="inlineStr"/>
-      <c r="L74" t="inlineStr"/>
-      <c r="N74" t="inlineStr"/>
-      <c r="P74" t="inlineStr">
-        <is>
-          <t>Stortannsjön, Ång</t>
-        </is>
-      </c>
-      <c r="Q74" t="n">
-        <v>636772</v>
-      </c>
-      <c r="R74" t="n">
-        <v>7014326</v>
-      </c>
-      <c r="S74" t="n">
-        <v>5</v>
-      </c>
-      <c r="T74" t="inlineStr">
-        <is>
-          <t>Västernorrland</t>
-        </is>
-      </c>
-      <c r="U74" t="inlineStr">
-        <is>
-          <t>Sollefteå</t>
-        </is>
-      </c>
-      <c r="V74" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W74" t="inlineStr">
-        <is>
-          <t>Överlännäs</t>
-        </is>
-      </c>
-      <c r="Y74" t="inlineStr">
-        <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="Z74" t="inlineStr">
-        <is>
-          <t>10:26</t>
-        </is>
-      </c>
-      <c r="AA74" t="inlineStr">
-        <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="AB74" t="inlineStr">
-        <is>
-          <t>10:26</t>
-        </is>
-      </c>
-      <c r="AD74" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE74" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF74" t="inlineStr"/>
-      <c r="AG74" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT74" t="inlineStr"/>
-      <c r="AW74" t="inlineStr">
-        <is>
-          <t>Ann-Christine Borja</t>
-        </is>
-      </c>
-      <c r="AX74" t="inlineStr">
-        <is>
-          <t>Ann-Christine Borja, Markus Borja, Vivien Renaut</t>
-        </is>
-      </c>
-      <c r="AY74" t="inlineStr"/>
-      <c r="AZ74" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/137044062</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="n">
-        <v>137044064</v>
-      </c>
-      <c r="B75" t="n">
-        <v>99368</v>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E75" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
-      </c>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K75" t="inlineStr"/>
-      <c r="L75" t="inlineStr"/>
-      <c r="N75" t="inlineStr"/>
-      <c r="P75" t="inlineStr">
-        <is>
-          <t>Stortannsjön, Ång</t>
-        </is>
-      </c>
-      <c r="Q75" t="n">
-        <v>636806</v>
-      </c>
-      <c r="R75" t="n">
-        <v>7014282</v>
-      </c>
-      <c r="S75" t="n">
-        <v>5</v>
-      </c>
-      <c r="T75" t="inlineStr">
-        <is>
-          <t>Västernorrland</t>
-        </is>
-      </c>
-      <c r="U75" t="inlineStr">
-        <is>
-          <t>Sollefteå</t>
-        </is>
-      </c>
-      <c r="V75" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W75" t="inlineStr">
-        <is>
-          <t>Överlännäs</t>
-        </is>
-      </c>
-      <c r="Y75" t="inlineStr">
-        <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="Z75" t="inlineStr">
-        <is>
-          <t>10:48</t>
-        </is>
-      </c>
-      <c r="AA75" t="inlineStr">
-        <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="AB75" t="inlineStr">
-        <is>
-          <t>10:48</t>
-        </is>
-      </c>
-      <c r="AD75" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE75" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF75" t="inlineStr"/>
-      <c r="AG75" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT75" t="inlineStr"/>
-      <c r="AW75" t="inlineStr">
-        <is>
-          <t>Ann-Christine Borja</t>
-        </is>
-      </c>
-      <c r="AX75" t="inlineStr">
-        <is>
-          <t>Ann-Christine Borja, Markus Borja, Vivien Renaut</t>
-        </is>
-      </c>
-      <c r="AY75" t="inlineStr"/>
-      <c r="AZ75" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/137044064</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="n">
-        <v>137044080</v>
-      </c>
-      <c r="B76" t="n">
-        <v>99368</v>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E76" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
-      <c r="J76" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K76" t="inlineStr"/>
-      <c r="L76" t="inlineStr"/>
-      <c r="N76" t="inlineStr"/>
-      <c r="P76" t="inlineStr">
-        <is>
-          <t>Stortannsjön, Ång</t>
-        </is>
-      </c>
-      <c r="Q76" t="n">
-        <v>636598</v>
-      </c>
-      <c r="R76" t="n">
-        <v>7014517</v>
-      </c>
-      <c r="S76" t="n">
-        <v>5</v>
-      </c>
-      <c r="T76" t="inlineStr">
-        <is>
-          <t>Västernorrland</t>
-        </is>
-      </c>
-      <c r="U76" t="inlineStr">
-        <is>
-          <t>Sollefteå</t>
-        </is>
-      </c>
-      <c r="V76" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W76" t="inlineStr">
-        <is>
-          <t>Överlännäs</t>
-        </is>
-      </c>
-      <c r="Y76" t="inlineStr">
-        <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="Z76" t="inlineStr">
-        <is>
-          <t>14:32</t>
-        </is>
-      </c>
-      <c r="AA76" t="inlineStr">
-        <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="AB76" t="inlineStr">
-        <is>
-          <t>14:32</t>
-        </is>
-      </c>
-      <c r="AD76" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE76" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF76" t="inlineStr"/>
-      <c r="AG76" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT76" t="inlineStr"/>
-      <c r="AW76" t="inlineStr">
-        <is>
-          <t>Ann-Christine Borja</t>
-        </is>
-      </c>
-      <c r="AX76" t="inlineStr">
-        <is>
-          <t>Ann-Christine Borja, Markus Borja, Vivien Renaut</t>
-        </is>
-      </c>
-      <c r="AY76" t="inlineStr"/>
-      <c r="AZ76" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/137044080</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="n">
-        <v>137040134</v>
-      </c>
-      <c r="B77" t="n">
-        <v>79241</v>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E77" t="n">
-        <v>228912</v>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>Mörk kolflarnlav</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>Carbonicola myrmecina</t>
-        </is>
-      </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr"/>
-      <c r="P77" t="inlineStr">
-        <is>
-          <t>Stortannsjön, Ång</t>
-        </is>
-      </c>
-      <c r="Q77" t="n">
-        <v>636580</v>
-      </c>
-      <c r="R77" t="n">
-        <v>7014518</v>
-      </c>
-      <c r="S77" t="n">
-        <v>3</v>
-      </c>
-      <c r="T77" t="inlineStr">
-        <is>
-          <t>Västernorrland</t>
-        </is>
-      </c>
-      <c r="U77" t="inlineStr">
-        <is>
-          <t>Sollefteå</t>
-        </is>
-      </c>
-      <c r="V77" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W77" t="inlineStr">
-        <is>
-          <t>Överlännäs</t>
-        </is>
-      </c>
-      <c r="Y77" t="inlineStr">
-        <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="Z77" t="inlineStr">
-        <is>
-          <t>14:37</t>
-        </is>
-      </c>
-      <c r="AA77" t="inlineStr">
-        <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="AB77" t="inlineStr">
-        <is>
-          <t>14:37</t>
-        </is>
-      </c>
-      <c r="AD77" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE77" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG77" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT77" t="inlineStr"/>
-      <c r="AW77" t="inlineStr">
-        <is>
-          <t>Markus Borja</t>
-        </is>
-      </c>
-      <c r="AX77" t="inlineStr">
-        <is>
-          <t>Markus Borja</t>
-        </is>
-      </c>
-      <c r="AY77" t="inlineStr"/>
-      <c r="AZ77" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/137040134</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="n">
-        <v>137040136</v>
-      </c>
-      <c r="B78" t="n">
-        <v>79241</v>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E78" t="n">
-        <v>228912</v>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>Mörk kolflarnlav</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>Carbonicola myrmecina</t>
-        </is>
-      </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr"/>
-      <c r="P78" t="inlineStr">
-        <is>
-          <t>Stortannsjön, Ång</t>
-        </is>
-      </c>
-      <c r="Q78" t="n">
-        <v>636552</v>
-      </c>
-      <c r="R78" t="n">
-        <v>7014536</v>
-      </c>
-      <c r="S78" t="n">
-        <v>3</v>
-      </c>
-      <c r="T78" t="inlineStr">
-        <is>
-          <t>Västernorrland</t>
-        </is>
-      </c>
-      <c r="U78" t="inlineStr">
-        <is>
-          <t>Sollefteå</t>
-        </is>
-      </c>
-      <c r="V78" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W78" t="inlineStr">
-        <is>
-          <t>Överlännäs</t>
-        </is>
-      </c>
-      <c r="Y78" t="inlineStr">
-        <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="Z78" t="inlineStr">
-        <is>
-          <t>14:47</t>
-        </is>
-      </c>
-      <c r="AA78" t="inlineStr">
-        <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="AB78" t="inlineStr">
-        <is>
-          <t>14:47</t>
-        </is>
-      </c>
-      <c r="AD78" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE78" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG78" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT78" t="inlineStr"/>
-      <c r="AW78" t="inlineStr">
-        <is>
-          <t>Markus Borja</t>
-        </is>
-      </c>
-      <c r="AX78" t="inlineStr">
-        <is>
-          <t>Markus Borja</t>
-        </is>
-      </c>
-      <c r="AY78" t="inlineStr"/>
-      <c r="AZ78" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/137040136</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="n">
-        <v>137016336</v>
-      </c>
-      <c r="B79" t="n">
-        <v>79506</v>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E79" t="n">
-        <v>260591</v>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>Talltagel</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>Bryoria fremontii</t>
-        </is>
-      </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr"/>
-      <c r="J79" t="inlineStr"/>
-      <c r="K79" t="inlineStr"/>
-      <c r="N79" t="inlineStr"/>
-      <c r="P79" t="inlineStr">
-        <is>
-          <t>Stortannsjön, Ång</t>
-        </is>
-      </c>
-      <c r="Q79" t="n">
-        <v>636512</v>
-      </c>
-      <c r="R79" t="n">
-        <v>7014375</v>
-      </c>
-      <c r="S79" t="n">
-        <v>5</v>
-      </c>
-      <c r="T79" t="inlineStr">
-        <is>
-          <t>Västernorrland</t>
-        </is>
-      </c>
-      <c r="U79" t="inlineStr">
-        <is>
-          <t>Sollefteå</t>
-        </is>
-      </c>
-      <c r="V79" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W79" t="inlineStr">
-        <is>
-          <t>Överlännäs</t>
-        </is>
-      </c>
-      <c r="Y79" t="inlineStr">
-        <is>
-          <t>2026-10-02</t>
-        </is>
-      </c>
-      <c r="Z79" t="inlineStr">
-        <is>
-          <t>11:12</t>
-        </is>
-      </c>
-      <c r="AA79" t="inlineStr">
-        <is>
-          <t>2026-10-02</t>
-        </is>
-      </c>
-      <c r="AB79" t="inlineStr">
-        <is>
-          <t>11:12</t>
-        </is>
-      </c>
-      <c r="AD79" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE79" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF79" t="inlineStr"/>
-      <c r="AG79" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ79" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK79" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO79" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AT79" t="inlineStr"/>
-      <c r="AW79" t="inlineStr">
-        <is>
-          <t>Ann-Christine Borja</t>
-        </is>
-      </c>
-      <c r="AX79" t="inlineStr">
-        <is>
-          <t>Ann-Christine Borja, Markus Borja</t>
-        </is>
-      </c>
-      <c r="AY79" t="inlineStr"/>
-      <c r="AZ79" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/137016336</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="n">
-        <v>137016339</v>
-      </c>
-      <c r="B80" t="n">
-        <v>79506</v>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E80" t="n">
-        <v>260591</v>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>Talltagel</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>Bryoria fremontii</t>
-        </is>
-      </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr"/>
-      <c r="J80" t="inlineStr"/>
-      <c r="K80" t="inlineStr"/>
-      <c r="N80" t="inlineStr"/>
-      <c r="P80" t="inlineStr">
-        <is>
-          <t>Stortannsjön, Ång</t>
-        </is>
-      </c>
-      <c r="Q80" t="n">
-        <v>636457</v>
-      </c>
-      <c r="R80" t="n">
-        <v>7014405</v>
-      </c>
-      <c r="S80" t="n">
-        <v>5</v>
-      </c>
-      <c r="T80" t="inlineStr">
-        <is>
-          <t>Västernorrland</t>
-        </is>
-      </c>
-      <c r="U80" t="inlineStr">
-        <is>
-          <t>Sollefteå</t>
-        </is>
-      </c>
-      <c r="V80" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W80" t="inlineStr">
-        <is>
-          <t>Överlännäs</t>
-        </is>
-      </c>
-      <c r="Y80" t="inlineStr">
-        <is>
-          <t>2026-10-02</t>
-        </is>
-      </c>
-      <c r="Z80" t="inlineStr">
-        <is>
-          <t>11:22</t>
-        </is>
-      </c>
-      <c r="AA80" t="inlineStr">
-        <is>
-          <t>2026-10-02</t>
-        </is>
-      </c>
-      <c r="AB80" t="inlineStr">
-        <is>
-          <t>11:22</t>
-        </is>
-      </c>
-      <c r="AD80" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE80" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF80" t="inlineStr"/>
-      <c r="AG80" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ80" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK80" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO80" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AT80" t="inlineStr"/>
-      <c r="AW80" t="inlineStr">
-        <is>
-          <t>Ann-Christine Borja</t>
-        </is>
-      </c>
-      <c r="AX80" t="inlineStr">
-        <is>
-          <t>Ann-Christine Borja</t>
-        </is>
-      </c>
-      <c r="AY80" t="inlineStr"/>
-      <c r="AZ80" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/137016339</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="n">
-        <v>137016342</v>
-      </c>
-      <c r="B81" t="n">
-        <v>79506</v>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E81" t="n">
-        <v>260591</v>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>Talltagel</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>Bryoria fremontii</t>
-        </is>
-      </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr"/>
-      <c r="J81" t="inlineStr"/>
-      <c r="K81" t="inlineStr"/>
-      <c r="N81" t="inlineStr"/>
-      <c r="P81" t="inlineStr">
-        <is>
-          <t>Stortannsjön, Ång</t>
-        </is>
-      </c>
-      <c r="Q81" t="n">
-        <v>636417</v>
-      </c>
-      <c r="R81" t="n">
-        <v>7014452</v>
-      </c>
-      <c r="S81" t="n">
-        <v>5</v>
-      </c>
-      <c r="T81" t="inlineStr">
-        <is>
-          <t>Västernorrland</t>
-        </is>
-      </c>
-      <c r="U81" t="inlineStr">
-        <is>
-          <t>Sollefteå</t>
-        </is>
-      </c>
-      <c r="V81" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W81" t="inlineStr">
-        <is>
-          <t>Överlännäs</t>
-        </is>
-      </c>
-      <c r="Y81" t="inlineStr">
-        <is>
-          <t>2026-10-02</t>
-        </is>
-      </c>
-      <c r="Z81" t="inlineStr">
-        <is>
-          <t>11:40</t>
-        </is>
-      </c>
-      <c r="AA81" t="inlineStr">
-        <is>
-          <t>2026-10-02</t>
-        </is>
-      </c>
-      <c r="AB81" t="inlineStr">
-        <is>
-          <t>11:40</t>
-        </is>
-      </c>
-      <c r="AD81" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE81" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF81" t="inlineStr"/>
-      <c r="AG81" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ81" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK81" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO81" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AT81" t="inlineStr"/>
-      <c r="AW81" t="inlineStr">
-        <is>
-          <t>Ann-Christine Borja</t>
-        </is>
-      </c>
-      <c r="AX81" t="inlineStr">
-        <is>
-          <t>Ann-Christine Borja</t>
-        </is>
-      </c>
-      <c r="AY81" t="inlineStr"/>
-      <c r="AZ81" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/137016342</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="n">
-        <v>137016345</v>
-      </c>
-      <c r="B82" t="n">
-        <v>79506</v>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E82" t="n">
-        <v>260591</v>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>Talltagel</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>Bryoria fremontii</t>
-        </is>
-      </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr"/>
-      <c r="J82" t="inlineStr"/>
-      <c r="K82" t="inlineStr"/>
-      <c r="N82" t="inlineStr"/>
-      <c r="P82" t="inlineStr">
-        <is>
-          <t>Stortannsjön, Ång</t>
-        </is>
-      </c>
-      <c r="Q82" t="n">
-        <v>636407</v>
-      </c>
-      <c r="R82" t="n">
-        <v>7014480</v>
-      </c>
-      <c r="S82" t="n">
-        <v>5</v>
-      </c>
-      <c r="T82" t="inlineStr">
-        <is>
-          <t>Västernorrland</t>
-        </is>
-      </c>
-      <c r="U82" t="inlineStr">
-        <is>
-          <t>Sollefteå</t>
-        </is>
-      </c>
-      <c r="V82" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W82" t="inlineStr">
-        <is>
-          <t>Överlännäs</t>
-        </is>
-      </c>
-      <c r="Y82" t="inlineStr">
-        <is>
-          <t>2026-10-02</t>
-        </is>
-      </c>
-      <c r="Z82" t="inlineStr">
-        <is>
-          <t>11:59</t>
-        </is>
-      </c>
-      <c r="AA82" t="inlineStr">
-        <is>
-          <t>2026-10-02</t>
-        </is>
-      </c>
-      <c r="AB82" t="inlineStr">
-        <is>
-          <t>11:59</t>
-        </is>
-      </c>
-      <c r="AD82" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE82" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF82" t="inlineStr"/>
-      <c r="AG82" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ82" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK82" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO82" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AT82" t="inlineStr"/>
-      <c r="AW82" t="inlineStr">
-        <is>
-          <t>Ann-Christine Borja</t>
-        </is>
-      </c>
-      <c r="AX82" t="inlineStr">
-        <is>
-          <t>Ann-Christine Borja</t>
-        </is>
-      </c>
-      <c r="AY82" t="inlineStr"/>
-      <c r="AZ82" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/137016345</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="n">
-        <v>137016346</v>
-      </c>
-      <c r="B83" t="n">
-        <v>79506</v>
-      </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E83" t="n">
-        <v>260591</v>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>Talltagel</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>Bryoria fremontii</t>
-        </is>
-      </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr"/>
-      <c r="J83" t="inlineStr"/>
-      <c r="K83" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
-      <c r="N83" t="inlineStr"/>
-      <c r="P83" t="inlineStr">
-        <is>
-          <t>Stortannsjön, Ång</t>
-        </is>
-      </c>
-      <c r="Q83" t="n">
-        <v>636450</v>
-      </c>
-      <c r="R83" t="n">
-        <v>7014535</v>
-      </c>
-      <c r="S83" t="n">
-        <v>5</v>
-      </c>
-      <c r="T83" t="inlineStr">
-        <is>
-          <t>Västernorrland</t>
-        </is>
-      </c>
-      <c r="U83" t="inlineStr">
-        <is>
-          <t>Sollefteå</t>
-        </is>
-      </c>
-      <c r="V83" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W83" t="inlineStr">
-        <is>
-          <t>Överlännäs</t>
-        </is>
-      </c>
-      <c r="Y83" t="inlineStr">
-        <is>
-          <t>2026-10-02</t>
-        </is>
-      </c>
-      <c r="Z83" t="inlineStr">
-        <is>
-          <t>12:05</t>
-        </is>
-      </c>
-      <c r="AA83" t="inlineStr">
-        <is>
-          <t>2026-10-02</t>
-        </is>
-      </c>
-      <c r="AB83" t="inlineStr">
-        <is>
-          <t>12:05</t>
-        </is>
-      </c>
-      <c r="AD83" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE83" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF83" t="inlineStr"/>
-      <c r="AG83" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ83" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK83" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO83" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AT83" t="inlineStr"/>
-      <c r="AW83" t="inlineStr">
-        <is>
-          <t>Ann-Christine Borja</t>
-        </is>
-      </c>
-      <c r="AX83" t="inlineStr">
-        <is>
-          <t>Ann-Christine Borja</t>
-        </is>
-      </c>
-      <c r="AY83" t="inlineStr"/>
-      <c r="AZ83" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/137016346</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="n">
-        <v>137016348</v>
-      </c>
-      <c r="B84" t="n">
-        <v>79506</v>
-      </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E84" t="n">
-        <v>260591</v>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>Talltagel</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>Bryoria fremontii</t>
-        </is>
-      </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr"/>
-      <c r="J84" t="inlineStr"/>
-      <c r="K84" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
-      <c r="N84" t="inlineStr"/>
-      <c r="P84" t="inlineStr">
-        <is>
-          <t>Stortannsjön, Ång</t>
-        </is>
-      </c>
-      <c r="Q84" t="n">
-        <v>636479</v>
-      </c>
-      <c r="R84" t="n">
-        <v>7014523</v>
-      </c>
-      <c r="S84" t="n">
-        <v>5</v>
-      </c>
-      <c r="T84" t="inlineStr">
-        <is>
-          <t>Västernorrland</t>
-        </is>
-      </c>
-      <c r="U84" t="inlineStr">
-        <is>
-          <t>Sollefteå</t>
-        </is>
-      </c>
-      <c r="V84" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W84" t="inlineStr">
-        <is>
-          <t>Överlännäs</t>
-        </is>
-      </c>
-      <c r="Y84" t="inlineStr">
-        <is>
-          <t>2026-10-02</t>
-        </is>
-      </c>
-      <c r="Z84" t="inlineStr">
-        <is>
-          <t>12:09</t>
-        </is>
-      </c>
-      <c r="AA84" t="inlineStr">
-        <is>
-          <t>2026-10-02</t>
-        </is>
-      </c>
-      <c r="AB84" t="inlineStr">
-        <is>
-          <t>12:09</t>
-        </is>
-      </c>
-      <c r="AD84" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE84" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF84" t="inlineStr"/>
-      <c r="AG84" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ84" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK84" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO84" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AT84" t="inlineStr"/>
-      <c r="AW84" t="inlineStr">
-        <is>
-          <t>Ann-Christine Borja</t>
-        </is>
-      </c>
-      <c r="AX84" t="inlineStr">
-        <is>
-          <t>Ann-Christine Borja</t>
-        </is>
-      </c>
-      <c r="AY84" t="inlineStr"/>
-      <c r="AZ84" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/137016348</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="n">
-        <v>137016353</v>
-      </c>
-      <c r="B85" t="n">
-        <v>79506</v>
-      </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E85" t="n">
-        <v>260591</v>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>Talltagel</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>Bryoria fremontii</t>
-        </is>
-      </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr"/>
-      <c r="J85" t="inlineStr"/>
-      <c r="K85" t="inlineStr"/>
-      <c r="N85" t="inlineStr"/>
-      <c r="P85" t="inlineStr">
-        <is>
-          <t>Stortannsjön, Ång</t>
-        </is>
-      </c>
-      <c r="Q85" t="n">
-        <v>636460</v>
-      </c>
-      <c r="R85" t="n">
-        <v>7014451</v>
-      </c>
-      <c r="S85" t="n">
-        <v>5</v>
-      </c>
-      <c r="T85" t="inlineStr">
-        <is>
-          <t>Västernorrland</t>
-        </is>
-      </c>
-      <c r="U85" t="inlineStr">
-        <is>
-          <t>Sollefteå</t>
-        </is>
-      </c>
-      <c r="V85" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W85" t="inlineStr">
-        <is>
-          <t>Överlännäs</t>
-        </is>
-      </c>
-      <c r="Y85" t="inlineStr">
-        <is>
-          <t>2026-10-02</t>
-        </is>
-      </c>
-      <c r="Z85" t="inlineStr">
-        <is>
-          <t>12:28</t>
-        </is>
-      </c>
-      <c r="AA85" t="inlineStr">
-        <is>
-          <t>2026-10-02</t>
-        </is>
-      </c>
-      <c r="AB85" t="inlineStr">
-        <is>
-          <t>12:28</t>
-        </is>
-      </c>
-      <c r="AD85" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE85" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF85" t="inlineStr"/>
-      <c r="AG85" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ85" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK85" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO85" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AT85" t="inlineStr"/>
-      <c r="AW85" t="inlineStr">
-        <is>
-          <t>Ann-Christine Borja</t>
-        </is>
-      </c>
-      <c r="AX85" t="inlineStr">
-        <is>
-          <t>Ann-Christine Borja</t>
-        </is>
-      </c>
-      <c r="AY85" t="inlineStr"/>
-      <c r="AZ85" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/137016353</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="n">
-        <v>137040099</v>
-      </c>
-      <c r="B86" t="n">
-        <v>79506</v>
-      </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E86" t="n">
-        <v>260591</v>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>Talltagel</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>Bryoria fremontii</t>
-        </is>
-      </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr"/>
-      <c r="P86" t="inlineStr">
-        <is>
-          <t>Stortannsjön, Ång</t>
-        </is>
-      </c>
-      <c r="Q86" t="n">
-        <v>636705</v>
-      </c>
-      <c r="R86" t="n">
-        <v>7014243</v>
-      </c>
-      <c r="S86" t="n">
-        <v>3</v>
-      </c>
-      <c r="T86" t="inlineStr">
-        <is>
-          <t>Västernorrland</t>
-        </is>
-      </c>
-      <c r="U86" t="inlineStr">
-        <is>
-          <t>Sollefteå</t>
-        </is>
-      </c>
-      <c r="V86" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W86" t="inlineStr">
-        <is>
-          <t>Överlännäs</t>
-        </is>
-      </c>
-      <c r="Y86" t="inlineStr">
-        <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="Z86" t="inlineStr">
-        <is>
-          <t>08:49</t>
-        </is>
-      </c>
-      <c r="AA86" t="inlineStr">
-        <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="AB86" t="inlineStr">
-        <is>
-          <t>08:49</t>
-        </is>
-      </c>
-      <c r="AD86" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE86" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG86" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT86" t="inlineStr"/>
-      <c r="AW86" t="inlineStr">
-        <is>
-          <t>Markus Borja</t>
-        </is>
-      </c>
-      <c r="AX86" t="inlineStr">
-        <is>
-          <t>Markus Borja, Vivien Renaut, Ann-Christine Borja</t>
-        </is>
-      </c>
-      <c r="AY86" t="inlineStr"/>
-      <c r="AZ86" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/137040099</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="n">
-        <v>137044071</v>
-      </c>
-      <c r="B87" t="n">
-        <v>79506</v>
-      </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E87" t="n">
-        <v>260591</v>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>Talltagel</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>Bryoria fremontii</t>
-        </is>
-      </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr"/>
-      <c r="J87" t="inlineStr"/>
-      <c r="K87" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
-      <c r="N87" t="inlineStr"/>
-      <c r="P87" t="inlineStr">
-        <is>
-          <t>Stortannsjön, Ång</t>
-        </is>
-      </c>
-      <c r="Q87" t="n">
-        <v>636845</v>
-      </c>
-      <c r="R87" t="n">
-        <v>7014233</v>
-      </c>
-      <c r="S87" t="n">
-        <v>5</v>
-      </c>
-      <c r="T87" t="inlineStr">
-        <is>
-          <t>Västernorrland</t>
-        </is>
-      </c>
-      <c r="U87" t="inlineStr">
-        <is>
-          <t>Sollefteå</t>
-        </is>
-      </c>
-      <c r="V87" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W87" t="inlineStr">
-        <is>
-          <t>Överlännäs</t>
-        </is>
-      </c>
-      <c r="Y87" t="inlineStr">
-        <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="Z87" t="inlineStr">
-        <is>
-          <t>12:09</t>
-        </is>
-      </c>
-      <c r="AA87" t="inlineStr">
-        <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="AB87" t="inlineStr">
-        <is>
-          <t>12:09</t>
-        </is>
-      </c>
-      <c r="AD87" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE87" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF87" t="inlineStr"/>
-      <c r="AG87" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ87" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK87" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO87" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AT87" t="inlineStr"/>
-      <c r="AW87" t="inlineStr">
-        <is>
-          <t>Ann-Christine Borja</t>
-        </is>
-      </c>
-      <c r="AX87" t="inlineStr">
-        <is>
-          <t>Ann-Christine Borja</t>
-        </is>
-      </c>
-      <c r="AY87" t="inlineStr"/>
-      <c r="AZ87" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/137044071</t>
         </is>
@@ -11478,31 +8411,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 25855-2025 artfynd.xlsx
+++ b/artfynd/A 25855-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ62"/>
+  <dimension ref="A1:AZ87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1156,48 +1156,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>137016298</v>
+        <v>137040122</v>
       </c>
       <c r="B6" t="n">
-        <v>93464</v>
+        <v>92091</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5966</v>
+        <v>5447</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Stortannsjön, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>636437</v>
+        <v>636830</v>
       </c>
       <c r="R6" t="n">
-        <v>7014437</v>
+        <v>7014277</v>
       </c>
       <c r="S6" t="n">
         <v>3</v>
@@ -1224,22 +1221,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1248,7 +1245,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1260,44 +1256,44 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Markus Borja, Diego Borja, Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016298</t>
+          <t>https://artportalen.se/Sighting/137040122</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>137016289</v>
+        <v>137016298</v>
       </c>
       <c r="B7" t="n">
-        <v>79485</v>
+        <v>93464</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>5966</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1310,10 +1306,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>636608</v>
+        <v>636437</v>
       </c>
       <c r="R7" t="n">
-        <v>7014302</v>
+        <v>7014437</v>
       </c>
       <c r="S7" t="n">
         <v>3</v>
@@ -1345,7 +1341,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1355,7 +1351,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1368,21 +1364,6 @@
       <c r="AG7" t="b">
         <v>0</v>
       </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
@@ -1391,19 +1372,19 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Markus Borja, Diego Borja, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016289</t>
+          <t>https://artportalen.se/Sighting/137016298</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>137016306</v>
+        <v>137016289</v>
       </c>
       <c r="B8" t="n">
         <v>79485</v>
@@ -1441,10 +1422,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>636566</v>
+        <v>636608</v>
       </c>
       <c r="R8" t="n">
-        <v>7014366</v>
+        <v>7014302</v>
       </c>
       <c r="S8" t="n">
         <v>3</v>
@@ -1476,7 +1457,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1486,7 +1467,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1528,13 +1509,13 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016306</t>
+          <t>https://artportalen.se/Sighting/137016289</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>137016332</v>
+        <v>137016306</v>
       </c>
       <c r="B9" t="n">
         <v>79485</v>
@@ -1572,13 +1553,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>636603</v>
+        <v>636566</v>
       </c>
       <c r="R9" t="n">
-        <v>7014322</v>
+        <v>7014366</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1607,7 +1588,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1617,7 +1598,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1648,24 +1629,24 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016332</t>
+          <t>https://artportalen.se/Sighting/137016306</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>137016333</v>
+        <v>137016332</v>
       </c>
       <c r="B10" t="n">
         <v>79485</v>
@@ -1703,10 +1684,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>636623</v>
+        <v>636603</v>
       </c>
       <c r="R10" t="n">
-        <v>7014305</v>
+        <v>7014322</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1738,7 +1719,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1748,7 +1729,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1790,13 +1771,13 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016333</t>
+          <t>https://artportalen.se/Sighting/137016332</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>137016335</v>
+        <v>137016333</v>
       </c>
       <c r="B11" t="n">
         <v>79485</v>
@@ -1834,10 +1815,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>636520</v>
+        <v>636623</v>
       </c>
       <c r="R11" t="n">
-        <v>7014374</v>
+        <v>7014305</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1869,7 +1850,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1879,7 +1860,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1921,13 +1902,13 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016335</t>
+          <t>https://artportalen.se/Sighting/137016333</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>137016337</v>
+        <v>137016335</v>
       </c>
       <c r="B12" t="n">
         <v>79485</v>
@@ -1965,10 +1946,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>636463</v>
+        <v>636520</v>
       </c>
       <c r="R12" t="n">
-        <v>7014402</v>
+        <v>7014374</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -2000,7 +1981,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2010,7 +1991,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2052,13 +2033,13 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016337</t>
+          <t>https://artportalen.se/Sighting/137016335</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>137016340</v>
+        <v>137016337</v>
       </c>
       <c r="B13" t="n">
         <v>79485</v>
@@ -2096,10 +2077,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>636419</v>
+        <v>636463</v>
       </c>
       <c r="R13" t="n">
-        <v>7014437</v>
+        <v>7014402</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2131,7 +2112,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2141,7 +2122,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2183,13 +2164,13 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016340</t>
+          <t>https://artportalen.se/Sighting/137016337</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>137016349</v>
+        <v>137016340</v>
       </c>
       <c r="B14" t="n">
         <v>79485</v>
@@ -2227,10 +2208,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>636488</v>
+        <v>636419</v>
       </c>
       <c r="R14" t="n">
-        <v>7014536</v>
+        <v>7014437</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2262,7 +2243,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2272,7 +2253,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2314,13 +2295,13 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016349</t>
+          <t>https://artportalen.se/Sighting/137016340</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>137016350</v>
+        <v>137016349</v>
       </c>
       <c r="B15" t="n">
         <v>79485</v>
@@ -2358,10 +2339,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>636466</v>
+        <v>636488</v>
       </c>
       <c r="R15" t="n">
-        <v>7014464</v>
+        <v>7014536</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2393,7 +2374,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2403,7 +2384,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2445,13 +2426,13 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016350</t>
+          <t>https://artportalen.se/Sighting/137016349</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>137040167</v>
+        <v>137016350</v>
       </c>
       <c r="B16" t="n">
         <v>79485</v>
@@ -2480,16 +2461,19 @@
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Stortannsjön, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>636743</v>
+        <v>636466</v>
       </c>
       <c r="R16" t="n">
-        <v>7014374</v>
+        <v>7014464</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2516,22 +2500,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2540,30 +2524,46 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Vivien Renaut</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Vivien Renaut</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137040167</t>
+          <t>https://artportalen.se/Sighting/137016350</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>137040169</v>
+        <v>137040102</v>
       </c>
       <c r="B17" t="n">
         <v>79485</v>
@@ -2592,19 +2592,22 @@
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Stortannsjön, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>636844</v>
+        <v>636758</v>
       </c>
       <c r="R17" t="n">
-        <v>7014273</v>
+        <v>7014258</v>
       </c>
       <c r="S17" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2633,7 +2636,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>09:08</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2643,7 +2646,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>09:08</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2652,30 +2655,46 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Vivien Renaut</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Vivien Renaut</t>
+          <t>Markus Borja, Ann-Christine Borja, Vivien Renaut</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137040169</t>
+          <t>https://artportalen.se/Sighting/137040102</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>137040181</v>
+        <v>137040133</v>
       </c>
       <c r="B18" t="n">
         <v>79485</v>
@@ -2704,19 +2723,22 @@
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Stortannsjön, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>636605</v>
+        <v>636608</v>
       </c>
       <c r="R18" t="n">
-        <v>7014506</v>
+        <v>7014515</v>
       </c>
       <c r="S18" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2745,7 +2767,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2755,12 +2777,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:28</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Garnlav på tall</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2769,30 +2786,46 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Vivien Renaut</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Vivien Renaut</t>
+          <t>Markus Borja, Ann-Christine Borja, Vivien Renaut</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137040181</t>
+          <t>https://artportalen.se/Sighting/137040133</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>137044055</v>
+        <v>137040161</v>
       </c>
       <c r="B19" t="n">
         <v>79485</v>
@@ -2830,13 +2863,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>636694</v>
+        <v>636549</v>
       </c>
       <c r="R19" t="n">
-        <v>7014252</v>
+        <v>7014491</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2865,7 +2898,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>08:47</t>
+          <t>18:07</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2875,7 +2908,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>08:47</t>
+          <t>18:07</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2906,24 +2939,24 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja, Ann-Christine Borja, Vivien Renaut</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137044055</t>
+          <t>https://artportalen.se/Sighting/137040161</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>137044068</v>
+        <v>137040162</v>
       </c>
       <c r="B20" t="n">
         <v>79485</v>
@@ -2961,13 +2994,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>636901</v>
+        <v>636606</v>
       </c>
       <c r="R20" t="n">
-        <v>7014208</v>
+        <v>7014419</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2996,7 +3029,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3006,7 +3039,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3021,40 +3054,40 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja, Ann-Christine Borja, Vivien Renaut</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137044068</t>
+          <t>https://artportalen.se/Sighting/137040162</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>137044072</v>
+        <v>137040167</v>
       </c>
       <c r="B21" t="n">
         <v>79485</v>
@@ -3083,19 +3116,16 @@
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Stortannsjön, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>636840</v>
+        <v>636743</v>
       </c>
       <c r="R21" t="n">
-        <v>7014233</v>
+        <v>7014374</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -3127,7 +3157,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3137,7 +3167,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3146,90 +3176,71 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Vivien Renaut</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Vivien Renaut</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137044072</t>
+          <t>https://artportalen.se/Sighting/137040167</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>137016334</v>
+        <v>137040169</v>
       </c>
       <c r="B22" t="n">
-        <v>79509</v>
+        <v>79485</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Stortannsjön, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>636591</v>
+        <v>636844</v>
       </c>
       <c r="R22" t="n">
-        <v>7014315</v>
+        <v>7014273</v>
       </c>
       <c r="S22" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3253,22 +3264,22 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3277,90 +3288,71 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Vivien Renaut</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Vivien Renaut</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016334</t>
+          <t>https://artportalen.se/Sighting/137040169</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>137016341</v>
+        <v>137040181</v>
       </c>
       <c r="B23" t="n">
-        <v>79509</v>
+        <v>79485</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Stortannsjön, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>636409</v>
+        <v>636605</v>
       </c>
       <c r="R23" t="n">
-        <v>7014452</v>
+        <v>7014506</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3384,22 +3376,27 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>14:28</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Garnlav på tall</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3408,71 +3405,55 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Vivien Renaut</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Vivien Renaut</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016341</t>
+          <t>https://artportalen.se/Sighting/137040181</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>137016351</v>
+        <v>137044055</v>
       </c>
       <c r="B24" t="n">
-        <v>79509</v>
+        <v>79485</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3485,10 +3466,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>636460</v>
+        <v>636694</v>
       </c>
       <c r="R24" t="n">
-        <v>7014454</v>
+        <v>7014252</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3515,22 +3496,22 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>08:47</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>08:47</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3572,38 +3553,38 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016351</t>
+          <t>https://artportalen.se/Sighting/137044055</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>137044056</v>
+        <v>137044068</v>
       </c>
       <c r="B25" t="n">
-        <v>79509</v>
+        <v>79485</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3616,10 +3597,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>636699</v>
+        <v>636901</v>
       </c>
       <c r="R25" t="n">
-        <v>7014271</v>
+        <v>7014208</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3651,7 +3632,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3661,7 +3642,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3703,54 +3684,57 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137044056</t>
+          <t>https://artportalen.se/Sighting/137044068</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>137016288</v>
+        <v>137044072</v>
       </c>
       <c r="B26" t="n">
-        <v>80104</v>
+        <v>79485</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Stortannsjön, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>636610</v>
+        <v>636840</v>
       </c>
       <c r="R26" t="n">
-        <v>7014307</v>
+        <v>7014233</v>
       </c>
       <c r="S26" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3774,22 +3758,22 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3798,71 +3782,90 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016288</t>
+          <t>https://artportalen.se/Sighting/137044072</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>137016299</v>
+        <v>137016334</v>
       </c>
       <c r="B27" t="n">
-        <v>80104</v>
+        <v>79509</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6453</v>
+        <v>6434</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Stortannsjön, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>636418</v>
+        <v>636591</v>
       </c>
       <c r="R27" t="n">
-        <v>7014453</v>
+        <v>7014315</v>
       </c>
       <c r="S27" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3891,7 +3894,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3901,7 +3904,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3910,71 +3913,90 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016299</t>
+          <t>https://artportalen.se/Sighting/137016334</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>137016303</v>
+        <v>137016341</v>
       </c>
       <c r="B28" t="n">
-        <v>80104</v>
+        <v>79509</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6453</v>
+        <v>6434</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Stortannsjön, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>636499</v>
+        <v>636409</v>
       </c>
       <c r="R28" t="n">
-        <v>7014546</v>
+        <v>7014452</v>
       </c>
       <c r="S28" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -4003,7 +4025,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -4013,7 +4035,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4022,33 +4044,49 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016303</t>
+          <t>https://artportalen.se/Sighting/137016341</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>137016301</v>
+        <v>137016351</v>
       </c>
       <c r="B29" t="n">
-        <v>58005</v>
+        <v>79509</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4056,31 +4094,26 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100049</v>
+        <v>6434</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -4088,13 +4121,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>636482</v>
+        <v>636460</v>
       </c>
       <c r="R29" t="n">
-        <v>7014533</v>
+        <v>7014454</v>
       </c>
       <c r="S29" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4123,7 +4156,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4133,7 +4166,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4142,33 +4175,49 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016301</t>
+          <t>https://artportalen.se/Sighting/137016351</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>137040182</v>
+        <v>137040100</v>
       </c>
       <c r="B30" t="n">
-        <v>58005</v>
+        <v>79509</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4176,31 +4225,26 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
+        <v>6434</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -4208,13 +4252,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>636550</v>
+        <v>636705</v>
       </c>
       <c r="R30" t="n">
-        <v>7014507</v>
+        <v>7014244</v>
       </c>
       <c r="S30" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4243,7 +4287,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4253,12 +4297,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:41</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Färska spår</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4267,65 +4306,76 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Vivien Renaut</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Vivien Renaut</t>
+          <t>Markus Borja, Ann-Christine Borja, Vivien Renaut</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137040182</t>
+          <t>https://artportalen.se/Sighting/137040100</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>137016287</v>
+        <v>137044056</v>
       </c>
       <c r="B31" t="n">
-        <v>58008</v>
+        <v>79509</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>6434</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -4333,13 +4383,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>636606</v>
+        <v>636699</v>
       </c>
       <c r="R31" t="n">
-        <v>7014302</v>
+        <v>7014271</v>
       </c>
       <c r="S31" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4363,27 +4413,22 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>10:34</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Färska och Äldre ringhack på tall</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4392,33 +4437,49 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja, Diego Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016287</t>
+          <t>https://artportalen.se/Sighting/137044056</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>137016290</v>
+        <v>137040105</v>
       </c>
       <c r="B32" t="n">
-        <v>58008</v>
+        <v>79242</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4426,42 +4487,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Stortannsjön, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>636608</v>
+        <v>636730</v>
       </c>
       <c r="R32" t="n">
-        <v>7014302</v>
+        <v>7014286</v>
       </c>
       <c r="S32" t="n">
         <v>3</v>
@@ -4488,27 +4541,22 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>10:54</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4528,22 +4576,22 @@
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja, Diego Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016290</t>
+          <t>https://artportalen.se/Sighting/137040105</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>137016291</v>
+        <v>137040135</v>
       </c>
       <c r="B33" t="n">
-        <v>58008</v>
+        <v>79242</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4551,42 +4599,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Stortannsjön, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>636578</v>
+        <v>636582</v>
       </c>
       <c r="R33" t="n">
-        <v>7014320</v>
+        <v>7014519</v>
       </c>
       <c r="S33" t="n">
         <v>3</v>
@@ -4613,27 +4653,22 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>10:59</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4653,22 +4688,22 @@
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja, Diego Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016291</t>
+          <t>https://artportalen.se/Sighting/137040135</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>137016292</v>
+        <v>137016288</v>
       </c>
       <c r="B34" t="n">
-        <v>58008</v>
+        <v>80104</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4676,42 +4711,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Stortannsjön, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>636501</v>
+        <v>636610</v>
       </c>
       <c r="R34" t="n">
-        <v>7014381</v>
+        <v>7014307</v>
       </c>
       <c r="S34" t="n">
         <v>3</v>
@@ -4743,7 +4770,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4753,12 +4780,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>11:09</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4778,22 +4800,22 @@
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016292</t>
+          <t>https://artportalen.se/Sighting/137016288</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>137016294</v>
+        <v>137016299</v>
       </c>
       <c r="B35" t="n">
-        <v>58008</v>
+        <v>80104</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4801,42 +4823,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Stortannsjön, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>636486</v>
+        <v>636418</v>
       </c>
       <c r="R35" t="n">
-        <v>7014403</v>
+        <v>7014453</v>
       </c>
       <c r="S35" t="n">
         <v>3</v>
@@ -4868,7 +4882,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4878,12 +4892,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:16</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4903,22 +4912,22 @@
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016294</t>
+          <t>https://artportalen.se/Sighting/137016299</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>137016295</v>
+        <v>137016303</v>
       </c>
       <c r="B36" t="n">
-        <v>58008</v>
+        <v>80104</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4926,42 +4935,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Stortannsjön, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>636432</v>
+        <v>636499</v>
       </c>
       <c r="R36" t="n">
-        <v>7014422</v>
+        <v>7014546</v>
       </c>
       <c r="S36" t="n">
         <v>3</v>
@@ -4993,7 +4994,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -5003,12 +5004,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:28</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5028,22 +5024,22 @@
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016295</t>
+          <t>https://artportalen.se/Sighting/137016303</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>137016296</v>
+        <v>137040101</v>
       </c>
       <c r="B37" t="n">
-        <v>58008</v>
+        <v>80104</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5051,42 +5047,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Stortannsjön, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>636424</v>
+        <v>636731</v>
       </c>
       <c r="R37" t="n">
-        <v>7014437</v>
+        <v>7014243</v>
       </c>
       <c r="S37" t="n">
         <v>3</v>
@@ -5113,27 +5101,22 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>09:05</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>11:30</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack på tall</t>
+          <t>09:05</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5153,22 +5136,22 @@
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016296</t>
+          <t>https://artportalen.se/Sighting/137040101</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>137016297</v>
+        <v>137040104</v>
       </c>
       <c r="B38" t="n">
-        <v>58008</v>
+        <v>80104</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5176,42 +5159,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Stortannsjön, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>636448</v>
+        <v>636746</v>
       </c>
       <c r="R38" t="n">
-        <v>7014424</v>
+        <v>7014291</v>
       </c>
       <c r="S38" t="n">
         <v>3</v>
@@ -5238,27 +5213,22 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>11:35</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5278,54 +5248,49 @@
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016297</t>
+          <t>https://artportalen.se/Sighting/137040104</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>137016300</v>
+        <v>137040108</v>
       </c>
       <c r="B39" t="n">
-        <v>58008</v>
+        <v>80494</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>6456</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -5333,13 +5298,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>636398</v>
+        <v>636817</v>
       </c>
       <c r="R39" t="n">
-        <v>7014509</v>
+        <v>7014280</v>
       </c>
       <c r="S39" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5363,27 +5328,22 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>11:46</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5392,8 +5352,24 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ39" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK39" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO39" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
@@ -5403,54 +5379,49 @@
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja</t>
+          <t>Markus Borja, Ann-Christine Borja, Vivien Renaut</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016300</t>
+          <t>https://artportalen.se/Sighting/137040108</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>137016304</v>
+        <v>137040110</v>
       </c>
       <c r="B40" t="n">
-        <v>58008</v>
+        <v>80494</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>6456</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -5458,10 +5429,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>636466</v>
+        <v>636815</v>
       </c>
       <c r="R40" t="n">
-        <v>7014462</v>
+        <v>7014278</v>
       </c>
       <c r="S40" t="n">
         <v>3</v>
@@ -5488,27 +5459,22 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>12:24</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5517,8 +5483,24 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ40" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK40" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO40" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
@@ -5528,54 +5510,49 @@
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja, Diego Borja</t>
+          <t>Markus Borja, Ann-Christine Borja, Vivien Renaut</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016304</t>
+          <t>https://artportalen.se/Sighting/137040110</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>137016307</v>
+        <v>137040111</v>
       </c>
       <c r="B41" t="n">
-        <v>58008</v>
+        <v>80494</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>6456</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -5583,13 +5560,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>636566</v>
+        <v>636803</v>
       </c>
       <c r="R41" t="n">
-        <v>7014367</v>
+        <v>7014259</v>
       </c>
       <c r="S41" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5613,27 +5590,22 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>12:35</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5642,8 +5614,24 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
@@ -5653,39 +5641,39 @@
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Markus Borja, Ann-Christine Borja, Vivien Renaut</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016307</t>
+          <t>https://artportalen.se/Sighting/137040111</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>137016344</v>
+        <v>137016301</v>
       </c>
       <c r="B42" t="n">
-        <v>58008</v>
+        <v>58005</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -5708,13 +5696,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>636392</v>
+        <v>636482</v>
       </c>
       <c r="R42" t="n">
-        <v>7014473</v>
+        <v>7014533</v>
       </c>
       <c r="S42" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5743,7 +5731,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5753,12 +5741,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>11:50</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall.</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5773,49 +5756,49 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja, Markus Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016344</t>
+          <t>https://artportalen.se/Sighting/137016301</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>137040177</v>
+        <v>137040182</v>
       </c>
       <c r="B43" t="n">
-        <v>58169</v>
+        <v>58005</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5823,7 +5806,7 @@
       <c r="L43" t="inlineStr"/>
       <c r="M43" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N43" t="inlineStr"/>
@@ -5833,13 +5816,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>636811</v>
+        <v>636550</v>
       </c>
       <c r="R43" t="n">
-        <v>7014284</v>
+        <v>7014507</v>
       </c>
       <c r="S43" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5868,7 +5851,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5878,12 +5861,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Läte</t>
+          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5909,52 +5892,48 @@
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137040177</t>
+          <t>https://artportalen.se/Sighting/137040182</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>137040164</v>
+        <v>137016287</v>
       </c>
       <c r="B44" t="n">
-        <v>99372</v>
+        <v>58008</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -5962,10 +5941,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>636776</v>
+        <v>636606</v>
       </c>
       <c r="R44" t="n">
-        <v>7014278</v>
+        <v>7014302</v>
       </c>
       <c r="S44" t="n">
         <v>3</v>
@@ -5992,22 +5971,27 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>09:05</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>09:05</t>
+          <t>10:34</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Färska och Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6016,70 +6000,65 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Vivien Renaut</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Vivien Renaut</t>
+          <t>Markus Borja, Ann-Christine Borja, Diego Borja</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137040164</t>
+          <t>https://artportalen.se/Sighting/137016287</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>137040166</v>
+        <v>137016290</v>
       </c>
       <c r="B45" t="n">
-        <v>99372</v>
+        <v>58008</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>115</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -6087,10 +6066,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>636782</v>
+        <v>636608</v>
       </c>
       <c r="R45" t="n">
-        <v>7014300</v>
+        <v>7014302</v>
       </c>
       <c r="S45" t="n">
         <v>3</v>
@@ -6117,22 +6096,27 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>10:54</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6141,70 +6125,65 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Vivien Renaut</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Vivien Renaut</t>
+          <t>Markus Borja, Ann-Christine Borja, Diego Borja</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137040166</t>
+          <t>https://artportalen.se/Sighting/137016290</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>137040168</v>
+        <v>137016291</v>
       </c>
       <c r="B46" t="n">
-        <v>99372</v>
+        <v>58008</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
@@ -6212,10 +6191,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>636758</v>
+        <v>636578</v>
       </c>
       <c r="R46" t="n">
-        <v>7014368</v>
+        <v>7014320</v>
       </c>
       <c r="S46" t="n">
         <v>3</v>
@@ -6242,22 +6221,27 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>10:59</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6266,70 +6250,65 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Vivien Renaut</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Vivien Renaut</t>
+          <t>Markus Borja, Ann-Christine Borja, Diego Borja</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137040168</t>
+          <t>https://artportalen.se/Sighting/137016291</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>137040189</v>
+        <v>137016292</v>
       </c>
       <c r="B47" t="n">
-        <v>99372</v>
+        <v>58008</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
@@ -6337,13 +6316,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>636424</v>
+        <v>636501</v>
       </c>
       <c r="R47" t="n">
-        <v>7014610</v>
+        <v>7014381</v>
       </c>
       <c r="S47" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6367,22 +6346,27 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>11:09</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6391,70 +6375,65 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Vivien Renaut</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Vivien Renaut</t>
+          <t>Markus Borja, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137040189</t>
+          <t>https://artportalen.se/Sighting/137016292</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>137044057</v>
+        <v>137016294</v>
       </c>
       <c r="B48" t="n">
-        <v>99372</v>
+        <v>58008</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -6462,13 +6441,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>636762</v>
+        <v>636486</v>
       </c>
       <c r="R48" t="n">
-        <v>7014263</v>
+        <v>7014403</v>
       </c>
       <c r="S48" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6492,22 +6471,27 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>11:16</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6516,70 +6500,65 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja, Markus Borja, Vivien Renaut</t>
+          <t>Markus Borja, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137044057</t>
+          <t>https://artportalen.se/Sighting/137016294</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>137044059</v>
+        <v>137016295</v>
       </c>
       <c r="B49" t="n">
-        <v>99372</v>
+        <v>58008</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>105</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
@@ -6587,13 +6566,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>636736</v>
+        <v>636432</v>
       </c>
       <c r="R49" t="n">
-        <v>7014341</v>
+        <v>7014422</v>
       </c>
       <c r="S49" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6617,22 +6596,27 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>11:28</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6641,70 +6625,65 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja, Markus Borja, Vivien Renaut</t>
+          <t>Markus Borja, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137044059</t>
+          <t>https://artportalen.se/Sighting/137016295</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>137044060</v>
+        <v>137016296</v>
       </c>
       <c r="B50" t="n">
-        <v>99372</v>
+        <v>58008</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>159</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
@@ -6712,13 +6691,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>636760</v>
+        <v>636424</v>
       </c>
       <c r="R50" t="n">
-        <v>7014309</v>
+        <v>7014437</v>
       </c>
       <c r="S50" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6742,22 +6721,27 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6766,70 +6750,65 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja, Markus Borja, Vivien Renaut</t>
+          <t>Markus Borja, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137044060</t>
+          <t>https://artportalen.se/Sighting/137016296</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>137044061</v>
+        <v>137016297</v>
       </c>
       <c r="B51" t="n">
-        <v>99372</v>
+        <v>58008</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
@@ -6837,13 +6816,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>636781</v>
+        <v>636448</v>
       </c>
       <c r="R51" t="n">
-        <v>7014323</v>
+        <v>7014424</v>
       </c>
       <c r="S51" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6867,22 +6846,27 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>11:35</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6891,70 +6875,65 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja, Markus Borja, Vivien Renaut</t>
+          <t>Markus Borja, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137044061</t>
+          <t>https://artportalen.se/Sighting/137016297</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>137044062</v>
+        <v>137016300</v>
       </c>
       <c r="B52" t="n">
-        <v>99372</v>
+        <v>58008</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>117</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
@@ -6962,13 +6941,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>636772</v>
+        <v>636398</v>
       </c>
       <c r="R52" t="n">
-        <v>7014326</v>
+        <v>7014509</v>
       </c>
       <c r="S52" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6992,22 +6971,27 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>11:46</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -7016,70 +7000,65 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja, Markus Borja, Vivien Renaut</t>
+          <t>Markus Borja, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137044062</t>
+          <t>https://artportalen.se/Sighting/137016300</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>137044064</v>
+        <v>137016304</v>
       </c>
       <c r="B53" t="n">
-        <v>99372</v>
+        <v>58008</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
@@ -7087,13 +7066,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>636806</v>
+        <v>636466</v>
       </c>
       <c r="R53" t="n">
-        <v>7014282</v>
+        <v>7014462</v>
       </c>
       <c r="S53" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -7117,22 +7096,27 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>12:24</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -7141,70 +7125,65 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja, Markus Borja, Vivien Renaut</t>
+          <t>Markus Borja, Ann-Christine Borja, Diego Borja</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137044064</t>
+          <t>https://artportalen.se/Sighting/137016304</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>137044080</v>
+        <v>137016307</v>
       </c>
       <c r="B54" t="n">
-        <v>99372</v>
+        <v>58008</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
@@ -7212,13 +7191,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>636598</v>
+        <v>636566</v>
       </c>
       <c r="R54" t="n">
-        <v>7014517</v>
+        <v>7014367</v>
       </c>
       <c r="S54" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -7242,22 +7221,27 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>12:35</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7266,34 +7250,33 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja, Markus Borja, Vivien Renaut</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137044080</t>
+          <t>https://artportalen.se/Sighting/137016307</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>137016336</v>
+        <v>137016344</v>
       </c>
       <c r="B55" t="n">
-        <v>79508</v>
+        <v>58008</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7301,26 +7284,31 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>260591</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
@@ -7328,10 +7316,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>636512</v>
+        <v>636392</v>
       </c>
       <c r="R55" t="n">
-        <v>7014375</v>
+        <v>7014473</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -7363,7 +7351,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -7373,7 +7361,12 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall.</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7382,24 +7375,8 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ55" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK55" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO55" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
@@ -7415,16 +7392,16 @@
       <c r="AY55" t="inlineStr"/>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016336</t>
+          <t>https://artportalen.se/Sighting/137016344</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>137016339</v>
+        <v>137040097</v>
       </c>
       <c r="B56" t="n">
-        <v>79508</v>
+        <v>58008</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7432,26 +7409,31 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>260591</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
@@ -7459,13 +7441,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>636457</v>
+        <v>636710</v>
       </c>
       <c r="R56" t="n">
-        <v>7014405</v>
+        <v>7014234</v>
       </c>
       <c r="S56" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -7489,22 +7471,27 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>08:39</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>08:39</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7513,49 +7500,33 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
-      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ56" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK56" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO56" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja, Ann-Christine Borja, Vivien Renaut</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016339</t>
+          <t>https://artportalen.se/Sighting/137040097</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>137016342</v>
+        <v>137040106</v>
       </c>
       <c r="B57" t="n">
-        <v>79508</v>
+        <v>58169</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7563,40 +7534,53 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>260591</v>
+        <v>103021</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="K57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Stortannsjön, Ång</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>636417</v>
+        <v>636783</v>
       </c>
       <c r="R57" t="n">
-        <v>7014452</v>
+        <v>7014328</v>
       </c>
       <c r="S57" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7620,22 +7604,22 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7644,49 +7628,33 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ57" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK57" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO57" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja, Vivien Renaut, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016342</t>
+          <t>https://artportalen.se/Sighting/137040106</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>137016345</v>
+        <v>137040109</v>
       </c>
       <c r="B58" t="n">
-        <v>79508</v>
+        <v>58169</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7694,26 +7662,31 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>260591</v>
+        <v>103021</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
@@ -7721,13 +7694,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>636407</v>
+        <v>636808</v>
       </c>
       <c r="R58" t="n">
-        <v>7014480</v>
+        <v>7014272</v>
       </c>
       <c r="S58" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7751,22 +7724,22 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7775,49 +7748,33 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
-      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ58" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK58" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO58" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja, Vivien Renaut</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016345</t>
+          <t>https://artportalen.se/Sighting/137040109</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>137016346</v>
+        <v>137040177</v>
       </c>
       <c r="B59" t="n">
-        <v>79508</v>
+        <v>58169</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7825,28 +7782,29 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>260591</v>
+        <v>103021</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N59" t="inlineStr"/>
@@ -7856,13 +7814,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>636450</v>
+        <v>636811</v>
       </c>
       <c r="R59" t="n">
-        <v>7014535</v>
+        <v>7014284</v>
       </c>
       <c r="S59" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7886,22 +7844,27 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>12:13</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Läte</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7910,80 +7873,69 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
-      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ59" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK59" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO59" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Vivien Renaut</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Vivien Renaut</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016346</t>
+          <t>https://artportalen.se/Sighting/137040177</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>137016348</v>
+        <v>137040107</v>
       </c>
       <c r="B60" t="n">
-        <v>79508</v>
+        <v>99372</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>260591</v>
+        <v>220787</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
       <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
@@ -7991,13 +7943,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>636479</v>
+        <v>636807</v>
       </c>
       <c r="R60" t="n">
-        <v>7014523</v>
+        <v>7014295</v>
       </c>
       <c r="S60" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -8021,22 +7973,22 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -8049,72 +8001,66 @@
       <c r="AG60" t="b">
         <v>0</v>
       </c>
-      <c r="AJ60" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK60" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO60" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja, Ann-Christine Borja, Vivien Renaut</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016348</t>
+          <t>https://artportalen.se/Sighting/137040107</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>137016353</v>
+        <v>137040121</v>
       </c>
       <c r="B61" t="n">
-        <v>79508</v>
+        <v>99372</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>260591</v>
+        <v>220787</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
       <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
@@ -8122,13 +8068,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>636460</v>
+        <v>636854</v>
       </c>
       <c r="R61" t="n">
-        <v>7014451</v>
+        <v>7014229</v>
       </c>
       <c r="S61" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -8152,22 +8098,22 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -8180,76 +8126,66 @@
       <c r="AG61" t="b">
         <v>0</v>
       </c>
-      <c r="AJ61" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK61" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO61" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja, Ann-Christine Borja, Vivien Renaut</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016353</t>
+          <t>https://artportalen.se/Sighting/137040121</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>137044071</v>
+        <v>137040123</v>
       </c>
       <c r="B62" t="n">
-        <v>79508</v>
+        <v>99372</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>260591</v>
+        <v>220787</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr"/>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
       <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
@@ -8257,13 +8193,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>636845</v>
+        <v>636843</v>
       </c>
       <c r="R62" t="n">
-        <v>7014233</v>
+        <v>7014251</v>
       </c>
       <c r="S62" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -8292,7 +8228,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -8302,7 +8238,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8315,34 +8251,3165 @@
       <c r="AG62" t="b">
         <v>0</v>
       </c>
-      <c r="AJ62" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK62" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO62" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja, Ann-Christine Borja, Vivien Renaut</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
       <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137040123</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>137040138</v>
+      </c>
+      <c r="B63" t="n">
+        <v>99372</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Stortannsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>636527</v>
+      </c>
+      <c r="R63" t="n">
+        <v>7014608</v>
+      </c>
+      <c r="S63" t="n">
+        <v>4</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Överlännäs</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>15:02</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>15:02</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF63" t="inlineStr"/>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Markus Borja, Ann-Christine Borja, Vivien Renaut</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137040138</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>137040160</v>
+      </c>
+      <c r="B64" t="n">
+        <v>99372</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="N64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Stortannsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>636474</v>
+      </c>
+      <c r="R64" t="n">
+        <v>7014608</v>
+      </c>
+      <c r="S64" t="n">
+        <v>3</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Överlännäs</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF64" t="inlineStr"/>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Markus Borja, Ann-Christine Borja, Vivien Renaut</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137040160</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>137040163</v>
+      </c>
+      <c r="B65" t="n">
+        <v>99372</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Stortannsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>636595</v>
+      </c>
+      <c r="R65" t="n">
+        <v>7014422</v>
+      </c>
+      <c r="S65" t="n">
+        <v>3</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Överlännäs</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>18:17</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>18:17</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF65" t="inlineStr"/>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Markus Borja, Ann-Christine Borja, Vivien Renaut</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137040163</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>137040164</v>
+      </c>
+      <c r="B66" t="n">
+        <v>99372</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="N66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Stortannsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>636776</v>
+      </c>
+      <c r="R66" t="n">
+        <v>7014278</v>
+      </c>
+      <c r="S66" t="n">
+        <v>3</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Överlännäs</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>09:05</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>09:05</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF66" t="inlineStr"/>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Vivien Renaut</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Vivien Renaut</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137040164</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>137040166</v>
+      </c>
+      <c r="B67" t="n">
+        <v>99372</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="N67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Stortannsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>636782</v>
+      </c>
+      <c r="R67" t="n">
+        <v>7014300</v>
+      </c>
+      <c r="S67" t="n">
+        <v>3</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Överlännäs</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF67" t="inlineStr"/>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Vivien Renaut</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Vivien Renaut</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137040166</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>137040168</v>
+      </c>
+      <c r="B68" t="n">
+        <v>99372</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="N68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Stortannsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>636758</v>
+      </c>
+      <c r="R68" t="n">
+        <v>7014368</v>
+      </c>
+      <c r="S68" t="n">
+        <v>3</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Överlännäs</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>09:42</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>09:42</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF68" t="inlineStr"/>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Vivien Renaut</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Vivien Renaut</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137040168</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>137040189</v>
+      </c>
+      <c r="B69" t="n">
+        <v>99372</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="N69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Stortannsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>636424</v>
+      </c>
+      <c r="R69" t="n">
+        <v>7014610</v>
+      </c>
+      <c r="S69" t="n">
+        <v>15</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Överlännäs</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>17:52</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>17:52</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF69" t="inlineStr"/>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Vivien Renaut</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Vivien Renaut</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137040189</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>137044057</v>
+      </c>
+      <c r="B70" t="n">
+        <v>99372</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="N70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Stortannsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>636762</v>
+      </c>
+      <c r="R70" t="n">
+        <v>7014263</v>
+      </c>
+      <c r="S70" t="n">
+        <v>5</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Överlännäs</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF70" t="inlineStr"/>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja, Markus Borja, Vivien Renaut</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137044057</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>137044059</v>
+      </c>
+      <c r="B71" t="n">
+        <v>99372</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="N71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Stortannsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>636736</v>
+      </c>
+      <c r="R71" t="n">
+        <v>7014341</v>
+      </c>
+      <c r="S71" t="n">
+        <v>5</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Överlännäs</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>09:41</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>09:41</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF71" t="inlineStr"/>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja, Markus Borja, Vivien Renaut</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137044059</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>137044060</v>
+      </c>
+      <c r="B72" t="n">
+        <v>99372</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>159</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
+      <c r="N72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Stortannsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>636760</v>
+      </c>
+      <c r="R72" t="n">
+        <v>7014309</v>
+      </c>
+      <c r="S72" t="n">
+        <v>5</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Överlännäs</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>10:02</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>10:02</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF72" t="inlineStr"/>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja, Markus Borja, Vivien Renaut</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137044060</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>137044061</v>
+      </c>
+      <c r="B73" t="n">
+        <v>99372</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
+      <c r="N73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Stortannsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>636781</v>
+      </c>
+      <c r="R73" t="n">
+        <v>7014323</v>
+      </c>
+      <c r="S73" t="n">
+        <v>5</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Överlännäs</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF73" t="inlineStr"/>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja, Markus Borja, Vivien Renaut</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137044061</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>137044062</v>
+      </c>
+      <c r="B74" t="n">
+        <v>99372</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>117</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr"/>
+      <c r="N74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Stortannsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>636772</v>
+      </c>
+      <c r="R74" t="n">
+        <v>7014326</v>
+      </c>
+      <c r="S74" t="n">
+        <v>5</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Överlännäs</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>10:26</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>10:26</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF74" t="inlineStr"/>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja, Markus Borja, Vivien Renaut</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137044062</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>137044064</v>
+      </c>
+      <c r="B75" t="n">
+        <v>99372</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr"/>
+      <c r="N75" t="inlineStr"/>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Stortannsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>636806</v>
+      </c>
+      <c r="R75" t="n">
+        <v>7014282</v>
+      </c>
+      <c r="S75" t="n">
+        <v>5</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Överlännäs</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>10:48</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>10:48</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="inlineStr"/>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja, Markus Borja, Vivien Renaut</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137044064</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>137044080</v>
+      </c>
+      <c r="B76" t="n">
+        <v>99372</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr"/>
+      <c r="N76" t="inlineStr"/>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Stortannsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>636598</v>
+      </c>
+      <c r="R76" t="n">
+        <v>7014517</v>
+      </c>
+      <c r="S76" t="n">
+        <v>5</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Överlännäs</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>14:32</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>14:32</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF76" t="inlineStr"/>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja, Markus Borja, Vivien Renaut</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137044080</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>137040134</v>
+      </c>
+      <c r="B77" t="n">
+        <v>79243</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Stortannsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>636580</v>
+      </c>
+      <c r="R77" t="n">
+        <v>7014518</v>
+      </c>
+      <c r="S77" t="n">
+        <v>3</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Överlännäs</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>14:37</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>14:37</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137040134</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>137040136</v>
+      </c>
+      <c r="B78" t="n">
+        <v>79243</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Stortannsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>636552</v>
+      </c>
+      <c r="R78" t="n">
+        <v>7014536</v>
+      </c>
+      <c r="S78" t="n">
+        <v>3</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Överlännäs</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>14:47</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>14:47</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137040136</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>137016336</v>
+      </c>
+      <c r="B79" t="n">
+        <v>79508</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="J79" t="inlineStr"/>
+      <c r="K79" t="inlineStr"/>
+      <c r="N79" t="inlineStr"/>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Stortannsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>636512</v>
+      </c>
+      <c r="R79" t="n">
+        <v>7014375</v>
+      </c>
+      <c r="S79" t="n">
+        <v>5</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Överlännäs</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>11:12</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>11:12</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF79" t="inlineStr"/>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ79" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK79" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO79" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja, Markus Borja</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137016336</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>137016339</v>
+      </c>
+      <c r="B80" t="n">
+        <v>79508</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="J80" t="inlineStr"/>
+      <c r="K80" t="inlineStr"/>
+      <c r="N80" t="inlineStr"/>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Stortannsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>636457</v>
+      </c>
+      <c r="R80" t="n">
+        <v>7014405</v>
+      </c>
+      <c r="S80" t="n">
+        <v>5</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Överlännäs</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>11:22</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="AB80" t="inlineStr">
+        <is>
+          <t>11:22</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF80" t="inlineStr"/>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ80" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK80" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO80" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137016339</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>137016342</v>
+      </c>
+      <c r="B81" t="n">
+        <v>79508</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="J81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
+      <c r="N81" t="inlineStr"/>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Stortannsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>636417</v>
+      </c>
+      <c r="R81" t="n">
+        <v>7014452</v>
+      </c>
+      <c r="S81" t="n">
+        <v>5</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Överlännäs</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF81" t="inlineStr"/>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ81" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK81" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO81" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137016342</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>137016345</v>
+      </c>
+      <c r="B82" t="n">
+        <v>79508</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="J82" t="inlineStr"/>
+      <c r="K82" t="inlineStr"/>
+      <c r="N82" t="inlineStr"/>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Stortannsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>636407</v>
+      </c>
+      <c r="R82" t="n">
+        <v>7014480</v>
+      </c>
+      <c r="S82" t="n">
+        <v>5</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Överlännäs</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="Z82" t="inlineStr">
+        <is>
+          <t>11:59</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="AB82" t="inlineStr">
+        <is>
+          <t>11:59</t>
+        </is>
+      </c>
+      <c r="AD82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF82" t="inlineStr"/>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ82" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK82" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO82" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137016345</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>137016346</v>
+      </c>
+      <c r="B83" t="n">
+        <v>79508</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="J83" t="inlineStr"/>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr"/>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Stortannsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>636450</v>
+      </c>
+      <c r="R83" t="n">
+        <v>7014535</v>
+      </c>
+      <c r="S83" t="n">
+        <v>5</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Överlännäs</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="Z83" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="AB83" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="AD83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF83" t="inlineStr"/>
+      <c r="AG83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ83" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK83" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO83" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT83" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137016346</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>137016348</v>
+      </c>
+      <c r="B84" t="n">
+        <v>79508</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="J84" t="inlineStr"/>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr"/>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Stortannsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q84" t="n">
+        <v>636479</v>
+      </c>
+      <c r="R84" t="n">
+        <v>7014523</v>
+      </c>
+      <c r="S84" t="n">
+        <v>5</v>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>Överlännäs</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="Z84" t="inlineStr">
+        <is>
+          <t>12:09</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="AB84" t="inlineStr">
+        <is>
+          <t>12:09</t>
+        </is>
+      </c>
+      <c r="AD84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF84" t="inlineStr"/>
+      <c r="AG84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ84" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK84" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO84" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT84" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137016348</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>137016353</v>
+      </c>
+      <c r="B85" t="n">
+        <v>79508</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
+      <c r="J85" t="inlineStr"/>
+      <c r="K85" t="inlineStr"/>
+      <c r="N85" t="inlineStr"/>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>Stortannsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q85" t="n">
+        <v>636460</v>
+      </c>
+      <c r="R85" t="n">
+        <v>7014451</v>
+      </c>
+      <c r="S85" t="n">
+        <v>5</v>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>Överlännäs</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="Z85" t="inlineStr">
+        <is>
+          <t>12:28</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="AB85" t="inlineStr">
+        <is>
+          <t>12:28</t>
+        </is>
+      </c>
+      <c r="AD85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF85" t="inlineStr"/>
+      <c r="AG85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ85" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK85" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO85" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT85" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AX85" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137016353</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>137040099</v>
+      </c>
+      <c r="B86" t="n">
+        <v>79508</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>Stortannsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q86" t="n">
+        <v>636705</v>
+      </c>
+      <c r="R86" t="n">
+        <v>7014243</v>
+      </c>
+      <c r="S86" t="n">
+        <v>3</v>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>Överlännäs</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="Z86" t="inlineStr">
+        <is>
+          <t>08:49</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="AB86" t="inlineStr">
+        <is>
+          <t>08:49</t>
+        </is>
+      </c>
+      <c r="AD86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT86" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>Markus Borja, Ann-Christine Borja, Vivien Renaut</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137040099</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>137044071</v>
+      </c>
+      <c r="B87" t="n">
+        <v>79508</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
+      <c r="J87" t="inlineStr"/>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr"/>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>Stortannsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q87" t="n">
+        <v>636845</v>
+      </c>
+      <c r="R87" t="n">
+        <v>7014233</v>
+      </c>
+      <c r="S87" t="n">
+        <v>5</v>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>Överlännäs</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="Z87" t="inlineStr">
+        <is>
+          <t>12:09</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="AB87" t="inlineStr">
+        <is>
+          <t>12:09</t>
+        </is>
+      </c>
+      <c r="AD87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF87" t="inlineStr"/>
+      <c r="AG87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ87" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK87" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO87" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT87" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AX87" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/137044071</t>
         </is>
@@ -8411,6 +11478,31 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 25855-2025 artfynd.xlsx
+++ b/artfynd/A 25855-2025 artfynd.xlsx
@@ -2682,7 +2682,7 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja, Vivien Renaut</t>
+          <t>Markus Borja, Vivien Renaut, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2813,7 +2813,7 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja, Vivien Renaut</t>
+          <t>Markus Borja, Vivien Renaut, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2944,7 +2944,7 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja, Vivien Renaut</t>
+          <t>Markus Borja, Vivien Renaut, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -3075,7 +3075,7 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja, Vivien Renaut</t>
+          <t>Markus Borja, Vivien Renaut, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -4333,7 +4333,7 @@
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja, Vivien Renaut</t>
+          <t>Markus Borja, Vivien Renaut, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
@@ -5379,7 +5379,7 @@
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja, Vivien Renaut</t>
+          <t>Markus Borja, Vivien Renaut, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
@@ -5510,7 +5510,7 @@
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja, Vivien Renaut</t>
+          <t>Markus Borja, Vivien Renaut, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
@@ -5641,7 +5641,7 @@
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja, Vivien Renaut</t>
+          <t>Markus Borja, Vivien Renaut, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
@@ -7511,7 +7511,7 @@
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja, Vivien Renaut</t>
+          <t>Markus Borja, Vivien Renaut, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
@@ -7639,7 +7639,7 @@
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Markus Borja, Vivien Renaut, Ann-Christine Borja</t>
+          <t>Markus Borja, Ann-Christine Borja, Vivien Renaut</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
@@ -7899,7 +7899,7 @@
         <v>137040107</v>
       </c>
       <c r="B60" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -8009,7 +8009,7 @@
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja, Vivien Renaut</t>
+          <t>Markus Borja, Vivien Renaut, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
@@ -8024,7 +8024,7 @@
         <v>137040121</v>
       </c>
       <c r="B61" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -8134,7 +8134,7 @@
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja, Vivien Renaut</t>
+          <t>Markus Borja, Vivien Renaut, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
@@ -8149,7 +8149,7 @@
         <v>137040123</v>
       </c>
       <c r="B62" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -8259,7 +8259,7 @@
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja, Vivien Renaut</t>
+          <t>Markus Borja, Vivien Renaut, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
@@ -8274,7 +8274,7 @@
         <v>137040138</v>
       </c>
       <c r="B63" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8384,7 +8384,7 @@
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja, Vivien Renaut</t>
+          <t>Markus Borja, Vivien Renaut, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
@@ -8399,7 +8399,7 @@
         <v>137040160</v>
       </c>
       <c r="B64" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8509,7 +8509,7 @@
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja, Vivien Renaut</t>
+          <t>Markus Borja, Vivien Renaut, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
@@ -8524,7 +8524,7 @@
         <v>137040163</v>
       </c>
       <c r="B65" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8634,7 +8634,7 @@
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja, Vivien Renaut</t>
+          <t>Markus Borja, Vivien Renaut, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
@@ -8649,7 +8649,7 @@
         <v>137040164</v>
       </c>
       <c r="B66" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8774,7 +8774,7 @@
         <v>137040166</v>
       </c>
       <c r="B67" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8899,7 +8899,7 @@
         <v>137040168</v>
       </c>
       <c r="B68" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -9024,7 +9024,7 @@
         <v>137040189</v>
       </c>
       <c r="B69" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -9149,7 +9149,7 @@
         <v>137044057</v>
       </c>
       <c r="B70" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -9274,7 +9274,7 @@
         <v>137044059</v>
       </c>
       <c r="B71" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9399,7 +9399,7 @@
         <v>137044060</v>
       </c>
       <c r="B72" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9524,7 +9524,7 @@
         <v>137044061</v>
       </c>
       <c r="B73" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9649,7 +9649,7 @@
         <v>137044062</v>
       </c>
       <c r="B74" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9774,7 +9774,7 @@
         <v>137044064</v>
       </c>
       <c r="B75" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9899,7 +9899,7 @@
         <v>137044080</v>
       </c>
       <c r="B76" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -11270,7 +11270,7 @@
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja, Vivien Renaut</t>
+          <t>Markus Borja, Vivien Renaut, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>

--- a/artfynd/A 25855-2025 artfynd.xlsx
+++ b/artfynd/A 25855-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137044063</v>
       </c>
       <c r="B2" t="n">
-        <v>92399</v>
+        <v>92401</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -814,7 +814,7 @@
         <v>137040165</v>
       </c>
       <c r="B3" t="n">
-        <v>92961</v>
+        <v>92963</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -931,7 +931,7 @@
         <v>137016354</v>
       </c>
       <c r="B4" t="n">
-        <v>93442</v>
+        <v>93444</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1047,7 +1047,7 @@
         <v>137016293</v>
       </c>
       <c r="B5" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1159,7 +1159,7 @@
         <v>137040122</v>
       </c>
       <c r="B6" t="n">
-        <v>92091</v>
+        <v>92093</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1271,7 +1271,7 @@
         <v>137016298</v>
       </c>
       <c r="B7" t="n">
-        <v>93464</v>
+        <v>93466</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1387,7 +1387,7 @@
         <v>137016289</v>
       </c>
       <c r="B8" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1518,7 +1518,7 @@
         <v>137016306</v>
       </c>
       <c r="B9" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1649,7 +1649,7 @@
         <v>137016332</v>
       </c>
       <c r="B10" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1780,7 +1780,7 @@
         <v>137016333</v>
       </c>
       <c r="B11" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1911,7 +1911,7 @@
         <v>137016335</v>
       </c>
       <c r="B12" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2042,7 +2042,7 @@
         <v>137016337</v>
       </c>
       <c r="B13" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2173,7 +2173,7 @@
         <v>137016340</v>
       </c>
       <c r="B14" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2304,7 +2304,7 @@
         <v>137016349</v>
       </c>
       <c r="B15" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2435,7 +2435,7 @@
         <v>137016350</v>
       </c>
       <c r="B16" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2566,7 +2566,7 @@
         <v>137040102</v>
       </c>
       <c r="B17" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2697,7 +2697,7 @@
         <v>137040133</v>
       </c>
       <c r="B18" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2828,7 +2828,7 @@
         <v>137040161</v>
       </c>
       <c r="B19" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2959,7 +2959,7 @@
         <v>137040162</v>
       </c>
       <c r="B20" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3090,7 +3090,7 @@
         <v>137040167</v>
       </c>
       <c r="B21" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3202,7 +3202,7 @@
         <v>137040169</v>
       </c>
       <c r="B22" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3314,7 +3314,7 @@
         <v>137040181</v>
       </c>
       <c r="B23" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3431,7 +3431,7 @@
         <v>137044055</v>
       </c>
       <c r="B24" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3562,7 +3562,7 @@
         <v>137044068</v>
       </c>
       <c r="B25" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3693,7 +3693,7 @@
         <v>137044072</v>
       </c>
       <c r="B26" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3824,7 +3824,7 @@
         <v>137016334</v>
       </c>
       <c r="B27" t="n">
-        <v>79509</v>
+        <v>79512</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3955,7 +3955,7 @@
         <v>137016341</v>
       </c>
       <c r="B28" t="n">
-        <v>79509</v>
+        <v>79512</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4086,7 +4086,7 @@
         <v>137016351</v>
       </c>
       <c r="B29" t="n">
-        <v>79509</v>
+        <v>79512</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4217,7 +4217,7 @@
         <v>137040100</v>
       </c>
       <c r="B30" t="n">
-        <v>79509</v>
+        <v>79512</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4348,7 +4348,7 @@
         <v>137044056</v>
       </c>
       <c r="B31" t="n">
-        <v>79509</v>
+        <v>79512</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4479,7 +4479,7 @@
         <v>137040105</v>
       </c>
       <c r="B32" t="n">
-        <v>79242</v>
+        <v>79245</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4591,7 +4591,7 @@
         <v>137040135</v>
       </c>
       <c r="B33" t="n">
-        <v>79242</v>
+        <v>79245</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4703,7 +4703,7 @@
         <v>137016288</v>
       </c>
       <c r="B34" t="n">
-        <v>80104</v>
+        <v>80107</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4815,7 +4815,7 @@
         <v>137016299</v>
       </c>
       <c r="B35" t="n">
-        <v>80104</v>
+        <v>80107</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4927,7 +4927,7 @@
         <v>137016303</v>
       </c>
       <c r="B36" t="n">
-        <v>80104</v>
+        <v>80107</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5039,7 +5039,7 @@
         <v>137040101</v>
       </c>
       <c r="B37" t="n">
-        <v>80104</v>
+        <v>80107</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5151,7 +5151,7 @@
         <v>137040104</v>
       </c>
       <c r="B38" t="n">
-        <v>80104</v>
+        <v>80107</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5263,7 +5263,7 @@
         <v>137040108</v>
       </c>
       <c r="B39" t="n">
-        <v>80494</v>
+        <v>80497</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5394,7 +5394,7 @@
         <v>137040110</v>
       </c>
       <c r="B40" t="n">
-        <v>80494</v>
+        <v>80497</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5525,7 +5525,7 @@
         <v>137040111</v>
       </c>
       <c r="B41" t="n">
-        <v>80494</v>
+        <v>80497</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -7899,7 +7899,7 @@
         <v>137040107</v>
       </c>
       <c r="B60" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -8024,7 +8024,7 @@
         <v>137040121</v>
       </c>
       <c r="B61" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -8149,7 +8149,7 @@
         <v>137040123</v>
       </c>
       <c r="B62" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -8274,7 +8274,7 @@
         <v>137040138</v>
       </c>
       <c r="B63" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8399,7 +8399,7 @@
         <v>137040160</v>
       </c>
       <c r="B64" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8524,7 +8524,7 @@
         <v>137040163</v>
       </c>
       <c r="B65" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8649,7 +8649,7 @@
         <v>137040164</v>
       </c>
       <c r="B66" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8774,7 +8774,7 @@
         <v>137040166</v>
       </c>
       <c r="B67" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8899,7 +8899,7 @@
         <v>137040168</v>
       </c>
       <c r="B68" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -9024,7 +9024,7 @@
         <v>137040189</v>
       </c>
       <c r="B69" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -9149,7 +9149,7 @@
         <v>137044057</v>
       </c>
       <c r="B70" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -9274,7 +9274,7 @@
         <v>137044059</v>
       </c>
       <c r="B71" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9399,7 +9399,7 @@
         <v>137044060</v>
       </c>
       <c r="B72" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9524,7 +9524,7 @@
         <v>137044061</v>
       </c>
       <c r="B73" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9649,7 +9649,7 @@
         <v>137044062</v>
       </c>
       <c r="B74" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9774,7 +9774,7 @@
         <v>137044064</v>
       </c>
       <c r="B75" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9899,7 +9899,7 @@
         <v>137044080</v>
       </c>
       <c r="B76" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -10024,7 +10024,7 @@
         <v>137040134</v>
       </c>
       <c r="B77" t="n">
-        <v>79243</v>
+        <v>79246</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -10136,7 +10136,7 @@
         <v>137040136</v>
       </c>
       <c r="B78" t="n">
-        <v>79243</v>
+        <v>79246</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -10248,7 +10248,7 @@
         <v>137016336</v>
       </c>
       <c r="B79" t="n">
-        <v>79508</v>
+        <v>79511</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -10379,7 +10379,7 @@
         <v>137016339</v>
       </c>
       <c r="B80" t="n">
-        <v>79508</v>
+        <v>79511</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -10510,7 +10510,7 @@
         <v>137016342</v>
       </c>
       <c r="B81" t="n">
-        <v>79508</v>
+        <v>79511</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10641,7 +10641,7 @@
         <v>137016345</v>
       </c>
       <c r="B82" t="n">
-        <v>79508</v>
+        <v>79511</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10772,7 +10772,7 @@
         <v>137016346</v>
       </c>
       <c r="B83" t="n">
-        <v>79508</v>
+        <v>79511</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10907,7 +10907,7 @@
         <v>137016348</v>
       </c>
       <c r="B84" t="n">
-        <v>79508</v>
+        <v>79511</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -11042,7 +11042,7 @@
         <v>137016353</v>
       </c>
       <c r="B85" t="n">
-        <v>79508</v>
+        <v>79511</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -11173,7 +11173,7 @@
         <v>137040099</v>
       </c>
       <c r="B86" t="n">
-        <v>79508</v>
+        <v>79511</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -11285,7 +11285,7 @@
         <v>137044071</v>
       </c>
       <c r="B87" t="n">
-        <v>79508</v>
+        <v>79511</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>

--- a/artfynd/A 25855-2025 artfynd.xlsx
+++ b/artfynd/A 25855-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ87"/>
+  <dimension ref="A1:AZ62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -683,7 +683,7 @@
         <v>137044063</v>
       </c>
       <c r="B2" t="n">
-        <v>92401</v>
+        <v>92414</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -814,7 +814,7 @@
         <v>137040165</v>
       </c>
       <c r="B3" t="n">
-        <v>92963</v>
+        <v>92976</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -931,7 +931,7 @@
         <v>137016354</v>
       </c>
       <c r="B4" t="n">
-        <v>93444</v>
+        <v>93457</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1047,7 +1047,7 @@
         <v>137016293</v>
       </c>
       <c r="B5" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1156,45 +1156,48 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>137040122</v>
+        <v>137016298</v>
       </c>
       <c r="B6" t="n">
-        <v>92093</v>
+        <v>93479</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5447</v>
+        <v>5966</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Stortannsjön, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>636830</v>
+        <v>636437</v>
       </c>
       <c r="R6" t="n">
-        <v>7014277</v>
+        <v>7014437</v>
       </c>
       <c r="S6" t="n">
         <v>3</v>
@@ -1221,22 +1224,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1245,6 +1248,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1256,44 +1260,44 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Markus Borja, Diego Borja, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137040122</t>
+          <t>https://artportalen.se/Sighting/137016298</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>137016298</v>
+        <v>137016289</v>
       </c>
       <c r="B7" t="n">
-        <v>93466</v>
+        <v>79501</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5966</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1306,10 +1310,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>636437</v>
+        <v>636608</v>
       </c>
       <c r="R7" t="n">
-        <v>7014437</v>
+        <v>7014302</v>
       </c>
       <c r="S7" t="n">
         <v>3</v>
@@ -1341,7 +1345,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1351,7 +1355,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1364,6 +1368,21 @@
       <c r="AG7" t="b">
         <v>0</v>
       </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
@@ -1372,22 +1391,22 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Markus Borja, Diego Borja, Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016298</t>
+          <t>https://artportalen.se/Sighting/137016289</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>137016289</v>
+        <v>137016306</v>
       </c>
       <c r="B8" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1422,10 +1441,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>636608</v>
+        <v>636566</v>
       </c>
       <c r="R8" t="n">
-        <v>7014302</v>
+        <v>7014366</v>
       </c>
       <c r="S8" t="n">
         <v>3</v>
@@ -1457,7 +1476,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1467,7 +1486,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1509,16 +1528,16 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016289</t>
+          <t>https://artportalen.se/Sighting/137016306</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>137016306</v>
+        <v>137016332</v>
       </c>
       <c r="B9" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1553,13 +1572,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>636566</v>
+        <v>636603</v>
       </c>
       <c r="R9" t="n">
-        <v>7014366</v>
+        <v>7014322</v>
       </c>
       <c r="S9" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1588,7 +1607,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1598,7 +1617,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1629,27 +1648,27 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016306</t>
+          <t>https://artportalen.se/Sighting/137016332</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>137016332</v>
+        <v>137016333</v>
       </c>
       <c r="B10" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1684,10 +1703,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>636603</v>
+        <v>636623</v>
       </c>
       <c r="R10" t="n">
-        <v>7014322</v>
+        <v>7014305</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1719,7 +1738,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1729,7 +1748,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1771,16 +1790,16 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016332</t>
+          <t>https://artportalen.se/Sighting/137016333</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>137016333</v>
+        <v>137016335</v>
       </c>
       <c r="B11" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1815,10 +1834,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>636623</v>
+        <v>636520</v>
       </c>
       <c r="R11" t="n">
-        <v>7014305</v>
+        <v>7014374</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1850,7 +1869,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1860,7 +1879,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1902,16 +1921,16 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016333</t>
+          <t>https://artportalen.se/Sighting/137016335</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>137016335</v>
+        <v>137016337</v>
       </c>
       <c r="B12" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1946,10 +1965,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>636520</v>
+        <v>636463</v>
       </c>
       <c r="R12" t="n">
-        <v>7014374</v>
+        <v>7014402</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1981,7 +2000,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1991,7 +2010,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2033,16 +2052,16 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016335</t>
+          <t>https://artportalen.se/Sighting/137016337</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>137016337</v>
+        <v>137016340</v>
       </c>
       <c r="B13" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2077,10 +2096,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>636463</v>
+        <v>636419</v>
       </c>
       <c r="R13" t="n">
-        <v>7014402</v>
+        <v>7014437</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2112,7 +2131,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2122,7 +2141,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2164,16 +2183,16 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016337</t>
+          <t>https://artportalen.se/Sighting/137016340</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>137016340</v>
+        <v>137016349</v>
       </c>
       <c r="B14" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2208,10 +2227,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>636419</v>
+        <v>636488</v>
       </c>
       <c r="R14" t="n">
-        <v>7014437</v>
+        <v>7014536</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2243,7 +2262,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2253,7 +2272,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2295,16 +2314,16 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016340</t>
+          <t>https://artportalen.se/Sighting/137016349</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>137016349</v>
+        <v>137016350</v>
       </c>
       <c r="B15" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2339,10 +2358,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>636488</v>
+        <v>636466</v>
       </c>
       <c r="R15" t="n">
-        <v>7014536</v>
+        <v>7014464</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2374,7 +2393,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2384,7 +2403,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2426,16 +2445,16 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016349</t>
+          <t>https://artportalen.se/Sighting/137016350</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>137016350</v>
+        <v>137040167</v>
       </c>
       <c r="B16" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2461,19 +2480,16 @@
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Stortannsjön, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>636466</v>
+        <v>636743</v>
       </c>
       <c r="R16" t="n">
-        <v>7014464</v>
+        <v>7014374</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2500,22 +2516,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2524,49 +2540,33 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Vivien Renaut</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Vivien Renaut</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016350</t>
+          <t>https://artportalen.se/Sighting/137040167</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>137040102</v>
+        <v>137040169</v>
       </c>
       <c r="B17" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2592,22 +2592,19 @@
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Stortannsjön, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>636758</v>
+        <v>636844</v>
       </c>
       <c r="R17" t="n">
-        <v>7014258</v>
+        <v>7014273</v>
       </c>
       <c r="S17" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2636,7 +2633,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>09:08</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2646,7 +2643,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>09:08</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2655,49 +2652,33 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Vivien Renaut</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Markus Borja, Vivien Renaut, Ann-Christine Borja</t>
+          <t>Vivien Renaut</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137040102</t>
+          <t>https://artportalen.se/Sighting/137040169</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>137040133</v>
+        <v>137040181</v>
       </c>
       <c r="B18" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2723,22 +2704,19 @@
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Stortannsjön, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>636608</v>
+        <v>636605</v>
       </c>
       <c r="R18" t="n">
-        <v>7014515</v>
+        <v>7014506</v>
       </c>
       <c r="S18" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2767,7 +2745,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2777,7 +2755,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:28</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Garnlav på tall</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2786,49 +2769,33 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Vivien Renaut</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Markus Borja, Vivien Renaut, Ann-Christine Borja</t>
+          <t>Vivien Renaut</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137040133</t>
+          <t>https://artportalen.se/Sighting/137040181</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>137040161</v>
+        <v>137044055</v>
       </c>
       <c r="B19" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2863,13 +2830,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>636549</v>
+        <v>636694</v>
       </c>
       <c r="R19" t="n">
-        <v>7014491</v>
+        <v>7014252</v>
       </c>
       <c r="S19" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2898,7 +2865,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>18:07</t>
+          <t>08:47</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2908,7 +2875,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>18:07</t>
+          <t>08:47</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2939,27 +2906,27 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Markus Borja, Vivien Renaut, Ann-Christine Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137040161</t>
+          <t>https://artportalen.se/Sighting/137044055</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>137040162</v>
+        <v>137044068</v>
       </c>
       <c r="B20" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2994,13 +2961,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>636606</v>
+        <v>636901</v>
       </c>
       <c r="R20" t="n">
-        <v>7014419</v>
+        <v>7014208</v>
       </c>
       <c r="S20" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3029,7 +2996,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3039,7 +3006,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3054,43 +3021,43 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Markus Borja, Vivien Renaut, Ann-Christine Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137040162</t>
+          <t>https://artportalen.se/Sighting/137044068</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>137040167</v>
+        <v>137044072</v>
       </c>
       <c r="B21" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3116,16 +3083,19 @@
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Stortannsjön, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>636743</v>
+        <v>636840</v>
       </c>
       <c r="R21" t="n">
-        <v>7014374</v>
+        <v>7014233</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -3157,7 +3127,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3167,7 +3137,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3176,71 +3146,90 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Vivien Renaut</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Vivien Renaut</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137040167</t>
+          <t>https://artportalen.se/Sighting/137044072</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>137040169</v>
+        <v>137016334</v>
       </c>
       <c r="B22" t="n">
-        <v>79488</v>
+        <v>79525</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Stortannsjön, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>636844</v>
+        <v>636591</v>
       </c>
       <c r="R22" t="n">
-        <v>7014273</v>
+        <v>7014315</v>
       </c>
       <c r="S22" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3264,22 +3253,22 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3288,71 +3277,90 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Vivien Renaut</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Vivien Renaut</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137040169</t>
+          <t>https://artportalen.se/Sighting/137016334</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>137040181</v>
+        <v>137016341</v>
       </c>
       <c r="B23" t="n">
-        <v>79488</v>
+        <v>79525</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Stortannsjön, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>636605</v>
+        <v>636409</v>
       </c>
       <c r="R23" t="n">
-        <v>7014506</v>
+        <v>7014452</v>
       </c>
       <c r="S23" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3376,27 +3384,22 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:28</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Garnlav på tall</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3405,55 +3408,71 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Vivien Renaut</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Vivien Renaut</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137040181</t>
+          <t>https://artportalen.se/Sighting/137016341</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>137044055</v>
+        <v>137016351</v>
       </c>
       <c r="B24" t="n">
-        <v>79488</v>
+        <v>79525</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3466,10 +3485,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>636694</v>
+        <v>636460</v>
       </c>
       <c r="R24" t="n">
-        <v>7014252</v>
+        <v>7014454</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3496,22 +3515,22 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>08:47</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>08:47</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3553,38 +3572,38 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137044055</t>
+          <t>https://artportalen.se/Sighting/137016351</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>137044068</v>
+        <v>137044056</v>
       </c>
       <c r="B25" t="n">
-        <v>79488</v>
+        <v>79525</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3597,10 +3616,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>636901</v>
+        <v>636699</v>
       </c>
       <c r="R25" t="n">
-        <v>7014208</v>
+        <v>7014271</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3632,7 +3651,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3642,7 +3661,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3684,57 +3703,54 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137044068</t>
+          <t>https://artportalen.se/Sighting/137044056</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>137044072</v>
+        <v>137016288</v>
       </c>
       <c r="B26" t="n">
-        <v>79488</v>
+        <v>80120</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Stortannsjön, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>636840</v>
+        <v>636610</v>
       </c>
       <c r="R26" t="n">
-        <v>7014233</v>
+        <v>7014307</v>
       </c>
       <c r="S26" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3758,22 +3774,22 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3782,90 +3798,71 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ26" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK26" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137044072</t>
+          <t>https://artportalen.se/Sighting/137016288</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>137016334</v>
+        <v>137016299</v>
       </c>
       <c r="B27" t="n">
-        <v>79512</v>
+        <v>80120</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6434</v>
+        <v>6453</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Stortannsjön, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>636591</v>
+        <v>636418</v>
       </c>
       <c r="R27" t="n">
-        <v>7014315</v>
+        <v>7014453</v>
       </c>
       <c r="S27" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3894,7 +3891,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3904,7 +3901,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3913,90 +3910,71 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016334</t>
+          <t>https://artportalen.se/Sighting/137016299</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>137016341</v>
+        <v>137016303</v>
       </c>
       <c r="B28" t="n">
-        <v>79512</v>
+        <v>80120</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6434</v>
+        <v>6453</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Stortannsjön, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>636409</v>
+        <v>636499</v>
       </c>
       <c r="R28" t="n">
-        <v>7014452</v>
+        <v>7014546</v>
       </c>
       <c r="S28" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -4025,7 +4003,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -4035,7 +4013,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4044,49 +4022,33 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ28" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK28" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO28" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016341</t>
+          <t>https://artportalen.se/Sighting/137016303</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>137016351</v>
+        <v>137016301</v>
       </c>
       <c r="B29" t="n">
-        <v>79512</v>
+        <v>58018</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4094,26 +4056,31 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6434</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -4121,13 +4088,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>636460</v>
+        <v>636482</v>
       </c>
       <c r="R29" t="n">
-        <v>7014454</v>
+        <v>7014533</v>
       </c>
       <c r="S29" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4156,7 +4123,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4166,7 +4133,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4175,49 +4142,33 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ29" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK29" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016351</t>
+          <t>https://artportalen.se/Sighting/137016301</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>137040100</v>
+        <v>137040182</v>
       </c>
       <c r="B30" t="n">
-        <v>79512</v>
+        <v>58018</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4225,26 +4176,31 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6434</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -4252,13 +4208,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>636705</v>
+        <v>636550</v>
       </c>
       <c r="R30" t="n">
-        <v>7014244</v>
+        <v>7014507</v>
       </c>
       <c r="S30" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4287,7 +4243,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4297,7 +4253,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>14:41</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4306,76 +4267,65 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ30" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK30" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Vivien Renaut</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Markus Borja, Vivien Renaut, Ann-Christine Borja</t>
+          <t>Vivien Renaut</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137040100</t>
+          <t>https://artportalen.se/Sighting/137040182</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>137044056</v>
+        <v>137016287</v>
       </c>
       <c r="B31" t="n">
-        <v>79512</v>
+        <v>58021</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6434</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -4383,13 +4333,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>636699</v>
+        <v>636606</v>
       </c>
       <c r="R31" t="n">
-        <v>7014271</v>
+        <v>7014302</v>
       </c>
       <c r="S31" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4413,22 +4363,27 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>10:34</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Färska och Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4437,49 +4392,33 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja, Ann-Christine Borja, Diego Borja</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137044056</t>
+          <t>https://artportalen.se/Sighting/137016287</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>137040105</v>
+        <v>137016290</v>
       </c>
       <c r="B32" t="n">
-        <v>79245</v>
+        <v>58021</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4487,34 +4426,42 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Stortannsjön, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>636730</v>
+        <v>636608</v>
       </c>
       <c r="R32" t="n">
-        <v>7014286</v>
+        <v>7014302</v>
       </c>
       <c r="S32" t="n">
         <v>3</v>
@@ -4541,22 +4488,27 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>10:54</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4576,22 +4528,22 @@
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Markus Borja, Ann-Christine Borja, Diego Borja</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137040105</t>
+          <t>https://artportalen.se/Sighting/137016290</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>137040135</v>
+        <v>137016291</v>
       </c>
       <c r="B33" t="n">
-        <v>79245</v>
+        <v>58021</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4599,34 +4551,42 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Stortannsjön, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>636582</v>
+        <v>636578</v>
       </c>
       <c r="R33" t="n">
-        <v>7014519</v>
+        <v>7014320</v>
       </c>
       <c r="S33" t="n">
         <v>3</v>
@@ -4653,22 +4613,27 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>10:59</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4688,22 +4653,22 @@
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Markus Borja, Ann-Christine Borja, Diego Borja</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137040135</t>
+          <t>https://artportalen.se/Sighting/137016291</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>137016288</v>
+        <v>137016292</v>
       </c>
       <c r="B34" t="n">
-        <v>80107</v>
+        <v>58021</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4711,34 +4676,42 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Stortannsjön, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>636610</v>
+        <v>636501</v>
       </c>
       <c r="R34" t="n">
-        <v>7014307</v>
+        <v>7014381</v>
       </c>
       <c r="S34" t="n">
         <v>3</v>
@@ -4770,7 +4743,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4780,7 +4753,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>11:09</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4800,22 +4778,22 @@
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Markus Borja, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016288</t>
+          <t>https://artportalen.se/Sighting/137016292</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>137016299</v>
+        <v>137016294</v>
       </c>
       <c r="B35" t="n">
-        <v>80107</v>
+        <v>58021</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4823,34 +4801,42 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Stortannsjön, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>636418</v>
+        <v>636486</v>
       </c>
       <c r="R35" t="n">
-        <v>7014453</v>
+        <v>7014403</v>
       </c>
       <c r="S35" t="n">
         <v>3</v>
@@ -4882,7 +4868,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4892,7 +4878,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>11:16</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4912,22 +4903,22 @@
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Markus Borja, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016299</t>
+          <t>https://artportalen.se/Sighting/137016294</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>137016303</v>
+        <v>137016295</v>
       </c>
       <c r="B36" t="n">
-        <v>80107</v>
+        <v>58021</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4935,34 +4926,42 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Stortannsjön, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>636499</v>
+        <v>636432</v>
       </c>
       <c r="R36" t="n">
-        <v>7014546</v>
+        <v>7014422</v>
       </c>
       <c r="S36" t="n">
         <v>3</v>
@@ -4994,7 +4993,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -5004,7 +5003,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:28</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5024,22 +5028,22 @@
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Markus Borja, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016303</t>
+          <t>https://artportalen.se/Sighting/137016295</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>137040101</v>
+        <v>137016296</v>
       </c>
       <c r="B37" t="n">
-        <v>80107</v>
+        <v>58021</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5047,34 +5051,42 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Stortannsjön, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>636731</v>
+        <v>636424</v>
       </c>
       <c r="R37" t="n">
-        <v>7014243</v>
+        <v>7014437</v>
       </c>
       <c r="S37" t="n">
         <v>3</v>
@@ -5101,22 +5113,27 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>09:05</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>09:05</t>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5136,22 +5153,22 @@
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Markus Borja, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137040101</t>
+          <t>https://artportalen.se/Sighting/137016296</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>137040104</v>
+        <v>137016297</v>
       </c>
       <c r="B38" t="n">
-        <v>80107</v>
+        <v>58021</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5159,34 +5176,42 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Stortannsjön, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>636746</v>
+        <v>636448</v>
       </c>
       <c r="R38" t="n">
-        <v>7014291</v>
+        <v>7014424</v>
       </c>
       <c r="S38" t="n">
         <v>3</v>
@@ -5213,22 +5238,27 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>11:35</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5248,49 +5278,54 @@
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Markus Borja, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137040104</t>
+          <t>https://artportalen.se/Sighting/137016297</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>137040108</v>
+        <v>137016300</v>
       </c>
       <c r="B39" t="n">
-        <v>80497</v>
+        <v>58021</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6456</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -5298,13 +5333,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>636817</v>
+        <v>636398</v>
       </c>
       <c r="R39" t="n">
-        <v>7014280</v>
+        <v>7014509</v>
       </c>
       <c r="S39" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5328,22 +5363,27 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>11:46</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5352,24 +5392,8 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ39" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK39" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO39" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
@@ -5379,49 +5403,54 @@
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Markus Borja, Vivien Renaut, Ann-Christine Borja</t>
+          <t>Markus Borja, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137040108</t>
+          <t>https://artportalen.se/Sighting/137016300</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>137040110</v>
+        <v>137016304</v>
       </c>
       <c r="B40" t="n">
-        <v>80497</v>
+        <v>58021</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6456</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -5429,10 +5458,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>636815</v>
+        <v>636466</v>
       </c>
       <c r="R40" t="n">
-        <v>7014278</v>
+        <v>7014462</v>
       </c>
       <c r="S40" t="n">
         <v>3</v>
@@ -5459,22 +5488,27 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>12:24</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5483,24 +5517,8 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ40" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK40" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO40" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
@@ -5510,49 +5528,54 @@
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Markus Borja, Vivien Renaut, Ann-Christine Borja</t>
+          <t>Markus Borja, Ann-Christine Borja, Diego Borja</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137040110</t>
+          <t>https://artportalen.se/Sighting/137016304</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>137040111</v>
+        <v>137016307</v>
       </c>
       <c r="B41" t="n">
-        <v>80497</v>
+        <v>58021</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6456</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -5560,13 +5583,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>636803</v>
+        <v>636566</v>
       </c>
       <c r="R41" t="n">
-        <v>7014259</v>
+        <v>7014367</v>
       </c>
       <c r="S41" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5590,22 +5613,27 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>12:35</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5614,24 +5642,8 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ41" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK41" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO41" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
@@ -5641,39 +5653,39 @@
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Markus Borja, Vivien Renaut, Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137040111</t>
+          <t>https://artportalen.se/Sighting/137016307</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>137016301</v>
+        <v>137016344</v>
       </c>
       <c r="B42" t="n">
-        <v>58005</v>
+        <v>58021</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -5696,13 +5708,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>636482</v>
+        <v>636392</v>
       </c>
       <c r="R42" t="n">
-        <v>7014533</v>
+        <v>7014473</v>
       </c>
       <c r="S42" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5731,7 +5743,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5741,7 +5753,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5756,49 +5773,49 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja, Markus Borja</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016301</t>
+          <t>https://artportalen.se/Sighting/137016344</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>137040182</v>
+        <v>137040177</v>
       </c>
       <c r="B43" t="n">
-        <v>58005</v>
+        <v>58182</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5806,7 +5823,7 @@
       <c r="L43" t="inlineStr"/>
       <c r="M43" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N43" t="inlineStr"/>
@@ -5816,13 +5833,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>636550</v>
+        <v>636811</v>
       </c>
       <c r="R43" t="n">
-        <v>7014507</v>
+        <v>7014284</v>
       </c>
       <c r="S43" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5851,7 +5868,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5861,12 +5878,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Färska spår</t>
+          <t>Läte</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5892,48 +5909,52 @@
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137040182</t>
+          <t>https://artportalen.se/Sighting/137040177</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>137016287</v>
+        <v>137040164</v>
       </c>
       <c r="B44" t="n">
-        <v>58008</v>
+        <v>99389</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -5941,10 +5962,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>636606</v>
+        <v>636776</v>
       </c>
       <c r="R44" t="n">
-        <v>7014302</v>
+        <v>7014278</v>
       </c>
       <c r="S44" t="n">
         <v>3</v>
@@ -5971,27 +5992,22 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>09:05</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>10:34</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Färska och Äldre ringhack på tall</t>
+          <t>09:05</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6000,65 +6016,70 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Vivien Renaut</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja, Diego Borja</t>
+          <t>Vivien Renaut</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016287</t>
+          <t>https://artportalen.se/Sighting/137040164</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>137016290</v>
+        <v>137040166</v>
       </c>
       <c r="B45" t="n">
-        <v>58008</v>
+        <v>99389</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -6066,10 +6087,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>636608</v>
+        <v>636782</v>
       </c>
       <c r="R45" t="n">
-        <v>7014302</v>
+        <v>7014300</v>
       </c>
       <c r="S45" t="n">
         <v>3</v>
@@ -6096,27 +6117,22 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>10:54</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6125,65 +6141,70 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Vivien Renaut</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja, Diego Borja</t>
+          <t>Vivien Renaut</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016290</t>
+          <t>https://artportalen.se/Sighting/137040166</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>137016291</v>
+        <v>137040168</v>
       </c>
       <c r="B46" t="n">
-        <v>58008</v>
+        <v>99389</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
@@ -6191,10 +6212,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>636578</v>
+        <v>636758</v>
       </c>
       <c r="R46" t="n">
-        <v>7014320</v>
+        <v>7014368</v>
       </c>
       <c r="S46" t="n">
         <v>3</v>
@@ -6221,27 +6242,22 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>10:59</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6250,65 +6266,70 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Vivien Renaut</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja, Diego Borja</t>
+          <t>Vivien Renaut</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016291</t>
+          <t>https://artportalen.se/Sighting/137040168</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>137016292</v>
+        <v>137040189</v>
       </c>
       <c r="B47" t="n">
-        <v>58008</v>
+        <v>99389</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
@@ -6316,13 +6337,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>636501</v>
+        <v>636424</v>
       </c>
       <c r="R47" t="n">
-        <v>7014381</v>
+        <v>7014610</v>
       </c>
       <c r="S47" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6346,27 +6367,22 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>11:09</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6375,65 +6391,70 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Vivien Renaut</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja</t>
+          <t>Vivien Renaut</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016292</t>
+          <t>https://artportalen.se/Sighting/137040189</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>137016294</v>
+        <v>137044057</v>
       </c>
       <c r="B48" t="n">
-        <v>58008</v>
+        <v>99389</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -6441,13 +6462,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>636486</v>
+        <v>636762</v>
       </c>
       <c r="R48" t="n">
-        <v>7014403</v>
+        <v>7014263</v>
       </c>
       <c r="S48" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6471,27 +6492,22 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>11:16</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6500,65 +6516,70 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja</t>
+          <t>Ann-Christine Borja, Markus Borja, Vivien Renaut</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016294</t>
+          <t>https://artportalen.se/Sighting/137044057</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>137016295</v>
+        <v>137044059</v>
       </c>
       <c r="B49" t="n">
-        <v>58008</v>
+        <v>99389</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
@@ -6566,13 +6587,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>636432</v>
+        <v>636736</v>
       </c>
       <c r="R49" t="n">
-        <v>7014422</v>
+        <v>7014341</v>
       </c>
       <c r="S49" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6596,27 +6617,22 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>11:28</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6625,65 +6641,70 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja</t>
+          <t>Ann-Christine Borja, Markus Borja, Vivien Renaut</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016295</t>
+          <t>https://artportalen.se/Sighting/137044059</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>137016296</v>
+        <v>137044060</v>
       </c>
       <c r="B50" t="n">
-        <v>58008</v>
+        <v>99389</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>159</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
@@ -6691,13 +6712,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>636424</v>
+        <v>636760</v>
       </c>
       <c r="R50" t="n">
-        <v>7014437</v>
+        <v>7014309</v>
       </c>
       <c r="S50" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6721,27 +6742,22 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>11:30</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack på tall</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6750,65 +6766,70 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja</t>
+          <t>Ann-Christine Borja, Markus Borja, Vivien Renaut</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016296</t>
+          <t>https://artportalen.se/Sighting/137044060</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>137016297</v>
+        <v>137044061</v>
       </c>
       <c r="B51" t="n">
-        <v>58008</v>
+        <v>99389</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
@@ -6816,13 +6837,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>636448</v>
+        <v>636781</v>
       </c>
       <c r="R51" t="n">
-        <v>7014424</v>
+        <v>7014323</v>
       </c>
       <c r="S51" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6846,27 +6867,22 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>11:35</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6875,65 +6891,70 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja</t>
+          <t>Ann-Christine Borja, Markus Borja, Vivien Renaut</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016297</t>
+          <t>https://artportalen.se/Sighting/137044061</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>137016300</v>
+        <v>137044062</v>
       </c>
       <c r="B52" t="n">
-        <v>58008</v>
+        <v>99389</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>117</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
@@ -6941,13 +6962,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>636398</v>
+        <v>636772</v>
       </c>
       <c r="R52" t="n">
-        <v>7014509</v>
+        <v>7014326</v>
       </c>
       <c r="S52" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6971,27 +6992,22 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>11:46</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -7000,65 +7016,70 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja</t>
+          <t>Ann-Christine Borja, Markus Borja, Vivien Renaut</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016300</t>
+          <t>https://artportalen.se/Sighting/137044062</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>137016304</v>
+        <v>137044064</v>
       </c>
       <c r="B53" t="n">
-        <v>58008</v>
+        <v>99389</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
@@ -7066,13 +7087,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>636466</v>
+        <v>636806</v>
       </c>
       <c r="R53" t="n">
-        <v>7014462</v>
+        <v>7014282</v>
       </c>
       <c r="S53" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -7096,27 +7117,22 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>12:24</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -7125,65 +7141,70 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja, Diego Borja</t>
+          <t>Ann-Christine Borja, Markus Borja, Vivien Renaut</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016304</t>
+          <t>https://artportalen.se/Sighting/137044064</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>137016307</v>
+        <v>137044080</v>
       </c>
       <c r="B54" t="n">
-        <v>58008</v>
+        <v>99389</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
@@ -7191,13 +7212,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>636566</v>
+        <v>636598</v>
       </c>
       <c r="R54" t="n">
-        <v>7014367</v>
+        <v>7014517</v>
       </c>
       <c r="S54" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -7221,27 +7242,22 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>12:35</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7250,33 +7266,34 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja, Markus Borja, Vivien Renaut</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016307</t>
+          <t>https://artportalen.se/Sighting/137044080</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>137016344</v>
+        <v>137016336</v>
       </c>
       <c r="B55" t="n">
-        <v>58008</v>
+        <v>79524</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7284,31 +7301,26 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100109</v>
+        <v>260591</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltagel</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria fremontii</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
@@ -7316,10 +7328,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>636392</v>
+        <v>636512</v>
       </c>
       <c r="R55" t="n">
-        <v>7014473</v>
+        <v>7014375</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -7351,7 +7363,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -7361,12 +7373,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>11:50</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall.</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7375,8 +7382,24 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ55" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK55" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO55" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
@@ -7392,16 +7415,16 @@
       <c r="AY55" t="inlineStr"/>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016344</t>
+          <t>https://artportalen.se/Sighting/137016336</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>137040097</v>
+        <v>137016339</v>
       </c>
       <c r="B56" t="n">
-        <v>58008</v>
+        <v>79524</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7409,31 +7432,26 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>260591</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltagel</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria fremontii</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
@@ -7441,13 +7459,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>636710</v>
+        <v>636457</v>
       </c>
       <c r="R56" t="n">
-        <v>7014234</v>
+        <v>7014405</v>
       </c>
       <c r="S56" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -7471,27 +7489,22 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>08:39</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>08:39</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7500,33 +7513,49 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
+      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ56" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK56" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO56" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Markus Borja, Vivien Renaut, Ann-Christine Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137040097</t>
+          <t>https://artportalen.se/Sighting/137016339</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>137040106</v>
+        <v>137016342</v>
       </c>
       <c r="B57" t="n">
-        <v>58169</v>
+        <v>79524</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7534,53 +7563,40 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>103021</v>
+        <v>260591</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Talltagel</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Bryoria fremontii</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N57" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Stortannsjön, Ång</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>636783</v>
+        <v>636417</v>
       </c>
       <c r="R57" t="n">
-        <v>7014328</v>
+        <v>7014452</v>
       </c>
       <c r="S57" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7604,22 +7620,22 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7628,33 +7644,49 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ57" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK57" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO57" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja, Vivien Renaut</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137040106</t>
+          <t>https://artportalen.se/Sighting/137016342</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>137040109</v>
+        <v>137016345</v>
       </c>
       <c r="B58" t="n">
-        <v>58169</v>
+        <v>79524</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7662,31 +7694,26 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>103021</v>
+        <v>260591</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Talltagel</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Bryoria fremontii</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
@@ -7694,13 +7721,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>636808</v>
+        <v>636407</v>
       </c>
       <c r="R58" t="n">
-        <v>7014272</v>
+        <v>7014480</v>
       </c>
       <c r="S58" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7724,22 +7751,22 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7748,33 +7775,49 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ58" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK58" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO58" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Markus Borja, Vivien Renaut</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137040109</t>
+          <t>https://artportalen.se/Sighting/137016345</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>137040177</v>
+        <v>137016346</v>
       </c>
       <c r="B59" t="n">
-        <v>58169</v>
+        <v>79524</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7782,29 +7825,28 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>103021</v>
+        <v>260591</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Talltagel</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Bryoria fremontii</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="N59" t="inlineStr"/>
@@ -7814,13 +7856,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>636811</v>
+        <v>636450</v>
       </c>
       <c r="R59" t="n">
-        <v>7014284</v>
+        <v>7014535</v>
       </c>
       <c r="S59" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7844,27 +7886,22 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>12:13</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Läte</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7873,69 +7910,80 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
+      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ59" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK59" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO59" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Vivien Renaut</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Vivien Renaut</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137040177</t>
+          <t>https://artportalen.se/Sighting/137016346</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>137040107</v>
+        <v>137016348</v>
       </c>
       <c r="B60" t="n">
-        <v>99376</v>
+        <v>79524</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220787</v>
+        <v>260591</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltagel</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria fremontii</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
@@ -7943,13 +7991,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>636807</v>
+        <v>636479</v>
       </c>
       <c r="R60" t="n">
-        <v>7014295</v>
+        <v>7014523</v>
       </c>
       <c r="S60" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7973,22 +8021,22 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -8001,66 +8049,72 @@
       <c r="AG60" t="b">
         <v>0</v>
       </c>
+      <c r="AJ60" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK60" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO60" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Markus Borja, Vivien Renaut, Ann-Christine Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137040107</t>
+          <t>https://artportalen.se/Sighting/137016348</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>137040121</v>
+        <v>137016353</v>
       </c>
       <c r="B61" t="n">
-        <v>99376</v>
+        <v>79524</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220787</v>
+        <v>260591</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltagel</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria fremontii</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
       <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
@@ -8068,13 +8122,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>636854</v>
+        <v>636460</v>
       </c>
       <c r="R61" t="n">
-        <v>7014229</v>
+        <v>7014451</v>
       </c>
       <c r="S61" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -8098,22 +8152,22 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -8126,66 +8180,76 @@
       <c r="AG61" t="b">
         <v>0</v>
       </c>
+      <c r="AJ61" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK61" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO61" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Markus Borja, Vivien Renaut, Ann-Christine Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137040121</t>
+          <t>https://artportalen.se/Sighting/137016353</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>137040123</v>
+        <v>137044071</v>
       </c>
       <c r="B62" t="n">
-        <v>99376</v>
+        <v>79524</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>220787</v>
+        <v>260591</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltagel</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria fremontii</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
@@ -8193,13 +8257,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>636843</v>
+        <v>636845</v>
       </c>
       <c r="R62" t="n">
-        <v>7014251</v>
+        <v>7014233</v>
       </c>
       <c r="S62" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -8228,7 +8292,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -8238,7 +8302,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8251,3165 +8315,34 @@
       <c r="AG62" t="b">
         <v>0</v>
       </c>
+      <c r="AJ62" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK62" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO62" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Markus Borja, Vivien Renaut, Ann-Christine Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
       <c r="AZ62" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/137040123</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="n">
-        <v>137040138</v>
-      </c>
-      <c r="B63" t="n">
-        <v>99376</v>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E63" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
-      <c r="N63" t="inlineStr"/>
-      <c r="P63" t="inlineStr">
-        <is>
-          <t>Stortannsjön, Ång</t>
-        </is>
-      </c>
-      <c r="Q63" t="n">
-        <v>636527</v>
-      </c>
-      <c r="R63" t="n">
-        <v>7014608</v>
-      </c>
-      <c r="S63" t="n">
-        <v>4</v>
-      </c>
-      <c r="T63" t="inlineStr">
-        <is>
-          <t>Västernorrland</t>
-        </is>
-      </c>
-      <c r="U63" t="inlineStr">
-        <is>
-          <t>Sollefteå</t>
-        </is>
-      </c>
-      <c r="V63" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W63" t="inlineStr">
-        <is>
-          <t>Överlännäs</t>
-        </is>
-      </c>
-      <c r="Y63" t="inlineStr">
-        <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="Z63" t="inlineStr">
-        <is>
-          <t>15:02</t>
-        </is>
-      </c>
-      <c r="AA63" t="inlineStr">
-        <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="AB63" t="inlineStr">
-        <is>
-          <t>15:02</t>
-        </is>
-      </c>
-      <c r="AD63" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE63" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF63" t="inlineStr"/>
-      <c r="AG63" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT63" t="inlineStr"/>
-      <c r="AW63" t="inlineStr">
-        <is>
-          <t>Markus Borja</t>
-        </is>
-      </c>
-      <c r="AX63" t="inlineStr">
-        <is>
-          <t>Markus Borja, Vivien Renaut, Ann-Christine Borja</t>
-        </is>
-      </c>
-      <c r="AY63" t="inlineStr"/>
-      <c r="AZ63" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/137040138</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="n">
-        <v>137040160</v>
-      </c>
-      <c r="B64" t="n">
-        <v>99376</v>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E64" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr"/>
-      <c r="N64" t="inlineStr"/>
-      <c r="P64" t="inlineStr">
-        <is>
-          <t>Stortannsjön, Ång</t>
-        </is>
-      </c>
-      <c r="Q64" t="n">
-        <v>636474</v>
-      </c>
-      <c r="R64" t="n">
-        <v>7014608</v>
-      </c>
-      <c r="S64" t="n">
-        <v>3</v>
-      </c>
-      <c r="T64" t="inlineStr">
-        <is>
-          <t>Västernorrland</t>
-        </is>
-      </c>
-      <c r="U64" t="inlineStr">
-        <is>
-          <t>Sollefteå</t>
-        </is>
-      </c>
-      <c r="V64" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W64" t="inlineStr">
-        <is>
-          <t>Överlännäs</t>
-        </is>
-      </c>
-      <c r="Y64" t="inlineStr">
-        <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="Z64" t="inlineStr">
-        <is>
-          <t>18:00</t>
-        </is>
-      </c>
-      <c r="AA64" t="inlineStr">
-        <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="AB64" t="inlineStr">
-        <is>
-          <t>18:00</t>
-        </is>
-      </c>
-      <c r="AD64" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE64" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF64" t="inlineStr"/>
-      <c r="AG64" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT64" t="inlineStr"/>
-      <c r="AW64" t="inlineStr">
-        <is>
-          <t>Markus Borja</t>
-        </is>
-      </c>
-      <c r="AX64" t="inlineStr">
-        <is>
-          <t>Markus Borja, Vivien Renaut, Ann-Christine Borja</t>
-        </is>
-      </c>
-      <c r="AY64" t="inlineStr"/>
-      <c r="AZ64" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/137040160</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="n">
-        <v>137040163</v>
-      </c>
-      <c r="B65" t="n">
-        <v>99376</v>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E65" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
-      <c r="N65" t="inlineStr"/>
-      <c r="P65" t="inlineStr">
-        <is>
-          <t>Stortannsjön, Ång</t>
-        </is>
-      </c>
-      <c r="Q65" t="n">
-        <v>636595</v>
-      </c>
-      <c r="R65" t="n">
-        <v>7014422</v>
-      </c>
-      <c r="S65" t="n">
-        <v>3</v>
-      </c>
-      <c r="T65" t="inlineStr">
-        <is>
-          <t>Västernorrland</t>
-        </is>
-      </c>
-      <c r="U65" t="inlineStr">
-        <is>
-          <t>Sollefteå</t>
-        </is>
-      </c>
-      <c r="V65" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W65" t="inlineStr">
-        <is>
-          <t>Överlännäs</t>
-        </is>
-      </c>
-      <c r="Y65" t="inlineStr">
-        <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="Z65" t="inlineStr">
-        <is>
-          <t>18:17</t>
-        </is>
-      </c>
-      <c r="AA65" t="inlineStr">
-        <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="AB65" t="inlineStr">
-        <is>
-          <t>18:17</t>
-        </is>
-      </c>
-      <c r="AD65" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE65" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF65" t="inlineStr"/>
-      <c r="AG65" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT65" t="inlineStr"/>
-      <c r="AW65" t="inlineStr">
-        <is>
-          <t>Markus Borja</t>
-        </is>
-      </c>
-      <c r="AX65" t="inlineStr">
-        <is>
-          <t>Markus Borja, Vivien Renaut, Ann-Christine Borja</t>
-        </is>
-      </c>
-      <c r="AY65" t="inlineStr"/>
-      <c r="AZ65" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/137040163</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="n">
-        <v>137040164</v>
-      </c>
-      <c r="B66" t="n">
-        <v>99376</v>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E66" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
-      <c r="N66" t="inlineStr"/>
-      <c r="P66" t="inlineStr">
-        <is>
-          <t>Stortannsjön, Ång</t>
-        </is>
-      </c>
-      <c r="Q66" t="n">
-        <v>636776</v>
-      </c>
-      <c r="R66" t="n">
-        <v>7014278</v>
-      </c>
-      <c r="S66" t="n">
-        <v>3</v>
-      </c>
-      <c r="T66" t="inlineStr">
-        <is>
-          <t>Västernorrland</t>
-        </is>
-      </c>
-      <c r="U66" t="inlineStr">
-        <is>
-          <t>Sollefteå</t>
-        </is>
-      </c>
-      <c r="V66" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W66" t="inlineStr">
-        <is>
-          <t>Överlännäs</t>
-        </is>
-      </c>
-      <c r="Y66" t="inlineStr">
-        <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="Z66" t="inlineStr">
-        <is>
-          <t>09:05</t>
-        </is>
-      </c>
-      <c r="AA66" t="inlineStr">
-        <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="AB66" t="inlineStr">
-        <is>
-          <t>09:05</t>
-        </is>
-      </c>
-      <c r="AD66" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE66" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF66" t="inlineStr"/>
-      <c r="AG66" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT66" t="inlineStr"/>
-      <c r="AW66" t="inlineStr">
-        <is>
-          <t>Vivien Renaut</t>
-        </is>
-      </c>
-      <c r="AX66" t="inlineStr">
-        <is>
-          <t>Vivien Renaut</t>
-        </is>
-      </c>
-      <c r="AY66" t="inlineStr"/>
-      <c r="AZ66" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/137040164</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="n">
-        <v>137040166</v>
-      </c>
-      <c r="B67" t="n">
-        <v>99376</v>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E67" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>115</t>
-        </is>
-      </c>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
-      <c r="N67" t="inlineStr"/>
-      <c r="P67" t="inlineStr">
-        <is>
-          <t>Stortannsjön, Ång</t>
-        </is>
-      </c>
-      <c r="Q67" t="n">
-        <v>636782</v>
-      </c>
-      <c r="R67" t="n">
-        <v>7014300</v>
-      </c>
-      <c r="S67" t="n">
-        <v>3</v>
-      </c>
-      <c r="T67" t="inlineStr">
-        <is>
-          <t>Västernorrland</t>
-        </is>
-      </c>
-      <c r="U67" t="inlineStr">
-        <is>
-          <t>Sollefteå</t>
-        </is>
-      </c>
-      <c r="V67" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W67" t="inlineStr">
-        <is>
-          <t>Överlännäs</t>
-        </is>
-      </c>
-      <c r="Y67" t="inlineStr">
-        <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="Z67" t="inlineStr">
-        <is>
-          <t>09:15</t>
-        </is>
-      </c>
-      <c r="AA67" t="inlineStr">
-        <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="AB67" t="inlineStr">
-        <is>
-          <t>09:15</t>
-        </is>
-      </c>
-      <c r="AD67" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE67" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF67" t="inlineStr"/>
-      <c r="AG67" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT67" t="inlineStr"/>
-      <c r="AW67" t="inlineStr">
-        <is>
-          <t>Vivien Renaut</t>
-        </is>
-      </c>
-      <c r="AX67" t="inlineStr">
-        <is>
-          <t>Vivien Renaut</t>
-        </is>
-      </c>
-      <c r="AY67" t="inlineStr"/>
-      <c r="AZ67" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/137040166</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="n">
-        <v>137040168</v>
-      </c>
-      <c r="B68" t="n">
-        <v>99376</v>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E68" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
-      <c r="N68" t="inlineStr"/>
-      <c r="P68" t="inlineStr">
-        <is>
-          <t>Stortannsjön, Ång</t>
-        </is>
-      </c>
-      <c r="Q68" t="n">
-        <v>636758</v>
-      </c>
-      <c r="R68" t="n">
-        <v>7014368</v>
-      </c>
-      <c r="S68" t="n">
-        <v>3</v>
-      </c>
-      <c r="T68" t="inlineStr">
-        <is>
-          <t>Västernorrland</t>
-        </is>
-      </c>
-      <c r="U68" t="inlineStr">
-        <is>
-          <t>Sollefteå</t>
-        </is>
-      </c>
-      <c r="V68" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W68" t="inlineStr">
-        <is>
-          <t>Överlännäs</t>
-        </is>
-      </c>
-      <c r="Y68" t="inlineStr">
-        <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="Z68" t="inlineStr">
-        <is>
-          <t>09:42</t>
-        </is>
-      </c>
-      <c r="AA68" t="inlineStr">
-        <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="AB68" t="inlineStr">
-        <is>
-          <t>09:42</t>
-        </is>
-      </c>
-      <c r="AD68" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE68" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF68" t="inlineStr"/>
-      <c r="AG68" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT68" t="inlineStr"/>
-      <c r="AW68" t="inlineStr">
-        <is>
-          <t>Vivien Renaut</t>
-        </is>
-      </c>
-      <c r="AX68" t="inlineStr">
-        <is>
-          <t>Vivien Renaut</t>
-        </is>
-      </c>
-      <c r="AY68" t="inlineStr"/>
-      <c r="AZ68" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/137040168</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="n">
-        <v>137040189</v>
-      </c>
-      <c r="B69" t="n">
-        <v>99376</v>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E69" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
-      <c r="N69" t="inlineStr"/>
-      <c r="P69" t="inlineStr">
-        <is>
-          <t>Stortannsjön, Ång</t>
-        </is>
-      </c>
-      <c r="Q69" t="n">
-        <v>636424</v>
-      </c>
-      <c r="R69" t="n">
-        <v>7014610</v>
-      </c>
-      <c r="S69" t="n">
-        <v>15</v>
-      </c>
-      <c r="T69" t="inlineStr">
-        <is>
-          <t>Västernorrland</t>
-        </is>
-      </c>
-      <c r="U69" t="inlineStr">
-        <is>
-          <t>Sollefteå</t>
-        </is>
-      </c>
-      <c r="V69" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W69" t="inlineStr">
-        <is>
-          <t>Överlännäs</t>
-        </is>
-      </c>
-      <c r="Y69" t="inlineStr">
-        <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="Z69" t="inlineStr">
-        <is>
-          <t>17:52</t>
-        </is>
-      </c>
-      <c r="AA69" t="inlineStr">
-        <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="AB69" t="inlineStr">
-        <is>
-          <t>17:52</t>
-        </is>
-      </c>
-      <c r="AD69" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE69" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF69" t="inlineStr"/>
-      <c r="AG69" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT69" t="inlineStr"/>
-      <c r="AW69" t="inlineStr">
-        <is>
-          <t>Vivien Renaut</t>
-        </is>
-      </c>
-      <c r="AX69" t="inlineStr">
-        <is>
-          <t>Vivien Renaut</t>
-        </is>
-      </c>
-      <c r="AY69" t="inlineStr"/>
-      <c r="AZ69" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/137040189</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="n">
-        <v>137044057</v>
-      </c>
-      <c r="B70" t="n">
-        <v>99376</v>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E70" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
-      <c r="N70" t="inlineStr"/>
-      <c r="P70" t="inlineStr">
-        <is>
-          <t>Stortannsjön, Ång</t>
-        </is>
-      </c>
-      <c r="Q70" t="n">
-        <v>636762</v>
-      </c>
-      <c r="R70" t="n">
-        <v>7014263</v>
-      </c>
-      <c r="S70" t="n">
-        <v>5</v>
-      </c>
-      <c r="T70" t="inlineStr">
-        <is>
-          <t>Västernorrland</t>
-        </is>
-      </c>
-      <c r="U70" t="inlineStr">
-        <is>
-          <t>Sollefteå</t>
-        </is>
-      </c>
-      <c r="V70" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W70" t="inlineStr">
-        <is>
-          <t>Överlännäs</t>
-        </is>
-      </c>
-      <c r="Y70" t="inlineStr">
-        <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="Z70" t="inlineStr">
-        <is>
-          <t>09:10</t>
-        </is>
-      </c>
-      <c r="AA70" t="inlineStr">
-        <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="AB70" t="inlineStr">
-        <is>
-          <t>09:10</t>
-        </is>
-      </c>
-      <c r="AD70" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE70" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF70" t="inlineStr"/>
-      <c r="AG70" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT70" t="inlineStr"/>
-      <c r="AW70" t="inlineStr">
-        <is>
-          <t>Ann-Christine Borja</t>
-        </is>
-      </c>
-      <c r="AX70" t="inlineStr">
-        <is>
-          <t>Ann-Christine Borja, Markus Borja, Vivien Renaut</t>
-        </is>
-      </c>
-      <c r="AY70" t="inlineStr"/>
-      <c r="AZ70" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/137044057</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="n">
-        <v>137044059</v>
-      </c>
-      <c r="B71" t="n">
-        <v>99376</v>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E71" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>105</t>
-        </is>
-      </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr"/>
-      <c r="N71" t="inlineStr"/>
-      <c r="P71" t="inlineStr">
-        <is>
-          <t>Stortannsjön, Ång</t>
-        </is>
-      </c>
-      <c r="Q71" t="n">
-        <v>636736</v>
-      </c>
-      <c r="R71" t="n">
-        <v>7014341</v>
-      </c>
-      <c r="S71" t="n">
-        <v>5</v>
-      </c>
-      <c r="T71" t="inlineStr">
-        <is>
-          <t>Västernorrland</t>
-        </is>
-      </c>
-      <c r="U71" t="inlineStr">
-        <is>
-          <t>Sollefteå</t>
-        </is>
-      </c>
-      <c r="V71" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W71" t="inlineStr">
-        <is>
-          <t>Överlännäs</t>
-        </is>
-      </c>
-      <c r="Y71" t="inlineStr">
-        <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="Z71" t="inlineStr">
-        <is>
-          <t>09:41</t>
-        </is>
-      </c>
-      <c r="AA71" t="inlineStr">
-        <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="AB71" t="inlineStr">
-        <is>
-          <t>09:41</t>
-        </is>
-      </c>
-      <c r="AD71" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE71" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF71" t="inlineStr"/>
-      <c r="AG71" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT71" t="inlineStr"/>
-      <c r="AW71" t="inlineStr">
-        <is>
-          <t>Ann-Christine Borja</t>
-        </is>
-      </c>
-      <c r="AX71" t="inlineStr">
-        <is>
-          <t>Ann-Christine Borja, Markus Borja, Vivien Renaut</t>
-        </is>
-      </c>
-      <c r="AY71" t="inlineStr"/>
-      <c r="AZ71" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/137044059</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="n">
-        <v>137044060</v>
-      </c>
-      <c r="B72" t="n">
-        <v>99376</v>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E72" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>159</t>
-        </is>
-      </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K72" t="inlineStr"/>
-      <c r="L72" t="inlineStr"/>
-      <c r="N72" t="inlineStr"/>
-      <c r="P72" t="inlineStr">
-        <is>
-          <t>Stortannsjön, Ång</t>
-        </is>
-      </c>
-      <c r="Q72" t="n">
-        <v>636760</v>
-      </c>
-      <c r="R72" t="n">
-        <v>7014309</v>
-      </c>
-      <c r="S72" t="n">
-        <v>5</v>
-      </c>
-      <c r="T72" t="inlineStr">
-        <is>
-          <t>Västernorrland</t>
-        </is>
-      </c>
-      <c r="U72" t="inlineStr">
-        <is>
-          <t>Sollefteå</t>
-        </is>
-      </c>
-      <c r="V72" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W72" t="inlineStr">
-        <is>
-          <t>Överlännäs</t>
-        </is>
-      </c>
-      <c r="Y72" t="inlineStr">
-        <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="Z72" t="inlineStr">
-        <is>
-          <t>10:02</t>
-        </is>
-      </c>
-      <c r="AA72" t="inlineStr">
-        <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="AB72" t="inlineStr">
-        <is>
-          <t>10:02</t>
-        </is>
-      </c>
-      <c r="AD72" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE72" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF72" t="inlineStr"/>
-      <c r="AG72" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT72" t="inlineStr"/>
-      <c r="AW72" t="inlineStr">
-        <is>
-          <t>Ann-Christine Borja</t>
-        </is>
-      </c>
-      <c r="AX72" t="inlineStr">
-        <is>
-          <t>Ann-Christine Borja, Markus Borja, Vivien Renaut</t>
-        </is>
-      </c>
-      <c r="AY72" t="inlineStr"/>
-      <c r="AZ72" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/137044060</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="n">
-        <v>137044061</v>
-      </c>
-      <c r="B73" t="n">
-        <v>99376</v>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E73" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K73" t="inlineStr"/>
-      <c r="L73" t="inlineStr"/>
-      <c r="N73" t="inlineStr"/>
-      <c r="P73" t="inlineStr">
-        <is>
-          <t>Stortannsjön, Ång</t>
-        </is>
-      </c>
-      <c r="Q73" t="n">
-        <v>636781</v>
-      </c>
-      <c r="R73" t="n">
-        <v>7014323</v>
-      </c>
-      <c r="S73" t="n">
-        <v>5</v>
-      </c>
-      <c r="T73" t="inlineStr">
-        <is>
-          <t>Västernorrland</t>
-        </is>
-      </c>
-      <c r="U73" t="inlineStr">
-        <is>
-          <t>Sollefteå</t>
-        </is>
-      </c>
-      <c r="V73" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W73" t="inlineStr">
-        <is>
-          <t>Överlännäs</t>
-        </is>
-      </c>
-      <c r="Y73" t="inlineStr">
-        <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="Z73" t="inlineStr">
-        <is>
-          <t>10:10</t>
-        </is>
-      </c>
-      <c r="AA73" t="inlineStr">
-        <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="AB73" t="inlineStr">
-        <is>
-          <t>10:10</t>
-        </is>
-      </c>
-      <c r="AD73" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE73" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF73" t="inlineStr"/>
-      <c r="AG73" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT73" t="inlineStr"/>
-      <c r="AW73" t="inlineStr">
-        <is>
-          <t>Ann-Christine Borja</t>
-        </is>
-      </c>
-      <c r="AX73" t="inlineStr">
-        <is>
-          <t>Ann-Christine Borja, Markus Borja, Vivien Renaut</t>
-        </is>
-      </c>
-      <c r="AY73" t="inlineStr"/>
-      <c r="AZ73" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/137044061</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="n">
-        <v>137044062</v>
-      </c>
-      <c r="B74" t="n">
-        <v>99376</v>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E74" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>117</t>
-        </is>
-      </c>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K74" t="inlineStr"/>
-      <c r="L74" t="inlineStr"/>
-      <c r="N74" t="inlineStr"/>
-      <c r="P74" t="inlineStr">
-        <is>
-          <t>Stortannsjön, Ång</t>
-        </is>
-      </c>
-      <c r="Q74" t="n">
-        <v>636772</v>
-      </c>
-      <c r="R74" t="n">
-        <v>7014326</v>
-      </c>
-      <c r="S74" t="n">
-        <v>5</v>
-      </c>
-      <c r="T74" t="inlineStr">
-        <is>
-          <t>Västernorrland</t>
-        </is>
-      </c>
-      <c r="U74" t="inlineStr">
-        <is>
-          <t>Sollefteå</t>
-        </is>
-      </c>
-      <c r="V74" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W74" t="inlineStr">
-        <is>
-          <t>Överlännäs</t>
-        </is>
-      </c>
-      <c r="Y74" t="inlineStr">
-        <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="Z74" t="inlineStr">
-        <is>
-          <t>10:26</t>
-        </is>
-      </c>
-      <c r="AA74" t="inlineStr">
-        <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="AB74" t="inlineStr">
-        <is>
-          <t>10:26</t>
-        </is>
-      </c>
-      <c r="AD74" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE74" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF74" t="inlineStr"/>
-      <c r="AG74" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT74" t="inlineStr"/>
-      <c r="AW74" t="inlineStr">
-        <is>
-          <t>Ann-Christine Borja</t>
-        </is>
-      </c>
-      <c r="AX74" t="inlineStr">
-        <is>
-          <t>Ann-Christine Borja, Markus Borja, Vivien Renaut</t>
-        </is>
-      </c>
-      <c r="AY74" t="inlineStr"/>
-      <c r="AZ74" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/137044062</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="n">
-        <v>137044064</v>
-      </c>
-      <c r="B75" t="n">
-        <v>99376</v>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E75" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
-      </c>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K75" t="inlineStr"/>
-      <c r="L75" t="inlineStr"/>
-      <c r="N75" t="inlineStr"/>
-      <c r="P75" t="inlineStr">
-        <is>
-          <t>Stortannsjön, Ång</t>
-        </is>
-      </c>
-      <c r="Q75" t="n">
-        <v>636806</v>
-      </c>
-      <c r="R75" t="n">
-        <v>7014282</v>
-      </c>
-      <c r="S75" t="n">
-        <v>5</v>
-      </c>
-      <c r="T75" t="inlineStr">
-        <is>
-          <t>Västernorrland</t>
-        </is>
-      </c>
-      <c r="U75" t="inlineStr">
-        <is>
-          <t>Sollefteå</t>
-        </is>
-      </c>
-      <c r="V75" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W75" t="inlineStr">
-        <is>
-          <t>Överlännäs</t>
-        </is>
-      </c>
-      <c r="Y75" t="inlineStr">
-        <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="Z75" t="inlineStr">
-        <is>
-          <t>10:48</t>
-        </is>
-      </c>
-      <c r="AA75" t="inlineStr">
-        <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="AB75" t="inlineStr">
-        <is>
-          <t>10:48</t>
-        </is>
-      </c>
-      <c r="AD75" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE75" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF75" t="inlineStr"/>
-      <c r="AG75" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT75" t="inlineStr"/>
-      <c r="AW75" t="inlineStr">
-        <is>
-          <t>Ann-Christine Borja</t>
-        </is>
-      </c>
-      <c r="AX75" t="inlineStr">
-        <is>
-          <t>Ann-Christine Borja, Markus Borja, Vivien Renaut</t>
-        </is>
-      </c>
-      <c r="AY75" t="inlineStr"/>
-      <c r="AZ75" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/137044064</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="n">
-        <v>137044080</v>
-      </c>
-      <c r="B76" t="n">
-        <v>99376</v>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E76" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
-      <c r="J76" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K76" t="inlineStr"/>
-      <c r="L76" t="inlineStr"/>
-      <c r="N76" t="inlineStr"/>
-      <c r="P76" t="inlineStr">
-        <is>
-          <t>Stortannsjön, Ång</t>
-        </is>
-      </c>
-      <c r="Q76" t="n">
-        <v>636598</v>
-      </c>
-      <c r="R76" t="n">
-        <v>7014517</v>
-      </c>
-      <c r="S76" t="n">
-        <v>5</v>
-      </c>
-      <c r="T76" t="inlineStr">
-        <is>
-          <t>Västernorrland</t>
-        </is>
-      </c>
-      <c r="U76" t="inlineStr">
-        <is>
-          <t>Sollefteå</t>
-        </is>
-      </c>
-      <c r="V76" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W76" t="inlineStr">
-        <is>
-          <t>Överlännäs</t>
-        </is>
-      </c>
-      <c r="Y76" t="inlineStr">
-        <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="Z76" t="inlineStr">
-        <is>
-          <t>14:32</t>
-        </is>
-      </c>
-      <c r="AA76" t="inlineStr">
-        <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="AB76" t="inlineStr">
-        <is>
-          <t>14:32</t>
-        </is>
-      </c>
-      <c r="AD76" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE76" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF76" t="inlineStr"/>
-      <c r="AG76" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT76" t="inlineStr"/>
-      <c r="AW76" t="inlineStr">
-        <is>
-          <t>Ann-Christine Borja</t>
-        </is>
-      </c>
-      <c r="AX76" t="inlineStr">
-        <is>
-          <t>Ann-Christine Borja, Markus Borja, Vivien Renaut</t>
-        </is>
-      </c>
-      <c r="AY76" t="inlineStr"/>
-      <c r="AZ76" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/137044080</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="n">
-        <v>137040134</v>
-      </c>
-      <c r="B77" t="n">
-        <v>79246</v>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E77" t="n">
-        <v>228912</v>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>Mörk kolflarnlav</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>Carbonicola myrmecina</t>
-        </is>
-      </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr"/>
-      <c r="P77" t="inlineStr">
-        <is>
-          <t>Stortannsjön, Ång</t>
-        </is>
-      </c>
-      <c r="Q77" t="n">
-        <v>636580</v>
-      </c>
-      <c r="R77" t="n">
-        <v>7014518</v>
-      </c>
-      <c r="S77" t="n">
-        <v>3</v>
-      </c>
-      <c r="T77" t="inlineStr">
-        <is>
-          <t>Västernorrland</t>
-        </is>
-      </c>
-      <c r="U77" t="inlineStr">
-        <is>
-          <t>Sollefteå</t>
-        </is>
-      </c>
-      <c r="V77" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W77" t="inlineStr">
-        <is>
-          <t>Överlännäs</t>
-        </is>
-      </c>
-      <c r="Y77" t="inlineStr">
-        <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="Z77" t="inlineStr">
-        <is>
-          <t>14:37</t>
-        </is>
-      </c>
-      <c r="AA77" t="inlineStr">
-        <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="AB77" t="inlineStr">
-        <is>
-          <t>14:37</t>
-        </is>
-      </c>
-      <c r="AD77" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE77" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG77" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT77" t="inlineStr"/>
-      <c r="AW77" t="inlineStr">
-        <is>
-          <t>Markus Borja</t>
-        </is>
-      </c>
-      <c r="AX77" t="inlineStr">
-        <is>
-          <t>Markus Borja</t>
-        </is>
-      </c>
-      <c r="AY77" t="inlineStr"/>
-      <c r="AZ77" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/137040134</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="n">
-        <v>137040136</v>
-      </c>
-      <c r="B78" t="n">
-        <v>79246</v>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E78" t="n">
-        <v>228912</v>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>Mörk kolflarnlav</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>Carbonicola myrmecina</t>
-        </is>
-      </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr"/>
-      <c r="P78" t="inlineStr">
-        <is>
-          <t>Stortannsjön, Ång</t>
-        </is>
-      </c>
-      <c r="Q78" t="n">
-        <v>636552</v>
-      </c>
-      <c r="R78" t="n">
-        <v>7014536</v>
-      </c>
-      <c r="S78" t="n">
-        <v>3</v>
-      </c>
-      <c r="T78" t="inlineStr">
-        <is>
-          <t>Västernorrland</t>
-        </is>
-      </c>
-      <c r="U78" t="inlineStr">
-        <is>
-          <t>Sollefteå</t>
-        </is>
-      </c>
-      <c r="V78" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W78" t="inlineStr">
-        <is>
-          <t>Överlännäs</t>
-        </is>
-      </c>
-      <c r="Y78" t="inlineStr">
-        <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="Z78" t="inlineStr">
-        <is>
-          <t>14:47</t>
-        </is>
-      </c>
-      <c r="AA78" t="inlineStr">
-        <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="AB78" t="inlineStr">
-        <is>
-          <t>14:47</t>
-        </is>
-      </c>
-      <c r="AD78" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE78" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG78" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT78" t="inlineStr"/>
-      <c r="AW78" t="inlineStr">
-        <is>
-          <t>Markus Borja</t>
-        </is>
-      </c>
-      <c r="AX78" t="inlineStr">
-        <is>
-          <t>Markus Borja</t>
-        </is>
-      </c>
-      <c r="AY78" t="inlineStr"/>
-      <c r="AZ78" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/137040136</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="n">
-        <v>137016336</v>
-      </c>
-      <c r="B79" t="n">
-        <v>79511</v>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E79" t="n">
-        <v>260591</v>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>Talltagel</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>Bryoria fremontii</t>
-        </is>
-      </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr"/>
-      <c r="J79" t="inlineStr"/>
-      <c r="K79" t="inlineStr"/>
-      <c r="N79" t="inlineStr"/>
-      <c r="P79" t="inlineStr">
-        <is>
-          <t>Stortannsjön, Ång</t>
-        </is>
-      </c>
-      <c r="Q79" t="n">
-        <v>636512</v>
-      </c>
-      <c r="R79" t="n">
-        <v>7014375</v>
-      </c>
-      <c r="S79" t="n">
-        <v>5</v>
-      </c>
-      <c r="T79" t="inlineStr">
-        <is>
-          <t>Västernorrland</t>
-        </is>
-      </c>
-      <c r="U79" t="inlineStr">
-        <is>
-          <t>Sollefteå</t>
-        </is>
-      </c>
-      <c r="V79" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W79" t="inlineStr">
-        <is>
-          <t>Överlännäs</t>
-        </is>
-      </c>
-      <c r="Y79" t="inlineStr">
-        <is>
-          <t>2026-10-02</t>
-        </is>
-      </c>
-      <c r="Z79" t="inlineStr">
-        <is>
-          <t>11:12</t>
-        </is>
-      </c>
-      <c r="AA79" t="inlineStr">
-        <is>
-          <t>2026-10-02</t>
-        </is>
-      </c>
-      <c r="AB79" t="inlineStr">
-        <is>
-          <t>11:12</t>
-        </is>
-      </c>
-      <c r="AD79" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE79" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF79" t="inlineStr"/>
-      <c r="AG79" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ79" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK79" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO79" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AT79" t="inlineStr"/>
-      <c r="AW79" t="inlineStr">
-        <is>
-          <t>Ann-Christine Borja</t>
-        </is>
-      </c>
-      <c r="AX79" t="inlineStr">
-        <is>
-          <t>Ann-Christine Borja, Markus Borja</t>
-        </is>
-      </c>
-      <c r="AY79" t="inlineStr"/>
-      <c r="AZ79" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/137016336</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="n">
-        <v>137016339</v>
-      </c>
-      <c r="B80" t="n">
-        <v>79511</v>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E80" t="n">
-        <v>260591</v>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>Talltagel</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>Bryoria fremontii</t>
-        </is>
-      </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr"/>
-      <c r="J80" t="inlineStr"/>
-      <c r="K80" t="inlineStr"/>
-      <c r="N80" t="inlineStr"/>
-      <c r="P80" t="inlineStr">
-        <is>
-          <t>Stortannsjön, Ång</t>
-        </is>
-      </c>
-      <c r="Q80" t="n">
-        <v>636457</v>
-      </c>
-      <c r="R80" t="n">
-        <v>7014405</v>
-      </c>
-      <c r="S80" t="n">
-        <v>5</v>
-      </c>
-      <c r="T80" t="inlineStr">
-        <is>
-          <t>Västernorrland</t>
-        </is>
-      </c>
-      <c r="U80" t="inlineStr">
-        <is>
-          <t>Sollefteå</t>
-        </is>
-      </c>
-      <c r="V80" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W80" t="inlineStr">
-        <is>
-          <t>Överlännäs</t>
-        </is>
-      </c>
-      <c r="Y80" t="inlineStr">
-        <is>
-          <t>2026-10-02</t>
-        </is>
-      </c>
-      <c r="Z80" t="inlineStr">
-        <is>
-          <t>11:22</t>
-        </is>
-      </c>
-      <c r="AA80" t="inlineStr">
-        <is>
-          <t>2026-10-02</t>
-        </is>
-      </c>
-      <c r="AB80" t="inlineStr">
-        <is>
-          <t>11:22</t>
-        </is>
-      </c>
-      <c r="AD80" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE80" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF80" t="inlineStr"/>
-      <c r="AG80" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ80" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK80" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO80" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AT80" t="inlineStr"/>
-      <c r="AW80" t="inlineStr">
-        <is>
-          <t>Ann-Christine Borja</t>
-        </is>
-      </c>
-      <c r="AX80" t="inlineStr">
-        <is>
-          <t>Ann-Christine Borja</t>
-        </is>
-      </c>
-      <c r="AY80" t="inlineStr"/>
-      <c r="AZ80" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/137016339</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="n">
-        <v>137016342</v>
-      </c>
-      <c r="B81" t="n">
-        <v>79511</v>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E81" t="n">
-        <v>260591</v>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>Talltagel</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>Bryoria fremontii</t>
-        </is>
-      </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr"/>
-      <c r="J81" t="inlineStr"/>
-      <c r="K81" t="inlineStr"/>
-      <c r="N81" t="inlineStr"/>
-      <c r="P81" t="inlineStr">
-        <is>
-          <t>Stortannsjön, Ång</t>
-        </is>
-      </c>
-      <c r="Q81" t="n">
-        <v>636417</v>
-      </c>
-      <c r="R81" t="n">
-        <v>7014452</v>
-      </c>
-      <c r="S81" t="n">
-        <v>5</v>
-      </c>
-      <c r="T81" t="inlineStr">
-        <is>
-          <t>Västernorrland</t>
-        </is>
-      </c>
-      <c r="U81" t="inlineStr">
-        <is>
-          <t>Sollefteå</t>
-        </is>
-      </c>
-      <c r="V81" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W81" t="inlineStr">
-        <is>
-          <t>Överlännäs</t>
-        </is>
-      </c>
-      <c r="Y81" t="inlineStr">
-        <is>
-          <t>2026-10-02</t>
-        </is>
-      </c>
-      <c r="Z81" t="inlineStr">
-        <is>
-          <t>11:40</t>
-        </is>
-      </c>
-      <c r="AA81" t="inlineStr">
-        <is>
-          <t>2026-10-02</t>
-        </is>
-      </c>
-      <c r="AB81" t="inlineStr">
-        <is>
-          <t>11:40</t>
-        </is>
-      </c>
-      <c r="AD81" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE81" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF81" t="inlineStr"/>
-      <c r="AG81" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ81" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK81" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO81" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AT81" t="inlineStr"/>
-      <c r="AW81" t="inlineStr">
-        <is>
-          <t>Ann-Christine Borja</t>
-        </is>
-      </c>
-      <c r="AX81" t="inlineStr">
-        <is>
-          <t>Ann-Christine Borja</t>
-        </is>
-      </c>
-      <c r="AY81" t="inlineStr"/>
-      <c r="AZ81" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/137016342</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="n">
-        <v>137016345</v>
-      </c>
-      <c r="B82" t="n">
-        <v>79511</v>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E82" t="n">
-        <v>260591</v>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>Talltagel</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>Bryoria fremontii</t>
-        </is>
-      </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr"/>
-      <c r="J82" t="inlineStr"/>
-      <c r="K82" t="inlineStr"/>
-      <c r="N82" t="inlineStr"/>
-      <c r="P82" t="inlineStr">
-        <is>
-          <t>Stortannsjön, Ång</t>
-        </is>
-      </c>
-      <c r="Q82" t="n">
-        <v>636407</v>
-      </c>
-      <c r="R82" t="n">
-        <v>7014480</v>
-      </c>
-      <c r="S82" t="n">
-        <v>5</v>
-      </c>
-      <c r="T82" t="inlineStr">
-        <is>
-          <t>Västernorrland</t>
-        </is>
-      </c>
-      <c r="U82" t="inlineStr">
-        <is>
-          <t>Sollefteå</t>
-        </is>
-      </c>
-      <c r="V82" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W82" t="inlineStr">
-        <is>
-          <t>Överlännäs</t>
-        </is>
-      </c>
-      <c r="Y82" t="inlineStr">
-        <is>
-          <t>2026-10-02</t>
-        </is>
-      </c>
-      <c r="Z82" t="inlineStr">
-        <is>
-          <t>11:59</t>
-        </is>
-      </c>
-      <c r="AA82" t="inlineStr">
-        <is>
-          <t>2026-10-02</t>
-        </is>
-      </c>
-      <c r="AB82" t="inlineStr">
-        <is>
-          <t>11:59</t>
-        </is>
-      </c>
-      <c r="AD82" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE82" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF82" t="inlineStr"/>
-      <c r="AG82" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ82" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK82" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO82" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AT82" t="inlineStr"/>
-      <c r="AW82" t="inlineStr">
-        <is>
-          <t>Ann-Christine Borja</t>
-        </is>
-      </c>
-      <c r="AX82" t="inlineStr">
-        <is>
-          <t>Ann-Christine Borja</t>
-        </is>
-      </c>
-      <c r="AY82" t="inlineStr"/>
-      <c r="AZ82" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/137016345</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="n">
-        <v>137016346</v>
-      </c>
-      <c r="B83" t="n">
-        <v>79511</v>
-      </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E83" t="n">
-        <v>260591</v>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>Talltagel</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>Bryoria fremontii</t>
-        </is>
-      </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr"/>
-      <c r="J83" t="inlineStr"/>
-      <c r="K83" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
-      <c r="N83" t="inlineStr"/>
-      <c r="P83" t="inlineStr">
-        <is>
-          <t>Stortannsjön, Ång</t>
-        </is>
-      </c>
-      <c r="Q83" t="n">
-        <v>636450</v>
-      </c>
-      <c r="R83" t="n">
-        <v>7014535</v>
-      </c>
-      <c r="S83" t="n">
-        <v>5</v>
-      </c>
-      <c r="T83" t="inlineStr">
-        <is>
-          <t>Västernorrland</t>
-        </is>
-      </c>
-      <c r="U83" t="inlineStr">
-        <is>
-          <t>Sollefteå</t>
-        </is>
-      </c>
-      <c r="V83" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W83" t="inlineStr">
-        <is>
-          <t>Överlännäs</t>
-        </is>
-      </c>
-      <c r="Y83" t="inlineStr">
-        <is>
-          <t>2026-10-02</t>
-        </is>
-      </c>
-      <c r="Z83" t="inlineStr">
-        <is>
-          <t>12:05</t>
-        </is>
-      </c>
-      <c r="AA83" t="inlineStr">
-        <is>
-          <t>2026-10-02</t>
-        </is>
-      </c>
-      <c r="AB83" t="inlineStr">
-        <is>
-          <t>12:05</t>
-        </is>
-      </c>
-      <c r="AD83" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE83" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF83" t="inlineStr"/>
-      <c r="AG83" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ83" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK83" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO83" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AT83" t="inlineStr"/>
-      <c r="AW83" t="inlineStr">
-        <is>
-          <t>Ann-Christine Borja</t>
-        </is>
-      </c>
-      <c r="AX83" t="inlineStr">
-        <is>
-          <t>Ann-Christine Borja</t>
-        </is>
-      </c>
-      <c r="AY83" t="inlineStr"/>
-      <c r="AZ83" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/137016346</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="n">
-        <v>137016348</v>
-      </c>
-      <c r="B84" t="n">
-        <v>79511</v>
-      </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E84" t="n">
-        <v>260591</v>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>Talltagel</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>Bryoria fremontii</t>
-        </is>
-      </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr"/>
-      <c r="J84" t="inlineStr"/>
-      <c r="K84" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
-      <c r="N84" t="inlineStr"/>
-      <c r="P84" t="inlineStr">
-        <is>
-          <t>Stortannsjön, Ång</t>
-        </is>
-      </c>
-      <c r="Q84" t="n">
-        <v>636479</v>
-      </c>
-      <c r="R84" t="n">
-        <v>7014523</v>
-      </c>
-      <c r="S84" t="n">
-        <v>5</v>
-      </c>
-      <c r="T84" t="inlineStr">
-        <is>
-          <t>Västernorrland</t>
-        </is>
-      </c>
-      <c r="U84" t="inlineStr">
-        <is>
-          <t>Sollefteå</t>
-        </is>
-      </c>
-      <c r="V84" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W84" t="inlineStr">
-        <is>
-          <t>Överlännäs</t>
-        </is>
-      </c>
-      <c r="Y84" t="inlineStr">
-        <is>
-          <t>2026-10-02</t>
-        </is>
-      </c>
-      <c r="Z84" t="inlineStr">
-        <is>
-          <t>12:09</t>
-        </is>
-      </c>
-      <c r="AA84" t="inlineStr">
-        <is>
-          <t>2026-10-02</t>
-        </is>
-      </c>
-      <c r="AB84" t="inlineStr">
-        <is>
-          <t>12:09</t>
-        </is>
-      </c>
-      <c r="AD84" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE84" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF84" t="inlineStr"/>
-      <c r="AG84" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ84" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK84" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO84" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AT84" t="inlineStr"/>
-      <c r="AW84" t="inlineStr">
-        <is>
-          <t>Ann-Christine Borja</t>
-        </is>
-      </c>
-      <c r="AX84" t="inlineStr">
-        <is>
-          <t>Ann-Christine Borja</t>
-        </is>
-      </c>
-      <c r="AY84" t="inlineStr"/>
-      <c r="AZ84" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/137016348</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="n">
-        <v>137016353</v>
-      </c>
-      <c r="B85" t="n">
-        <v>79511</v>
-      </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E85" t="n">
-        <v>260591</v>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>Talltagel</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>Bryoria fremontii</t>
-        </is>
-      </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr"/>
-      <c r="J85" t="inlineStr"/>
-      <c r="K85" t="inlineStr"/>
-      <c r="N85" t="inlineStr"/>
-      <c r="P85" t="inlineStr">
-        <is>
-          <t>Stortannsjön, Ång</t>
-        </is>
-      </c>
-      <c r="Q85" t="n">
-        <v>636460</v>
-      </c>
-      <c r="R85" t="n">
-        <v>7014451</v>
-      </c>
-      <c r="S85" t="n">
-        <v>5</v>
-      </c>
-      <c r="T85" t="inlineStr">
-        <is>
-          <t>Västernorrland</t>
-        </is>
-      </c>
-      <c r="U85" t="inlineStr">
-        <is>
-          <t>Sollefteå</t>
-        </is>
-      </c>
-      <c r="V85" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W85" t="inlineStr">
-        <is>
-          <t>Överlännäs</t>
-        </is>
-      </c>
-      <c r="Y85" t="inlineStr">
-        <is>
-          <t>2026-10-02</t>
-        </is>
-      </c>
-      <c r="Z85" t="inlineStr">
-        <is>
-          <t>12:28</t>
-        </is>
-      </c>
-      <c r="AA85" t="inlineStr">
-        <is>
-          <t>2026-10-02</t>
-        </is>
-      </c>
-      <c r="AB85" t="inlineStr">
-        <is>
-          <t>12:28</t>
-        </is>
-      </c>
-      <c r="AD85" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE85" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF85" t="inlineStr"/>
-      <c r="AG85" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ85" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK85" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO85" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AT85" t="inlineStr"/>
-      <c r="AW85" t="inlineStr">
-        <is>
-          <t>Ann-Christine Borja</t>
-        </is>
-      </c>
-      <c r="AX85" t="inlineStr">
-        <is>
-          <t>Ann-Christine Borja</t>
-        </is>
-      </c>
-      <c r="AY85" t="inlineStr"/>
-      <c r="AZ85" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/137016353</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="n">
-        <v>137040099</v>
-      </c>
-      <c r="B86" t="n">
-        <v>79511</v>
-      </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E86" t="n">
-        <v>260591</v>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>Talltagel</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>Bryoria fremontii</t>
-        </is>
-      </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr"/>
-      <c r="P86" t="inlineStr">
-        <is>
-          <t>Stortannsjön, Ång</t>
-        </is>
-      </c>
-      <c r="Q86" t="n">
-        <v>636705</v>
-      </c>
-      <c r="R86" t="n">
-        <v>7014243</v>
-      </c>
-      <c r="S86" t="n">
-        <v>3</v>
-      </c>
-      <c r="T86" t="inlineStr">
-        <is>
-          <t>Västernorrland</t>
-        </is>
-      </c>
-      <c r="U86" t="inlineStr">
-        <is>
-          <t>Sollefteå</t>
-        </is>
-      </c>
-      <c r="V86" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W86" t="inlineStr">
-        <is>
-          <t>Överlännäs</t>
-        </is>
-      </c>
-      <c r="Y86" t="inlineStr">
-        <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="Z86" t="inlineStr">
-        <is>
-          <t>08:49</t>
-        </is>
-      </c>
-      <c r="AA86" t="inlineStr">
-        <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="AB86" t="inlineStr">
-        <is>
-          <t>08:49</t>
-        </is>
-      </c>
-      <c r="AD86" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE86" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG86" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT86" t="inlineStr"/>
-      <c r="AW86" t="inlineStr">
-        <is>
-          <t>Markus Borja</t>
-        </is>
-      </c>
-      <c r="AX86" t="inlineStr">
-        <is>
-          <t>Markus Borja, Vivien Renaut, Ann-Christine Borja</t>
-        </is>
-      </c>
-      <c r="AY86" t="inlineStr"/>
-      <c r="AZ86" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/137040099</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="n">
-        <v>137044071</v>
-      </c>
-      <c r="B87" t="n">
-        <v>79511</v>
-      </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E87" t="n">
-        <v>260591</v>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>Talltagel</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>Bryoria fremontii</t>
-        </is>
-      </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr"/>
-      <c r="J87" t="inlineStr"/>
-      <c r="K87" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
-      <c r="N87" t="inlineStr"/>
-      <c r="P87" t="inlineStr">
-        <is>
-          <t>Stortannsjön, Ång</t>
-        </is>
-      </c>
-      <c r="Q87" t="n">
-        <v>636845</v>
-      </c>
-      <c r="R87" t="n">
-        <v>7014233</v>
-      </c>
-      <c r="S87" t="n">
-        <v>5</v>
-      </c>
-      <c r="T87" t="inlineStr">
-        <is>
-          <t>Västernorrland</t>
-        </is>
-      </c>
-      <c r="U87" t="inlineStr">
-        <is>
-          <t>Sollefteå</t>
-        </is>
-      </c>
-      <c r="V87" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W87" t="inlineStr">
-        <is>
-          <t>Överlännäs</t>
-        </is>
-      </c>
-      <c r="Y87" t="inlineStr">
-        <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="Z87" t="inlineStr">
-        <is>
-          <t>12:09</t>
-        </is>
-      </c>
-      <c r="AA87" t="inlineStr">
-        <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="AB87" t="inlineStr">
-        <is>
-          <t>12:09</t>
-        </is>
-      </c>
-      <c r="AD87" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE87" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF87" t="inlineStr"/>
-      <c r="AG87" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ87" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK87" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO87" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AT87" t="inlineStr"/>
-      <c r="AW87" t="inlineStr">
-        <is>
-          <t>Ann-Christine Borja</t>
-        </is>
-      </c>
-      <c r="AX87" t="inlineStr">
-        <is>
-          <t>Ann-Christine Borja</t>
-        </is>
-      </c>
-      <c r="AY87" t="inlineStr"/>
-      <c r="AZ87" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/137044071</t>
         </is>
@@ -11478,31 +8411,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 25855-2025 artfynd.xlsx
+++ b/artfynd/A 25855-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137044063</v>
       </c>
       <c r="B2" t="n">
-        <v>92414</v>
+        <v>92416</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -814,7 +814,7 @@
         <v>137040165</v>
       </c>
       <c r="B3" t="n">
-        <v>92976</v>
+        <v>92978</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -931,7 +931,7 @@
         <v>137016354</v>
       </c>
       <c r="B4" t="n">
-        <v>93457</v>
+        <v>93458</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1047,7 +1047,7 @@
         <v>137016293</v>
       </c>
       <c r="B5" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1159,7 +1159,7 @@
         <v>137016298</v>
       </c>
       <c r="B6" t="n">
-        <v>93479</v>
+        <v>93480</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1275,7 +1275,7 @@
         <v>137016289</v>
       </c>
       <c r="B7" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1406,7 +1406,7 @@
         <v>137016306</v>
       </c>
       <c r="B8" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1537,7 +1537,7 @@
         <v>137016332</v>
       </c>
       <c r="B9" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1668,7 +1668,7 @@
         <v>137016333</v>
       </c>
       <c r="B10" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1799,7 +1799,7 @@
         <v>137016335</v>
       </c>
       <c r="B11" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1930,7 +1930,7 @@
         <v>137016337</v>
       </c>
       <c r="B12" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2061,7 +2061,7 @@
         <v>137016340</v>
       </c>
       <c r="B13" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2192,7 +2192,7 @@
         <v>137016349</v>
       </c>
       <c r="B14" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2323,7 +2323,7 @@
         <v>137016350</v>
       </c>
       <c r="B15" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2454,7 +2454,7 @@
         <v>137040167</v>
       </c>
       <c r="B16" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2566,7 +2566,7 @@
         <v>137040169</v>
       </c>
       <c r="B17" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2678,7 +2678,7 @@
         <v>137040181</v>
       </c>
       <c r="B18" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2795,7 +2795,7 @@
         <v>137044055</v>
       </c>
       <c r="B19" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2926,7 +2926,7 @@
         <v>137044068</v>
       </c>
       <c r="B20" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3057,7 +3057,7 @@
         <v>137044072</v>
       </c>
       <c r="B21" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3188,7 +3188,7 @@
         <v>137016334</v>
       </c>
       <c r="B22" t="n">
-        <v>79525</v>
+        <v>79527</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3319,7 +3319,7 @@
         <v>137016341</v>
       </c>
       <c r="B23" t="n">
-        <v>79525</v>
+        <v>79527</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3450,7 +3450,7 @@
         <v>137016351</v>
       </c>
       <c r="B24" t="n">
-        <v>79525</v>
+        <v>79527</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3581,7 +3581,7 @@
         <v>137044056</v>
       </c>
       <c r="B25" t="n">
-        <v>79525</v>
+        <v>79527</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3712,7 +3712,7 @@
         <v>137016288</v>
       </c>
       <c r="B26" t="n">
-        <v>80120</v>
+        <v>80122</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3824,7 +3824,7 @@
         <v>137016299</v>
       </c>
       <c r="B27" t="n">
-        <v>80120</v>
+        <v>80122</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3936,7 +3936,7 @@
         <v>137016303</v>
       </c>
       <c r="B28" t="n">
-        <v>80120</v>
+        <v>80122</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4048,7 +4048,7 @@
         <v>137016301</v>
       </c>
       <c r="B29" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4168,7 +4168,7 @@
         <v>137040182</v>
       </c>
       <c r="B30" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4293,7 +4293,7 @@
         <v>137016287</v>
       </c>
       <c r="B31" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4418,7 +4418,7 @@
         <v>137016290</v>
       </c>
       <c r="B32" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4543,7 +4543,7 @@
         <v>137016291</v>
       </c>
       <c r="B33" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4668,7 +4668,7 @@
         <v>137016292</v>
       </c>
       <c r="B34" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4793,7 +4793,7 @@
         <v>137016294</v>
       </c>
       <c r="B35" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4918,7 +4918,7 @@
         <v>137016295</v>
       </c>
       <c r="B36" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5043,7 +5043,7 @@
         <v>137016296</v>
       </c>
       <c r="B37" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5168,7 +5168,7 @@
         <v>137016297</v>
       </c>
       <c r="B38" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5293,7 +5293,7 @@
         <v>137016300</v>
       </c>
       <c r="B39" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5418,7 +5418,7 @@
         <v>137016304</v>
       </c>
       <c r="B40" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5543,7 +5543,7 @@
         <v>137016307</v>
       </c>
       <c r="B41" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5668,7 +5668,7 @@
         <v>137016344</v>
       </c>
       <c r="B42" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5793,7 +5793,7 @@
         <v>137040177</v>
       </c>
       <c r="B43" t="n">
-        <v>58182</v>
+        <v>58184</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5918,7 +5918,7 @@
         <v>137040164</v>
       </c>
       <c r="B44" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6043,7 +6043,7 @@
         <v>137040166</v>
       </c>
       <c r="B45" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6168,7 +6168,7 @@
         <v>137040168</v>
       </c>
       <c r="B46" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6293,7 +6293,7 @@
         <v>137040189</v>
       </c>
       <c r="B47" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6418,7 +6418,7 @@
         <v>137044057</v>
       </c>
       <c r="B48" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6543,7 +6543,7 @@
         <v>137044059</v>
       </c>
       <c r="B49" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6668,7 +6668,7 @@
         <v>137044060</v>
       </c>
       <c r="B50" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6793,7 +6793,7 @@
         <v>137044061</v>
       </c>
       <c r="B51" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6918,7 +6918,7 @@
         <v>137044062</v>
       </c>
       <c r="B52" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -7043,7 +7043,7 @@
         <v>137044064</v>
       </c>
       <c r="B53" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -7168,7 +7168,7 @@
         <v>137044080</v>
       </c>
       <c r="B54" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7293,7 +7293,7 @@
         <v>137016336</v>
       </c>
       <c r="B55" t="n">
-        <v>79524</v>
+        <v>79526</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7424,7 +7424,7 @@
         <v>137016339</v>
       </c>
       <c r="B56" t="n">
-        <v>79524</v>
+        <v>79526</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7555,7 +7555,7 @@
         <v>137016342</v>
       </c>
       <c r="B57" t="n">
-        <v>79524</v>
+        <v>79526</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7686,7 +7686,7 @@
         <v>137016345</v>
       </c>
       <c r="B58" t="n">
-        <v>79524</v>
+        <v>79526</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7817,7 +7817,7 @@
         <v>137016346</v>
       </c>
       <c r="B59" t="n">
-        <v>79524</v>
+        <v>79526</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7952,7 +7952,7 @@
         <v>137016348</v>
       </c>
       <c r="B60" t="n">
-        <v>79524</v>
+        <v>79526</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -8087,7 +8087,7 @@
         <v>137016353</v>
       </c>
       <c r="B61" t="n">
-        <v>79524</v>
+        <v>79526</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -8218,7 +8218,7 @@
         <v>137044071</v>
       </c>
       <c r="B62" t="n">
-        <v>79524</v>
+        <v>79526</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>

--- a/artfynd/A 25855-2025 artfynd.xlsx
+++ b/artfynd/A 25855-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ62"/>
+  <dimension ref="A1:AZ87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1156,48 +1156,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>137016298</v>
+        <v>137040122</v>
       </c>
       <c r="B6" t="n">
-        <v>93480</v>
+        <v>92108</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5966</v>
+        <v>5447</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Stortannsjön, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>636437</v>
+        <v>636830</v>
       </c>
       <c r="R6" t="n">
-        <v>7014437</v>
+        <v>7014277</v>
       </c>
       <c r="S6" t="n">
         <v>3</v>
@@ -1224,22 +1221,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1248,7 +1245,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1260,44 +1256,44 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Markus Borja, Diego Borja, Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016298</t>
+          <t>https://artportalen.se/Sighting/137040122</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>137016289</v>
+        <v>137016298</v>
       </c>
       <c r="B7" t="n">
-        <v>79503</v>
+        <v>93480</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>5966</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1310,10 +1306,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>636608</v>
+        <v>636437</v>
       </c>
       <c r="R7" t="n">
-        <v>7014302</v>
+        <v>7014437</v>
       </c>
       <c r="S7" t="n">
         <v>3</v>
@@ -1345,7 +1341,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1355,7 +1351,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1368,21 +1364,6 @@
       <c r="AG7" t="b">
         <v>0</v>
       </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
@@ -1391,19 +1372,19 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Markus Borja, Diego Borja, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016289</t>
+          <t>https://artportalen.se/Sighting/137016298</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>137016306</v>
+        <v>137016289</v>
       </c>
       <c r="B8" t="n">
         <v>79503</v>
@@ -1441,10 +1422,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>636566</v>
+        <v>636608</v>
       </c>
       <c r="R8" t="n">
-        <v>7014366</v>
+        <v>7014302</v>
       </c>
       <c r="S8" t="n">
         <v>3</v>
@@ -1476,7 +1457,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1486,7 +1467,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1528,13 +1509,13 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016306</t>
+          <t>https://artportalen.se/Sighting/137016289</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>137016332</v>
+        <v>137016306</v>
       </c>
       <c r="B9" t="n">
         <v>79503</v>
@@ -1572,13 +1553,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>636603</v>
+        <v>636566</v>
       </c>
       <c r="R9" t="n">
-        <v>7014322</v>
+        <v>7014366</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1607,7 +1588,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1617,7 +1598,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1648,24 +1629,24 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016332</t>
+          <t>https://artportalen.se/Sighting/137016306</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>137016333</v>
+        <v>137016332</v>
       </c>
       <c r="B10" t="n">
         <v>79503</v>
@@ -1703,10 +1684,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>636623</v>
+        <v>636603</v>
       </c>
       <c r="R10" t="n">
-        <v>7014305</v>
+        <v>7014322</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1738,7 +1719,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1748,7 +1729,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1790,13 +1771,13 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016333</t>
+          <t>https://artportalen.se/Sighting/137016332</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>137016335</v>
+        <v>137016333</v>
       </c>
       <c r="B11" t="n">
         <v>79503</v>
@@ -1834,10 +1815,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>636520</v>
+        <v>636623</v>
       </c>
       <c r="R11" t="n">
-        <v>7014374</v>
+        <v>7014305</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1869,7 +1850,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1879,7 +1860,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1921,13 +1902,13 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016335</t>
+          <t>https://artportalen.se/Sighting/137016333</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>137016337</v>
+        <v>137016335</v>
       </c>
       <c r="B12" t="n">
         <v>79503</v>
@@ -1965,10 +1946,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>636463</v>
+        <v>636520</v>
       </c>
       <c r="R12" t="n">
-        <v>7014402</v>
+        <v>7014374</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -2000,7 +1981,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2010,7 +1991,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2052,13 +2033,13 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016337</t>
+          <t>https://artportalen.se/Sighting/137016335</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>137016340</v>
+        <v>137016337</v>
       </c>
       <c r="B13" t="n">
         <v>79503</v>
@@ -2096,10 +2077,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>636419</v>
+        <v>636463</v>
       </c>
       <c r="R13" t="n">
-        <v>7014437</v>
+        <v>7014402</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2131,7 +2112,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2141,7 +2122,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2183,13 +2164,13 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016340</t>
+          <t>https://artportalen.se/Sighting/137016337</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>137016349</v>
+        <v>137016340</v>
       </c>
       <c r="B14" t="n">
         <v>79503</v>
@@ -2227,10 +2208,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>636488</v>
+        <v>636419</v>
       </c>
       <c r="R14" t="n">
-        <v>7014536</v>
+        <v>7014437</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2262,7 +2243,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2272,7 +2253,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2314,13 +2295,13 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016349</t>
+          <t>https://artportalen.se/Sighting/137016340</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>137016350</v>
+        <v>137016349</v>
       </c>
       <c r="B15" t="n">
         <v>79503</v>
@@ -2358,10 +2339,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>636466</v>
+        <v>636488</v>
       </c>
       <c r="R15" t="n">
-        <v>7014464</v>
+        <v>7014536</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2393,7 +2374,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2403,7 +2384,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2445,13 +2426,13 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016350</t>
+          <t>https://artportalen.se/Sighting/137016349</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>137040167</v>
+        <v>137016350</v>
       </c>
       <c r="B16" t="n">
         <v>79503</v>
@@ -2480,16 +2461,19 @@
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Stortannsjön, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>636743</v>
+        <v>636466</v>
       </c>
       <c r="R16" t="n">
-        <v>7014374</v>
+        <v>7014464</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2516,22 +2500,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2540,30 +2524,46 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Vivien Renaut</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Vivien Renaut</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137040167</t>
+          <t>https://artportalen.se/Sighting/137016350</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>137040169</v>
+        <v>137040102</v>
       </c>
       <c r="B17" t="n">
         <v>79503</v>
@@ -2592,19 +2592,22 @@
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Stortannsjön, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>636844</v>
+        <v>636758</v>
       </c>
       <c r="R17" t="n">
-        <v>7014273</v>
+        <v>7014258</v>
       </c>
       <c r="S17" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2633,7 +2636,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>09:08</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2643,7 +2646,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>09:08</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2652,30 +2655,46 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Vivien Renaut</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Vivien Renaut</t>
+          <t>Markus Borja, Vivien Renaut, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137040169</t>
+          <t>https://artportalen.se/Sighting/137040102</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>137040181</v>
+        <v>137040133</v>
       </c>
       <c r="B18" t="n">
         <v>79503</v>
@@ -2704,19 +2723,22 @@
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Stortannsjön, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>636605</v>
+        <v>636608</v>
       </c>
       <c r="R18" t="n">
-        <v>7014506</v>
+        <v>7014515</v>
       </c>
       <c r="S18" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2745,7 +2767,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2755,12 +2777,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:28</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Garnlav på tall</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2769,30 +2786,46 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Vivien Renaut</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Vivien Renaut</t>
+          <t>Markus Borja, Vivien Renaut, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137040181</t>
+          <t>https://artportalen.se/Sighting/137040133</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>137044055</v>
+        <v>137040161</v>
       </c>
       <c r="B19" t="n">
         <v>79503</v>
@@ -2830,13 +2863,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>636694</v>
+        <v>636549</v>
       </c>
       <c r="R19" t="n">
-        <v>7014252</v>
+        <v>7014491</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2865,7 +2898,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>08:47</t>
+          <t>18:07</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2875,7 +2908,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>08:47</t>
+          <t>18:07</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2906,24 +2939,24 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja, Vivien Renaut, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137044055</t>
+          <t>https://artportalen.se/Sighting/137040161</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>137044068</v>
+        <v>137040162</v>
       </c>
       <c r="B20" t="n">
         <v>79503</v>
@@ -2961,13 +2994,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>636901</v>
+        <v>636606</v>
       </c>
       <c r="R20" t="n">
-        <v>7014208</v>
+        <v>7014419</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2996,7 +3029,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3006,7 +3039,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3021,40 +3054,40 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja, Vivien Renaut, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137044068</t>
+          <t>https://artportalen.se/Sighting/137040162</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>137044072</v>
+        <v>137040167</v>
       </c>
       <c r="B21" t="n">
         <v>79503</v>
@@ -3083,19 +3116,16 @@
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Stortannsjön, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>636840</v>
+        <v>636743</v>
       </c>
       <c r="R21" t="n">
-        <v>7014233</v>
+        <v>7014374</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -3127,7 +3157,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3137,7 +3167,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3146,90 +3176,71 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Vivien Renaut</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Vivien Renaut</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137044072</t>
+          <t>https://artportalen.se/Sighting/137040167</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>137016334</v>
+        <v>137040169</v>
       </c>
       <c r="B22" t="n">
-        <v>79527</v>
+        <v>79503</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Stortannsjön, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>636591</v>
+        <v>636844</v>
       </c>
       <c r="R22" t="n">
-        <v>7014315</v>
+        <v>7014273</v>
       </c>
       <c r="S22" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3253,22 +3264,22 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3277,90 +3288,71 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Vivien Renaut</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Vivien Renaut</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016334</t>
+          <t>https://artportalen.se/Sighting/137040169</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>137016341</v>
+        <v>137040181</v>
       </c>
       <c r="B23" t="n">
-        <v>79527</v>
+        <v>79503</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Stortannsjön, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>636409</v>
+        <v>636605</v>
       </c>
       <c r="R23" t="n">
-        <v>7014452</v>
+        <v>7014506</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3384,22 +3376,27 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>14:28</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Garnlav på tall</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3408,71 +3405,55 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Vivien Renaut</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Vivien Renaut</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016341</t>
+          <t>https://artportalen.se/Sighting/137040181</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>137016351</v>
+        <v>137044055</v>
       </c>
       <c r="B24" t="n">
-        <v>79527</v>
+        <v>79503</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3485,10 +3466,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>636460</v>
+        <v>636694</v>
       </c>
       <c r="R24" t="n">
-        <v>7014454</v>
+        <v>7014252</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3515,22 +3496,22 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>08:47</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>08:47</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3572,38 +3553,38 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016351</t>
+          <t>https://artportalen.se/Sighting/137044055</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>137044056</v>
+        <v>137044068</v>
       </c>
       <c r="B25" t="n">
-        <v>79527</v>
+        <v>79503</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3616,10 +3597,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>636699</v>
+        <v>636901</v>
       </c>
       <c r="R25" t="n">
-        <v>7014271</v>
+        <v>7014208</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3651,7 +3632,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3661,7 +3642,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3703,54 +3684,57 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137044056</t>
+          <t>https://artportalen.se/Sighting/137044068</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>137016288</v>
+        <v>137044072</v>
       </c>
       <c r="B26" t="n">
-        <v>80122</v>
+        <v>79503</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Stortannsjön, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>636610</v>
+        <v>636840</v>
       </c>
       <c r="R26" t="n">
-        <v>7014307</v>
+        <v>7014233</v>
       </c>
       <c r="S26" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3774,22 +3758,22 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3798,71 +3782,90 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016288</t>
+          <t>https://artportalen.se/Sighting/137044072</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>137016299</v>
+        <v>137016334</v>
       </c>
       <c r="B27" t="n">
-        <v>80122</v>
+        <v>79527</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6453</v>
+        <v>6434</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Stortannsjön, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>636418</v>
+        <v>636591</v>
       </c>
       <c r="R27" t="n">
-        <v>7014453</v>
+        <v>7014315</v>
       </c>
       <c r="S27" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3891,7 +3894,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3901,7 +3904,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3910,71 +3913,90 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016299</t>
+          <t>https://artportalen.se/Sighting/137016334</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>137016303</v>
+        <v>137016341</v>
       </c>
       <c r="B28" t="n">
-        <v>80122</v>
+        <v>79527</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6453</v>
+        <v>6434</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Stortannsjön, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>636499</v>
+        <v>636409</v>
       </c>
       <c r="R28" t="n">
-        <v>7014546</v>
+        <v>7014452</v>
       </c>
       <c r="S28" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -4003,7 +4025,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -4013,7 +4035,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4022,33 +4044,49 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016303</t>
+          <t>https://artportalen.se/Sighting/137016341</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>137016301</v>
+        <v>137016351</v>
       </c>
       <c r="B29" t="n">
-        <v>58020</v>
+        <v>79527</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4056,31 +4094,26 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100049</v>
+        <v>6434</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -4088,13 +4121,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>636482</v>
+        <v>636460</v>
       </c>
       <c r="R29" t="n">
-        <v>7014533</v>
+        <v>7014454</v>
       </c>
       <c r="S29" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4123,7 +4156,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4133,7 +4166,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4142,33 +4175,49 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016301</t>
+          <t>https://artportalen.se/Sighting/137016351</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>137040182</v>
+        <v>137040100</v>
       </c>
       <c r="B30" t="n">
-        <v>58020</v>
+        <v>79527</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4176,31 +4225,26 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
+        <v>6434</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -4208,13 +4252,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>636550</v>
+        <v>636705</v>
       </c>
       <c r="R30" t="n">
-        <v>7014507</v>
+        <v>7014244</v>
       </c>
       <c r="S30" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4243,7 +4287,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4253,12 +4297,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:41</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Färska spår</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4267,65 +4306,76 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Vivien Renaut</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Vivien Renaut</t>
+          <t>Markus Borja, Vivien Renaut, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137040182</t>
+          <t>https://artportalen.se/Sighting/137040100</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>137016287</v>
+        <v>137044056</v>
       </c>
       <c r="B31" t="n">
-        <v>58023</v>
+        <v>79527</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>6434</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -4333,13 +4383,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>636606</v>
+        <v>636699</v>
       </c>
       <c r="R31" t="n">
-        <v>7014302</v>
+        <v>7014271</v>
       </c>
       <c r="S31" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4363,27 +4413,22 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>10:34</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Färska och Äldre ringhack på tall</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4392,33 +4437,49 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja, Diego Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016287</t>
+          <t>https://artportalen.se/Sighting/137044056</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>137016290</v>
+        <v>137040105</v>
       </c>
       <c r="B32" t="n">
-        <v>58023</v>
+        <v>79260</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4426,42 +4487,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Stortannsjön, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>636608</v>
+        <v>636730</v>
       </c>
       <c r="R32" t="n">
-        <v>7014302</v>
+        <v>7014286</v>
       </c>
       <c r="S32" t="n">
         <v>3</v>
@@ -4488,27 +4541,22 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>10:54</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4528,22 +4576,22 @@
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja, Diego Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016290</t>
+          <t>https://artportalen.se/Sighting/137040105</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>137016291</v>
+        <v>137040135</v>
       </c>
       <c r="B33" t="n">
-        <v>58023</v>
+        <v>79260</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4551,42 +4599,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Stortannsjön, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>636578</v>
+        <v>636582</v>
       </c>
       <c r="R33" t="n">
-        <v>7014320</v>
+        <v>7014519</v>
       </c>
       <c r="S33" t="n">
         <v>3</v>
@@ -4613,27 +4653,22 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>10:59</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4653,22 +4688,22 @@
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja, Diego Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016291</t>
+          <t>https://artportalen.se/Sighting/137040135</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>137016292</v>
+        <v>137016288</v>
       </c>
       <c r="B34" t="n">
-        <v>58023</v>
+        <v>80122</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4676,42 +4711,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Stortannsjön, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>636501</v>
+        <v>636610</v>
       </c>
       <c r="R34" t="n">
-        <v>7014381</v>
+        <v>7014307</v>
       </c>
       <c r="S34" t="n">
         <v>3</v>
@@ -4743,7 +4770,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4753,12 +4780,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>11:09</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4778,22 +4800,22 @@
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016292</t>
+          <t>https://artportalen.se/Sighting/137016288</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>137016294</v>
+        <v>137016299</v>
       </c>
       <c r="B35" t="n">
-        <v>58023</v>
+        <v>80122</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4801,42 +4823,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Stortannsjön, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>636486</v>
+        <v>636418</v>
       </c>
       <c r="R35" t="n">
-        <v>7014403</v>
+        <v>7014453</v>
       </c>
       <c r="S35" t="n">
         <v>3</v>
@@ -4868,7 +4882,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4878,12 +4892,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:16</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4903,22 +4912,22 @@
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016294</t>
+          <t>https://artportalen.se/Sighting/137016299</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>137016295</v>
+        <v>137016303</v>
       </c>
       <c r="B36" t="n">
-        <v>58023</v>
+        <v>80122</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4926,42 +4935,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Stortannsjön, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>636432</v>
+        <v>636499</v>
       </c>
       <c r="R36" t="n">
-        <v>7014422</v>
+        <v>7014546</v>
       </c>
       <c r="S36" t="n">
         <v>3</v>
@@ -4993,7 +4994,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -5003,12 +5004,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:28</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5028,22 +5024,22 @@
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016295</t>
+          <t>https://artportalen.se/Sighting/137016303</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>137016296</v>
+        <v>137040101</v>
       </c>
       <c r="B37" t="n">
-        <v>58023</v>
+        <v>80122</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5051,42 +5047,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Stortannsjön, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>636424</v>
+        <v>636731</v>
       </c>
       <c r="R37" t="n">
-        <v>7014437</v>
+        <v>7014243</v>
       </c>
       <c r="S37" t="n">
         <v>3</v>
@@ -5113,27 +5101,22 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>09:05</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>11:30</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack på tall</t>
+          <t>09:05</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5153,22 +5136,22 @@
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016296</t>
+          <t>https://artportalen.se/Sighting/137040101</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>137016297</v>
+        <v>137040104</v>
       </c>
       <c r="B38" t="n">
-        <v>58023</v>
+        <v>80122</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5176,42 +5159,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Stortannsjön, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>636448</v>
+        <v>636746</v>
       </c>
       <c r="R38" t="n">
-        <v>7014424</v>
+        <v>7014291</v>
       </c>
       <c r="S38" t="n">
         <v>3</v>
@@ -5238,27 +5213,22 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>11:35</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5278,54 +5248,49 @@
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016297</t>
+          <t>https://artportalen.se/Sighting/137040104</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>137016300</v>
+        <v>137040108</v>
       </c>
       <c r="B39" t="n">
-        <v>58023</v>
+        <v>80512</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>6456</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -5333,13 +5298,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>636398</v>
+        <v>636817</v>
       </c>
       <c r="R39" t="n">
-        <v>7014509</v>
+        <v>7014280</v>
       </c>
       <c r="S39" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5363,27 +5328,22 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>11:46</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5392,8 +5352,24 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ39" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK39" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO39" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
@@ -5403,54 +5379,49 @@
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja</t>
+          <t>Markus Borja, Vivien Renaut, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016300</t>
+          <t>https://artportalen.se/Sighting/137040108</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>137016304</v>
+        <v>137040110</v>
       </c>
       <c r="B40" t="n">
-        <v>58023</v>
+        <v>80512</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>6456</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -5458,10 +5429,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>636466</v>
+        <v>636815</v>
       </c>
       <c r="R40" t="n">
-        <v>7014462</v>
+        <v>7014278</v>
       </c>
       <c r="S40" t="n">
         <v>3</v>
@@ -5488,27 +5459,22 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>12:24</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5517,8 +5483,24 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ40" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK40" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO40" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
@@ -5528,54 +5510,49 @@
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja, Diego Borja</t>
+          <t>Markus Borja, Vivien Renaut, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016304</t>
+          <t>https://artportalen.se/Sighting/137040110</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>137016307</v>
+        <v>137040111</v>
       </c>
       <c r="B41" t="n">
-        <v>58023</v>
+        <v>80512</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>6456</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -5583,13 +5560,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>636566</v>
+        <v>636803</v>
       </c>
       <c r="R41" t="n">
-        <v>7014367</v>
+        <v>7014259</v>
       </c>
       <c r="S41" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5613,27 +5590,22 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>12:35</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5642,8 +5614,24 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
@@ -5653,39 +5641,39 @@
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Markus Borja, Vivien Renaut, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016307</t>
+          <t>https://artportalen.se/Sighting/137040111</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>137016344</v>
+        <v>137016301</v>
       </c>
       <c r="B42" t="n">
-        <v>58023</v>
+        <v>58020</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -5696,11 +5684,7 @@
       <c r="I42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M42" t="inlineStr"/>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -5708,13 +5692,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>636392</v>
+        <v>636482</v>
       </c>
       <c r="R42" t="n">
-        <v>7014473</v>
+        <v>7014533</v>
       </c>
       <c r="S42" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5743,7 +5727,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5753,12 +5737,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>11:50</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall.</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5773,59 +5752,55 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja, Markus Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016344</t>
+          <t>https://artportalen.se/Sighting/137016301</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>137040177</v>
+        <v>137040182</v>
       </c>
       <c r="B43" t="n">
-        <v>58184</v>
+        <v>58020</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+      <c r="M43" t="inlineStr"/>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -5833,13 +5808,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>636811</v>
+        <v>636550</v>
       </c>
       <c r="R43" t="n">
-        <v>7014284</v>
+        <v>7014507</v>
       </c>
       <c r="S43" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5868,7 +5843,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5878,12 +5853,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Läte</t>
+          <t>Färska spår</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5909,52 +5884,44 @@
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137040177</t>
+          <t>https://artportalen.se/Sighting/137040182</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>137040164</v>
+        <v>137016287</v>
       </c>
       <c r="B44" t="n">
-        <v>99391</v>
+        <v>58023</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr"/>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -5962,10 +5929,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>636776</v>
+        <v>636606</v>
       </c>
       <c r="R44" t="n">
-        <v>7014278</v>
+        <v>7014302</v>
       </c>
       <c r="S44" t="n">
         <v>3</v>
@@ -5992,22 +5959,27 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>09:05</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>09:05</t>
+          <t>10:34</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Färska och Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6016,70 +5988,61 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Vivien Renaut</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Vivien Renaut</t>
+          <t>Markus Borja, Ann-Christine Borja, Diego Borja</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137040164</t>
+          <t>https://artportalen.se/Sighting/137016287</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>137040166</v>
+        <v>137016290</v>
       </c>
       <c r="B45" t="n">
-        <v>99391</v>
+        <v>58023</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>115</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr"/>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -6087,10 +6050,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>636782</v>
+        <v>636608</v>
       </c>
       <c r="R45" t="n">
-        <v>7014300</v>
+        <v>7014302</v>
       </c>
       <c r="S45" t="n">
         <v>3</v>
@@ -6117,22 +6080,27 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>10:54</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6141,70 +6109,61 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Vivien Renaut</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Vivien Renaut</t>
+          <t>Markus Borja, Ann-Christine Borja, Diego Borja</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137040166</t>
+          <t>https://artportalen.se/Sighting/137016290</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>137040168</v>
+        <v>137016291</v>
       </c>
       <c r="B46" t="n">
-        <v>99391</v>
+        <v>58023</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr"/>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
@@ -6212,10 +6171,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>636758</v>
+        <v>636578</v>
       </c>
       <c r="R46" t="n">
-        <v>7014368</v>
+        <v>7014320</v>
       </c>
       <c r="S46" t="n">
         <v>3</v>
@@ -6242,22 +6201,27 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>10:59</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6266,70 +6230,61 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Vivien Renaut</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Vivien Renaut</t>
+          <t>Markus Borja, Ann-Christine Borja, Diego Borja</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137040168</t>
+          <t>https://artportalen.se/Sighting/137016291</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>137040189</v>
+        <v>137016292</v>
       </c>
       <c r="B47" t="n">
-        <v>99391</v>
+        <v>58023</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr"/>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
@@ -6337,13 +6292,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>636424</v>
+        <v>636501</v>
       </c>
       <c r="R47" t="n">
-        <v>7014610</v>
+        <v>7014381</v>
       </c>
       <c r="S47" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6367,22 +6322,27 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>11:09</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6391,70 +6351,61 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Vivien Renaut</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Vivien Renaut</t>
+          <t>Markus Borja, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137040189</t>
+          <t>https://artportalen.se/Sighting/137016292</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>137044057</v>
+        <v>137016294</v>
       </c>
       <c r="B48" t="n">
-        <v>99391</v>
+        <v>58023</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr"/>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -6462,13 +6413,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>636762</v>
+        <v>636486</v>
       </c>
       <c r="R48" t="n">
-        <v>7014263</v>
+        <v>7014403</v>
       </c>
       <c r="S48" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6492,22 +6443,27 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>11:16</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6516,70 +6472,61 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja, Markus Borja, Vivien Renaut</t>
+          <t>Markus Borja, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137044057</t>
+          <t>https://artportalen.se/Sighting/137016294</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>137044059</v>
+        <v>137016295</v>
       </c>
       <c r="B49" t="n">
-        <v>99391</v>
+        <v>58023</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>105</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr"/>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
@@ -6587,13 +6534,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>636736</v>
+        <v>636432</v>
       </c>
       <c r="R49" t="n">
-        <v>7014341</v>
+        <v>7014422</v>
       </c>
       <c r="S49" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6617,22 +6564,27 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>11:28</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6641,70 +6593,61 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja, Markus Borja, Vivien Renaut</t>
+          <t>Markus Borja, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137044059</t>
+          <t>https://artportalen.se/Sighting/137016295</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>137044060</v>
+        <v>137016296</v>
       </c>
       <c r="B50" t="n">
-        <v>99391</v>
+        <v>58023</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>159</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr"/>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
@@ -6712,13 +6655,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>636760</v>
+        <v>636424</v>
       </c>
       <c r="R50" t="n">
-        <v>7014309</v>
+        <v>7014437</v>
       </c>
       <c r="S50" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6742,22 +6685,27 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6766,70 +6714,61 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja, Markus Borja, Vivien Renaut</t>
+          <t>Markus Borja, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137044060</t>
+          <t>https://artportalen.se/Sighting/137016296</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>137044061</v>
+        <v>137016297</v>
       </c>
       <c r="B51" t="n">
-        <v>99391</v>
+        <v>58023</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr"/>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
@@ -6837,13 +6776,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>636781</v>
+        <v>636448</v>
       </c>
       <c r="R51" t="n">
-        <v>7014323</v>
+        <v>7014424</v>
       </c>
       <c r="S51" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6867,22 +6806,27 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>11:35</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6891,70 +6835,61 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja, Markus Borja, Vivien Renaut</t>
+          <t>Markus Borja, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137044061</t>
+          <t>https://artportalen.se/Sighting/137016297</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>137044062</v>
+        <v>137016300</v>
       </c>
       <c r="B52" t="n">
-        <v>99391</v>
+        <v>58023</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>117</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr"/>
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
@@ -6962,13 +6897,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>636772</v>
+        <v>636398</v>
       </c>
       <c r="R52" t="n">
-        <v>7014326</v>
+        <v>7014509</v>
       </c>
       <c r="S52" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6992,22 +6927,27 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>11:46</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -7016,70 +6956,61 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja, Markus Borja, Vivien Renaut</t>
+          <t>Markus Borja, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137044062</t>
+          <t>https://artportalen.se/Sighting/137016300</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>137044064</v>
+        <v>137016304</v>
       </c>
       <c r="B53" t="n">
-        <v>99391</v>
+        <v>58023</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr"/>
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
@@ -7087,13 +7018,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>636806</v>
+        <v>636466</v>
       </c>
       <c r="R53" t="n">
-        <v>7014282</v>
+        <v>7014462</v>
       </c>
       <c r="S53" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -7117,22 +7048,27 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>12:24</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -7141,70 +7077,61 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja, Markus Borja, Vivien Renaut</t>
+          <t>Markus Borja, Ann-Christine Borja, Diego Borja</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137044064</t>
+          <t>https://artportalen.se/Sighting/137016304</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>137044080</v>
+        <v>137016307</v>
       </c>
       <c r="B54" t="n">
-        <v>99391</v>
+        <v>58023</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr"/>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
@@ -7212,13 +7139,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>636598</v>
+        <v>636566</v>
       </c>
       <c r="R54" t="n">
-        <v>7014517</v>
+        <v>7014367</v>
       </c>
       <c r="S54" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -7242,22 +7169,27 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>12:35</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7266,34 +7198,33 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja, Markus Borja, Vivien Renaut</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137044080</t>
+          <t>https://artportalen.se/Sighting/137016307</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>137016336</v>
+        <v>137016344</v>
       </c>
       <c r="B55" t="n">
-        <v>79526</v>
+        <v>58023</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7301,26 +7232,27 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>260591</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr"/>
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
@@ -7328,10 +7260,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>636512</v>
+        <v>636392</v>
       </c>
       <c r="R55" t="n">
-        <v>7014375</v>
+        <v>7014473</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -7363,7 +7295,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -7373,7 +7305,12 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall.</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7382,24 +7319,8 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ55" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK55" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO55" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
@@ -7415,16 +7336,16 @@
       <c r="AY55" t="inlineStr"/>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016336</t>
+          <t>https://artportalen.se/Sighting/137016344</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>137016339</v>
+        <v>137040097</v>
       </c>
       <c r="B56" t="n">
-        <v>79526</v>
+        <v>58023</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7432,26 +7353,27 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>260591</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr"/>
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
@@ -7459,13 +7381,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>636457</v>
+        <v>636710</v>
       </c>
       <c r="R56" t="n">
-        <v>7014405</v>
+        <v>7014234</v>
       </c>
       <c r="S56" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -7489,22 +7411,27 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>08:39</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>08:39</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7513,49 +7440,33 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
-      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ56" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK56" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO56" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja, Vivien Renaut, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016339</t>
+          <t>https://artportalen.se/Sighting/137040097</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>137016342</v>
+        <v>137040106</v>
       </c>
       <c r="B57" t="n">
-        <v>79526</v>
+        <v>58184</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7563,40 +7474,49 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>260591</v>
+        <v>103021</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="K57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr"/>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Stortannsjön, Ång</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>636417</v>
+        <v>636783</v>
       </c>
       <c r="R57" t="n">
-        <v>7014452</v>
+        <v>7014328</v>
       </c>
       <c r="S57" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7620,22 +7540,22 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7644,49 +7564,33 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ57" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK57" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO57" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja, Ann-Christine Borja, Vivien Renaut</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016342</t>
+          <t>https://artportalen.se/Sighting/137040106</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>137016345</v>
+        <v>137040109</v>
       </c>
       <c r="B58" t="n">
-        <v>79526</v>
+        <v>58184</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7694,26 +7598,27 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>260591</v>
+        <v>103021</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr"/>
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
@@ -7721,13 +7626,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>636407</v>
+        <v>636808</v>
       </c>
       <c r="R58" t="n">
-        <v>7014480</v>
+        <v>7014272</v>
       </c>
       <c r="S58" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7751,22 +7656,22 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7775,49 +7680,33 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
-      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ58" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK58" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO58" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja, Vivien Renaut</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016345</t>
+          <t>https://artportalen.se/Sighting/137040109</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>137016346</v>
+        <v>137040177</v>
       </c>
       <c r="B59" t="n">
-        <v>79526</v>
+        <v>58184</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7825,30 +7714,27 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>260591</v>
+        <v>103021</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr"/>
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
@@ -7856,13 +7742,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>636450</v>
+        <v>636811</v>
       </c>
       <c r="R59" t="n">
-        <v>7014535</v>
+        <v>7014284</v>
       </c>
       <c r="S59" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7886,22 +7772,27 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>12:13</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Läte</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7910,80 +7801,69 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
-      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ59" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK59" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO59" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Vivien Renaut</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Vivien Renaut</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016346</t>
+          <t>https://artportalen.se/Sighting/137040177</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>137016348</v>
+        <v>137040107</v>
       </c>
       <c r="B60" t="n">
-        <v>79526</v>
+        <v>99391</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>260591</v>
+        <v>220787</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
       <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
@@ -7991,13 +7871,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>636479</v>
+        <v>636807</v>
       </c>
       <c r="R60" t="n">
-        <v>7014523</v>
+        <v>7014295</v>
       </c>
       <c r="S60" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -8021,22 +7901,22 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -8049,72 +7929,66 @@
       <c r="AG60" t="b">
         <v>0</v>
       </c>
-      <c r="AJ60" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK60" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO60" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja, Vivien Renaut, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016348</t>
+          <t>https://artportalen.se/Sighting/137040107</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>137016353</v>
+        <v>137040121</v>
       </c>
       <c r="B61" t="n">
-        <v>79526</v>
+        <v>99391</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>260591</v>
+        <v>220787</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
       <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
@@ -8122,13 +7996,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>636460</v>
+        <v>636854</v>
       </c>
       <c r="R61" t="n">
-        <v>7014451</v>
+        <v>7014229</v>
       </c>
       <c r="S61" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -8152,22 +8026,22 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -8180,76 +8054,66 @@
       <c r="AG61" t="b">
         <v>0</v>
       </c>
-      <c r="AJ61" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK61" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO61" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja, Vivien Renaut, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016353</t>
+          <t>https://artportalen.se/Sighting/137040121</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>137044071</v>
+        <v>137040123</v>
       </c>
       <c r="B62" t="n">
-        <v>79526</v>
+        <v>99391</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>260591</v>
+        <v>220787</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr"/>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
       <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
@@ -8257,13 +8121,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>636845</v>
+        <v>636843</v>
       </c>
       <c r="R62" t="n">
-        <v>7014233</v>
+        <v>7014251</v>
       </c>
       <c r="S62" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -8292,7 +8156,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -8302,7 +8166,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8315,34 +8179,3153 @@
       <c r="AG62" t="b">
         <v>0</v>
       </c>
-      <c r="AJ62" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK62" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO62" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja, Vivien Renaut, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
       <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137040123</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>137040138</v>
+      </c>
+      <c r="B63" t="n">
+        <v>99391</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Stortannsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>636527</v>
+      </c>
+      <c r="R63" t="n">
+        <v>7014608</v>
+      </c>
+      <c r="S63" t="n">
+        <v>4</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Överlännäs</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>15:02</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>15:02</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF63" t="inlineStr"/>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Markus Borja, Vivien Renaut, Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137040138</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>137040160</v>
+      </c>
+      <c r="B64" t="n">
+        <v>99391</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="N64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Stortannsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>636474</v>
+      </c>
+      <c r="R64" t="n">
+        <v>7014608</v>
+      </c>
+      <c r="S64" t="n">
+        <v>3</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Överlännäs</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF64" t="inlineStr"/>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Markus Borja, Vivien Renaut, Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137040160</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>137040163</v>
+      </c>
+      <c r="B65" t="n">
+        <v>99391</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Stortannsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>636595</v>
+      </c>
+      <c r="R65" t="n">
+        <v>7014422</v>
+      </c>
+      <c r="S65" t="n">
+        <v>3</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Överlännäs</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>18:17</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>18:17</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF65" t="inlineStr"/>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Markus Borja, Vivien Renaut, Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137040163</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>137040164</v>
+      </c>
+      <c r="B66" t="n">
+        <v>99391</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="N66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Stortannsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>636776</v>
+      </c>
+      <c r="R66" t="n">
+        <v>7014278</v>
+      </c>
+      <c r="S66" t="n">
+        <v>3</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Överlännäs</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>09:05</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>09:05</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF66" t="inlineStr"/>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Vivien Renaut</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Vivien Renaut</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137040164</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>137040166</v>
+      </c>
+      <c r="B67" t="n">
+        <v>99391</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="N67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Stortannsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>636782</v>
+      </c>
+      <c r="R67" t="n">
+        <v>7014300</v>
+      </c>
+      <c r="S67" t="n">
+        <v>3</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Överlännäs</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF67" t="inlineStr"/>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Vivien Renaut</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Vivien Renaut</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137040166</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>137040168</v>
+      </c>
+      <c r="B68" t="n">
+        <v>99391</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="N68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Stortannsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>636758</v>
+      </c>
+      <c r="R68" t="n">
+        <v>7014368</v>
+      </c>
+      <c r="S68" t="n">
+        <v>3</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Överlännäs</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>09:42</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>09:42</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF68" t="inlineStr"/>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Vivien Renaut</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Vivien Renaut</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137040168</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>137040189</v>
+      </c>
+      <c r="B69" t="n">
+        <v>99391</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="N69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Stortannsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>636424</v>
+      </c>
+      <c r="R69" t="n">
+        <v>7014610</v>
+      </c>
+      <c r="S69" t="n">
+        <v>15</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Överlännäs</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>17:52</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>17:52</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF69" t="inlineStr"/>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Vivien Renaut</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Vivien Renaut</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137040189</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>137044057</v>
+      </c>
+      <c r="B70" t="n">
+        <v>99391</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="N70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Stortannsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>636762</v>
+      </c>
+      <c r="R70" t="n">
+        <v>7014263</v>
+      </c>
+      <c r="S70" t="n">
+        <v>5</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Överlännäs</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF70" t="inlineStr"/>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja, Markus Borja, Vivien Renaut</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137044057</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>137044059</v>
+      </c>
+      <c r="B71" t="n">
+        <v>99391</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="N71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Stortannsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>636736</v>
+      </c>
+      <c r="R71" t="n">
+        <v>7014341</v>
+      </c>
+      <c r="S71" t="n">
+        <v>5</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Överlännäs</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>09:41</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>09:41</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF71" t="inlineStr"/>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja, Markus Borja, Vivien Renaut</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137044059</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>137044060</v>
+      </c>
+      <c r="B72" t="n">
+        <v>99391</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>159</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
+      <c r="N72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Stortannsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>636760</v>
+      </c>
+      <c r="R72" t="n">
+        <v>7014309</v>
+      </c>
+      <c r="S72" t="n">
+        <v>5</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Överlännäs</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>10:02</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>10:02</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF72" t="inlineStr"/>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja, Markus Borja, Vivien Renaut</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137044060</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>137044061</v>
+      </c>
+      <c r="B73" t="n">
+        <v>99391</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
+      <c r="N73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Stortannsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>636781</v>
+      </c>
+      <c r="R73" t="n">
+        <v>7014323</v>
+      </c>
+      <c r="S73" t="n">
+        <v>5</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Överlännäs</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF73" t="inlineStr"/>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja, Markus Borja, Vivien Renaut</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137044061</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>137044062</v>
+      </c>
+      <c r="B74" t="n">
+        <v>99391</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>117</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr"/>
+      <c r="N74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Stortannsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>636772</v>
+      </c>
+      <c r="R74" t="n">
+        <v>7014326</v>
+      </c>
+      <c r="S74" t="n">
+        <v>5</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Överlännäs</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>10:26</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>10:26</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF74" t="inlineStr"/>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja, Markus Borja, Vivien Renaut</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137044062</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>137044064</v>
+      </c>
+      <c r="B75" t="n">
+        <v>99391</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr"/>
+      <c r="N75" t="inlineStr"/>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Stortannsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>636806</v>
+      </c>
+      <c r="R75" t="n">
+        <v>7014282</v>
+      </c>
+      <c r="S75" t="n">
+        <v>5</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Överlännäs</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>10:48</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>10:48</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="inlineStr"/>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja, Markus Borja, Vivien Renaut</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137044064</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>137044080</v>
+      </c>
+      <c r="B76" t="n">
+        <v>99391</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr"/>
+      <c r="N76" t="inlineStr"/>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Stortannsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>636598</v>
+      </c>
+      <c r="R76" t="n">
+        <v>7014517</v>
+      </c>
+      <c r="S76" t="n">
+        <v>5</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Överlännäs</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>14:32</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>14:32</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF76" t="inlineStr"/>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja, Markus Borja, Vivien Renaut</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137044080</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>137040134</v>
+      </c>
+      <c r="B77" t="n">
+        <v>79261</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Stortannsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>636580</v>
+      </c>
+      <c r="R77" t="n">
+        <v>7014518</v>
+      </c>
+      <c r="S77" t="n">
+        <v>3</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Överlännäs</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>14:37</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>14:37</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137040134</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>137040136</v>
+      </c>
+      <c r="B78" t="n">
+        <v>79261</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Stortannsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>636552</v>
+      </c>
+      <c r="R78" t="n">
+        <v>7014536</v>
+      </c>
+      <c r="S78" t="n">
+        <v>3</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Överlännäs</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>14:47</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>14:47</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137040136</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>137016336</v>
+      </c>
+      <c r="B79" t="n">
+        <v>79526</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="J79" t="inlineStr"/>
+      <c r="K79" t="inlineStr"/>
+      <c r="N79" t="inlineStr"/>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Stortannsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>636512</v>
+      </c>
+      <c r="R79" t="n">
+        <v>7014375</v>
+      </c>
+      <c r="S79" t="n">
+        <v>5</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Överlännäs</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>11:12</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>11:12</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF79" t="inlineStr"/>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ79" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK79" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO79" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja, Markus Borja</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137016336</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>137016339</v>
+      </c>
+      <c r="B80" t="n">
+        <v>79526</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="J80" t="inlineStr"/>
+      <c r="K80" t="inlineStr"/>
+      <c r="N80" t="inlineStr"/>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Stortannsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>636457</v>
+      </c>
+      <c r="R80" t="n">
+        <v>7014405</v>
+      </c>
+      <c r="S80" t="n">
+        <v>5</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Överlännäs</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>11:22</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="AB80" t="inlineStr">
+        <is>
+          <t>11:22</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF80" t="inlineStr"/>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ80" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK80" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO80" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137016339</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>137016342</v>
+      </c>
+      <c r="B81" t="n">
+        <v>79526</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="J81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
+      <c r="N81" t="inlineStr"/>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Stortannsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>636417</v>
+      </c>
+      <c r="R81" t="n">
+        <v>7014452</v>
+      </c>
+      <c r="S81" t="n">
+        <v>5</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Överlännäs</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF81" t="inlineStr"/>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ81" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK81" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO81" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137016342</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>137016345</v>
+      </c>
+      <c r="B82" t="n">
+        <v>79526</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="J82" t="inlineStr"/>
+      <c r="K82" t="inlineStr"/>
+      <c r="N82" t="inlineStr"/>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Stortannsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>636407</v>
+      </c>
+      <c r="R82" t="n">
+        <v>7014480</v>
+      </c>
+      <c r="S82" t="n">
+        <v>5</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Överlännäs</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="Z82" t="inlineStr">
+        <is>
+          <t>11:59</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="AB82" t="inlineStr">
+        <is>
+          <t>11:59</t>
+        </is>
+      </c>
+      <c r="AD82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF82" t="inlineStr"/>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ82" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK82" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO82" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137016345</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>137016346</v>
+      </c>
+      <c r="B83" t="n">
+        <v>79526</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="J83" t="inlineStr"/>
+      <c r="K83" t="inlineStr"/>
+      <c r="N83" t="inlineStr"/>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Stortannsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>636450</v>
+      </c>
+      <c r="R83" t="n">
+        <v>7014535</v>
+      </c>
+      <c r="S83" t="n">
+        <v>5</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Överlännäs</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="Z83" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="AB83" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="AD83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF83" t="inlineStr"/>
+      <c r="AG83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ83" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK83" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO83" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT83" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137016346</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>137016348</v>
+      </c>
+      <c r="B84" t="n">
+        <v>79526</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="J84" t="inlineStr"/>
+      <c r="K84" t="inlineStr"/>
+      <c r="N84" t="inlineStr"/>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Stortannsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q84" t="n">
+        <v>636479</v>
+      </c>
+      <c r="R84" t="n">
+        <v>7014523</v>
+      </c>
+      <c r="S84" t="n">
+        <v>5</v>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>Överlännäs</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="Z84" t="inlineStr">
+        <is>
+          <t>12:09</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="AB84" t="inlineStr">
+        <is>
+          <t>12:09</t>
+        </is>
+      </c>
+      <c r="AD84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF84" t="inlineStr"/>
+      <c r="AG84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ84" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK84" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO84" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT84" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137016348</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>137016353</v>
+      </c>
+      <c r="B85" t="n">
+        <v>79526</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
+      <c r="J85" t="inlineStr"/>
+      <c r="K85" t="inlineStr"/>
+      <c r="N85" t="inlineStr"/>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>Stortannsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q85" t="n">
+        <v>636460</v>
+      </c>
+      <c r="R85" t="n">
+        <v>7014451</v>
+      </c>
+      <c r="S85" t="n">
+        <v>5</v>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>Överlännäs</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="Z85" t="inlineStr">
+        <is>
+          <t>12:28</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="AB85" t="inlineStr">
+        <is>
+          <t>12:28</t>
+        </is>
+      </c>
+      <c r="AD85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF85" t="inlineStr"/>
+      <c r="AG85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ85" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK85" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO85" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT85" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AX85" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137016353</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>137040099</v>
+      </c>
+      <c r="B86" t="n">
+        <v>79526</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>Stortannsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q86" t="n">
+        <v>636705</v>
+      </c>
+      <c r="R86" t="n">
+        <v>7014243</v>
+      </c>
+      <c r="S86" t="n">
+        <v>3</v>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>Överlännäs</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="Z86" t="inlineStr">
+        <is>
+          <t>08:49</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="AB86" t="inlineStr">
+        <is>
+          <t>08:49</t>
+        </is>
+      </c>
+      <c r="AD86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT86" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>Markus Borja, Vivien Renaut, Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137040099</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>137044071</v>
+      </c>
+      <c r="B87" t="n">
+        <v>79526</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
+      <c r="J87" t="inlineStr"/>
+      <c r="K87" t="inlineStr"/>
+      <c r="N87" t="inlineStr"/>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>Stortannsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q87" t="n">
+        <v>636845</v>
+      </c>
+      <c r="R87" t="n">
+        <v>7014233</v>
+      </c>
+      <c r="S87" t="n">
+        <v>5</v>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>Överlännäs</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="Z87" t="inlineStr">
+        <is>
+          <t>12:09</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="AB87" t="inlineStr">
+        <is>
+          <t>12:09</t>
+        </is>
+      </c>
+      <c r="AD87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF87" t="inlineStr"/>
+      <c r="AG87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ87" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK87" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO87" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT87" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AX87" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/137044071</t>
         </is>
@@ -8411,6 +11394,31 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 25855-2025 artfynd.xlsx
+++ b/artfynd/A 25855-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137044063</v>
       </c>
       <c r="B2" t="n">
-        <v>92416</v>
+        <v>92419</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -814,7 +814,7 @@
         <v>137040165</v>
       </c>
       <c r="B3" t="n">
-        <v>92978</v>
+        <v>92981</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -931,7 +931,7 @@
         <v>137016354</v>
       </c>
       <c r="B4" t="n">
-        <v>93458</v>
+        <v>93461</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1047,7 +1047,7 @@
         <v>137016293</v>
       </c>
       <c r="B5" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1159,7 +1159,7 @@
         <v>137040122</v>
       </c>
       <c r="B6" t="n">
-        <v>92108</v>
+        <v>92111</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1271,7 +1271,7 @@
         <v>137016298</v>
       </c>
       <c r="B7" t="n">
-        <v>93480</v>
+        <v>93483</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -7827,7 +7827,7 @@
         <v>137040107</v>
       </c>
       <c r="B60" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7952,7 +7952,7 @@
         <v>137040121</v>
       </c>
       <c r="B61" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -8077,7 +8077,7 @@
         <v>137040123</v>
       </c>
       <c r="B62" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -8202,7 +8202,7 @@
         <v>137040138</v>
       </c>
       <c r="B63" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8327,7 +8327,7 @@
         <v>137040160</v>
       </c>
       <c r="B64" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8452,7 +8452,7 @@
         <v>137040163</v>
       </c>
       <c r="B65" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8577,7 +8577,7 @@
         <v>137040164</v>
       </c>
       <c r="B66" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8702,7 +8702,7 @@
         <v>137040166</v>
       </c>
       <c r="B67" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8827,7 +8827,7 @@
         <v>137040168</v>
       </c>
       <c r="B68" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8952,7 +8952,7 @@
         <v>137040189</v>
       </c>
       <c r="B69" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -9077,7 +9077,7 @@
         <v>137044057</v>
       </c>
       <c r="B70" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -9202,7 +9202,7 @@
         <v>137044059</v>
       </c>
       <c r="B71" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9327,7 +9327,7 @@
         <v>137044060</v>
       </c>
       <c r="B72" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9452,7 +9452,7 @@
         <v>137044061</v>
       </c>
       <c r="B73" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9577,7 +9577,7 @@
         <v>137044062</v>
       </c>
       <c r="B74" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9702,7 +9702,7 @@
         <v>137044064</v>
       </c>
       <c r="B75" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9827,7 +9827,7 @@
         <v>137044080</v>
       </c>
       <c r="B76" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>

--- a/artfynd/A 25855-2025 artfynd.xlsx
+++ b/artfynd/A 25855-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137044063</v>
       </c>
       <c r="B2" t="n">
-        <v>92419</v>
+        <v>92429</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -814,7 +814,7 @@
         <v>137040165</v>
       </c>
       <c r="B3" t="n">
-        <v>92981</v>
+        <v>92991</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -931,7 +931,7 @@
         <v>137016354</v>
       </c>
       <c r="B4" t="n">
-        <v>93461</v>
+        <v>93471</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1047,7 +1047,7 @@
         <v>137016293</v>
       </c>
       <c r="B5" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1159,7 +1159,7 @@
         <v>137040122</v>
       </c>
       <c r="B6" t="n">
-        <v>92111</v>
+        <v>92121</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1271,7 +1271,7 @@
         <v>137016298</v>
       </c>
       <c r="B7" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1387,7 +1387,7 @@
         <v>137016289</v>
       </c>
       <c r="B8" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1518,7 +1518,7 @@
         <v>137016306</v>
       </c>
       <c r="B9" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1649,7 +1649,7 @@
         <v>137016332</v>
       </c>
       <c r="B10" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1780,7 +1780,7 @@
         <v>137016333</v>
       </c>
       <c r="B11" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1911,7 +1911,7 @@
         <v>137016335</v>
       </c>
       <c r="B12" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2042,7 +2042,7 @@
         <v>137016337</v>
       </c>
       <c r="B13" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2173,7 +2173,7 @@
         <v>137016340</v>
       </c>
       <c r="B14" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2304,7 +2304,7 @@
         <v>137016349</v>
       </c>
       <c r="B15" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2435,7 +2435,7 @@
         <v>137016350</v>
       </c>
       <c r="B16" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2566,7 +2566,7 @@
         <v>137040102</v>
       </c>
       <c r="B17" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2697,7 +2697,7 @@
         <v>137040133</v>
       </c>
       <c r="B18" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2828,7 +2828,7 @@
         <v>137040161</v>
       </c>
       <c r="B19" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2959,7 +2959,7 @@
         <v>137040162</v>
       </c>
       <c r="B20" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3090,7 +3090,7 @@
         <v>137040167</v>
       </c>
       <c r="B21" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3202,7 +3202,7 @@
         <v>137040169</v>
       </c>
       <c r="B22" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3314,7 +3314,7 @@
         <v>137040181</v>
       </c>
       <c r="B23" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3431,7 +3431,7 @@
         <v>137044055</v>
       </c>
       <c r="B24" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3562,7 +3562,7 @@
         <v>137044068</v>
       </c>
       <c r="B25" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3693,7 +3693,7 @@
         <v>137044072</v>
       </c>
       <c r="B26" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3824,7 +3824,7 @@
         <v>137016334</v>
       </c>
       <c r="B27" t="n">
-        <v>79527</v>
+        <v>79537</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3955,7 +3955,7 @@
         <v>137016341</v>
       </c>
       <c r="B28" t="n">
-        <v>79527</v>
+        <v>79537</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4086,7 +4086,7 @@
         <v>137016351</v>
       </c>
       <c r="B29" t="n">
-        <v>79527</v>
+        <v>79537</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4217,7 +4217,7 @@
         <v>137040100</v>
       </c>
       <c r="B30" t="n">
-        <v>79527</v>
+        <v>79537</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4348,7 +4348,7 @@
         <v>137044056</v>
       </c>
       <c r="B31" t="n">
-        <v>79527</v>
+        <v>79537</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4479,7 +4479,7 @@
         <v>137040105</v>
       </c>
       <c r="B32" t="n">
-        <v>79260</v>
+        <v>79270</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4591,7 +4591,7 @@
         <v>137040135</v>
       </c>
       <c r="B33" t="n">
-        <v>79260</v>
+        <v>79270</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4703,7 +4703,7 @@
         <v>137016288</v>
       </c>
       <c r="B34" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4815,7 +4815,7 @@
         <v>137016299</v>
       </c>
       <c r="B35" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4927,7 +4927,7 @@
         <v>137016303</v>
       </c>
       <c r="B36" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5039,7 +5039,7 @@
         <v>137040101</v>
       </c>
       <c r="B37" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5151,7 +5151,7 @@
         <v>137040104</v>
       </c>
       <c r="B38" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5263,7 +5263,7 @@
         <v>137040108</v>
       </c>
       <c r="B39" t="n">
-        <v>80512</v>
+        <v>80522</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5394,7 +5394,7 @@
         <v>137040110</v>
       </c>
       <c r="B40" t="n">
-        <v>80512</v>
+        <v>80522</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5525,7 +5525,7 @@
         <v>137040111</v>
       </c>
       <c r="B41" t="n">
-        <v>80512</v>
+        <v>80522</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5656,7 +5656,7 @@
         <v>137016301</v>
       </c>
       <c r="B42" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5772,7 +5772,7 @@
         <v>137040182</v>
       </c>
       <c r="B43" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5893,7 +5893,7 @@
         <v>137016287</v>
       </c>
       <c r="B44" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6014,7 +6014,7 @@
         <v>137016290</v>
       </c>
       <c r="B45" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6135,7 +6135,7 @@
         <v>137016291</v>
       </c>
       <c r="B46" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6256,7 +6256,7 @@
         <v>137016292</v>
       </c>
       <c r="B47" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6377,7 +6377,7 @@
         <v>137016294</v>
       </c>
       <c r="B48" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6498,7 +6498,7 @@
         <v>137016295</v>
       </c>
       <c r="B49" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6619,7 +6619,7 @@
         <v>137016296</v>
       </c>
       <c r="B50" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6740,7 +6740,7 @@
         <v>137016297</v>
       </c>
       <c r="B51" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6861,7 +6861,7 @@
         <v>137016300</v>
       </c>
       <c r="B52" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6982,7 +6982,7 @@
         <v>137016304</v>
       </c>
       <c r="B53" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -7103,7 +7103,7 @@
         <v>137016307</v>
       </c>
       <c r="B54" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7224,7 +7224,7 @@
         <v>137016344</v>
       </c>
       <c r="B55" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7345,7 +7345,7 @@
         <v>137040097</v>
       </c>
       <c r="B56" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7466,7 +7466,7 @@
         <v>137040106</v>
       </c>
       <c r="B57" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7590,7 +7590,7 @@
         <v>137040109</v>
       </c>
       <c r="B58" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7706,7 +7706,7 @@
         <v>137040177</v>
       </c>
       <c r="B59" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7827,7 +7827,7 @@
         <v>137040107</v>
       </c>
       <c r="B60" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7952,7 +7952,7 @@
         <v>137040121</v>
       </c>
       <c r="B61" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -8077,7 +8077,7 @@
         <v>137040123</v>
       </c>
       <c r="B62" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -8202,7 +8202,7 @@
         <v>137040138</v>
       </c>
       <c r="B63" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8327,7 +8327,7 @@
         <v>137040160</v>
       </c>
       <c r="B64" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8452,7 +8452,7 @@
         <v>137040163</v>
       </c>
       <c r="B65" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8577,7 +8577,7 @@
         <v>137040164</v>
       </c>
       <c r="B66" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8702,7 +8702,7 @@
         <v>137040166</v>
       </c>
       <c r="B67" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8827,7 +8827,7 @@
         <v>137040168</v>
       </c>
       <c r="B68" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8952,7 +8952,7 @@
         <v>137040189</v>
       </c>
       <c r="B69" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -9077,7 +9077,7 @@
         <v>137044057</v>
       </c>
       <c r="B70" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -9202,7 +9202,7 @@
         <v>137044059</v>
       </c>
       <c r="B71" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9327,7 +9327,7 @@
         <v>137044060</v>
       </c>
       <c r="B72" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9452,7 +9452,7 @@
         <v>137044061</v>
       </c>
       <c r="B73" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9577,7 +9577,7 @@
         <v>137044062</v>
       </c>
       <c r="B74" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9702,7 +9702,7 @@
         <v>137044064</v>
       </c>
       <c r="B75" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9827,7 +9827,7 @@
         <v>137044080</v>
       </c>
       <c r="B76" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9952,7 +9952,7 @@
         <v>137040134</v>
       </c>
       <c r="B77" t="n">
-        <v>79261</v>
+        <v>79271</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -10064,7 +10064,7 @@
         <v>137040136</v>
       </c>
       <c r="B78" t="n">
-        <v>79261</v>
+        <v>79271</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -10176,7 +10176,7 @@
         <v>137016336</v>
       </c>
       <c r="B79" t="n">
-        <v>79526</v>
+        <v>79536</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -10307,7 +10307,7 @@
         <v>137016339</v>
       </c>
       <c r="B80" t="n">
-        <v>79526</v>
+        <v>79536</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -10438,7 +10438,7 @@
         <v>137016342</v>
       </c>
       <c r="B81" t="n">
-        <v>79526</v>
+        <v>79536</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10569,7 +10569,7 @@
         <v>137016345</v>
       </c>
       <c r="B82" t="n">
-        <v>79526</v>
+        <v>79536</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10700,7 +10700,7 @@
         <v>137016346</v>
       </c>
       <c r="B83" t="n">
-        <v>79526</v>
+        <v>79536</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10831,7 +10831,7 @@
         <v>137016348</v>
       </c>
       <c r="B84" t="n">
-        <v>79526</v>
+        <v>79536</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10962,7 +10962,7 @@
         <v>137016353</v>
       </c>
       <c r="B85" t="n">
-        <v>79526</v>
+        <v>79536</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -11093,7 +11093,7 @@
         <v>137040099</v>
       </c>
       <c r="B86" t="n">
-        <v>79526</v>
+        <v>79536</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -11205,7 +11205,7 @@
         <v>137044071</v>
       </c>
       <c r="B87" t="n">
-        <v>79526</v>
+        <v>79536</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>

--- a/artfynd/A 25855-2025 artfynd.xlsx
+++ b/artfynd/A 25855-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137044063</v>
       </c>
       <c r="B2" t="n">
-        <v>92429</v>
+        <v>92430</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -814,7 +814,7 @@
         <v>137040165</v>
       </c>
       <c r="B3" t="n">
-        <v>92991</v>
+        <v>92992</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -931,7 +931,7 @@
         <v>137016354</v>
       </c>
       <c r="B4" t="n">
-        <v>93471</v>
+        <v>93472</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1047,7 +1047,7 @@
         <v>137016293</v>
       </c>
       <c r="B5" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1159,7 +1159,7 @@
         <v>137040122</v>
       </c>
       <c r="B6" t="n">
-        <v>92121</v>
+        <v>92122</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1271,7 +1271,7 @@
         <v>137016298</v>
       </c>
       <c r="B7" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -7827,7 +7827,7 @@
         <v>137040107</v>
       </c>
       <c r="B60" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7952,7 +7952,7 @@
         <v>137040121</v>
       </c>
       <c r="B61" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -8077,7 +8077,7 @@
         <v>137040123</v>
       </c>
       <c r="B62" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -8202,7 +8202,7 @@
         <v>137040138</v>
       </c>
       <c r="B63" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8327,7 +8327,7 @@
         <v>137040160</v>
       </c>
       <c r="B64" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8452,7 +8452,7 @@
         <v>137040163</v>
       </c>
       <c r="B65" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8577,7 +8577,7 @@
         <v>137040164</v>
       </c>
       <c r="B66" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8702,7 +8702,7 @@
         <v>137040166</v>
       </c>
       <c r="B67" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8827,7 +8827,7 @@
         <v>137040168</v>
       </c>
       <c r="B68" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8952,7 +8952,7 @@
         <v>137040189</v>
       </c>
       <c r="B69" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -9077,7 +9077,7 @@
         <v>137044057</v>
       </c>
       <c r="B70" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -9202,7 +9202,7 @@
         <v>137044059</v>
       </c>
       <c r="B71" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9327,7 +9327,7 @@
         <v>137044060</v>
       </c>
       <c r="B72" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9452,7 +9452,7 @@
         <v>137044061</v>
       </c>
       <c r="B73" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9577,7 +9577,7 @@
         <v>137044062</v>
       </c>
       <c r="B74" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9702,7 +9702,7 @@
         <v>137044064</v>
       </c>
       <c r="B75" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9827,7 +9827,7 @@
         <v>137044080</v>
       </c>
       <c r="B76" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>

--- a/artfynd/A 25855-2025 artfynd.xlsx
+++ b/artfynd/A 25855-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137044063</v>
       </c>
       <c r="B2" t="n">
-        <v>92430</v>
+        <v>92433</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -814,7 +814,7 @@
         <v>137040165</v>
       </c>
       <c r="B3" t="n">
-        <v>92992</v>
+        <v>92995</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -931,7 +931,7 @@
         <v>137016354</v>
       </c>
       <c r="B4" t="n">
-        <v>93472</v>
+        <v>93477</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1047,7 +1047,7 @@
         <v>137016293</v>
       </c>
       <c r="B5" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1159,7 +1159,7 @@
         <v>137040122</v>
       </c>
       <c r="B6" t="n">
-        <v>92122</v>
+        <v>92125</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1271,7 +1271,7 @@
         <v>137016298</v>
       </c>
       <c r="B7" t="n">
-        <v>93494</v>
+        <v>93499</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1387,7 +1387,7 @@
         <v>137016289</v>
       </c>
       <c r="B8" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1518,7 +1518,7 @@
         <v>137016306</v>
       </c>
       <c r="B9" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1649,7 +1649,7 @@
         <v>137016332</v>
       </c>
       <c r="B10" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1780,7 +1780,7 @@
         <v>137016333</v>
       </c>
       <c r="B11" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1911,7 +1911,7 @@
         <v>137016335</v>
       </c>
       <c r="B12" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2042,7 +2042,7 @@
         <v>137016337</v>
       </c>
       <c r="B13" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2173,7 +2173,7 @@
         <v>137016340</v>
       </c>
       <c r="B14" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2304,7 +2304,7 @@
         <v>137016349</v>
       </c>
       <c r="B15" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2435,7 +2435,7 @@
         <v>137016350</v>
       </c>
       <c r="B16" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2566,7 +2566,7 @@
         <v>137040102</v>
       </c>
       <c r="B17" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2682,7 +2682,7 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Markus Borja, Vivien Renaut, Ann-Christine Borja</t>
+          <t>Markus Borja, Ann-Christine Borja, Vivien Renaut</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2697,7 +2697,7 @@
         <v>137040133</v>
       </c>
       <c r="B18" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2813,7 +2813,7 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Markus Borja, Vivien Renaut, Ann-Christine Borja</t>
+          <t>Markus Borja, Ann-Christine Borja, Vivien Renaut</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2828,7 +2828,7 @@
         <v>137040161</v>
       </c>
       <c r="B19" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2944,7 +2944,7 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Markus Borja, Vivien Renaut, Ann-Christine Borja</t>
+          <t>Markus Borja, Ann-Christine Borja, Vivien Renaut</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -2959,7 +2959,7 @@
         <v>137040162</v>
       </c>
       <c r="B20" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3075,7 +3075,7 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Markus Borja, Vivien Renaut, Ann-Christine Borja</t>
+          <t>Markus Borja, Ann-Christine Borja, Vivien Renaut</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -3090,7 +3090,7 @@
         <v>137040167</v>
       </c>
       <c r="B21" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3202,7 +3202,7 @@
         <v>137040169</v>
       </c>
       <c r="B22" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3314,7 +3314,7 @@
         <v>137040181</v>
       </c>
       <c r="B23" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3431,7 +3431,7 @@
         <v>137044055</v>
       </c>
       <c r="B24" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3562,7 +3562,7 @@
         <v>137044068</v>
       </c>
       <c r="B25" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3693,7 +3693,7 @@
         <v>137044072</v>
       </c>
       <c r="B26" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3824,7 +3824,7 @@
         <v>137016334</v>
       </c>
       <c r="B27" t="n">
-        <v>79537</v>
+        <v>79540</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3955,7 +3955,7 @@
         <v>137016341</v>
       </c>
       <c r="B28" t="n">
-        <v>79537</v>
+        <v>79540</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4086,7 +4086,7 @@
         <v>137016351</v>
       </c>
       <c r="B29" t="n">
-        <v>79537</v>
+        <v>79540</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4217,7 +4217,7 @@
         <v>137040100</v>
       </c>
       <c r="B30" t="n">
-        <v>79537</v>
+        <v>79540</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4333,7 +4333,7 @@
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Markus Borja, Vivien Renaut, Ann-Christine Borja</t>
+          <t>Markus Borja, Ann-Christine Borja, Vivien Renaut</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
@@ -4348,7 +4348,7 @@
         <v>137044056</v>
       </c>
       <c r="B31" t="n">
-        <v>79537</v>
+        <v>79540</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4479,7 +4479,7 @@
         <v>137040105</v>
       </c>
       <c r="B32" t="n">
-        <v>79270</v>
+        <v>79273</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4591,7 +4591,7 @@
         <v>137040135</v>
       </c>
       <c r="B33" t="n">
-        <v>79270</v>
+        <v>79273</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4703,7 +4703,7 @@
         <v>137016288</v>
       </c>
       <c r="B34" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4815,7 +4815,7 @@
         <v>137016299</v>
       </c>
       <c r="B35" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4927,7 +4927,7 @@
         <v>137016303</v>
       </c>
       <c r="B36" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5039,7 +5039,7 @@
         <v>137040101</v>
       </c>
       <c r="B37" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5151,7 +5151,7 @@
         <v>137040104</v>
       </c>
       <c r="B38" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5263,7 +5263,7 @@
         <v>137040108</v>
       </c>
       <c r="B39" t="n">
-        <v>80522</v>
+        <v>80525</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5379,7 +5379,7 @@
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Markus Borja, Vivien Renaut, Ann-Christine Borja</t>
+          <t>Markus Borja, Ann-Christine Borja, Vivien Renaut</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
@@ -5394,7 +5394,7 @@
         <v>137040110</v>
       </c>
       <c r="B40" t="n">
-        <v>80522</v>
+        <v>80525</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5510,7 +5510,7 @@
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Markus Borja, Vivien Renaut, Ann-Christine Borja</t>
+          <t>Markus Borja, Ann-Christine Borja, Vivien Renaut</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
@@ -5525,7 +5525,7 @@
         <v>137040111</v>
       </c>
       <c r="B41" t="n">
-        <v>80522</v>
+        <v>80525</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5641,7 +5641,7 @@
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Markus Borja, Vivien Renaut, Ann-Christine Borja</t>
+          <t>Markus Borja, Ann-Christine Borja, Vivien Renaut</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
@@ -5656,7 +5656,7 @@
         <v>137016301</v>
       </c>
       <c r="B42" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5772,7 +5772,7 @@
         <v>137040182</v>
       </c>
       <c r="B43" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5893,7 +5893,7 @@
         <v>137016287</v>
       </c>
       <c r="B44" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6014,7 +6014,7 @@
         <v>137016290</v>
       </c>
       <c r="B45" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6135,7 +6135,7 @@
         <v>137016291</v>
       </c>
       <c r="B46" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6256,7 +6256,7 @@
         <v>137016292</v>
       </c>
       <c r="B47" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6377,7 +6377,7 @@
         <v>137016294</v>
       </c>
       <c r="B48" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6498,7 +6498,7 @@
         <v>137016295</v>
       </c>
       <c r="B49" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6619,7 +6619,7 @@
         <v>137016296</v>
       </c>
       <c r="B50" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6740,7 +6740,7 @@
         <v>137016297</v>
       </c>
       <c r="B51" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6861,7 +6861,7 @@
         <v>137016300</v>
       </c>
       <c r="B52" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6982,7 +6982,7 @@
         <v>137016304</v>
       </c>
       <c r="B53" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -7103,7 +7103,7 @@
         <v>137016307</v>
       </c>
       <c r="B54" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7224,7 +7224,7 @@
         <v>137016344</v>
       </c>
       <c r="B55" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7345,7 +7345,7 @@
         <v>137040097</v>
       </c>
       <c r="B56" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Markus Borja, Vivien Renaut, Ann-Christine Borja</t>
+          <t>Markus Borja, Ann-Christine Borja, Vivien Renaut</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
@@ -7466,7 +7466,7 @@
         <v>137040106</v>
       </c>
       <c r="B57" t="n">
-        <v>58194</v>
+        <v>58195</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7575,7 +7575,7 @@
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja, Vivien Renaut</t>
+          <t>Markus Borja, Vivien Renaut, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
@@ -7590,7 +7590,7 @@
         <v>137040109</v>
       </c>
       <c r="B58" t="n">
-        <v>58194</v>
+        <v>58195</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7706,7 +7706,7 @@
         <v>137040177</v>
       </c>
       <c r="B59" t="n">
-        <v>58194</v>
+        <v>58195</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7827,7 +7827,7 @@
         <v>137040107</v>
       </c>
       <c r="B60" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7937,7 +7937,7 @@
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Markus Borja, Vivien Renaut, Ann-Christine Borja</t>
+          <t>Markus Borja, Ann-Christine Borja, Vivien Renaut</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
@@ -7952,7 +7952,7 @@
         <v>137040121</v>
       </c>
       <c r="B61" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -8062,7 +8062,7 @@
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Markus Borja, Vivien Renaut, Ann-Christine Borja</t>
+          <t>Markus Borja, Ann-Christine Borja, Vivien Renaut</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
@@ -8077,7 +8077,7 @@
         <v>137040123</v>
       </c>
       <c r="B62" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -8187,7 +8187,7 @@
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Markus Borja, Vivien Renaut, Ann-Christine Borja</t>
+          <t>Markus Borja, Ann-Christine Borja, Vivien Renaut</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
@@ -8202,7 +8202,7 @@
         <v>137040138</v>
       </c>
       <c r="B63" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8312,7 +8312,7 @@
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Markus Borja, Vivien Renaut, Ann-Christine Borja</t>
+          <t>Markus Borja, Ann-Christine Borja, Vivien Renaut</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
@@ -8327,7 +8327,7 @@
         <v>137040160</v>
       </c>
       <c r="B64" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8437,7 +8437,7 @@
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Markus Borja, Vivien Renaut, Ann-Christine Borja</t>
+          <t>Markus Borja, Ann-Christine Borja, Vivien Renaut</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
@@ -8452,7 +8452,7 @@
         <v>137040163</v>
       </c>
       <c r="B65" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8562,7 +8562,7 @@
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Markus Borja, Vivien Renaut, Ann-Christine Borja</t>
+          <t>Markus Borja, Ann-Christine Borja, Vivien Renaut</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
@@ -8577,7 +8577,7 @@
         <v>137040164</v>
       </c>
       <c r="B66" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8702,7 +8702,7 @@
         <v>137040166</v>
       </c>
       <c r="B67" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8827,7 +8827,7 @@
         <v>137040168</v>
       </c>
       <c r="B68" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8952,7 +8952,7 @@
         <v>137040189</v>
       </c>
       <c r="B69" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -9077,7 +9077,7 @@
         <v>137044057</v>
       </c>
       <c r="B70" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -9202,7 +9202,7 @@
         <v>137044059</v>
       </c>
       <c r="B71" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9327,7 +9327,7 @@
         <v>137044060</v>
       </c>
       <c r="B72" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9452,7 +9452,7 @@
         <v>137044061</v>
       </c>
       <c r="B73" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9577,7 +9577,7 @@
         <v>137044062</v>
       </c>
       <c r="B74" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9702,7 +9702,7 @@
         <v>137044064</v>
       </c>
       <c r="B75" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9827,7 +9827,7 @@
         <v>137044080</v>
       </c>
       <c r="B76" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9952,7 +9952,7 @@
         <v>137040134</v>
       </c>
       <c r="B77" t="n">
-        <v>79271</v>
+        <v>79274</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -10064,7 +10064,7 @@
         <v>137040136</v>
       </c>
       <c r="B78" t="n">
-        <v>79271</v>
+        <v>79274</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -10176,7 +10176,7 @@
         <v>137016336</v>
       </c>
       <c r="B79" t="n">
-        <v>79536</v>
+        <v>79539</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -10307,7 +10307,7 @@
         <v>137016339</v>
       </c>
       <c r="B80" t="n">
-        <v>79536</v>
+        <v>79539</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -10438,7 +10438,7 @@
         <v>137016342</v>
       </c>
       <c r="B81" t="n">
-        <v>79536</v>
+        <v>79539</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10569,7 +10569,7 @@
         <v>137016345</v>
       </c>
       <c r="B82" t="n">
-        <v>79536</v>
+        <v>79539</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10700,7 +10700,7 @@
         <v>137016346</v>
       </c>
       <c r="B83" t="n">
-        <v>79536</v>
+        <v>79539</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10831,7 +10831,7 @@
         <v>137016348</v>
       </c>
       <c r="B84" t="n">
-        <v>79536</v>
+        <v>79539</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10962,7 +10962,7 @@
         <v>137016353</v>
       </c>
       <c r="B85" t="n">
-        <v>79536</v>
+        <v>79539</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -11093,7 +11093,7 @@
         <v>137040099</v>
       </c>
       <c r="B86" t="n">
-        <v>79536</v>
+        <v>79539</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -11190,7 +11190,7 @@
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Markus Borja, Vivien Renaut, Ann-Christine Borja</t>
+          <t>Markus Borja, Ann-Christine Borja, Vivien Renaut</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
@@ -11205,7 +11205,7 @@
         <v>137044071</v>
       </c>
       <c r="B87" t="n">
-        <v>79536</v>
+        <v>79539</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>

--- a/artfynd/A 25855-2025 artfynd.xlsx
+++ b/artfynd/A 25855-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137044063</v>
       </c>
       <c r="B2" t="n">
-        <v>92433</v>
+        <v>92435</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -814,7 +814,7 @@
         <v>137040165</v>
       </c>
       <c r="B3" t="n">
-        <v>92995</v>
+        <v>92997</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -931,7 +931,7 @@
         <v>137016354</v>
       </c>
       <c r="B4" t="n">
-        <v>93477</v>
+        <v>93479</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1047,7 +1047,7 @@
         <v>137016293</v>
       </c>
       <c r="B5" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1159,7 +1159,7 @@
         <v>137040122</v>
       </c>
       <c r="B6" t="n">
-        <v>92125</v>
+        <v>92127</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1271,7 +1271,7 @@
         <v>137016298</v>
       </c>
       <c r="B7" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -2682,7 +2682,7 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja, Vivien Renaut</t>
+          <t>Markus Borja, Vivien Renaut, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2813,7 +2813,7 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja, Vivien Renaut</t>
+          <t>Markus Borja, Vivien Renaut, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2944,7 +2944,7 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja, Vivien Renaut</t>
+          <t>Markus Borja, Vivien Renaut, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -3075,7 +3075,7 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja, Vivien Renaut</t>
+          <t>Markus Borja, Vivien Renaut, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -4333,7 +4333,7 @@
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja, Vivien Renaut</t>
+          <t>Markus Borja, Vivien Renaut, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
@@ -5379,7 +5379,7 @@
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja, Vivien Renaut</t>
+          <t>Markus Borja, Vivien Renaut, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
@@ -5510,7 +5510,7 @@
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja, Vivien Renaut</t>
+          <t>Markus Borja, Vivien Renaut, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
@@ -5641,7 +5641,7 @@
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja, Vivien Renaut</t>
+          <t>Markus Borja, Vivien Renaut, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja, Vivien Renaut</t>
+          <t>Markus Borja, Vivien Renaut, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
@@ -7575,7 +7575,7 @@
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Markus Borja, Vivien Renaut, Ann-Christine Borja</t>
+          <t>Markus Borja, Ann-Christine Borja, Vivien Renaut</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
@@ -7827,7 +7827,7 @@
         <v>137040107</v>
       </c>
       <c r="B60" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7937,7 +7937,7 @@
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja, Vivien Renaut</t>
+          <t>Markus Borja, Vivien Renaut, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
@@ -7952,7 +7952,7 @@
         <v>137040121</v>
       </c>
       <c r="B61" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -8062,7 +8062,7 @@
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja, Vivien Renaut</t>
+          <t>Markus Borja, Vivien Renaut, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
@@ -8077,7 +8077,7 @@
         <v>137040123</v>
       </c>
       <c r="B62" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -8187,7 +8187,7 @@
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja, Vivien Renaut</t>
+          <t>Markus Borja, Vivien Renaut, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
@@ -8202,7 +8202,7 @@
         <v>137040138</v>
       </c>
       <c r="B63" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8312,7 +8312,7 @@
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja, Vivien Renaut</t>
+          <t>Markus Borja, Vivien Renaut, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
@@ -8327,7 +8327,7 @@
         <v>137040160</v>
       </c>
       <c r="B64" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8437,7 +8437,7 @@
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja, Vivien Renaut</t>
+          <t>Markus Borja, Vivien Renaut, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
@@ -8452,7 +8452,7 @@
         <v>137040163</v>
       </c>
       <c r="B65" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8562,7 +8562,7 @@
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja, Vivien Renaut</t>
+          <t>Markus Borja, Vivien Renaut, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
@@ -8577,7 +8577,7 @@
         <v>137040164</v>
       </c>
       <c r="B66" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8702,7 +8702,7 @@
         <v>137040166</v>
       </c>
       <c r="B67" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8827,7 +8827,7 @@
         <v>137040168</v>
       </c>
       <c r="B68" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8952,7 +8952,7 @@
         <v>137040189</v>
       </c>
       <c r="B69" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -9077,7 +9077,7 @@
         <v>137044057</v>
       </c>
       <c r="B70" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -9202,7 +9202,7 @@
         <v>137044059</v>
       </c>
       <c r="B71" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9327,7 +9327,7 @@
         <v>137044060</v>
       </c>
       <c r="B72" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9452,7 +9452,7 @@
         <v>137044061</v>
       </c>
       <c r="B73" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9577,7 +9577,7 @@
         <v>137044062</v>
       </c>
       <c r="B74" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9702,7 +9702,7 @@
         <v>137044064</v>
       </c>
       <c r="B75" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9827,7 +9827,7 @@
         <v>137044080</v>
       </c>
       <c r="B76" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -11190,7 +11190,7 @@
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja, Vivien Renaut</t>
+          <t>Markus Borja, Vivien Renaut, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>

--- a/artfynd/A 25855-2025 artfynd.xlsx
+++ b/artfynd/A 25855-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137044063</v>
       </c>
       <c r="B2" t="n">
-        <v>92435</v>
+        <v>92440</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -814,7 +814,7 @@
         <v>137040165</v>
       </c>
       <c r="B3" t="n">
-        <v>92997</v>
+        <v>93003</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -931,7 +931,7 @@
         <v>137016354</v>
       </c>
       <c r="B4" t="n">
-        <v>93479</v>
+        <v>93485</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1047,7 +1047,7 @@
         <v>137016293</v>
       </c>
       <c r="B5" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1159,7 +1159,7 @@
         <v>137040122</v>
       </c>
       <c r="B6" t="n">
-        <v>92127</v>
+        <v>92132</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1271,7 +1271,7 @@
         <v>137016298</v>
       </c>
       <c r="B7" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1387,7 +1387,7 @@
         <v>137016289</v>
       </c>
       <c r="B8" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1518,7 +1518,7 @@
         <v>137016306</v>
       </c>
       <c r="B9" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1649,7 +1649,7 @@
         <v>137016332</v>
       </c>
       <c r="B10" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1780,7 +1780,7 @@
         <v>137016333</v>
       </c>
       <c r="B11" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1911,7 +1911,7 @@
         <v>137016335</v>
       </c>
       <c r="B12" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2042,7 +2042,7 @@
         <v>137016337</v>
       </c>
       <c r="B13" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2173,7 +2173,7 @@
         <v>137016340</v>
       </c>
       <c r="B14" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2304,7 +2304,7 @@
         <v>137016349</v>
       </c>
       <c r="B15" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2435,7 +2435,7 @@
         <v>137016350</v>
       </c>
       <c r="B16" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2566,7 +2566,7 @@
         <v>137040102</v>
       </c>
       <c r="B17" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2697,7 +2697,7 @@
         <v>137040133</v>
       </c>
       <c r="B18" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2828,7 +2828,7 @@
         <v>137040161</v>
       </c>
       <c r="B19" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2959,7 +2959,7 @@
         <v>137040162</v>
       </c>
       <c r="B20" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3090,7 +3090,7 @@
         <v>137040167</v>
       </c>
       <c r="B21" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3202,7 +3202,7 @@
         <v>137040169</v>
       </c>
       <c r="B22" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3314,7 +3314,7 @@
         <v>137040181</v>
       </c>
       <c r="B23" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3431,7 +3431,7 @@
         <v>137044055</v>
       </c>
       <c r="B24" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3562,7 +3562,7 @@
         <v>137044068</v>
       </c>
       <c r="B25" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3693,7 +3693,7 @@
         <v>137044072</v>
       </c>
       <c r="B26" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3824,7 +3824,7 @@
         <v>137016334</v>
       </c>
       <c r="B27" t="n">
-        <v>79540</v>
+        <v>79545</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3955,7 +3955,7 @@
         <v>137016341</v>
       </c>
       <c r="B28" t="n">
-        <v>79540</v>
+        <v>79545</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4086,7 +4086,7 @@
         <v>137016351</v>
       </c>
       <c r="B29" t="n">
-        <v>79540</v>
+        <v>79545</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4217,7 +4217,7 @@
         <v>137040100</v>
       </c>
       <c r="B30" t="n">
-        <v>79540</v>
+        <v>79545</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4348,7 +4348,7 @@
         <v>137044056</v>
       </c>
       <c r="B31" t="n">
-        <v>79540</v>
+        <v>79545</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4479,7 +4479,7 @@
         <v>137040105</v>
       </c>
       <c r="B32" t="n">
-        <v>79273</v>
+        <v>79278</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4591,7 +4591,7 @@
         <v>137040135</v>
       </c>
       <c r="B33" t="n">
-        <v>79273</v>
+        <v>79278</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4703,7 +4703,7 @@
         <v>137016288</v>
       </c>
       <c r="B34" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4815,7 +4815,7 @@
         <v>137016299</v>
       </c>
       <c r="B35" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4927,7 +4927,7 @@
         <v>137016303</v>
       </c>
       <c r="B36" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5039,7 +5039,7 @@
         <v>137040101</v>
       </c>
       <c r="B37" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5151,7 +5151,7 @@
         <v>137040104</v>
       </c>
       <c r="B38" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5263,7 +5263,7 @@
         <v>137040108</v>
       </c>
       <c r="B39" t="n">
-        <v>80525</v>
+        <v>80530</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5394,7 +5394,7 @@
         <v>137040110</v>
       </c>
       <c r="B40" t="n">
-        <v>80525</v>
+        <v>80530</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5525,7 +5525,7 @@
         <v>137040111</v>
       </c>
       <c r="B41" t="n">
-        <v>80525</v>
+        <v>80530</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5656,7 +5656,7 @@
         <v>137016301</v>
       </c>
       <c r="B42" t="n">
-        <v>58031</v>
+        <v>58032</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5772,7 +5772,7 @@
         <v>137040182</v>
       </c>
       <c r="B43" t="n">
-        <v>58031</v>
+        <v>58032</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5893,7 +5893,7 @@
         <v>137016287</v>
       </c>
       <c r="B44" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6014,7 +6014,7 @@
         <v>137016290</v>
       </c>
       <c r="B45" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6135,7 +6135,7 @@
         <v>137016291</v>
       </c>
       <c r="B46" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6256,7 +6256,7 @@
         <v>137016292</v>
       </c>
       <c r="B47" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6377,7 +6377,7 @@
         <v>137016294</v>
       </c>
       <c r="B48" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6498,7 +6498,7 @@
         <v>137016295</v>
       </c>
       <c r="B49" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6619,7 +6619,7 @@
         <v>137016296</v>
       </c>
       <c r="B50" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6740,7 +6740,7 @@
         <v>137016297</v>
       </c>
       <c r="B51" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6861,7 +6861,7 @@
         <v>137016300</v>
       </c>
       <c r="B52" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6982,7 +6982,7 @@
         <v>137016304</v>
       </c>
       <c r="B53" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -7088,7 +7088,7 @@
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja, Diego Borja</t>
+          <t>Markus Borja, Diego Borja, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
@@ -7103,7 +7103,7 @@
         <v>137016307</v>
       </c>
       <c r="B54" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7224,7 +7224,7 @@
         <v>137016344</v>
       </c>
       <c r="B55" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7345,7 +7345,7 @@
         <v>137040097</v>
       </c>
       <c r="B56" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7466,7 +7466,7 @@
         <v>137040106</v>
       </c>
       <c r="B57" t="n">
-        <v>58195</v>
+        <v>58196</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7590,7 +7590,7 @@
         <v>137040109</v>
       </c>
       <c r="B58" t="n">
-        <v>58195</v>
+        <v>58196</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7706,7 +7706,7 @@
         <v>137040177</v>
       </c>
       <c r="B59" t="n">
-        <v>58195</v>
+        <v>58196</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7827,7 +7827,7 @@
         <v>137040107</v>
       </c>
       <c r="B60" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7952,7 +7952,7 @@
         <v>137040121</v>
       </c>
       <c r="B61" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -8077,7 +8077,7 @@
         <v>137040123</v>
       </c>
       <c r="B62" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -8202,7 +8202,7 @@
         <v>137040138</v>
       </c>
       <c r="B63" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8327,7 +8327,7 @@
         <v>137040160</v>
       </c>
       <c r="B64" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8452,7 +8452,7 @@
         <v>137040163</v>
       </c>
       <c r="B65" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8577,7 +8577,7 @@
         <v>137040164</v>
       </c>
       <c r="B66" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8702,7 +8702,7 @@
         <v>137040166</v>
       </c>
       <c r="B67" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8827,7 +8827,7 @@
         <v>137040168</v>
       </c>
       <c r="B68" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8952,7 +8952,7 @@
         <v>137040189</v>
       </c>
       <c r="B69" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -9077,7 +9077,7 @@
         <v>137044057</v>
       </c>
       <c r="B70" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -9202,7 +9202,7 @@
         <v>137044059</v>
       </c>
       <c r="B71" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9327,7 +9327,7 @@
         <v>137044060</v>
       </c>
       <c r="B72" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9452,7 +9452,7 @@
         <v>137044061</v>
       </c>
       <c r="B73" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9577,7 +9577,7 @@
         <v>137044062</v>
       </c>
       <c r="B74" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9702,7 +9702,7 @@
         <v>137044064</v>
       </c>
       <c r="B75" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9827,7 +9827,7 @@
         <v>137044080</v>
       </c>
       <c r="B76" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9952,7 +9952,7 @@
         <v>137040134</v>
       </c>
       <c r="B77" t="n">
-        <v>79274</v>
+        <v>79279</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -10064,7 +10064,7 @@
         <v>137040136</v>
       </c>
       <c r="B78" t="n">
-        <v>79274</v>
+        <v>79279</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -10176,7 +10176,7 @@
         <v>137016336</v>
       </c>
       <c r="B79" t="n">
-        <v>79539</v>
+        <v>79544</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -10307,7 +10307,7 @@
         <v>137016339</v>
       </c>
       <c r="B80" t="n">
-        <v>79539</v>
+        <v>79544</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -10438,7 +10438,7 @@
         <v>137016342</v>
       </c>
       <c r="B81" t="n">
-        <v>79539</v>
+        <v>79544</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10569,7 +10569,7 @@
         <v>137016345</v>
       </c>
       <c r="B82" t="n">
-        <v>79539</v>
+        <v>79544</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10700,7 +10700,7 @@
         <v>137016346</v>
       </c>
       <c r="B83" t="n">
-        <v>79539</v>
+        <v>79544</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10831,7 +10831,7 @@
         <v>137016348</v>
       </c>
       <c r="B84" t="n">
-        <v>79539</v>
+        <v>79544</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10962,7 +10962,7 @@
         <v>137016353</v>
       </c>
       <c r="B85" t="n">
-        <v>79539</v>
+        <v>79544</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -11093,7 +11093,7 @@
         <v>137040099</v>
       </c>
       <c r="B86" t="n">
-        <v>79539</v>
+        <v>79544</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -11205,7 +11205,7 @@
         <v>137044071</v>
       </c>
       <c r="B87" t="n">
-        <v>79539</v>
+        <v>79544</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>

--- a/artfynd/A 25855-2025 artfynd.xlsx
+++ b/artfynd/A 25855-2025 artfynd.xlsx
@@ -7088,7 +7088,7 @@
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Markus Borja, Diego Borja, Ann-Christine Borja</t>
+          <t>Markus Borja, Ann-Christine Borja, Diego Borja</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>

--- a/artfynd/A 25855-2025 artfynd.xlsx
+++ b/artfynd/A 25855-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137044063</v>
       </c>
       <c r="B2" t="n">
-        <v>92440</v>
+        <v>92452</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -814,7 +814,7 @@
         <v>137040165</v>
       </c>
       <c r="B3" t="n">
-        <v>93003</v>
+        <v>93015</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -931,7 +931,7 @@
         <v>137016354</v>
       </c>
       <c r="B4" t="n">
-        <v>93485</v>
+        <v>93497</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1047,7 +1047,7 @@
         <v>137016293</v>
       </c>
       <c r="B5" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1159,7 +1159,7 @@
         <v>137040122</v>
       </c>
       <c r="B6" t="n">
-        <v>92132</v>
+        <v>92144</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1271,7 +1271,7 @@
         <v>137016298</v>
       </c>
       <c r="B7" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1387,7 +1387,7 @@
         <v>137016289</v>
       </c>
       <c r="B8" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1518,7 +1518,7 @@
         <v>137016306</v>
       </c>
       <c r="B9" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1649,7 +1649,7 @@
         <v>137016332</v>
       </c>
       <c r="B10" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1780,7 +1780,7 @@
         <v>137016333</v>
       </c>
       <c r="B11" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1911,7 +1911,7 @@
         <v>137016335</v>
       </c>
       <c r="B12" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2042,7 +2042,7 @@
         <v>137016337</v>
       </c>
       <c r="B13" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2173,7 +2173,7 @@
         <v>137016340</v>
       </c>
       <c r="B14" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2304,7 +2304,7 @@
         <v>137016349</v>
       </c>
       <c r="B15" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2435,7 +2435,7 @@
         <v>137016350</v>
       </c>
       <c r="B16" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2566,7 +2566,7 @@
         <v>137040102</v>
       </c>
       <c r="B17" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2697,7 +2697,7 @@
         <v>137040133</v>
       </c>
       <c r="B18" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2828,7 +2828,7 @@
         <v>137040161</v>
       </c>
       <c r="B19" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2959,7 +2959,7 @@
         <v>137040162</v>
       </c>
       <c r="B20" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3090,7 +3090,7 @@
         <v>137040167</v>
       </c>
       <c r="B21" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3202,7 +3202,7 @@
         <v>137040169</v>
       </c>
       <c r="B22" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3314,7 +3314,7 @@
         <v>137040181</v>
       </c>
       <c r="B23" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3431,7 +3431,7 @@
         <v>137044055</v>
       </c>
       <c r="B24" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3562,7 +3562,7 @@
         <v>137044068</v>
       </c>
       <c r="B25" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3693,7 +3693,7 @@
         <v>137044072</v>
       </c>
       <c r="B26" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3824,7 +3824,7 @@
         <v>137016334</v>
       </c>
       <c r="B27" t="n">
-        <v>79545</v>
+        <v>79556</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3955,7 +3955,7 @@
         <v>137016341</v>
       </c>
       <c r="B28" t="n">
-        <v>79545</v>
+        <v>79556</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4086,7 +4086,7 @@
         <v>137016351</v>
       </c>
       <c r="B29" t="n">
-        <v>79545</v>
+        <v>79556</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4217,7 +4217,7 @@
         <v>137040100</v>
       </c>
       <c r="B30" t="n">
-        <v>79545</v>
+        <v>79556</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4348,7 +4348,7 @@
         <v>137044056</v>
       </c>
       <c r="B31" t="n">
-        <v>79545</v>
+        <v>79556</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4479,7 +4479,7 @@
         <v>137040105</v>
       </c>
       <c r="B32" t="n">
-        <v>79278</v>
+        <v>79289</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4591,7 +4591,7 @@
         <v>137040135</v>
       </c>
       <c r="B33" t="n">
-        <v>79278</v>
+        <v>79289</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4703,7 +4703,7 @@
         <v>137016288</v>
       </c>
       <c r="B34" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4815,7 +4815,7 @@
         <v>137016299</v>
       </c>
       <c r="B35" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4927,7 +4927,7 @@
         <v>137016303</v>
       </c>
       <c r="B36" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5039,7 +5039,7 @@
         <v>137040101</v>
       </c>
       <c r="B37" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5151,7 +5151,7 @@
         <v>137040104</v>
       </c>
       <c r="B38" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5263,7 +5263,7 @@
         <v>137040108</v>
       </c>
       <c r="B39" t="n">
-        <v>80530</v>
+        <v>80541</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5394,7 +5394,7 @@
         <v>137040110</v>
       </c>
       <c r="B40" t="n">
-        <v>80530</v>
+        <v>80541</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5525,7 +5525,7 @@
         <v>137040111</v>
       </c>
       <c r="B41" t="n">
-        <v>80530</v>
+        <v>80541</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -7827,7 +7827,7 @@
         <v>137040107</v>
       </c>
       <c r="B60" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7952,7 +7952,7 @@
         <v>137040121</v>
       </c>
       <c r="B61" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -8077,7 +8077,7 @@
         <v>137040123</v>
       </c>
       <c r="B62" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -8202,7 +8202,7 @@
         <v>137040138</v>
       </c>
       <c r="B63" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8327,7 +8327,7 @@
         <v>137040160</v>
       </c>
       <c r="B64" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8452,7 +8452,7 @@
         <v>137040163</v>
       </c>
       <c r="B65" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8577,7 +8577,7 @@
         <v>137040164</v>
       </c>
       <c r="B66" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8702,7 +8702,7 @@
         <v>137040166</v>
       </c>
       <c r="B67" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8827,7 +8827,7 @@
         <v>137040168</v>
       </c>
       <c r="B68" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8952,7 +8952,7 @@
         <v>137040189</v>
       </c>
       <c r="B69" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -9077,7 +9077,7 @@
         <v>137044057</v>
       </c>
       <c r="B70" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -9202,7 +9202,7 @@
         <v>137044059</v>
       </c>
       <c r="B71" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9327,7 +9327,7 @@
         <v>137044060</v>
       </c>
       <c r="B72" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9452,7 +9452,7 @@
         <v>137044061</v>
       </c>
       <c r="B73" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9577,7 +9577,7 @@
         <v>137044062</v>
       </c>
       <c r="B74" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9702,7 +9702,7 @@
         <v>137044064</v>
       </c>
       <c r="B75" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9827,7 +9827,7 @@
         <v>137044080</v>
       </c>
       <c r="B76" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9952,7 +9952,7 @@
         <v>137040134</v>
       </c>
       <c r="B77" t="n">
-        <v>79279</v>
+        <v>79290</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -10064,7 +10064,7 @@
         <v>137040136</v>
       </c>
       <c r="B78" t="n">
-        <v>79279</v>
+        <v>79290</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -10176,7 +10176,7 @@
         <v>137016336</v>
       </c>
       <c r="B79" t="n">
-        <v>79544</v>
+        <v>79555</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -10307,7 +10307,7 @@
         <v>137016339</v>
       </c>
       <c r="B80" t="n">
-        <v>79544</v>
+        <v>79555</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -10438,7 +10438,7 @@
         <v>137016342</v>
       </c>
       <c r="B81" t="n">
-        <v>79544</v>
+        <v>79555</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10569,7 +10569,7 @@
         <v>137016345</v>
       </c>
       <c r="B82" t="n">
-        <v>79544</v>
+        <v>79555</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10700,7 +10700,7 @@
         <v>137016346</v>
       </c>
       <c r="B83" t="n">
-        <v>79544</v>
+        <v>79555</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10831,7 +10831,7 @@
         <v>137016348</v>
       </c>
       <c r="B84" t="n">
-        <v>79544</v>
+        <v>79555</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10962,7 +10962,7 @@
         <v>137016353</v>
       </c>
       <c r="B85" t="n">
-        <v>79544</v>
+        <v>79555</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -11093,7 +11093,7 @@
         <v>137040099</v>
       </c>
       <c r="B86" t="n">
-        <v>79544</v>
+        <v>79555</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -11205,7 +11205,7 @@
         <v>137044071</v>
       </c>
       <c r="B87" t="n">
-        <v>79544</v>
+        <v>79555</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>

--- a/artfynd/A 25855-2025 artfynd.xlsx
+++ b/artfynd/A 25855-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137044063</v>
       </c>
       <c r="B2" t="n">
-        <v>92452</v>
+        <v>92453</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -814,7 +814,7 @@
         <v>137040165</v>
       </c>
       <c r="B3" t="n">
-        <v>93015</v>
+        <v>93016</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -931,7 +931,7 @@
         <v>137016354</v>
       </c>
       <c r="B4" t="n">
-        <v>93497</v>
+        <v>93498</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1047,7 +1047,7 @@
         <v>137016293</v>
       </c>
       <c r="B5" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1159,7 +1159,7 @@
         <v>137040122</v>
       </c>
       <c r="B6" t="n">
-        <v>92144</v>
+        <v>92145</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1271,7 +1271,7 @@
         <v>137016298</v>
       </c>
       <c r="B7" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1387,7 +1387,7 @@
         <v>137016289</v>
       </c>
       <c r="B8" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1518,7 +1518,7 @@
         <v>137016306</v>
       </c>
       <c r="B9" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1649,7 +1649,7 @@
         <v>137016332</v>
       </c>
       <c r="B10" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1780,7 +1780,7 @@
         <v>137016333</v>
       </c>
       <c r="B11" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1911,7 +1911,7 @@
         <v>137016335</v>
       </c>
       <c r="B12" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2042,7 +2042,7 @@
         <v>137016337</v>
       </c>
       <c r="B13" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2173,7 +2173,7 @@
         <v>137016340</v>
       </c>
       <c r="B14" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2304,7 +2304,7 @@
         <v>137016349</v>
       </c>
       <c r="B15" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2435,7 +2435,7 @@
         <v>137016350</v>
       </c>
       <c r="B16" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2566,7 +2566,7 @@
         <v>137040102</v>
       </c>
       <c r="B17" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2697,7 +2697,7 @@
         <v>137040133</v>
       </c>
       <c r="B18" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2828,7 +2828,7 @@
         <v>137040161</v>
       </c>
       <c r="B19" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2959,7 +2959,7 @@
         <v>137040162</v>
       </c>
       <c r="B20" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3090,7 +3090,7 @@
         <v>137040167</v>
       </c>
       <c r="B21" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3202,7 +3202,7 @@
         <v>137040169</v>
       </c>
       <c r="B22" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3314,7 +3314,7 @@
         <v>137040181</v>
       </c>
       <c r="B23" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3431,7 +3431,7 @@
         <v>137044055</v>
       </c>
       <c r="B24" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3562,7 +3562,7 @@
         <v>137044068</v>
       </c>
       <c r="B25" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3693,7 +3693,7 @@
         <v>137044072</v>
       </c>
       <c r="B26" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3824,7 +3824,7 @@
         <v>137016334</v>
       </c>
       <c r="B27" t="n">
-        <v>79556</v>
+        <v>79557</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3955,7 +3955,7 @@
         <v>137016341</v>
       </c>
       <c r="B28" t="n">
-        <v>79556</v>
+        <v>79557</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4086,7 +4086,7 @@
         <v>137016351</v>
       </c>
       <c r="B29" t="n">
-        <v>79556</v>
+        <v>79557</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4217,7 +4217,7 @@
         <v>137040100</v>
       </c>
       <c r="B30" t="n">
-        <v>79556</v>
+        <v>79557</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4348,7 +4348,7 @@
         <v>137044056</v>
       </c>
       <c r="B31" t="n">
-        <v>79556</v>
+        <v>79557</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4479,7 +4479,7 @@
         <v>137040105</v>
       </c>
       <c r="B32" t="n">
-        <v>79289</v>
+        <v>79290</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4591,7 +4591,7 @@
         <v>137040135</v>
       </c>
       <c r="B33" t="n">
-        <v>79289</v>
+        <v>79290</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4703,7 +4703,7 @@
         <v>137016288</v>
       </c>
       <c r="B34" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4815,7 +4815,7 @@
         <v>137016299</v>
       </c>
       <c r="B35" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4927,7 +4927,7 @@
         <v>137016303</v>
       </c>
       <c r="B36" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5039,7 +5039,7 @@
         <v>137040101</v>
       </c>
       <c r="B37" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5151,7 +5151,7 @@
         <v>137040104</v>
       </c>
       <c r="B38" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5263,7 +5263,7 @@
         <v>137040108</v>
       </c>
       <c r="B39" t="n">
-        <v>80541</v>
+        <v>80542</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5394,7 +5394,7 @@
         <v>137040110</v>
       </c>
       <c r="B40" t="n">
-        <v>80541</v>
+        <v>80542</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5525,7 +5525,7 @@
         <v>137040111</v>
       </c>
       <c r="B41" t="n">
-        <v>80541</v>
+        <v>80542</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -7827,7 +7827,7 @@
         <v>137040107</v>
       </c>
       <c r="B60" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7952,7 +7952,7 @@
         <v>137040121</v>
       </c>
       <c r="B61" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -8077,7 +8077,7 @@
         <v>137040123</v>
       </c>
       <c r="B62" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -8202,7 +8202,7 @@
         <v>137040138</v>
       </c>
       <c r="B63" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8327,7 +8327,7 @@
         <v>137040160</v>
       </c>
       <c r="B64" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8452,7 +8452,7 @@
         <v>137040163</v>
       </c>
       <c r="B65" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8577,7 +8577,7 @@
         <v>137040164</v>
       </c>
       <c r="B66" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8702,7 +8702,7 @@
         <v>137040166</v>
       </c>
       <c r="B67" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8827,7 +8827,7 @@
         <v>137040168</v>
       </c>
       <c r="B68" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8952,7 +8952,7 @@
         <v>137040189</v>
       </c>
       <c r="B69" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -9077,7 +9077,7 @@
         <v>137044057</v>
       </c>
       <c r="B70" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -9202,7 +9202,7 @@
         <v>137044059</v>
       </c>
       <c r="B71" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9327,7 +9327,7 @@
         <v>137044060</v>
       </c>
       <c r="B72" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9452,7 +9452,7 @@
         <v>137044061</v>
       </c>
       <c r="B73" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9577,7 +9577,7 @@
         <v>137044062</v>
       </c>
       <c r="B74" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9702,7 +9702,7 @@
         <v>137044064</v>
       </c>
       <c r="B75" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9827,7 +9827,7 @@
         <v>137044080</v>
       </c>
       <c r="B76" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9952,7 +9952,7 @@
         <v>137040134</v>
       </c>
       <c r="B77" t="n">
-        <v>79290</v>
+        <v>79291</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -10064,7 +10064,7 @@
         <v>137040136</v>
       </c>
       <c r="B78" t="n">
-        <v>79290</v>
+        <v>79291</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -10176,7 +10176,7 @@
         <v>137016336</v>
       </c>
       <c r="B79" t="n">
-        <v>79555</v>
+        <v>79556</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -10307,7 +10307,7 @@
         <v>137016339</v>
       </c>
       <c r="B80" t="n">
-        <v>79555</v>
+        <v>79556</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -10438,7 +10438,7 @@
         <v>137016342</v>
       </c>
       <c r="B81" t="n">
-        <v>79555</v>
+        <v>79556</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10569,7 +10569,7 @@
         <v>137016345</v>
       </c>
       <c r="B82" t="n">
-        <v>79555</v>
+        <v>79556</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10700,7 +10700,7 @@
         <v>137016346</v>
       </c>
       <c r="B83" t="n">
-        <v>79555</v>
+        <v>79556</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10831,7 +10831,7 @@
         <v>137016348</v>
       </c>
       <c r="B84" t="n">
-        <v>79555</v>
+        <v>79556</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10962,7 +10962,7 @@
         <v>137016353</v>
       </c>
       <c r="B85" t="n">
-        <v>79555</v>
+        <v>79556</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -11093,7 +11093,7 @@
         <v>137040099</v>
       </c>
       <c r="B86" t="n">
-        <v>79555</v>
+        <v>79556</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -11205,7 +11205,7 @@
         <v>137044071</v>
       </c>
       <c r="B87" t="n">
-        <v>79555</v>
+        <v>79556</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>

--- a/artfynd/A 25855-2025 artfynd.xlsx
+++ b/artfynd/A 25855-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137044063</v>
       </c>
       <c r="B2" t="n">
-        <v>92453</v>
+        <v>92456</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -814,7 +814,7 @@
         <v>137040165</v>
       </c>
       <c r="B3" t="n">
-        <v>93016</v>
+        <v>93019</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -931,7 +931,7 @@
         <v>137016354</v>
       </c>
       <c r="B4" t="n">
-        <v>93498</v>
+        <v>93501</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1047,7 +1047,7 @@
         <v>137016293</v>
       </c>
       <c r="B5" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1159,7 +1159,7 @@
         <v>137040122</v>
       </c>
       <c r="B6" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1271,7 +1271,7 @@
         <v>137016298</v>
       </c>
       <c r="B7" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1372,7 +1372,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Markus Borja, Diego Borja, Ann-Christine Borja</t>
+          <t>Markus Borja, Ann-Christine Borja, Diego Borja</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1387,7 +1387,7 @@
         <v>137016289</v>
       </c>
       <c r="B8" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1518,7 +1518,7 @@
         <v>137016306</v>
       </c>
       <c r="B9" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1649,7 +1649,7 @@
         <v>137016332</v>
       </c>
       <c r="B10" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1780,7 +1780,7 @@
         <v>137016333</v>
       </c>
       <c r="B11" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1911,7 +1911,7 @@
         <v>137016335</v>
       </c>
       <c r="B12" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2042,7 +2042,7 @@
         <v>137016337</v>
       </c>
       <c r="B13" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2173,7 +2173,7 @@
         <v>137016340</v>
       </c>
       <c r="B14" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2304,7 +2304,7 @@
         <v>137016349</v>
       </c>
       <c r="B15" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2435,7 +2435,7 @@
         <v>137016350</v>
       </c>
       <c r="B16" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2566,7 +2566,7 @@
         <v>137040102</v>
       </c>
       <c r="B17" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2697,7 +2697,7 @@
         <v>137040133</v>
       </c>
       <c r="B18" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2828,7 +2828,7 @@
         <v>137040161</v>
       </c>
       <c r="B19" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2959,7 +2959,7 @@
         <v>137040162</v>
       </c>
       <c r="B20" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3090,7 +3090,7 @@
         <v>137040167</v>
       </c>
       <c r="B21" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3202,7 +3202,7 @@
         <v>137040169</v>
       </c>
       <c r="B22" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3314,7 +3314,7 @@
         <v>137040181</v>
       </c>
       <c r="B23" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3431,7 +3431,7 @@
         <v>137044055</v>
       </c>
       <c r="B24" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3562,7 +3562,7 @@
         <v>137044068</v>
       </c>
       <c r="B25" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3693,7 +3693,7 @@
         <v>137044072</v>
       </c>
       <c r="B26" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3824,7 +3824,7 @@
         <v>137016334</v>
       </c>
       <c r="B27" t="n">
-        <v>79557</v>
+        <v>79559</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3955,7 +3955,7 @@
         <v>137016341</v>
       </c>
       <c r="B28" t="n">
-        <v>79557</v>
+        <v>79559</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4086,7 +4086,7 @@
         <v>137016351</v>
       </c>
       <c r="B29" t="n">
-        <v>79557</v>
+        <v>79559</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4217,7 +4217,7 @@
         <v>137040100</v>
       </c>
       <c r="B30" t="n">
-        <v>79557</v>
+        <v>79559</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4348,7 +4348,7 @@
         <v>137044056</v>
       </c>
       <c r="B31" t="n">
-        <v>79557</v>
+        <v>79559</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4479,7 +4479,7 @@
         <v>137040105</v>
       </c>
       <c r="B32" t="n">
-        <v>79290</v>
+        <v>79292</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4591,7 +4591,7 @@
         <v>137040135</v>
       </c>
       <c r="B33" t="n">
-        <v>79290</v>
+        <v>79292</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4703,7 +4703,7 @@
         <v>137016288</v>
       </c>
       <c r="B34" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4815,7 +4815,7 @@
         <v>137016299</v>
       </c>
       <c r="B35" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4927,7 +4927,7 @@
         <v>137016303</v>
       </c>
       <c r="B36" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5039,7 +5039,7 @@
         <v>137040101</v>
       </c>
       <c r="B37" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5151,7 +5151,7 @@
         <v>137040104</v>
       </c>
       <c r="B38" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5263,7 +5263,7 @@
         <v>137040108</v>
       </c>
       <c r="B39" t="n">
-        <v>80542</v>
+        <v>80544</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5394,7 +5394,7 @@
         <v>137040110</v>
       </c>
       <c r="B40" t="n">
-        <v>80542</v>
+        <v>80544</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5525,7 +5525,7 @@
         <v>137040111</v>
       </c>
       <c r="B41" t="n">
-        <v>80542</v>
+        <v>80544</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -7088,7 +7088,7 @@
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja, Diego Borja</t>
+          <t>Markus Borja, Diego Borja, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
@@ -7827,7 +7827,7 @@
         <v>137040107</v>
       </c>
       <c r="B60" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7952,7 +7952,7 @@
         <v>137040121</v>
       </c>
       <c r="B61" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -8077,7 +8077,7 @@
         <v>137040123</v>
       </c>
       <c r="B62" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -8202,7 +8202,7 @@
         <v>137040138</v>
       </c>
       <c r="B63" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8327,7 +8327,7 @@
         <v>137040160</v>
       </c>
       <c r="B64" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8452,7 +8452,7 @@
         <v>137040163</v>
       </c>
       <c r="B65" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8577,7 +8577,7 @@
         <v>137040164</v>
       </c>
       <c r="B66" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8702,7 +8702,7 @@
         <v>137040166</v>
       </c>
       <c r="B67" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8827,7 +8827,7 @@
         <v>137040168</v>
       </c>
       <c r="B68" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8952,7 +8952,7 @@
         <v>137040189</v>
       </c>
       <c r="B69" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -9077,7 +9077,7 @@
         <v>137044057</v>
       </c>
       <c r="B70" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -9202,7 +9202,7 @@
         <v>137044059</v>
       </c>
       <c r="B71" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9327,7 +9327,7 @@
         <v>137044060</v>
       </c>
       <c r="B72" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9452,7 +9452,7 @@
         <v>137044061</v>
       </c>
       <c r="B73" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9577,7 +9577,7 @@
         <v>137044062</v>
       </c>
       <c r="B74" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9702,7 +9702,7 @@
         <v>137044064</v>
       </c>
       <c r="B75" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9827,7 +9827,7 @@
         <v>137044080</v>
       </c>
       <c r="B76" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9952,7 +9952,7 @@
         <v>137040134</v>
       </c>
       <c r="B77" t="n">
-        <v>79291</v>
+        <v>79293</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -10064,7 +10064,7 @@
         <v>137040136</v>
       </c>
       <c r="B78" t="n">
-        <v>79291</v>
+        <v>79293</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -10176,7 +10176,7 @@
         <v>137016336</v>
       </c>
       <c r="B79" t="n">
-        <v>79556</v>
+        <v>79558</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -10307,7 +10307,7 @@
         <v>137016339</v>
       </c>
       <c r="B80" t="n">
-        <v>79556</v>
+        <v>79558</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -10438,7 +10438,7 @@
         <v>137016342</v>
       </c>
       <c r="B81" t="n">
-        <v>79556</v>
+        <v>79558</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10569,7 +10569,7 @@
         <v>137016345</v>
       </c>
       <c r="B82" t="n">
-        <v>79556</v>
+        <v>79558</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10700,7 +10700,7 @@
         <v>137016346</v>
       </c>
       <c r="B83" t="n">
-        <v>79556</v>
+        <v>79558</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10831,7 +10831,7 @@
         <v>137016348</v>
       </c>
       <c r="B84" t="n">
-        <v>79556</v>
+        <v>79558</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10962,7 +10962,7 @@
         <v>137016353</v>
       </c>
       <c r="B85" t="n">
-        <v>79556</v>
+        <v>79558</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -11093,7 +11093,7 @@
         <v>137040099</v>
       </c>
       <c r="B86" t="n">
-        <v>79556</v>
+        <v>79558</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -11205,7 +11205,7 @@
         <v>137044071</v>
       </c>
       <c r="B87" t="n">
-        <v>79556</v>
+        <v>79558</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>

--- a/artfynd/A 25855-2025 artfynd.xlsx
+++ b/artfynd/A 25855-2025 artfynd.xlsx
@@ -1372,7 +1372,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja, Diego Borja</t>
+          <t>Markus Borja, Diego Borja, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -7088,7 +7088,7 @@
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Markus Borja, Diego Borja, Ann-Christine Borja</t>
+          <t>Markus Borja, Ann-Christine Borja, Diego Borja</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>

--- a/artfynd/A 25855-2025 artfynd.xlsx
+++ b/artfynd/A 25855-2025 artfynd.xlsx
@@ -931,7 +931,7 @@
         <v>137016354</v>
       </c>
       <c r="B4" t="n">
-        <v>93501</v>
+        <v>93502</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1047,7 +1047,7 @@
         <v>137016293</v>
       </c>
       <c r="B5" t="n">
-        <v>93485</v>
+        <v>93486</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1271,7 +1271,7 @@
         <v>137016298</v>
       </c>
       <c r="B7" t="n">
-        <v>93523</v>
+        <v>93524</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1387,7 +1387,7 @@
         <v>137016289</v>
       </c>
       <c r="B8" t="n">
-        <v>79535</v>
+        <v>79536</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1518,7 +1518,7 @@
         <v>137016306</v>
       </c>
       <c r="B9" t="n">
-        <v>79535</v>
+        <v>79536</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1649,7 +1649,7 @@
         <v>137016332</v>
       </c>
       <c r="B10" t="n">
-        <v>79535</v>
+        <v>79536</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1780,7 +1780,7 @@
         <v>137016333</v>
       </c>
       <c r="B11" t="n">
-        <v>79535</v>
+        <v>79536</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1911,7 +1911,7 @@
         <v>137016335</v>
       </c>
       <c r="B12" t="n">
-        <v>79535</v>
+        <v>79536</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2042,7 +2042,7 @@
         <v>137016337</v>
       </c>
       <c r="B13" t="n">
-        <v>79535</v>
+        <v>79536</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2173,7 +2173,7 @@
         <v>137016340</v>
       </c>
       <c r="B14" t="n">
-        <v>79535</v>
+        <v>79536</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2304,7 +2304,7 @@
         <v>137016349</v>
       </c>
       <c r="B15" t="n">
-        <v>79535</v>
+        <v>79536</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2435,7 +2435,7 @@
         <v>137016350</v>
       </c>
       <c r="B16" t="n">
-        <v>79535</v>
+        <v>79536</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -3824,7 +3824,7 @@
         <v>137016334</v>
       </c>
       <c r="B27" t="n">
-        <v>79559</v>
+        <v>79560</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3955,7 +3955,7 @@
         <v>137016341</v>
       </c>
       <c r="B28" t="n">
-        <v>79559</v>
+        <v>79560</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4086,7 +4086,7 @@
         <v>137016351</v>
       </c>
       <c r="B29" t="n">
-        <v>79559</v>
+        <v>79560</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4703,7 +4703,7 @@
         <v>137016288</v>
       </c>
       <c r="B34" t="n">
-        <v>80154</v>
+        <v>80155</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4815,7 +4815,7 @@
         <v>137016299</v>
       </c>
       <c r="B35" t="n">
-        <v>80154</v>
+        <v>80155</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4927,7 +4927,7 @@
         <v>137016303</v>
       </c>
       <c r="B36" t="n">
-        <v>80154</v>
+        <v>80155</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -10176,7 +10176,7 @@
         <v>137016336</v>
       </c>
       <c r="B79" t="n">
-        <v>79558</v>
+        <v>79559</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -10307,7 +10307,7 @@
         <v>137016339</v>
       </c>
       <c r="B80" t="n">
-        <v>79558</v>
+        <v>79559</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -10438,7 +10438,7 @@
         <v>137016342</v>
       </c>
       <c r="B81" t="n">
-        <v>79558</v>
+        <v>79559</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10569,7 +10569,7 @@
         <v>137016345</v>
       </c>
       <c r="B82" t="n">
-        <v>79558</v>
+        <v>79559</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10700,7 +10700,7 @@
         <v>137016346</v>
       </c>
       <c r="B83" t="n">
-        <v>79558</v>
+        <v>79559</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10831,7 +10831,7 @@
         <v>137016348</v>
       </c>
       <c r="B84" t="n">
-        <v>79558</v>
+        <v>79559</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10962,7 +10962,7 @@
         <v>137016353</v>
       </c>
       <c r="B85" t="n">
-        <v>79558</v>
+        <v>79559</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>

--- a/artfynd/A 25855-2025 artfynd.xlsx
+++ b/artfynd/A 25855-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137044063</v>
       </c>
       <c r="B2" t="n">
-        <v>92456</v>
+        <v>92460</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -814,7 +814,7 @@
         <v>137040165</v>
       </c>
       <c r="B3" t="n">
-        <v>93019</v>
+        <v>93023</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -931,7 +931,7 @@
         <v>137016354</v>
       </c>
       <c r="B4" t="n">
-        <v>93502</v>
+        <v>93505</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1047,7 +1047,7 @@
         <v>137016293</v>
       </c>
       <c r="B5" t="n">
-        <v>93486</v>
+        <v>93489</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1159,7 +1159,7 @@
         <v>137040122</v>
       </c>
       <c r="B6" t="n">
-        <v>92148</v>
+        <v>92152</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1271,7 +1271,7 @@
         <v>137016298</v>
       </c>
       <c r="B7" t="n">
-        <v>93524</v>
+        <v>93527</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1387,7 +1387,7 @@
         <v>137016289</v>
       </c>
       <c r="B8" t="n">
-        <v>79536</v>
+        <v>79539</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1518,7 +1518,7 @@
         <v>137016306</v>
       </c>
       <c r="B9" t="n">
-        <v>79536</v>
+        <v>79539</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1649,7 +1649,7 @@
         <v>137016332</v>
       </c>
       <c r="B10" t="n">
-        <v>79536</v>
+        <v>79539</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1780,7 +1780,7 @@
         <v>137016333</v>
       </c>
       <c r="B11" t="n">
-        <v>79536</v>
+        <v>79539</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1911,7 +1911,7 @@
         <v>137016335</v>
       </c>
       <c r="B12" t="n">
-        <v>79536</v>
+        <v>79539</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2042,7 +2042,7 @@
         <v>137016337</v>
       </c>
       <c r="B13" t="n">
-        <v>79536</v>
+        <v>79539</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2173,7 +2173,7 @@
         <v>137016340</v>
       </c>
       <c r="B14" t="n">
-        <v>79536</v>
+        <v>79539</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2304,7 +2304,7 @@
         <v>137016349</v>
       </c>
       <c r="B15" t="n">
-        <v>79536</v>
+        <v>79539</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2435,7 +2435,7 @@
         <v>137016350</v>
       </c>
       <c r="B16" t="n">
-        <v>79536</v>
+        <v>79539</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2566,7 +2566,7 @@
         <v>137040102</v>
       </c>
       <c r="B17" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2697,7 +2697,7 @@
         <v>137040133</v>
       </c>
       <c r="B18" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2828,7 +2828,7 @@
         <v>137040161</v>
       </c>
       <c r="B19" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2959,7 +2959,7 @@
         <v>137040162</v>
       </c>
       <c r="B20" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3090,7 +3090,7 @@
         <v>137040167</v>
       </c>
       <c r="B21" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3202,7 +3202,7 @@
         <v>137040169</v>
       </c>
       <c r="B22" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3314,7 +3314,7 @@
         <v>137040181</v>
       </c>
       <c r="B23" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3431,7 +3431,7 @@
         <v>137044055</v>
       </c>
       <c r="B24" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3562,7 +3562,7 @@
         <v>137044068</v>
       </c>
       <c r="B25" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3693,7 +3693,7 @@
         <v>137044072</v>
       </c>
       <c r="B26" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3824,7 +3824,7 @@
         <v>137016334</v>
       </c>
       <c r="B27" t="n">
-        <v>79560</v>
+        <v>79563</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3955,7 +3955,7 @@
         <v>137016341</v>
       </c>
       <c r="B28" t="n">
-        <v>79560</v>
+        <v>79563</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4086,7 +4086,7 @@
         <v>137016351</v>
       </c>
       <c r="B29" t="n">
-        <v>79560</v>
+        <v>79563</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4217,7 +4217,7 @@
         <v>137040100</v>
       </c>
       <c r="B30" t="n">
-        <v>79559</v>
+        <v>79563</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4348,7 +4348,7 @@
         <v>137044056</v>
       </c>
       <c r="B31" t="n">
-        <v>79559</v>
+        <v>79563</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4479,7 +4479,7 @@
         <v>137040105</v>
       </c>
       <c r="B32" t="n">
-        <v>79292</v>
+        <v>79296</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4591,7 +4591,7 @@
         <v>137040135</v>
       </c>
       <c r="B33" t="n">
-        <v>79292</v>
+        <v>79296</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4703,7 +4703,7 @@
         <v>137016288</v>
       </c>
       <c r="B34" t="n">
-        <v>80155</v>
+        <v>80158</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4815,7 +4815,7 @@
         <v>137016299</v>
       </c>
       <c r="B35" t="n">
-        <v>80155</v>
+        <v>80158</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4927,7 +4927,7 @@
         <v>137016303</v>
       </c>
       <c r="B36" t="n">
-        <v>80155</v>
+        <v>80158</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5039,7 +5039,7 @@
         <v>137040101</v>
       </c>
       <c r="B37" t="n">
-        <v>80154</v>
+        <v>80158</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5151,7 +5151,7 @@
         <v>137040104</v>
       </c>
       <c r="B38" t="n">
-        <v>80154</v>
+        <v>80158</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5263,7 +5263,7 @@
         <v>137040108</v>
       </c>
       <c r="B39" t="n">
-        <v>80544</v>
+        <v>80548</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5394,7 +5394,7 @@
         <v>137040110</v>
       </c>
       <c r="B40" t="n">
-        <v>80544</v>
+        <v>80548</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5525,7 +5525,7 @@
         <v>137040111</v>
       </c>
       <c r="B41" t="n">
-        <v>80544</v>
+        <v>80548</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5656,7 +5656,7 @@
         <v>137016301</v>
       </c>
       <c r="B42" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5772,7 +5772,7 @@
         <v>137040182</v>
       </c>
       <c r="B43" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5893,7 +5893,7 @@
         <v>137016287</v>
       </c>
       <c r="B44" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6014,7 +6014,7 @@
         <v>137016290</v>
       </c>
       <c r="B45" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6135,7 +6135,7 @@
         <v>137016291</v>
       </c>
       <c r="B46" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6256,7 +6256,7 @@
         <v>137016292</v>
       </c>
       <c r="B47" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6377,7 +6377,7 @@
         <v>137016294</v>
       </c>
       <c r="B48" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6498,7 +6498,7 @@
         <v>137016295</v>
       </c>
       <c r="B49" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6619,7 +6619,7 @@
         <v>137016296</v>
       </c>
       <c r="B50" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6740,7 +6740,7 @@
         <v>137016297</v>
       </c>
       <c r="B51" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6861,7 +6861,7 @@
         <v>137016300</v>
       </c>
       <c r="B52" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6982,7 +6982,7 @@
         <v>137016304</v>
       </c>
       <c r="B53" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -7103,7 +7103,7 @@
         <v>137016307</v>
       </c>
       <c r="B54" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7224,7 +7224,7 @@
         <v>137016344</v>
       </c>
       <c r="B55" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7345,7 +7345,7 @@
         <v>137040097</v>
       </c>
       <c r="B56" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7466,7 +7466,7 @@
         <v>137040106</v>
       </c>
       <c r="B57" t="n">
-        <v>58196</v>
+        <v>58199</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7590,7 +7590,7 @@
         <v>137040109</v>
       </c>
       <c r="B58" t="n">
-        <v>58196</v>
+        <v>58199</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7706,7 +7706,7 @@
         <v>137040177</v>
       </c>
       <c r="B59" t="n">
-        <v>58196</v>
+        <v>58199</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7827,7 +7827,7 @@
         <v>137040107</v>
       </c>
       <c r="B60" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7952,7 +7952,7 @@
         <v>137040121</v>
       </c>
       <c r="B61" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -8077,7 +8077,7 @@
         <v>137040123</v>
       </c>
       <c r="B62" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -8202,7 +8202,7 @@
         <v>137040138</v>
       </c>
       <c r="B63" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8327,7 +8327,7 @@
         <v>137040160</v>
       </c>
       <c r="B64" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8452,7 +8452,7 @@
         <v>137040163</v>
       </c>
       <c r="B65" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8577,7 +8577,7 @@
         <v>137040164</v>
       </c>
       <c r="B66" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8702,7 +8702,7 @@
         <v>137040166</v>
       </c>
       <c r="B67" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8827,7 +8827,7 @@
         <v>137040168</v>
       </c>
       <c r="B68" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8952,7 +8952,7 @@
         <v>137040189</v>
       </c>
       <c r="B69" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -9077,7 +9077,7 @@
         <v>137044057</v>
       </c>
       <c r="B70" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -9202,7 +9202,7 @@
         <v>137044059</v>
       </c>
       <c r="B71" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9327,7 +9327,7 @@
         <v>137044060</v>
       </c>
       <c r="B72" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9452,7 +9452,7 @@
         <v>137044061</v>
       </c>
       <c r="B73" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9577,7 +9577,7 @@
         <v>137044062</v>
       </c>
       <c r="B74" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9702,7 +9702,7 @@
         <v>137044064</v>
       </c>
       <c r="B75" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9827,7 +9827,7 @@
         <v>137044080</v>
       </c>
       <c r="B76" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9952,7 +9952,7 @@
         <v>137040134</v>
       </c>
       <c r="B77" t="n">
-        <v>79293</v>
+        <v>79297</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -10064,7 +10064,7 @@
         <v>137040136</v>
       </c>
       <c r="B78" t="n">
-        <v>79293</v>
+        <v>79297</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -10176,7 +10176,7 @@
         <v>137016336</v>
       </c>
       <c r="B79" t="n">
-        <v>79559</v>
+        <v>79562</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -10307,7 +10307,7 @@
         <v>137016339</v>
       </c>
       <c r="B80" t="n">
-        <v>79559</v>
+        <v>79562</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -10438,7 +10438,7 @@
         <v>137016342</v>
       </c>
       <c r="B81" t="n">
-        <v>79559</v>
+        <v>79562</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10569,7 +10569,7 @@
         <v>137016345</v>
       </c>
       <c r="B82" t="n">
-        <v>79559</v>
+        <v>79562</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10700,7 +10700,7 @@
         <v>137016346</v>
       </c>
       <c r="B83" t="n">
-        <v>79559</v>
+        <v>79562</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10831,7 +10831,7 @@
         <v>137016348</v>
       </c>
       <c r="B84" t="n">
-        <v>79559</v>
+        <v>79562</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10962,7 +10962,7 @@
         <v>137016353</v>
       </c>
       <c r="B85" t="n">
-        <v>79559</v>
+        <v>79562</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -11093,7 +11093,7 @@
         <v>137040099</v>
       </c>
       <c r="B86" t="n">
-        <v>79558</v>
+        <v>79562</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -11205,7 +11205,7 @@
         <v>137044071</v>
       </c>
       <c r="B87" t="n">
-        <v>79558</v>
+        <v>79562</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
